--- a/finance/outputs/mulligan-mints-5yr-model.xlsx
+++ b/finance/outputs/mulligan-mints-5yr-model.xlsx
@@ -1841,7 +1841,7 @@
         </is>
       </c>
       <c r="B23" s="13" t="n">
-        <v>558000</v>
+        <v>433000</v>
       </c>
       <c r="C23" s="13" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         </is>
       </c>
       <c r="B24" s="14" t="n">
-        <v>2006799</v>
+        <v>1881799</v>
       </c>
       <c r="C24" s="14" t="n">
         <v>3371212</v>
@@ -1885,7 +1885,7 @@
         </is>
       </c>
       <c r="B26" s="14" t="n">
-        <v>-1570328</v>
+        <v>-1445328</v>
       </c>
       <c r="C26" s="14" t="n">
         <v>-327544</v>
@@ -1916,7 +1916,7 @@
         <v>76327</v>
       </c>
       <c r="E27" s="13" t="n">
-        <v>1213816</v>
+        <v>1247566</v>
       </c>
       <c r="F27" s="13" t="n">
         <v>3605363</v>
@@ -1929,7 +1929,7 @@
         </is>
       </c>
       <c r="B28" s="14" t="n">
-        <v>-1570328</v>
+        <v>-1445328</v>
       </c>
       <c r="C28" s="14" t="n">
         <v>-332078</v>
@@ -1938,7 +1938,7 @@
         <v>696446</v>
       </c>
       <c r="E28" s="14" t="n">
-        <v>4706382</v>
+        <v>4672632</v>
       </c>
       <c r="F28" s="14" t="n">
         <v>9747834</v>
@@ -1973,7 +1973,7 @@
         </is>
       </c>
       <c r="B30" s="15" t="n">
-        <v>-2.208494280459387</v>
+        <v>-2.032695450576398</v>
       </c>
       <c r="C30" s="15" t="n">
         <v>-0.06953783182745936</v>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="B53" s="13" t="n">
-        <v>558000</v>
+        <v>433000</v>
       </c>
       <c r="C53" s="13" t="n">
         <v>0</v>
@@ -2409,7 +2409,7 @@
         </is>
       </c>
       <c r="B54" s="14" t="n">
-        <v>1298238</v>
+        <v>1173238</v>
       </c>
       <c r="C54" s="14" t="n">
         <v>2254066</v>
@@ -2431,7 +2431,7 @@
         </is>
       </c>
       <c r="B56" s="14" t="n">
-        <v>-1130138</v>
+        <v>-1005138</v>
       </c>
       <c r="C56" s="14" t="n">
         <v>-1143065</v>
@@ -2475,7 +2475,7 @@
         </is>
       </c>
       <c r="B58" s="14" t="n">
-        <v>-1130138</v>
+        <v>-1005138</v>
       </c>
       <c r="C58" s="14" t="n">
         <v>-1143065</v>
@@ -2519,7 +2519,7 @@
         </is>
       </c>
       <c r="B60" s="15" t="n">
-        <v>-3.757482179352015</v>
+        <v>-3.341882108706653</v>
       </c>
       <c r="C60" s="15" t="n">
         <v>-0.5736956051428735</v>
@@ -2933,7 +2933,7 @@
         </is>
       </c>
       <c r="B83" s="13" t="n">
-        <v>558000</v>
+        <v>433000</v>
       </c>
       <c r="C83" s="13" t="n">
         <v>0</v>
@@ -2955,7 +2955,7 @@
         </is>
       </c>
       <c r="B84" s="14" t="n">
-        <v>2201669</v>
+        <v>2076669</v>
       </c>
       <c r="C84" s="14" t="n">
         <v>4079252</v>
@@ -2977,7 +2977,7 @@
         </is>
       </c>
       <c r="B86" s="14" t="n">
-        <v>-1472455</v>
+        <v>-1347455</v>
       </c>
       <c r="C86" s="14" t="n">
         <v>949277</v>
@@ -3005,7 +3005,7 @@
         <v>56416</v>
       </c>
       <c r="D87" s="13" t="n">
-        <v>1159974</v>
+        <v>1193724</v>
       </c>
       <c r="E87" s="13" t="n">
         <v>3968180</v>
@@ -3021,13 +3021,13 @@
         </is>
       </c>
       <c r="B88" s="14" t="n">
-        <v>-1472455</v>
+        <v>-1347455</v>
       </c>
       <c r="C88" s="14" t="n">
         <v>892861</v>
       </c>
       <c r="D88" s="14" t="n">
-        <v>3868352</v>
+        <v>3834602</v>
       </c>
       <c r="E88" s="14" t="n">
         <v>10728784</v>
@@ -3065,7 +3065,7 @@
         </is>
       </c>
       <c r="B90" s="15" t="n">
-        <v>-1.297117060327608</v>
+        <v>-1.187001914769833</v>
       </c>
       <c r="C90" s="15" t="n">
         <v>0.1262336447685908</v>
@@ -5351,13 +5351,13 @@
         </is>
       </c>
       <c r="B14" s="13" t="n">
-        <v>138000</v>
+        <v>88000</v>
       </c>
       <c r="C14" s="13" t="n">
         <v>45000</v>
       </c>
       <c r="D14" s="13" t="n">
-        <v>115000</v>
+        <v>40000</v>
       </c>
       <c r="E14" s="13" t="n">
         <v>135000</v>
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>138000</v>
+        <v>88000</v>
       </c>
       <c r="C15" s="13" t="n">
         <v>45000</v>
       </c>
       <c r="D15" s="13" t="n">
-        <v>115000</v>
+        <v>40000</v>
       </c>
       <c r="E15" s="13" t="n">
         <v>227500</v>
@@ -5725,13 +5725,13 @@
         </is>
       </c>
       <c r="B16" s="14" t="n">
-        <v>-138000</v>
+        <v>-88000</v>
       </c>
       <c r="C16" s="14" t="n">
         <v>-45000</v>
       </c>
       <c r="D16" s="14" t="n">
-        <v>-115000</v>
+        <v>-40000</v>
       </c>
       <c r="E16" s="14" t="n">
         <v>-227500</v>
@@ -7054,13 +7054,13 @@
         </is>
       </c>
       <c r="B7" s="13" t="n">
-        <v>138000</v>
+        <v>88000</v>
       </c>
       <c r="C7" s="13" t="n">
         <v>45000</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>115000</v>
+        <v>40000</v>
       </c>
       <c r="E7" s="13" t="n">
         <v>227500</v>
@@ -7244,13 +7244,13 @@
         <v>0</v>
       </c>
       <c r="C8" s="13" t="n">
-        <v>24705</v>
+        <v>17955</v>
       </c>
       <c r="D8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="E8" s="13" t="n">
-        <v>41108</v>
+        <v>30982</v>
       </c>
       <c r="F8" s="13" t="n">
         <v>0</v>
@@ -7551,7 +7551,7 @@
         <v>0</v>
       </c>
       <c r="AQ9" s="13" t="n">
-        <v>-302830</v>
+        <v>-336580</v>
       </c>
       <c r="AR9" s="13" t="n">
         <v>0</v>
@@ -7802,16 +7802,16 @@
         </is>
       </c>
       <c r="B11" s="14" t="n">
-        <v>3298640</v>
+        <v>3348640</v>
       </c>
       <c r="C11" s="14" t="n">
-        <v>-20295</v>
+        <v>-27045</v>
       </c>
       <c r="D11" s="14" t="n">
-        <v>-277878</v>
+        <v>-202878</v>
       </c>
       <c r="E11" s="14" t="n">
-        <v>-186392</v>
+        <v>-196518</v>
       </c>
       <c r="F11" s="14" t="n">
         <v>-218738</v>
@@ -7925,7 +7925,7 @@
         <v>571514</v>
       </c>
       <c r="AQ11" s="14" t="n">
-        <v>64627</v>
+        <v>30877</v>
       </c>
       <c r="AR11" s="14" t="n">
         <v>557088</v>
@@ -7989,184 +7989,184 @@
         </is>
       </c>
       <c r="B12" s="14" t="n">
-        <v>3298640</v>
+        <v>3348640</v>
       </c>
       <c r="C12" s="14" t="n">
-        <v>3278345</v>
+        <v>3321595</v>
       </c>
       <c r="D12" s="14" t="n">
-        <v>3000467</v>
+        <v>3118717</v>
       </c>
       <c r="E12" s="14" t="n">
-        <v>2814074</v>
+        <v>2922199</v>
       </c>
       <c r="F12" s="14" t="n">
-        <v>2595337</v>
+        <v>2703462</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>2415415</v>
+        <v>2523540</v>
       </c>
       <c r="H12" s="14" t="n">
-        <v>2275617</v>
+        <v>2383742</v>
       </c>
       <c r="I12" s="14" t="n">
-        <v>2005963</v>
+        <v>2114088</v>
       </c>
       <c r="J12" s="14" t="n">
-        <v>1856609</v>
+        <v>1964734</v>
       </c>
       <c r="K12" s="14" t="n">
-        <v>1765491</v>
+        <v>1873616</v>
       </c>
       <c r="L12" s="14" t="n">
-        <v>1516785</v>
+        <v>1624910</v>
       </c>
       <c r="M12" s="14" t="n">
-        <v>1478263</v>
+        <v>1586388</v>
       </c>
       <c r="N12" s="14" t="n">
-        <v>1258594</v>
+        <v>1366719</v>
       </c>
       <c r="O12" s="14" t="n">
-        <v>1250942</v>
+        <v>1359067</v>
       </c>
       <c r="P12" s="14" t="n">
-        <v>1126523</v>
+        <v>1234648</v>
       </c>
       <c r="Q12" s="14" t="n">
-        <v>997426</v>
+        <v>1105551</v>
       </c>
       <c r="R12" s="14" t="n">
-        <v>1006157</v>
+        <v>1114282</v>
       </c>
       <c r="S12" s="14" t="n">
-        <v>863680</v>
+        <v>971805</v>
       </c>
       <c r="T12" s="14" t="n">
-        <v>609469</v>
+        <v>717594</v>
       </c>
       <c r="U12" s="14" t="n">
-        <v>12473679</v>
+        <v>12581804</v>
       </c>
       <c r="V12" s="14" t="n">
-        <v>12396748</v>
+        <v>12504873</v>
       </c>
       <c r="W12" s="14" t="n">
-        <v>12326183</v>
+        <v>12434308</v>
       </c>
       <c r="X12" s="14" t="n">
-        <v>12322891</v>
+        <v>12431016</v>
       </c>
       <c r="Y12" s="14" t="n">
-        <v>12269526</v>
+        <v>12377651</v>
       </c>
       <c r="Z12" s="14" t="n">
-        <v>12223453</v>
+        <v>12331578</v>
       </c>
       <c r="AA12" s="14" t="n">
-        <v>11709091</v>
+        <v>11817216</v>
       </c>
       <c r="AB12" s="14" t="n">
-        <v>11654288</v>
+        <v>11762413</v>
       </c>
       <c r="AC12" s="14" t="n">
-        <v>11488809</v>
+        <v>11596934</v>
       </c>
       <c r="AD12" s="14" t="n">
-        <v>11466561</v>
+        <v>11574686</v>
       </c>
       <c r="AE12" s="14" t="n">
-        <v>11293305</v>
+        <v>11401430</v>
       </c>
       <c r="AF12" s="14" t="n">
-        <v>11193062</v>
+        <v>11301187</v>
       </c>
       <c r="AG12" s="14" t="n">
-        <v>10890526</v>
+        <v>10998651</v>
       </c>
       <c r="AH12" s="14" t="n">
-        <v>10580239</v>
+        <v>10688364</v>
       </c>
       <c r="AI12" s="14" t="n">
-        <v>10641158</v>
+        <v>10749283</v>
       </c>
       <c r="AJ12" s="14" t="n">
-        <v>10810858</v>
+        <v>10918983</v>
       </c>
       <c r="AK12" s="14" t="n">
-        <v>10827405</v>
+        <v>10935530</v>
       </c>
       <c r="AL12" s="14" t="n">
-        <v>10971580</v>
+        <v>11079705</v>
       </c>
       <c r="AM12" s="14" t="n">
-        <v>10821772</v>
+        <v>10929897</v>
       </c>
       <c r="AN12" s="14" t="n">
-        <v>11422237</v>
+        <v>11530362</v>
       </c>
       <c r="AO12" s="14" t="n">
-        <v>11811585</v>
+        <v>11919710</v>
       </c>
       <c r="AP12" s="14" t="n">
-        <v>12383100</v>
+        <v>12491225</v>
       </c>
       <c r="AQ12" s="14" t="n">
-        <v>12447727</v>
+        <v>12522102</v>
       </c>
       <c r="AR12" s="14" t="n">
-        <v>13004814</v>
+        <v>13079189</v>
       </c>
       <c r="AS12" s="14" t="n">
-        <v>13274495</v>
+        <v>13348870</v>
       </c>
       <c r="AT12" s="14" t="n">
-        <v>13760548</v>
+        <v>13834923</v>
       </c>
       <c r="AU12" s="14" t="n">
-        <v>14076935</v>
+        <v>14151310</v>
       </c>
       <c r="AV12" s="14" t="n">
-        <v>14572547</v>
+        <v>14646922</v>
       </c>
       <c r="AW12" s="14" t="n">
-        <v>14135883</v>
+        <v>14210258</v>
       </c>
       <c r="AX12" s="14" t="n">
-        <v>14501751</v>
+        <v>14576126</v>
       </c>
       <c r="AY12" s="14" t="n">
-        <v>14913199</v>
+        <v>14987574</v>
       </c>
       <c r="AZ12" s="14" t="n">
-        <v>16237819</v>
+        <v>16312194</v>
       </c>
       <c r="BA12" s="14" t="n">
-        <v>17303197</v>
+        <v>17377572</v>
       </c>
       <c r="BB12" s="14" t="n">
-        <v>18589371</v>
+        <v>18663746</v>
       </c>
       <c r="BC12" s="14" t="n">
-        <v>17952141</v>
+        <v>18026516</v>
       </c>
       <c r="BD12" s="14" t="n">
-        <v>19296312</v>
+        <v>19370687</v>
       </c>
       <c r="BE12" s="14" t="n">
-        <v>20472039</v>
+        <v>20546414</v>
       </c>
       <c r="BF12" s="14" t="n">
-        <v>21890796</v>
+        <v>21965171</v>
       </c>
       <c r="BG12" s="14" t="n">
-        <v>23121298</v>
+        <v>23195673</v>
       </c>
       <c r="BH12" s="14" t="n">
-        <v>24614642</v>
+        <v>24689017</v>
       </c>
       <c r="BI12" s="14" t="n">
-        <v>24040987</v>
+        <v>24115362</v>
       </c>
     </row>
     <row r="13">
@@ -8945,13 +8945,13 @@
         </is>
       </c>
       <c r="B14" s="13" t="n">
-        <v>-5244797.0875</v>
+        <v>-5119797.0875</v>
       </c>
       <c r="C14" s="13" t="n">
-        <v>18148295.4026</v>
+        <v>18273295.4026</v>
       </c>
       <c r="D14" s="13" t="n">
-        <v>46020557.4812</v>
+        <v>46145557.4812</v>
       </c>
     </row>
     <row r="15">
@@ -8977,13 +8977,13 @@
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>7846824.4142</v>
+        <v>7738699.4142</v>
       </c>
       <c r="C16" s="13" t="n">
-        <v>4919761.3534</v>
+        <v>4811636.3534</v>
       </c>
       <c r="D16" s="13" t="n">
-        <v>2832757.3995</v>
+        <v>2724632.3995</v>
       </c>
     </row>
     <row r="17">
@@ -9009,13 +9009,13 @@
         </is>
       </c>
       <c r="B18" s="13" t="n">
-        <v>1165405.6191</v>
+        <v>1273530.6191</v>
       </c>
       <c r="C18" s="13" t="n">
-        <v>609468.8665</v>
+        <v>717593.8665</v>
       </c>
       <c r="D18" s="13" t="n">
-        <v>905441.4611</v>
+        <v>1013566.4611</v>
       </c>
     </row>
     <row r="19">
@@ -9025,13 +9025,13 @@
         </is>
       </c>
       <c r="B19" s="13" t="n">
-        <v>8607528.4871</v>
+        <v>8715653.4871</v>
       </c>
       <c r="C19" s="13" t="n">
-        <v>24040986.9414</v>
+        <v>24115361.9414</v>
       </c>
       <c r="D19" s="13" t="n">
-        <v>41172612.2519</v>
+        <v>41246987.2519</v>
       </c>
     </row>
   </sheetData>
@@ -9148,7 +9148,7 @@
         </is>
       </c>
       <c r="B10" s="13" t="n">
-        <v>558000</v>
+        <v>433000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -9234,7 +9234,7 @@
         </is>
       </c>
       <c r="B16" s="14" t="n">
-        <v>2275884</v>
+        <v>2150884</v>
       </c>
     </row>
     <row r="17">
@@ -9244,13 +9244,13 @@
         </is>
       </c>
       <c r="B17" s="14" t="n">
-        <v>1224116</v>
+        <v>1349116</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Note: the base case dips to its lowest cash balance in month 19 at R609,469. The growth round must be closed before then, not started then.</t>
+          <t>Note: the base case dips to its lowest cash balance in month 19 at R717,594. The growth round must be closed before then, not started then.</t>
         </is>
       </c>
     </row>

--- a/finance/outputs/mulligan-mints-5yr-model.xlsx
+++ b/finance/outputs/mulligan-mints-5yr-model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Read me" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Assumptions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Unit economics" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="P&amp;L annual" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="P&amp;L monthly" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Cashflow monthly" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Scenarios" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Funding" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Purchase orders" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unit economics" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P&amp;L annual" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P&amp;L monthly" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cashflow monthly" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenarios" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Funding" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Purchase orders" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1841,7 +1841,7 @@
         </is>
       </c>
       <c r="B23" s="13" t="n">
-        <v>433000</v>
+        <v>408000</v>
       </c>
       <c r="C23" s="13" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         </is>
       </c>
       <c r="B24" s="14" t="n">
-        <v>1881799</v>
+        <v>1856799</v>
       </c>
       <c r="C24" s="14" t="n">
         <v>3371212</v>
@@ -1885,7 +1885,7 @@
         </is>
       </c>
       <c r="B26" s="14" t="n">
-        <v>-1445328</v>
+        <v>-1420328</v>
       </c>
       <c r="C26" s="14" t="n">
         <v>-327544</v>
@@ -1916,7 +1916,7 @@
         <v>76327</v>
       </c>
       <c r="E27" s="13" t="n">
-        <v>1247566</v>
+        <v>1254316</v>
       </c>
       <c r="F27" s="13" t="n">
         <v>3605363</v>
@@ -1929,7 +1929,7 @@
         </is>
       </c>
       <c r="B28" s="14" t="n">
-        <v>-1445328</v>
+        <v>-1420328</v>
       </c>
       <c r="C28" s="14" t="n">
         <v>-332078</v>
@@ -1938,7 +1938,7 @@
         <v>696446</v>
       </c>
       <c r="E28" s="14" t="n">
-        <v>4672632</v>
+        <v>4665882</v>
       </c>
       <c r="F28" s="14" t="n">
         <v>9747834</v>
@@ -1973,7 +1973,7 @@
         </is>
       </c>
       <c r="B30" s="15" t="n">
-        <v>-2.032695450576398</v>
+        <v>-1.997535684599801</v>
       </c>
       <c r="C30" s="15" t="n">
         <v>-0.06953783182745936</v>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="B53" s="13" t="n">
-        <v>433000</v>
+        <v>408000</v>
       </c>
       <c r="C53" s="13" t="n">
         <v>0</v>
@@ -2409,7 +2409,7 @@
         </is>
       </c>
       <c r="B54" s="14" t="n">
-        <v>1173238</v>
+        <v>1148238</v>
       </c>
       <c r="C54" s="14" t="n">
         <v>2254066</v>
@@ -2431,7 +2431,7 @@
         </is>
       </c>
       <c r="B56" s="14" t="n">
-        <v>-1005138</v>
+        <v>-980138</v>
       </c>
       <c r="C56" s="14" t="n">
         <v>-1143065</v>
@@ -2475,7 +2475,7 @@
         </is>
       </c>
       <c r="B58" s="14" t="n">
-        <v>-1005138</v>
+        <v>-980138</v>
       </c>
       <c r="C58" s="14" t="n">
         <v>-1143065</v>
@@ -2519,7 +2519,7 @@
         </is>
       </c>
       <c r="B60" s="15" t="n">
-        <v>-3.341882108706653</v>
+        <v>-3.25876209457758</v>
       </c>
       <c r="C60" s="15" t="n">
         <v>-0.5736956051428735</v>
@@ -2933,7 +2933,7 @@
         </is>
       </c>
       <c r="B83" s="13" t="n">
-        <v>433000</v>
+        <v>408000</v>
       </c>
       <c r="C83" s="13" t="n">
         <v>0</v>
@@ -2955,7 +2955,7 @@
         </is>
       </c>
       <c r="B84" s="14" t="n">
-        <v>2076669</v>
+        <v>2051669</v>
       </c>
       <c r="C84" s="14" t="n">
         <v>4079252</v>
@@ -2977,7 +2977,7 @@
         </is>
       </c>
       <c r="B86" s="14" t="n">
-        <v>-1347455</v>
+        <v>-1322455</v>
       </c>
       <c r="C86" s="14" t="n">
         <v>949277</v>
@@ -3005,7 +3005,7 @@
         <v>56416</v>
       </c>
       <c r="D87" s="13" t="n">
-        <v>1193724</v>
+        <v>1200474</v>
       </c>
       <c r="E87" s="13" t="n">
         <v>3968180</v>
@@ -3021,13 +3021,13 @@
         </is>
       </c>
       <c r="B88" s="14" t="n">
-        <v>-1347455</v>
+        <v>-1322455</v>
       </c>
       <c r="C88" s="14" t="n">
         <v>892861</v>
       </c>
       <c r="D88" s="14" t="n">
-        <v>3834602</v>
+        <v>3827852</v>
       </c>
       <c r="E88" s="14" t="n">
         <v>10728784</v>
@@ -3065,7 +3065,7 @@
         </is>
       </c>
       <c r="B90" s="15" t="n">
-        <v>-1.187001914769833</v>
+        <v>-1.164978885658277</v>
       </c>
       <c r="C90" s="15" t="n">
         <v>0.1262336447685908</v>
@@ -5351,7 +5351,7 @@
         </is>
       </c>
       <c r="B14" s="13" t="n">
-        <v>88000</v>
+        <v>63000</v>
       </c>
       <c r="C14" s="13" t="n">
         <v>45000</v>
@@ -5538,7 +5538,7 @@
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>88000</v>
+        <v>63000</v>
       </c>
       <c r="C15" s="13" t="n">
         <v>45000</v>
@@ -5725,7 +5725,7 @@
         </is>
       </c>
       <c r="B16" s="14" t="n">
-        <v>-88000</v>
+        <v>-63000</v>
       </c>
       <c r="C16" s="14" t="n">
         <v>-45000</v>
@@ -7054,7 +7054,7 @@
         </is>
       </c>
       <c r="B7" s="13" t="n">
-        <v>88000</v>
+        <v>63000</v>
       </c>
       <c r="C7" s="13" t="n">
         <v>45000</v>
@@ -7244,7 +7244,7 @@
         <v>0</v>
       </c>
       <c r="C8" s="13" t="n">
-        <v>17955</v>
+        <v>14580</v>
       </c>
       <c r="D8" s="13" t="n">
         <v>0</v>
@@ -7551,7 +7551,7 @@
         <v>0</v>
       </c>
       <c r="AQ9" s="13" t="n">
-        <v>-336580</v>
+        <v>-343330</v>
       </c>
       <c r="AR9" s="13" t="n">
         <v>0</v>
@@ -7802,10 +7802,10 @@
         </is>
       </c>
       <c r="B11" s="14" t="n">
-        <v>3348640</v>
+        <v>3373640</v>
       </c>
       <c r="C11" s="14" t="n">
-        <v>-27045</v>
+        <v>-30420</v>
       </c>
       <c r="D11" s="14" t="n">
         <v>-202878</v>
@@ -7925,7 +7925,7 @@
         <v>571514</v>
       </c>
       <c r="AQ11" s="14" t="n">
-        <v>30877</v>
+        <v>24127</v>
       </c>
       <c r="AR11" s="14" t="n">
         <v>557088</v>
@@ -7989,184 +7989,184 @@
         </is>
       </c>
       <c r="B12" s="14" t="n">
-        <v>3348640</v>
+        <v>3373640</v>
       </c>
       <c r="C12" s="14" t="n">
-        <v>3321595</v>
+        <v>3343220</v>
       </c>
       <c r="D12" s="14" t="n">
-        <v>3118717</v>
+        <v>3140342</v>
       </c>
       <c r="E12" s="14" t="n">
-        <v>2922199</v>
+        <v>2943824</v>
       </c>
       <c r="F12" s="14" t="n">
-        <v>2703462</v>
+        <v>2725087</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>2523540</v>
+        <v>2545165</v>
       </c>
       <c r="H12" s="14" t="n">
-        <v>2383742</v>
+        <v>2405367</v>
       </c>
       <c r="I12" s="14" t="n">
-        <v>2114088</v>
+        <v>2135713</v>
       </c>
       <c r="J12" s="14" t="n">
-        <v>1964734</v>
+        <v>1986359</v>
       </c>
       <c r="K12" s="14" t="n">
-        <v>1873616</v>
+        <v>1895241</v>
       </c>
       <c r="L12" s="14" t="n">
-        <v>1624910</v>
+        <v>1646535</v>
       </c>
       <c r="M12" s="14" t="n">
-        <v>1586388</v>
+        <v>1608013</v>
       </c>
       <c r="N12" s="14" t="n">
-        <v>1366719</v>
+        <v>1388344</v>
       </c>
       <c r="O12" s="14" t="n">
-        <v>1359067</v>
+        <v>1380692</v>
       </c>
       <c r="P12" s="14" t="n">
-        <v>1234648</v>
+        <v>1256273</v>
       </c>
       <c r="Q12" s="14" t="n">
-        <v>1105551</v>
+        <v>1127176</v>
       </c>
       <c r="R12" s="14" t="n">
-        <v>1114282</v>
+        <v>1135907</v>
       </c>
       <c r="S12" s="14" t="n">
-        <v>971805</v>
+        <v>993430</v>
       </c>
       <c r="T12" s="14" t="n">
-        <v>717594</v>
+        <v>739219</v>
       </c>
       <c r="U12" s="14" t="n">
-        <v>12581804</v>
+        <v>12603429</v>
       </c>
       <c r="V12" s="14" t="n">
-        <v>12504873</v>
+        <v>12526498</v>
       </c>
       <c r="W12" s="14" t="n">
-        <v>12434308</v>
+        <v>12455933</v>
       </c>
       <c r="X12" s="14" t="n">
-        <v>12431016</v>
+        <v>12452641</v>
       </c>
       <c r="Y12" s="14" t="n">
-        <v>12377651</v>
+        <v>12399276</v>
       </c>
       <c r="Z12" s="14" t="n">
-        <v>12331578</v>
+        <v>12353203</v>
       </c>
       <c r="AA12" s="14" t="n">
-        <v>11817216</v>
+        <v>11838841</v>
       </c>
       <c r="AB12" s="14" t="n">
-        <v>11762413</v>
+        <v>11784038</v>
       </c>
       <c r="AC12" s="14" t="n">
-        <v>11596934</v>
+        <v>11618559</v>
       </c>
       <c r="AD12" s="14" t="n">
-        <v>11574686</v>
+        <v>11596311</v>
       </c>
       <c r="AE12" s="14" t="n">
-        <v>11401430</v>
+        <v>11423055</v>
       </c>
       <c r="AF12" s="14" t="n">
-        <v>11301187</v>
+        <v>11322812</v>
       </c>
       <c r="AG12" s="14" t="n">
-        <v>10998651</v>
+        <v>11020276</v>
       </c>
       <c r="AH12" s="14" t="n">
-        <v>10688364</v>
+        <v>10709989</v>
       </c>
       <c r="AI12" s="14" t="n">
-        <v>10749283</v>
+        <v>10770908</v>
       </c>
       <c r="AJ12" s="14" t="n">
-        <v>10918983</v>
+        <v>10940608</v>
       </c>
       <c r="AK12" s="14" t="n">
-        <v>10935530</v>
+        <v>10957155</v>
       </c>
       <c r="AL12" s="14" t="n">
-        <v>11079705</v>
+        <v>11101330</v>
       </c>
       <c r="AM12" s="14" t="n">
-        <v>10929897</v>
+        <v>10951522</v>
       </c>
       <c r="AN12" s="14" t="n">
-        <v>11530362</v>
+        <v>11551987</v>
       </c>
       <c r="AO12" s="14" t="n">
-        <v>11919710</v>
+        <v>11941335</v>
       </c>
       <c r="AP12" s="14" t="n">
-        <v>12491225</v>
+        <v>12512850</v>
       </c>
       <c r="AQ12" s="14" t="n">
-        <v>12522102</v>
+        <v>12536977</v>
       </c>
       <c r="AR12" s="14" t="n">
-        <v>13079189</v>
+        <v>13094064</v>
       </c>
       <c r="AS12" s="14" t="n">
-        <v>13348870</v>
+        <v>13363745</v>
       </c>
       <c r="AT12" s="14" t="n">
-        <v>13834923</v>
+        <v>13849798</v>
       </c>
       <c r="AU12" s="14" t="n">
-        <v>14151310</v>
+        <v>14166185</v>
       </c>
       <c r="AV12" s="14" t="n">
-        <v>14646922</v>
+        <v>14661797</v>
       </c>
       <c r="AW12" s="14" t="n">
-        <v>14210258</v>
+        <v>14225133</v>
       </c>
       <c r="AX12" s="14" t="n">
-        <v>14576126</v>
+        <v>14591001</v>
       </c>
       <c r="AY12" s="14" t="n">
-        <v>14987574</v>
+        <v>15002449</v>
       </c>
       <c r="AZ12" s="14" t="n">
-        <v>16312194</v>
+        <v>16327069</v>
       </c>
       <c r="BA12" s="14" t="n">
-        <v>17377572</v>
+        <v>17392447</v>
       </c>
       <c r="BB12" s="14" t="n">
-        <v>18663746</v>
+        <v>18678621</v>
       </c>
       <c r="BC12" s="14" t="n">
-        <v>18026516</v>
+        <v>18041391</v>
       </c>
       <c r="BD12" s="14" t="n">
-        <v>19370687</v>
+        <v>19385562</v>
       </c>
       <c r="BE12" s="14" t="n">
-        <v>20546414</v>
+        <v>20561289</v>
       </c>
       <c r="BF12" s="14" t="n">
-        <v>21965171</v>
+        <v>21980046</v>
       </c>
       <c r="BG12" s="14" t="n">
-        <v>23195673</v>
+        <v>23210548</v>
       </c>
       <c r="BH12" s="14" t="n">
-        <v>24689017</v>
+        <v>24703892</v>
       </c>
       <c r="BI12" s="14" t="n">
-        <v>24115362</v>
+        <v>24130237</v>
       </c>
     </row>
     <row r="13">
@@ -8945,13 +8945,13 @@
         </is>
       </c>
       <c r="B14" s="13" t="n">
-        <v>-5119797.0875</v>
+        <v>-5094797.0875</v>
       </c>
       <c r="C14" s="13" t="n">
-        <v>18273295.4026</v>
+        <v>18298295.4026</v>
       </c>
       <c r="D14" s="13" t="n">
-        <v>46145557.4812</v>
+        <v>46170557.4812</v>
       </c>
     </row>
     <row r="15">
@@ -8977,13 +8977,13 @@
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>7738699.4142</v>
+        <v>7717074.4142</v>
       </c>
       <c r="C16" s="13" t="n">
-        <v>4811636.3534</v>
+        <v>4790011.3534</v>
       </c>
       <c r="D16" s="13" t="n">
-        <v>2724632.3995</v>
+        <v>2703007.3995</v>
       </c>
     </row>
     <row r="17">
@@ -9009,13 +9009,13 @@
         </is>
       </c>
       <c r="B18" s="13" t="n">
-        <v>1273530.6191</v>
+        <v>1295155.6191</v>
       </c>
       <c r="C18" s="13" t="n">
-        <v>717593.8665</v>
+        <v>739218.8665</v>
       </c>
       <c r="D18" s="13" t="n">
-        <v>1013566.4611</v>
+        <v>1035191.4611</v>
       </c>
     </row>
     <row r="19">
@@ -9025,13 +9025,13 @@
         </is>
       </c>
       <c r="B19" s="13" t="n">
-        <v>8715653.4871</v>
+        <v>8737278.4871</v>
       </c>
       <c r="C19" s="13" t="n">
-        <v>24115361.9414</v>
+        <v>24130236.9414</v>
       </c>
       <c r="D19" s="13" t="n">
-        <v>41246987.2519</v>
+        <v>41261862.2519</v>
       </c>
     </row>
   </sheetData>
@@ -9148,7 +9148,7 @@
         </is>
       </c>
       <c r="B10" s="13" t="n">
-        <v>433000</v>
+        <v>408000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -9234,7 +9234,7 @@
         </is>
       </c>
       <c r="B16" s="14" t="n">
-        <v>2150884</v>
+        <v>2125884</v>
       </c>
     </row>
     <row r="17">
@@ -9244,13 +9244,13 @@
         </is>
       </c>
       <c r="B17" s="14" t="n">
-        <v>1349116</v>
+        <v>1374116</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Note: the base case dips to its lowest cash balance in month 19 at R717,594. The growth round must be closed before then, not started then.</t>
+          <t>Note: the base case dips to its lowest cash balance in month 19 at R739,219. The growth round must be closed before then, not started then.</t>
         </is>
       </c>
     </row>

--- a/finance/outputs/mulligan-mints-5yr-model.xlsx
+++ b/finance/outputs/mulligan-mints-5yr-model.xlsx
@@ -1378,14 +1378,14 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>At the month-12 cost base, break-even is 14,039 tins/month including marketing (9,728 excluding it).</t>
+          <t>At the month-12 cost base, break-even is 14,758 tins/month including marketing (9,728 excluding it).</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>At 38 tins per outlet per month that is ~369 active outlets. The year-1 plan exits with ~250. Break-even therefore lands early in year 2, not in year 1 —</t>
+          <t>At 38 tins per outlet per month that is ~388 active outlets. The year-1 plan exits with ~250. Break-even therefore lands early in year 2, not in year 1 —</t>
         </is>
       </c>
     </row>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="B5" s="12" t="n">
-        <v>28080</v>
+        <v>24520</v>
       </c>
       <c r="C5" s="12" t="n">
         <v>183100</v>
@@ -1511,7 +1511,7 @@
         </is>
       </c>
       <c r="B7" s="13" t="n">
-        <v>341440</v>
+        <v>298760</v>
       </c>
       <c r="C7" s="13" t="n">
         <v>1969015</v>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="B8" s="13" t="n">
-        <v>271600</v>
+        <v>237650</v>
       </c>
       <c r="C8" s="13" t="n">
         <v>1989827</v>
@@ -1555,7 +1555,7 @@
         </is>
       </c>
       <c r="B9" s="13" t="n">
-        <v>98000</v>
+        <v>84000</v>
       </c>
       <c r="C9" s="13" t="n">
         <v>529200</v>
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="B13" s="14" t="n">
-        <v>711040</v>
+        <v>620410</v>
       </c>
       <c r="C13" s="14" t="n">
         <v>4710306</v>
@@ -1665,19 +1665,19 @@
         </is>
       </c>
       <c r="B14" s="13" t="n">
-        <v>274569</v>
+        <v>239759</v>
       </c>
       <c r="C14" s="13" t="n">
-        <v>1666638</v>
+        <v>1668464</v>
       </c>
       <c r="D14" s="13" t="n">
-        <v>4746785</v>
+        <v>4733781</v>
       </c>
       <c r="E14" s="13" t="n">
-        <v>9288754</v>
+        <v>9292997</v>
       </c>
       <c r="F14" s="13" t="n">
-        <v>14314496</v>
+        <v>14316698</v>
       </c>
     </row>
     <row r="15">
@@ -1687,19 +1687,19 @@
         </is>
       </c>
       <c r="B15" s="14" t="n">
-        <v>436471</v>
+        <v>380651</v>
       </c>
       <c r="C15" s="14" t="n">
-        <v>3043667</v>
+        <v>3041842</v>
       </c>
       <c r="D15" s="14" t="n">
-        <v>8534354</v>
+        <v>8547358</v>
       </c>
       <c r="E15" s="14" t="n">
-        <v>17491863</v>
+        <v>17487620</v>
       </c>
       <c r="F15" s="14" t="n">
-        <v>29319032</v>
+        <v>29316830</v>
       </c>
     </row>
     <row r="17">
@@ -1753,7 +1753,7 @@
         </is>
       </c>
       <c r="B19" s="13" t="n">
-        <v>37908</v>
+        <v>33102</v>
       </c>
       <c r="C19" s="13" t="n">
         <v>250384</v>
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="B20" s="13" t="n">
-        <v>18391</v>
+        <v>16092</v>
       </c>
       <c r="C20" s="13" t="n">
         <v>109811</v>
@@ -1863,7 +1863,7 @@
         </is>
       </c>
       <c r="B24" s="14" t="n">
-        <v>1856799</v>
+        <v>1849694</v>
       </c>
       <c r="C24" s="14" t="n">
         <v>3371212</v>
@@ -1885,19 +1885,19 @@
         </is>
       </c>
       <c r="B26" s="14" t="n">
-        <v>-1420328</v>
+        <v>-1469043</v>
       </c>
       <c r="C26" s="14" t="n">
-        <v>-327544</v>
+        <v>-329370</v>
       </c>
       <c r="D26" s="14" t="n">
-        <v>772772</v>
+        <v>785777</v>
       </c>
       <c r="E26" s="14" t="n">
-        <v>5920198</v>
+        <v>5915955</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>13353197</v>
+        <v>13350995</v>
       </c>
     </row>
     <row r="27">
@@ -1910,16 +1910,16 @@
         <v>0</v>
       </c>
       <c r="C27" s="13" t="n">
-        <v>4534</v>
+        <v>4474</v>
       </c>
       <c r="D27" s="13" t="n">
-        <v>76327</v>
+        <v>76824</v>
       </c>
       <c r="E27" s="13" t="n">
-        <v>1254316</v>
+        <v>1242599</v>
       </c>
       <c r="F27" s="13" t="n">
-        <v>3605363</v>
+        <v>3604769</v>
       </c>
     </row>
     <row r="28">
@@ -1929,19 +1929,19 @@
         </is>
       </c>
       <c r="B28" s="14" t="n">
-        <v>-1420328</v>
+        <v>-1469043</v>
       </c>
       <c r="C28" s="14" t="n">
-        <v>-332078</v>
+        <v>-333843</v>
       </c>
       <c r="D28" s="14" t="n">
-        <v>696446</v>
+        <v>708953</v>
       </c>
       <c r="E28" s="14" t="n">
-        <v>4665882</v>
+        <v>4673356</v>
       </c>
       <c r="F28" s="14" t="n">
-        <v>9747834</v>
+        <v>9746227</v>
       </c>
     </row>
     <row r="29">
@@ -1951,19 +1951,19 @@
         </is>
       </c>
       <c r="B29" s="15" t="n">
-        <v>0.6138493289015491</v>
+        <v>0.6135481417512721</v>
       </c>
       <c r="C29" s="15" t="n">
-        <v>0.6461719373973884</v>
+        <v>0.645784443789404</v>
       </c>
       <c r="D29" s="15" t="n">
-        <v>0.6425919974413568</v>
+        <v>0.6435711697296859</v>
       </c>
       <c r="E29" s="15" t="n">
-        <v>0.6531538516793678</v>
+        <v>0.652995397221382</v>
       </c>
       <c r="F29" s="15" t="n">
-        <v>0.6719381442414655</v>
+        <v>0.6718876899395222</v>
       </c>
     </row>
     <row r="30">
@@ -1973,19 +1973,19 @@
         </is>
       </c>
       <c r="B30" s="15" t="n">
-        <v>-1.997535684599801</v>
+        <v>-2.367858186322099</v>
       </c>
       <c r="C30" s="15" t="n">
-        <v>-0.06953783182745936</v>
+        <v>-0.06992532543544379</v>
       </c>
       <c r="D30" s="15" t="n">
-        <v>0.05818570749371985</v>
+        <v>0.059164879782049</v>
       </c>
       <c r="E30" s="15" t="n">
-        <v>0.2210628017482604</v>
+        <v>0.2209043472902747</v>
       </c>
       <c r="F30" s="15" t="n">
-        <v>0.3060306516498935</v>
+        <v>0.3059801973479503</v>
       </c>
     </row>
     <row r="33">
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="B35" s="12" t="n">
-        <v>12636</v>
+        <v>11034</v>
       </c>
       <c r="C35" s="12" t="n">
         <v>82395</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B37" s="13" t="n">
-        <v>144429</v>
+        <v>126375</v>
       </c>
       <c r="C37" s="13" t="n">
         <v>832893</v>
@@ -2079,7 +2079,7 @@
         </is>
       </c>
       <c r="B38" s="13" t="n">
-        <v>114887</v>
+        <v>100526</v>
       </c>
       <c r="C38" s="13" t="n">
         <v>841697</v>
@@ -2101,7 +2101,7 @@
         </is>
       </c>
       <c r="B39" s="13" t="n">
-        <v>41454</v>
+        <v>35532</v>
       </c>
       <c r="C39" s="13" t="n">
         <v>223852</v>
@@ -2189,7 +2189,7 @@
         </is>
       </c>
       <c r="B43" s="14" t="n">
-        <v>300770</v>
+        <v>262433</v>
       </c>
       <c r="C43" s="14" t="n">
         <v>1992459</v>
@@ -2211,19 +2211,19 @@
         </is>
       </c>
       <c r="B44" s="13" t="n">
-        <v>132669</v>
+        <v>115850</v>
       </c>
       <c r="C44" s="13" t="n">
-        <v>881459</v>
+        <v>882160</v>
       </c>
       <c r="D44" s="13" t="n">
-        <v>2535805</v>
+        <v>2535480</v>
       </c>
       <c r="E44" s="13" t="n">
-        <v>4925705</v>
+        <v>4922897</v>
       </c>
       <c r="F44" s="13" t="n">
-        <v>7359648</v>
+        <v>7365261</v>
       </c>
     </row>
     <row r="45">
@@ -2233,19 +2233,19 @@
         </is>
       </c>
       <c r="B45" s="14" t="n">
-        <v>168100</v>
+        <v>146584</v>
       </c>
       <c r="C45" s="14" t="n">
-        <v>1111001</v>
+        <v>1110300</v>
       </c>
       <c r="D45" s="14" t="n">
-        <v>3082117</v>
+        <v>3082442</v>
       </c>
       <c r="E45" s="14" t="n">
-        <v>6233296</v>
+        <v>6236104</v>
       </c>
       <c r="F45" s="14" t="n">
-        <v>10335934</v>
+        <v>10330321</v>
       </c>
     </row>
     <row r="47">
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="B49" s="13" t="n">
-        <v>17059</v>
+        <v>14896</v>
       </c>
       <c r="C49" s="13" t="n">
         <v>112673</v>
@@ -2321,7 +2321,7 @@
         </is>
       </c>
       <c r="B50" s="13" t="n">
-        <v>7779</v>
+        <v>6807</v>
       </c>
       <c r="C50" s="13" t="n">
         <v>46450</v>
@@ -2409,7 +2409,7 @@
         </is>
       </c>
       <c r="B54" s="14" t="n">
-        <v>1148238</v>
+        <v>1145103</v>
       </c>
       <c r="C54" s="14" t="n">
         <v>2254066</v>
@@ -2431,19 +2431,19 @@
         </is>
       </c>
       <c r="B56" s="14" t="n">
-        <v>-980138</v>
+        <v>-998519</v>
       </c>
       <c r="C56" s="14" t="n">
-        <v>-1143065</v>
+        <v>-1143766</v>
       </c>
       <c r="D56" s="14" t="n">
-        <v>-1894826</v>
+        <v>-1894501</v>
       </c>
       <c r="E56" s="14" t="n">
-        <v>-1287043</v>
+        <v>-1284236</v>
       </c>
       <c r="F56" s="14" t="n">
-        <v>210275</v>
+        <v>204662</v>
       </c>
     </row>
     <row r="57">
@@ -2465,7 +2465,7 @@
         <v>0</v>
       </c>
       <c r="F57" s="13" t="n">
-        <v>16653</v>
+        <v>16325</v>
       </c>
     </row>
     <row r="58">
@@ -2475,19 +2475,19 @@
         </is>
       </c>
       <c r="B58" s="14" t="n">
-        <v>-980138</v>
+        <v>-998519</v>
       </c>
       <c r="C58" s="14" t="n">
-        <v>-1143065</v>
+        <v>-1143766</v>
       </c>
       <c r="D58" s="14" t="n">
-        <v>-1894826</v>
+        <v>-1894501</v>
       </c>
       <c r="E58" s="14" t="n">
-        <v>-1287043</v>
+        <v>-1284236</v>
       </c>
       <c r="F58" s="14" t="n">
-        <v>193622</v>
+        <v>188337</v>
       </c>
     </row>
     <row r="59">
@@ -2497,19 +2497,19 @@
         </is>
       </c>
       <c r="B59" s="15" t="n">
-        <v>0.5589005147684609</v>
+        <v>0.558556469019252</v>
       </c>
       <c r="C59" s="15" t="n">
-        <v>0.5576026549768547</v>
+        <v>0.5572507935931791</v>
       </c>
       <c r="D59" s="15" t="n">
-        <v>0.5486222846958062</v>
+        <v>0.5486801495635067</v>
       </c>
       <c r="E59" s="15" t="n">
-        <v>0.5585891107660995</v>
+        <v>0.5588407144215103</v>
       </c>
       <c r="F59" s="15" t="n">
-        <v>0.5840968728195877</v>
+        <v>0.5837796536514781</v>
       </c>
     </row>
     <row r="60">
@@ -2519,19 +2519,19 @@
         </is>
       </c>
       <c r="B60" s="15" t="n">
-        <v>-3.25876209457758</v>
+        <v>-3.80484701543774</v>
       </c>
       <c r="C60" s="15" t="n">
-        <v>-0.5736956051428735</v>
+        <v>-0.5740474665265493</v>
       </c>
       <c r="D60" s="15" t="n">
-        <v>-0.3372823859397821</v>
+        <v>-0.3372245210720815</v>
       </c>
       <c r="E60" s="15" t="n">
-        <v>-0.1153367920180302</v>
+        <v>-0.1150851883626193</v>
       </c>
       <c r="F60" s="15" t="n">
-        <v>0.01188291970917781</v>
+        <v>0.01156570054106826</v>
       </c>
     </row>
     <row r="63">
@@ -2581,7 +2581,7 @@
         </is>
       </c>
       <c r="B65" s="12" t="n">
-        <v>43524</v>
+        <v>38006</v>
       </c>
       <c r="C65" s="12" t="n">
         <v>283805</v>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="B67" s="13" t="n">
-        <v>545109</v>
+        <v>476970</v>
       </c>
       <c r="C67" s="13" t="n">
         <v>3143533</v>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="B68" s="13" t="n">
-        <v>433609</v>
+        <v>379408</v>
       </c>
       <c r="C68" s="13" t="n">
         <v>3176758</v>
@@ -2647,7 +2647,7 @@
         </is>
       </c>
       <c r="B69" s="13" t="n">
-        <v>156457</v>
+        <v>134106</v>
       </c>
       <c r="C69" s="13" t="n">
         <v>844868</v>
@@ -2735,7 +2735,7 @@
         </is>
       </c>
       <c r="B73" s="14" t="n">
-        <v>1135175</v>
+        <v>990485</v>
       </c>
       <c r="C73" s="14" t="n">
         <v>7520003</v>
@@ -2757,19 +2757,19 @@
         </is>
       </c>
       <c r="B74" s="13" t="n">
-        <v>405962</v>
+        <v>354494</v>
       </c>
       <c r="C74" s="13" t="n">
-        <v>2491474</v>
+        <v>2467118</v>
       </c>
       <c r="D74" s="13" t="n">
-        <v>6587103</v>
+        <v>6575706</v>
       </c>
       <c r="E74" s="13" t="n">
-        <v>12932407</v>
+        <v>12940289</v>
       </c>
       <c r="F74" s="13" t="n">
-        <v>20881319</v>
+        <v>20888303</v>
       </c>
     </row>
     <row r="75">
@@ -2779,19 +2779,19 @@
         </is>
       </c>
       <c r="B75" s="14" t="n">
-        <v>729214</v>
+        <v>635991</v>
       </c>
       <c r="C75" s="14" t="n">
-        <v>5028530</v>
+        <v>5052885</v>
       </c>
       <c r="D75" s="14" t="n">
-        <v>14616235</v>
+        <v>14627633</v>
       </c>
       <c r="E75" s="14" t="n">
-        <v>29584248</v>
+        <v>29576366</v>
       </c>
       <c r="F75" s="14" t="n">
-        <v>47705908</v>
+        <v>47698924</v>
       </c>
     </row>
     <row r="77">
@@ -2845,7 +2845,7 @@
         </is>
       </c>
       <c r="B79" s="13" t="n">
-        <v>58757</v>
+        <v>51308</v>
       </c>
       <c r="C79" s="13" t="n">
         <v>388094</v>
@@ -2867,7 +2867,7 @@
         </is>
       </c>
       <c r="B80" s="13" t="n">
-        <v>29362</v>
+        <v>25691</v>
       </c>
       <c r="C80" s="13" t="n">
         <v>175313</v>
@@ -2955,7 +2955,7 @@
         </is>
       </c>
       <c r="B84" s="14" t="n">
-        <v>2051669</v>
+        <v>2040549</v>
       </c>
       <c r="C84" s="14" t="n">
         <v>4079252</v>
@@ -2977,19 +2977,19 @@
         </is>
       </c>
       <c r="B86" s="14" t="n">
-        <v>-1322455</v>
+        <v>-1404559</v>
       </c>
       <c r="C86" s="14" t="n">
-        <v>949277</v>
+        <v>973633</v>
       </c>
       <c r="D86" s="14" t="n">
-        <v>5028326</v>
+        <v>5039724</v>
       </c>
       <c r="E86" s="14" t="n">
-        <v>14696965</v>
+        <v>14689083</v>
       </c>
       <c r="F86" s="14" t="n">
-        <v>26818445</v>
+        <v>26811461</v>
       </c>
     </row>
     <row r="87">
@@ -3002,16 +3002,16 @@
         <v>0</v>
       </c>
       <c r="C87" s="13" t="n">
-        <v>56416</v>
+        <v>57684</v>
       </c>
       <c r="D87" s="13" t="n">
-        <v>1200474</v>
+        <v>1186692</v>
       </c>
       <c r="E87" s="13" t="n">
-        <v>3968180</v>
+        <v>3966052</v>
       </c>
       <c r="F87" s="13" t="n">
-        <v>7240980</v>
+        <v>7239094</v>
       </c>
     </row>
     <row r="88">
@@ -3021,19 +3021,19 @@
         </is>
       </c>
       <c r="B88" s="14" t="n">
-        <v>-1322455</v>
+        <v>-1404559</v>
       </c>
       <c r="C88" s="14" t="n">
-        <v>892861</v>
+        <v>915949</v>
       </c>
       <c r="D88" s="14" t="n">
-        <v>3827852</v>
+        <v>3853032</v>
       </c>
       <c r="E88" s="14" t="n">
-        <v>10728784</v>
+        <v>10723031</v>
       </c>
       <c r="F88" s="14" t="n">
-        <v>19577465</v>
+        <v>19572366</v>
       </c>
     </row>
     <row r="89">
@@ -3043,19 +3043,19 @@
         </is>
       </c>
       <c r="B89" s="15" t="n">
-        <v>0.6423797155714043</v>
+        <v>0.6421007813563169</v>
       </c>
       <c r="C89" s="15" t="n">
-        <v>0.6686871603622193</v>
+        <v>0.6719258876704935</v>
       </c>
       <c r="D89" s="15" t="n">
-        <v>0.6893364965414489</v>
+        <v>0.6898740512262032</v>
       </c>
       <c r="E89" s="15" t="n">
-        <v>0.695827264084337</v>
+        <v>0.6956418890480596</v>
       </c>
       <c r="F89" s="15" t="n">
-        <v>0.6955509080978314</v>
+        <v>0.6954490796935608</v>
       </c>
     </row>
     <row r="90">
@@ -3065,19 +3065,19 @@
         </is>
       </c>
       <c r="B90" s="15" t="n">
-        <v>-1.164978885658277</v>
+        <v>-1.418051924758795</v>
       </c>
       <c r="C90" s="15" t="n">
-        <v>0.1262336447685908</v>
+        <v>0.1294723720768652</v>
       </c>
       <c r="D90" s="15" t="n">
-        <v>0.2371478351407653</v>
+        <v>0.2376853898255194</v>
       </c>
       <c r="E90" s="15" t="n">
-        <v>0.3456754699050679</v>
+        <v>0.3454900948687904</v>
       </c>
       <c r="F90" s="15" t="n">
-        <v>0.3910122332216432</v>
+        <v>0.3909104048173726</v>
       </c>
     </row>
   </sheetData>
@@ -3496,22 +3496,22 @@
         <v>0</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>1303</v>
+        <v>0</v>
       </c>
       <c r="H4" s="12" t="n">
-        <v>2206</v>
+        <v>1453</v>
       </c>
       <c r="I4" s="12" t="n">
-        <v>3109</v>
+        <v>2507</v>
       </c>
       <c r="J4" s="12" t="n">
-        <v>4011</v>
+        <v>3560</v>
       </c>
       <c r="K4" s="12" t="n">
-        <v>4914</v>
+        <v>4613</v>
       </c>
       <c r="L4" s="12" t="n">
-        <v>5817</v>
+        <v>5667</v>
       </c>
       <c r="M4" s="12" t="n">
         <v>6720</v>
@@ -3683,22 +3683,22 @@
         <v>0</v>
       </c>
       <c r="G5" s="13" t="n">
-        <v>35894</v>
+        <v>0</v>
       </c>
       <c r="H5" s="13" t="n">
-        <v>57789</v>
+        <v>39543</v>
       </c>
       <c r="I5" s="13" t="n">
-        <v>79683</v>
+        <v>65087</v>
       </c>
       <c r="J5" s="13" t="n">
-        <v>101577</v>
+        <v>90630</v>
       </c>
       <c r="K5" s="13" t="n">
-        <v>123471</v>
+        <v>116173</v>
       </c>
       <c r="L5" s="13" t="n">
-        <v>145366</v>
+        <v>141717</v>
       </c>
       <c r="M5" s="13" t="n">
         <v>167260</v>
@@ -3870,169 +3870,169 @@
         <v>0</v>
       </c>
       <c r="G6" s="13" t="n">
-        <v>12739</v>
+        <v>0</v>
       </c>
       <c r="H6" s="13" t="n">
-        <v>21568</v>
+        <v>14211</v>
       </c>
       <c r="I6" s="13" t="n">
-        <v>30396</v>
+        <v>24510</v>
       </c>
       <c r="J6" s="13" t="n">
-        <v>39224</v>
+        <v>34810</v>
       </c>
       <c r="K6" s="13" t="n">
-        <v>48052</v>
+        <v>45110</v>
       </c>
       <c r="L6" s="13" t="n">
-        <v>56881</v>
+        <v>55409</v>
       </c>
       <c r="M6" s="13" t="n">
         <v>65709</v>
       </c>
       <c r="N6" s="13" t="n">
-        <v>91686</v>
+        <v>87251</v>
       </c>
       <c r="O6" s="13" t="n">
-        <v>94539</v>
+        <v>95780</v>
       </c>
       <c r="P6" s="13" t="n">
-        <v>102958</v>
+        <v>101834</v>
       </c>
       <c r="Q6" s="13" t="n">
-        <v>108758</v>
+        <v>110161</v>
       </c>
       <c r="R6" s="13" t="n">
-        <v>116979</v>
+        <v>118527</v>
       </c>
       <c r="S6" s="13" t="n">
-        <v>126008</v>
+        <v>126857</v>
       </c>
       <c r="T6" s="13" t="n">
-        <v>138995</v>
+        <v>139577</v>
       </c>
       <c r="U6" s="13" t="n">
-        <v>151636</v>
+        <v>152288</v>
       </c>
       <c r="V6" s="13" t="n">
-        <v>164568</v>
+        <v>164995</v>
       </c>
       <c r="W6" s="13" t="n">
-        <v>177398</v>
+        <v>177691</v>
       </c>
       <c r="X6" s="13" t="n">
-        <v>190180</v>
+        <v>190398</v>
       </c>
       <c r="Y6" s="13" t="n">
-        <v>202935</v>
+        <v>203104</v>
       </c>
       <c r="Z6" s="13" t="n">
-        <v>256864</v>
+        <v>252085</v>
       </c>
       <c r="AA6" s="13" t="n">
-        <v>268339</v>
+        <v>264084</v>
       </c>
       <c r="AB6" s="13" t="n">
-        <v>280651</v>
+        <v>277201</v>
       </c>
       <c r="AC6" s="13" t="n">
-        <v>293600</v>
+        <v>290579</v>
       </c>
       <c r="AD6" s="13" t="n">
-        <v>305851</v>
+        <v>305785</v>
       </c>
       <c r="AE6" s="13" t="n">
-        <v>321066</v>
+        <v>321309</v>
       </c>
       <c r="AF6" s="13" t="n">
-        <v>463973</v>
+        <v>464438</v>
       </c>
       <c r="AG6" s="13" t="n">
-        <v>479603</v>
+        <v>480095</v>
       </c>
       <c r="AH6" s="13" t="n">
-        <v>495343</v>
+        <v>495803</v>
       </c>
       <c r="AI6" s="13" t="n">
-        <v>511234</v>
+        <v>511586</v>
       </c>
       <c r="AJ6" s="13" t="n">
-        <v>527136</v>
+        <v>527442</v>
       </c>
       <c r="AK6" s="13" t="n">
-        <v>543126</v>
+        <v>543373</v>
       </c>
       <c r="AL6" s="13" t="n">
-        <v>714584</v>
+        <v>702894</v>
       </c>
       <c r="AM6" s="13" t="n">
-        <v>713961</v>
+        <v>708624</v>
       </c>
       <c r="AN6" s="13" t="n">
-        <v>717697</v>
+        <v>717441</v>
       </c>
       <c r="AO6" s="13" t="n">
-        <v>726068</v>
+        <v>727203</v>
       </c>
       <c r="AP6" s="13" t="n">
-        <v>736077</v>
+        <v>745625</v>
       </c>
       <c r="AQ6" s="13" t="n">
-        <v>757786</v>
+        <v>763268</v>
       </c>
       <c r="AR6" s="13" t="n">
-        <v>777320</v>
+        <v>780346</v>
       </c>
       <c r="AS6" s="13" t="n">
-        <v>795465</v>
+        <v>797115</v>
       </c>
       <c r="AT6" s="13" t="n">
-        <v>812831</v>
+        <v>813426</v>
       </c>
       <c r="AU6" s="13" t="n">
-        <v>829466</v>
+        <v>829788</v>
       </c>
       <c r="AV6" s="13" t="n">
-        <v>845798</v>
+        <v>845740</v>
       </c>
       <c r="AW6" s="13" t="n">
-        <v>861701</v>
+        <v>861527</v>
       </c>
       <c r="AX6" s="13" t="n">
-        <v>1153847</v>
+        <v>1137681</v>
       </c>
       <c r="AY6" s="13" t="n">
-        <v>1144475</v>
+        <v>1137893</v>
       </c>
       <c r="AZ6" s="13" t="n">
-        <v>1143198</v>
+        <v>1140736</v>
       </c>
       <c r="BA6" s="13" t="n">
-        <v>1145172</v>
+        <v>1146509</v>
       </c>
       <c r="BB6" s="13" t="n">
-        <v>1151212</v>
+        <v>1164951</v>
       </c>
       <c r="BC6" s="13" t="n">
-        <v>1174360</v>
+        <v>1182219</v>
       </c>
       <c r="BD6" s="13" t="n">
-        <v>1194393</v>
+        <v>1198268</v>
       </c>
       <c r="BE6" s="13" t="n">
-        <v>1211809</v>
+        <v>1213439</v>
       </c>
       <c r="BF6" s="13" t="n">
-        <v>1227573</v>
+        <v>1227973</v>
       </c>
       <c r="BG6" s="13" t="n">
-        <v>1242280</v>
+        <v>1242040</v>
       </c>
       <c r="BH6" s="13" t="n">
-        <v>1256302</v>
+        <v>1255762</v>
       </c>
       <c r="BI6" s="13" t="n">
-        <v>1269874</v>
+        <v>1269227</v>
       </c>
     </row>
     <row r="7">
@@ -4057,169 +4057,169 @@
         <v>0</v>
       </c>
       <c r="G7" s="13" t="n">
-        <v>23155</v>
+        <v>0</v>
       </c>
       <c r="H7" s="13" t="n">
-        <v>36221</v>
+        <v>25333</v>
       </c>
       <c r="I7" s="13" t="n">
-        <v>49287</v>
+        <v>40576</v>
       </c>
       <c r="J7" s="13" t="n">
-        <v>62353</v>
+        <v>55820</v>
       </c>
       <c r="K7" s="13" t="n">
-        <v>75419</v>
+        <v>71064</v>
       </c>
       <c r="L7" s="13" t="n">
-        <v>88485</v>
+        <v>86308</v>
       </c>
       <c r="M7" s="13" t="n">
         <v>101551</v>
       </c>
       <c r="N7" s="13" t="n">
-        <v>157021</v>
+        <v>161456</v>
       </c>
       <c r="O7" s="13" t="n">
-        <v>176949</v>
+        <v>175708</v>
       </c>
       <c r="P7" s="13" t="n">
-        <v>191311</v>
+        <v>192435</v>
       </c>
       <c r="Q7" s="13" t="n">
-        <v>208293</v>
+        <v>206889</v>
       </c>
       <c r="R7" s="13" t="n">
-        <v>222853</v>
+        <v>221304</v>
       </c>
       <c r="S7" s="13" t="n">
-        <v>236605</v>
+        <v>235756</v>
       </c>
       <c r="T7" s="13" t="n">
-        <v>256983</v>
+        <v>256401</v>
       </c>
       <c r="U7" s="13" t="n">
-        <v>277707</v>
+        <v>277055</v>
       </c>
       <c r="V7" s="13" t="n">
-        <v>298141</v>
+        <v>297714</v>
       </c>
       <c r="W7" s="13" t="n">
-        <v>318676</v>
+        <v>318382</v>
       </c>
       <c r="X7" s="13" t="n">
-        <v>339259</v>
+        <v>339041</v>
       </c>
       <c r="Y7" s="13" t="n">
-        <v>359869</v>
+        <v>359700</v>
       </c>
       <c r="Z7" s="13" t="n">
-        <v>472966</v>
+        <v>477745</v>
       </c>
       <c r="AA7" s="13" t="n">
-        <v>506720</v>
+        <v>510976</v>
       </c>
       <c r="AB7" s="13" t="n">
-        <v>539640</v>
+        <v>543089</v>
       </c>
       <c r="AC7" s="13" t="n">
-        <v>571920</v>
+        <v>574941</v>
       </c>
       <c r="AD7" s="13" t="n">
-        <v>604900</v>
+        <v>604965</v>
       </c>
       <c r="AE7" s="13" t="n">
-        <v>634915</v>
+        <v>634672</v>
       </c>
       <c r="AF7" s="13" t="n">
-        <v>793569</v>
+        <v>793104</v>
       </c>
       <c r="AG7" s="13" t="n">
-        <v>823170</v>
+        <v>822678</v>
       </c>
       <c r="AH7" s="13" t="n">
-        <v>852660</v>
+        <v>852200</v>
       </c>
       <c r="AI7" s="13" t="n">
-        <v>881999</v>
+        <v>881647</v>
       </c>
       <c r="AJ7" s="13" t="n">
-        <v>911327</v>
+        <v>911021</v>
       </c>
       <c r="AK7" s="13" t="n">
-        <v>940568</v>
+        <v>940320</v>
       </c>
       <c r="AL7" s="13" t="n">
-        <v>1272385</v>
+        <v>1284075</v>
       </c>
       <c r="AM7" s="13" t="n">
-        <v>1317508</v>
+        <v>1322844</v>
       </c>
       <c r="AN7" s="13" t="n">
-        <v>1358272</v>
+        <v>1358528</v>
       </c>
       <c r="AO7" s="13" t="n">
-        <v>1394401</v>
+        <v>1393266</v>
       </c>
       <c r="AP7" s="13" t="n">
-        <v>1428891</v>
+        <v>1419343</v>
       </c>
       <c r="AQ7" s="13" t="n">
-        <v>1451682</v>
+        <v>1446201</v>
       </c>
       <c r="AR7" s="13" t="n">
-        <v>1476648</v>
+        <v>1473622</v>
       </c>
       <c r="AS7" s="13" t="n">
-        <v>1503003</v>
+        <v>1501352</v>
       </c>
       <c r="AT7" s="13" t="n">
-        <v>1530137</v>
+        <v>1529542</v>
       </c>
       <c r="AU7" s="13" t="n">
-        <v>1558001</v>
+        <v>1557679</v>
       </c>
       <c r="AV7" s="13" t="n">
-        <v>1586169</v>
+        <v>1586227</v>
       </c>
       <c r="AW7" s="13" t="n">
-        <v>1614766</v>
+        <v>1614940</v>
       </c>
       <c r="AX7" s="13" t="n">
-        <v>2269733</v>
+        <v>2285900</v>
       </c>
       <c r="AY7" s="13" t="n">
-        <v>2317750</v>
+        <v>2324332</v>
       </c>
       <c r="AZ7" s="13" t="n">
-        <v>2357672</v>
+        <v>2360134</v>
       </c>
       <c r="BA7" s="13" t="n">
-        <v>2394343</v>
+        <v>2393006</v>
       </c>
       <c r="BB7" s="13" t="n">
-        <v>2426948</v>
+        <v>2413209</v>
       </c>
       <c r="BC7" s="13" t="n">
-        <v>2442445</v>
+        <v>2434586</v>
       </c>
       <c r="BD7" s="13" t="n">
-        <v>2461056</v>
+        <v>2457182</v>
       </c>
       <c r="BE7" s="13" t="n">
-        <v>2482286</v>
+        <v>2480656</v>
       </c>
       <c r="BF7" s="13" t="n">
-        <v>2505167</v>
+        <v>2504766</v>
       </c>
       <c r="BG7" s="13" t="n">
-        <v>2529104</v>
+        <v>2529344</v>
       </c>
       <c r="BH7" s="13" t="n">
-        <v>2553727</v>
+        <v>2554267</v>
       </c>
       <c r="BI7" s="13" t="n">
-        <v>2578800</v>
+        <v>2579447</v>
       </c>
     </row>
     <row r="8">
@@ -4431,25 +4431,25 @@
         <v>0</v>
       </c>
       <c r="G9" s="13" t="n">
-        <v>54286</v>
+        <v>0</v>
       </c>
       <c r="H9" s="13" t="n">
-        <v>54286</v>
+        <v>63333</v>
       </c>
       <c r="I9" s="13" t="n">
-        <v>54286</v>
+        <v>63333</v>
       </c>
       <c r="J9" s="13" t="n">
-        <v>54286</v>
+        <v>63333</v>
       </c>
       <c r="K9" s="13" t="n">
-        <v>54286</v>
+        <v>63333</v>
       </c>
       <c r="L9" s="13" t="n">
-        <v>54286</v>
+        <v>63333</v>
       </c>
       <c r="M9" s="13" t="n">
-        <v>54286</v>
+        <v>63333</v>
       </c>
       <c r="N9" s="13" t="n">
         <v>34819</v>
@@ -4618,22 +4618,22 @@
         <v>0</v>
       </c>
       <c r="G10" s="13" t="n">
-        <v>1759</v>
+        <v>0</v>
       </c>
       <c r="H10" s="13" t="n">
-        <v>2978</v>
+        <v>1962</v>
       </c>
       <c r="I10" s="13" t="n">
-        <v>4197</v>
+        <v>3384</v>
       </c>
       <c r="J10" s="13" t="n">
-        <v>5415</v>
+        <v>4806</v>
       </c>
       <c r="K10" s="13" t="n">
-        <v>6634</v>
+        <v>6228</v>
       </c>
       <c r="L10" s="13" t="n">
-        <v>7853</v>
+        <v>7650</v>
       </c>
       <c r="M10" s="13" t="n">
         <v>9072</v>
@@ -4805,22 +4805,22 @@
         <v>0</v>
       </c>
       <c r="G11" s="13" t="n">
-        <v>657</v>
+        <v>0</v>
       </c>
       <c r="H11" s="13" t="n">
-        <v>1314</v>
+        <v>766</v>
       </c>
       <c r="I11" s="13" t="n">
-        <v>1970</v>
+        <v>1533</v>
       </c>
       <c r="J11" s="13" t="n">
-        <v>2627</v>
+        <v>2299</v>
       </c>
       <c r="K11" s="13" t="n">
-        <v>3284</v>
+        <v>3065</v>
       </c>
       <c r="L11" s="13" t="n">
-        <v>3941</v>
+        <v>3832</v>
       </c>
       <c r="M11" s="13" t="n">
         <v>4598</v>
@@ -5354,22 +5354,22 @@
         <v>63000</v>
       </c>
       <c r="C14" s="13" t="n">
-        <v>45000</v>
+        <v>85000</v>
       </c>
       <c r="D14" s="13" t="n">
-        <v>40000</v>
+        <v>32000</v>
       </c>
       <c r="E14" s="13" t="n">
-        <v>135000</v>
+        <v>103000</v>
       </c>
       <c r="F14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="13" t="n">
         <v>65000</v>
       </c>
-      <c r="G14" s="13" t="n">
+      <c r="H14" s="13" t="n">
         <v>60000</v>
-      </c>
-      <c r="H14" s="13" t="n">
-        <v>0</v>
       </c>
       <c r="I14" s="13" t="n">
         <v>0</v>
@@ -5541,37 +5541,37 @@
         <v>63000</v>
       </c>
       <c r="C15" s="13" t="n">
-        <v>45000</v>
+        <v>85000</v>
       </c>
       <c r="D15" s="13" t="n">
-        <v>40000</v>
+        <v>32000</v>
       </c>
       <c r="E15" s="13" t="n">
-        <v>227500</v>
+        <v>195500</v>
       </c>
       <c r="F15" s="13" t="n">
+        <v>92500</v>
+      </c>
+      <c r="G15" s="13" t="n">
         <v>157500</v>
       </c>
-      <c r="G15" s="13" t="n">
-        <v>209201</v>
-      </c>
       <c r="H15" s="13" t="n">
-        <v>181077</v>
+        <v>248562</v>
       </c>
       <c r="I15" s="13" t="n">
-        <v>182953</v>
+        <v>190750</v>
       </c>
       <c r="J15" s="13" t="n">
-        <v>184828</v>
+        <v>192938</v>
       </c>
       <c r="K15" s="13" t="n">
-        <v>186704</v>
+        <v>195127</v>
       </c>
       <c r="L15" s="13" t="n">
-        <v>188580</v>
+        <v>197315</v>
       </c>
       <c r="M15" s="13" t="n">
-        <v>190456</v>
+        <v>199503</v>
       </c>
       <c r="N15" s="13" t="n">
         <v>187032</v>
@@ -5728,181 +5728,181 @@
         <v>-63000</v>
       </c>
       <c r="C16" s="14" t="n">
-        <v>-45000</v>
+        <v>-85000</v>
       </c>
       <c r="D16" s="14" t="n">
-        <v>-40000</v>
+        <v>-32000</v>
       </c>
       <c r="E16" s="14" t="n">
-        <v>-227500</v>
+        <v>-195500</v>
       </c>
       <c r="F16" s="14" t="n">
+        <v>-92500</v>
+      </c>
+      <c r="G16" s="14" t="n">
         <v>-157500</v>
       </c>
-      <c r="G16" s="14" t="n">
-        <v>-186047</v>
-      </c>
       <c r="H16" s="14" t="n">
-        <v>-144856</v>
+        <v>-223229</v>
       </c>
       <c r="I16" s="14" t="n">
-        <v>-133666</v>
+        <v>-150174</v>
       </c>
       <c r="J16" s="14" t="n">
-        <v>-122475</v>
+        <v>-137118</v>
       </c>
       <c r="K16" s="14" t="n">
-        <v>-111285</v>
+        <v>-124063</v>
       </c>
       <c r="L16" s="14" t="n">
-        <v>-100095</v>
+        <v>-111007</v>
       </c>
       <c r="M16" s="14" t="n">
-        <v>-88904</v>
+        <v>-97952</v>
       </c>
       <c r="N16" s="14" t="n">
-        <v>-30011</v>
+        <v>-25576</v>
       </c>
       <c r="O16" s="14" t="n">
-        <v>-47265</v>
+        <v>-48506</v>
       </c>
       <c r="P16" s="14" t="n">
-        <v>-38285</v>
+        <v>-37161</v>
       </c>
       <c r="Q16" s="14" t="n">
-        <v>-26686</v>
+        <v>-28090</v>
       </c>
       <c r="R16" s="14" t="n">
-        <v>-17508</v>
+        <v>-19057</v>
       </c>
       <c r="S16" s="14" t="n">
-        <v>-36699</v>
+        <v>-37548</v>
       </c>
       <c r="T16" s="14" t="n">
-        <v>-204030</v>
+        <v>-204612</v>
       </c>
       <c r="U16" s="14" t="n">
-        <v>-11016</v>
+        <v>-11668</v>
       </c>
       <c r="V16" s="14" t="n">
-        <v>1708</v>
+        <v>1281</v>
       </c>
       <c r="W16" s="14" t="n">
-        <v>14533</v>
+        <v>14240</v>
       </c>
       <c r="X16" s="14" t="n">
-        <v>27407</v>
+        <v>27189</v>
       </c>
       <c r="Y16" s="14" t="n">
-        <v>40307</v>
+        <v>40138</v>
       </c>
       <c r="Z16" s="14" t="n">
-        <v>47731</v>
+        <v>52510</v>
       </c>
       <c r="AA16" s="14" t="n">
-        <v>-378296</v>
+        <v>-374041</v>
       </c>
       <c r="AB16" s="14" t="n">
-        <v>58886</v>
+        <v>62335</v>
       </c>
       <c r="AC16" s="14" t="n">
-        <v>81384</v>
+        <v>84405</v>
       </c>
       <c r="AD16" s="14" t="n">
-        <v>104582</v>
+        <v>104647</v>
       </c>
       <c r="AE16" s="14" t="n">
-        <v>124815</v>
+        <v>124572</v>
       </c>
       <c r="AF16" s="14" t="n">
-        <v>148087</v>
+        <v>147622</v>
       </c>
       <c r="AG16" s="14" t="n">
-        <v>167906</v>
+        <v>167414</v>
       </c>
       <c r="AH16" s="14" t="n">
-        <v>-262386</v>
+        <v>-262846</v>
       </c>
       <c r="AI16" s="14" t="n">
-        <v>207171</v>
+        <v>206820</v>
       </c>
       <c r="AJ16" s="14" t="n">
-        <v>226717</v>
+        <v>226411</v>
       </c>
       <c r="AK16" s="14" t="n">
-        <v>246176</v>
+        <v>245928</v>
       </c>
       <c r="AL16" s="14" t="n">
-        <v>438438</v>
+        <v>450129</v>
       </c>
       <c r="AM16" s="14" t="n">
-        <v>154778</v>
+        <v>160114</v>
       </c>
       <c r="AN16" s="14" t="n">
-        <v>506758</v>
+        <v>507014</v>
       </c>
       <c r="AO16" s="14" t="n">
-        <v>460260</v>
+        <v>459126</v>
       </c>
       <c r="AP16" s="14" t="n">
-        <v>485967</v>
+        <v>476419</v>
       </c>
       <c r="AQ16" s="14" t="n">
-        <v>499975</v>
+        <v>494493</v>
       </c>
       <c r="AR16" s="14" t="n">
-        <v>516157</v>
+        <v>513130</v>
       </c>
       <c r="AS16" s="14" t="n">
-        <v>533728</v>
+        <v>532077</v>
       </c>
       <c r="AT16" s="14" t="n">
-        <v>552078</v>
+        <v>551484</v>
       </c>
       <c r="AU16" s="14" t="n">
-        <v>571159</v>
+        <v>570837</v>
       </c>
       <c r="AV16" s="14" t="n">
-        <v>590543</v>
+        <v>590601</v>
       </c>
       <c r="AW16" s="14" t="n">
-        <v>610357</v>
+        <v>610531</v>
       </c>
       <c r="AX16" s="14" t="n">
-        <v>1035375</v>
+        <v>1051542</v>
       </c>
       <c r="AY16" s="14" t="n">
-        <v>1076243</v>
+        <v>1082825</v>
       </c>
       <c r="AZ16" s="14" t="n">
-        <v>1109017</v>
+        <v>1111479</v>
       </c>
       <c r="BA16" s="14" t="n">
-        <v>1062790</v>
+        <v>1061454</v>
       </c>
       <c r="BB16" s="14" t="n">
-        <v>1088247</v>
+        <v>1074508</v>
       </c>
       <c r="BC16" s="14" t="n">
-        <v>1096596</v>
+        <v>1088737</v>
       </c>
       <c r="BD16" s="14" t="n">
-        <v>1108059</v>
+        <v>1104185</v>
       </c>
       <c r="BE16" s="14" t="n">
-        <v>1122140</v>
+        <v>1120510</v>
       </c>
       <c r="BF16" s="14" t="n">
-        <v>1137872</v>
+        <v>1137472</v>
       </c>
       <c r="BG16" s="14" t="n">
-        <v>1154661</v>
+        <v>1154901</v>
       </c>
       <c r="BH16" s="14" t="n">
-        <v>1172136</v>
+        <v>1172676</v>
       </c>
       <c r="BI16" s="14" t="n">
-        <v>1190060</v>
+        <v>1190707</v>
       </c>
     </row>
     <row r="17">
@@ -6508,25 +6508,25 @@
         <v>0</v>
       </c>
       <c r="G4" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="13" t="n">
         <v>16100</v>
       </c>
-      <c r="H4" s="13" t="n">
-        <v>41278</v>
-      </c>
       <c r="I4" s="13" t="n">
-        <v>66457</v>
+        <v>45475</v>
       </c>
       <c r="J4" s="13" t="n">
-        <v>91635</v>
+        <v>74850</v>
       </c>
       <c r="K4" s="13" t="n">
-        <v>116814</v>
+        <v>104224</v>
       </c>
       <c r="L4" s="13" t="n">
-        <v>141992</v>
+        <v>133599</v>
       </c>
       <c r="M4" s="13" t="n">
-        <v>167171</v>
+        <v>162974</v>
       </c>
       <c r="N4" s="13" t="n">
         <v>226964</v>
@@ -6680,19 +6680,19 @@
         </is>
       </c>
       <c r="B5" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="13" t="n">
         <v>63360</v>
       </c>
-      <c r="C5" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="13" t="n">
+      <c r="E5" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="13" t="n">
         <v>162878</v>
-      </c>
-      <c r="E5" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="13" t="n">
-        <v>0</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>63360</v>
@@ -6719,40 +6719,40 @@
         <v>204365</v>
       </c>
       <c r="O5" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="13" t="n">
+        <v>210203</v>
+      </c>
+      <c r="Q5" s="13" t="n">
         <v>58406</v>
       </c>
-      <c r="P5" s="13" t="n">
+      <c r="R5" s="13" t="n">
+        <v>210203</v>
+      </c>
+      <c r="S5" s="13" t="n">
         <v>151796</v>
-      </c>
-      <c r="Q5" s="13" t="n">
-        <v>210203</v>
-      </c>
-      <c r="R5" s="13" t="n">
-        <v>58406</v>
-      </c>
-      <c r="S5" s="13" t="n">
-        <v>210203</v>
       </c>
       <c r="T5" s="13" t="n">
         <v>210203</v>
       </c>
       <c r="U5" s="13" t="n">
-        <v>210203</v>
+        <v>77875</v>
       </c>
       <c r="V5" s="13" t="n">
         <v>204961</v>
       </c>
       <c r="W5" s="13" t="n">
-        <v>204961</v>
+        <v>273282</v>
       </c>
       <c r="X5" s="13" t="n">
-        <v>192644</v>
+        <v>210365</v>
       </c>
       <c r="Y5" s="13" t="n">
-        <v>228087</v>
+        <v>274580</v>
       </c>
       <c r="Z5" s="13" t="n">
-        <v>250061</v>
+        <v>296554</v>
       </c>
       <c r="AA5" s="13" t="n">
         <v>343047</v>
@@ -6761,22 +6761,22 @@
         <v>392857</v>
       </c>
       <c r="AC5" s="13" t="n">
+        <v>392857</v>
+      </c>
+      <c r="AD5" s="13" t="n">
         <v>411287</v>
       </c>
-      <c r="AD5" s="13" t="n">
-        <v>392857</v>
-      </c>
       <c r="AE5" s="13" t="n">
+        <v>429718</v>
+      </c>
+      <c r="AF5" s="13" t="n">
         <v>495194</v>
       </c>
-      <c r="AF5" s="13" t="n">
-        <v>429718</v>
-      </c>
       <c r="AG5" s="13" t="n">
-        <v>589285</v>
+        <v>542240</v>
       </c>
       <c r="AH5" s="13" t="n">
-        <v>530558</v>
+        <v>577604</v>
       </c>
       <c r="AI5" s="13" t="n">
         <v>594737</v>
@@ -6800,28 +6800,28 @@
         <v>653550</v>
       </c>
       <c r="AP5" s="13" t="n">
-        <v>653550</v>
+        <v>635732</v>
       </c>
       <c r="AQ5" s="13" t="n">
-        <v>752759</v>
+        <v>770577</v>
       </c>
       <c r="AR5" s="13" t="n">
-        <v>752759</v>
+        <v>707004</v>
       </c>
       <c r="AS5" s="13" t="n">
-        <v>907843</v>
+        <v>953599</v>
       </c>
       <c r="AT5" s="13" t="n">
-        <v>891645</v>
+        <v>874907</v>
       </c>
       <c r="AU5" s="13" t="n">
-        <v>920663</v>
+        <v>937401</v>
       </c>
       <c r="AV5" s="13" t="n">
-        <v>916073</v>
+        <v>872855</v>
       </c>
       <c r="AW5" s="13" t="n">
-        <v>856117</v>
+        <v>899335</v>
       </c>
       <c r="AX5" s="13" t="n">
         <v>952596</v>
@@ -6879,13 +6879,13 @@
         <v>0</v>
       </c>
       <c r="F6" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="13" t="n">
         <v>61238</v>
-      </c>
-      <c r="G6" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="13" t="n">
-        <v>0</v>
       </c>
       <c r="I6" s="13" t="n">
         <v>0</v>
@@ -6918,10 +6918,10 @@
         <v>57110</v>
       </c>
       <c r="S6" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" s="13" t="n">
         <v>57110</v>
-      </c>
-      <c r="T6" s="13" t="n">
-        <v>0</v>
       </c>
       <c r="U6" s="13" t="n">
         <v>57110</v>
@@ -6930,22 +6930,22 @@
         <v>57110</v>
       </c>
       <c r="W6" s="13" t="n">
-        <v>57110</v>
+        <v>0</v>
       </c>
       <c r="X6" s="13" t="n">
         <v>57110</v>
       </c>
       <c r="Y6" s="13" t="n">
-        <v>57110</v>
+        <v>76146</v>
       </c>
       <c r="Z6" s="13" t="n">
         <v>52742</v>
       </c>
       <c r="AA6" s="13" t="n">
-        <v>52742</v>
+        <v>70322</v>
       </c>
       <c r="AB6" s="13" t="n">
-        <v>52742</v>
+        <v>70322</v>
       </c>
       <c r="AC6" s="13" t="n">
         <v>87902</v>
@@ -6960,16 +6960,16 @@
         <v>104652</v>
       </c>
       <c r="AG6" s="13" t="n">
+        <v>104652</v>
+      </c>
+      <c r="AH6" s="13" t="n">
         <v>122094</v>
       </c>
-      <c r="AH6" s="13" t="n">
-        <v>104652</v>
-      </c>
       <c r="AI6" s="13" t="n">
+        <v>139536</v>
+      </c>
+      <c r="AJ6" s="13" t="n">
         <v>156978</v>
-      </c>
-      <c r="AJ6" s="13" t="n">
-        <v>139536</v>
       </c>
       <c r="AK6" s="13" t="n">
         <v>156978</v>
@@ -6999,10 +6999,10 @@
         <v>186247</v>
       </c>
       <c r="AT6" s="13" t="n">
-        <v>186247</v>
+        <v>169315</v>
       </c>
       <c r="AU6" s="13" t="n">
-        <v>237042</v>
+        <v>253973</v>
       </c>
       <c r="AV6" s="13" t="n">
         <v>237042</v>
@@ -7011,10 +7011,10 @@
         <v>253973</v>
       </c>
       <c r="AX6" s="13" t="n">
+        <v>224443</v>
+      </c>
+      <c r="AY6" s="13" t="n">
         <v>240475</v>
-      </c>
-      <c r="AY6" s="13" t="n">
-        <v>224443</v>
       </c>
       <c r="AZ6" s="13" t="n">
         <v>256506</v>
@@ -7057,37 +7057,37 @@
         <v>63000</v>
       </c>
       <c r="C7" s="13" t="n">
-        <v>45000</v>
+        <v>85000</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>40000</v>
+        <v>32000</v>
       </c>
       <c r="E7" s="13" t="n">
-        <v>227500</v>
+        <v>195500</v>
       </c>
       <c r="F7" s="13" t="n">
+        <v>92500</v>
+      </c>
+      <c r="G7" s="13" t="n">
         <v>157500</v>
       </c>
-      <c r="G7" s="13" t="n">
-        <v>209201</v>
-      </c>
       <c r="H7" s="13" t="n">
-        <v>181077</v>
+        <v>248562</v>
       </c>
       <c r="I7" s="13" t="n">
-        <v>182953</v>
+        <v>190750</v>
       </c>
       <c r="J7" s="13" t="n">
-        <v>184828</v>
+        <v>192938</v>
       </c>
       <c r="K7" s="13" t="n">
-        <v>186704</v>
+        <v>195127</v>
       </c>
       <c r="L7" s="13" t="n">
-        <v>188580</v>
+        <v>197315</v>
       </c>
       <c r="M7" s="13" t="n">
-        <v>190456</v>
+        <v>199503</v>
       </c>
       <c r="N7" s="13" t="n">
         <v>187032</v>
@@ -7244,37 +7244,37 @@
         <v>0</v>
       </c>
       <c r="C8" s="13" t="n">
-        <v>14580</v>
+        <v>19980</v>
       </c>
       <c r="D8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="E8" s="13" t="n">
-        <v>30982</v>
+        <v>25582</v>
       </c>
       <c r="F8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="G8" s="13" t="n">
-        <v>76540</v>
+        <v>23490</v>
       </c>
       <c r="H8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="I8" s="13" t="n">
-        <v>9720</v>
+        <v>67710</v>
       </c>
       <c r="J8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="K8" s="13" t="n">
-        <v>40010</v>
+        <v>45052</v>
       </c>
       <c r="L8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="M8" s="13" t="n">
-        <v>-15237</v>
+        <v>-12274</v>
       </c>
       <c r="N8" s="13" t="n">
         <v>0</v>
@@ -7292,37 +7292,37 @@
         <v>0</v>
       </c>
       <c r="S8" s="13" t="n">
-        <v>7333</v>
+        <v>-32091</v>
       </c>
       <c r="T8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="U8" s="13" t="n">
-        <v>-22958</v>
+        <v>16466</v>
       </c>
       <c r="V8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="W8" s="13" t="n">
-        <v>-24295</v>
+        <v>-63719</v>
       </c>
       <c r="X8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="Y8" s="13" t="n">
-        <v>-40756</v>
+        <v>-27615</v>
       </c>
       <c r="Z8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="AA8" s="13" t="n">
-        <v>-39854</v>
+        <v>-27892</v>
       </c>
       <c r="AB8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="AC8" s="13" t="n">
-        <v>-99317</v>
+        <v>-87355</v>
       </c>
       <c r="AD8" s="13" t="n">
         <v>0</v>
@@ -7334,7 +7334,7 @@
         <v>0</v>
       </c>
       <c r="AG8" s="13" t="n">
-        <v>-67516</v>
+        <v>-79956</v>
       </c>
       <c r="AH8" s="13" t="n">
         <v>0</v>
@@ -7346,7 +7346,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="13" t="n">
-        <v>-63027</v>
+        <v>-50587</v>
       </c>
       <c r="AL8" s="13" t="n">
         <v>0</v>
@@ -7497,7 +7497,7 @@
         <v>0</v>
       </c>
       <c r="Y9" s="13" t="n">
-        <v>-4534</v>
+        <v>-4474</v>
       </c>
       <c r="Z9" s="13" t="n">
         <v>0</v>
@@ -7515,7 +7515,7 @@
         <v>0</v>
       </c>
       <c r="AE9" s="13" t="n">
-        <v>-22539</v>
+        <v>-23137</v>
       </c>
       <c r="AF9" s="13" t="n">
         <v>0</v>
@@ -7533,7 +7533,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="13" t="n">
-        <v>-53787</v>
+        <v>-53687</v>
       </c>
       <c r="AL9" s="13" t="n">
         <v>0</v>
@@ -7551,7 +7551,7 @@
         <v>0</v>
       </c>
       <c r="AQ9" s="13" t="n">
-        <v>-343330</v>
+        <v>-333060</v>
       </c>
       <c r="AR9" s="13" t="n">
         <v>0</v>
@@ -7569,7 +7569,7 @@
         <v>0</v>
       </c>
       <c r="AW9" s="13" t="n">
-        <v>-910986</v>
+        <v>-909538</v>
       </c>
       <c r="AX9" s="13" t="n">
         <v>0</v>
@@ -7587,7 +7587,7 @@
         <v>0</v>
       </c>
       <c r="BC9" s="13" t="n">
-        <v>-1746433</v>
+        <v>-1747047</v>
       </c>
       <c r="BD9" s="13" t="n">
         <v>0</v>
@@ -7605,7 +7605,7 @@
         <v>0</v>
       </c>
       <c r="BI9" s="13" t="n">
-        <v>-1858931</v>
+        <v>-1857722</v>
       </c>
     </row>
     <row r="10">
@@ -7802,112 +7802,112 @@
         </is>
       </c>
       <c r="B11" s="14" t="n">
-        <v>3373640</v>
+        <v>3437000</v>
       </c>
       <c r="C11" s="14" t="n">
-        <v>-30420</v>
+        <v>-65020</v>
       </c>
       <c r="D11" s="14" t="n">
-        <v>-202878</v>
+        <v>-95360</v>
       </c>
       <c r="E11" s="14" t="n">
-        <v>-196518</v>
+        <v>-169918</v>
       </c>
       <c r="F11" s="14" t="n">
-        <v>-218738</v>
+        <v>-255378</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-179922</v>
+        <v>-197370</v>
       </c>
       <c r="H11" s="14" t="n">
-        <v>-139799</v>
+        <v>-293699</v>
       </c>
       <c r="I11" s="14" t="n">
-        <v>-269654</v>
+        <v>-240443</v>
       </c>
       <c r="J11" s="14" t="n">
-        <v>-149353</v>
+        <v>-174249</v>
       </c>
       <c r="K11" s="14" t="n">
-        <v>-91118</v>
+        <v>-107087</v>
       </c>
       <c r="L11" s="14" t="n">
-        <v>-248706</v>
+        <v>-265834</v>
       </c>
       <c r="M11" s="14" t="n">
-        <v>-38522</v>
+        <v>-48803</v>
       </c>
       <c r="N11" s="14" t="n">
         <v>-219670</v>
       </c>
       <c r="O11" s="14" t="n">
-        <v>-7651</v>
+        <v>50755</v>
       </c>
       <c r="P11" s="14" t="n">
-        <v>-124419</v>
+        <v>-182825</v>
       </c>
       <c r="Q11" s="14" t="n">
-        <v>-129098</v>
+        <v>22699</v>
       </c>
       <c r="R11" s="14" t="n">
-        <v>8731</v>
+        <v>-143065</v>
       </c>
       <c r="S11" s="14" t="n">
-        <v>-142477</v>
+        <v>-66385</v>
       </c>
       <c r="T11" s="14" t="n">
-        <v>-254211</v>
+        <v>-311321</v>
       </c>
       <c r="U11" s="14" t="n">
-        <v>11864210</v>
+        <v>12035962</v>
       </c>
       <c r="V11" s="14" t="n">
         <v>-76930</v>
       </c>
       <c r="W11" s="14" t="n">
-        <v>-70565</v>
+        <v>-121200</v>
       </c>
       <c r="X11" s="14" t="n">
-        <v>-3292</v>
+        <v>-21014</v>
       </c>
       <c r="Y11" s="14" t="n">
-        <v>-53365</v>
+        <v>-105693</v>
       </c>
       <c r="Z11" s="14" t="n">
-        <v>-46073</v>
+        <v>-92566</v>
       </c>
       <c r="AA11" s="14" t="n">
-        <v>-514362</v>
+        <v>-519980</v>
       </c>
       <c r="AB11" s="14" t="n">
-        <v>-54803</v>
+        <v>-72383</v>
       </c>
       <c r="AC11" s="14" t="n">
-        <v>-165479</v>
+        <v>-135086</v>
       </c>
       <c r="AD11" s="14" t="n">
-        <v>-22248</v>
+        <v>-40679</v>
       </c>
       <c r="AE11" s="14" t="n">
-        <v>-173256</v>
+        <v>-108378</v>
       </c>
       <c r="AF11" s="14" t="n">
-        <v>-100243</v>
+        <v>-165720</v>
       </c>
       <c r="AG11" s="14" t="n">
-        <v>-302536</v>
+        <v>-250489</v>
       </c>
       <c r="AH11" s="14" t="n">
-        <v>-310287</v>
+        <v>-374775</v>
       </c>
       <c r="AI11" s="14" t="n">
-        <v>60920</v>
+        <v>78362</v>
       </c>
       <c r="AJ11" s="14" t="n">
-        <v>169700</v>
+        <v>152257</v>
       </c>
       <c r="AK11" s="14" t="n">
-        <v>16548</v>
+        <v>29089</v>
       </c>
       <c r="AL11" s="14" t="n">
         <v>144175</v>
@@ -7922,34 +7922,34 @@
         <v>389349</v>
       </c>
       <c r="AP11" s="14" t="n">
-        <v>571514</v>
+        <v>589332</v>
       </c>
       <c r="AQ11" s="14" t="n">
-        <v>24127</v>
+        <v>16579</v>
       </c>
       <c r="AR11" s="14" t="n">
-        <v>557088</v>
+        <v>602843</v>
       </c>
       <c r="AS11" s="14" t="n">
-        <v>269681</v>
+        <v>223926</v>
       </c>
       <c r="AT11" s="14" t="n">
-        <v>486053</v>
+        <v>519722</v>
       </c>
       <c r="AU11" s="14" t="n">
-        <v>316387</v>
+        <v>282718</v>
       </c>
       <c r="AV11" s="14" t="n">
-        <v>495612</v>
+        <v>538830</v>
       </c>
       <c r="AW11" s="14" t="n">
-        <v>-436665</v>
+        <v>-478435</v>
       </c>
       <c r="AX11" s="14" t="n">
-        <v>365868</v>
+        <v>381900</v>
       </c>
       <c r="AY11" s="14" t="n">
-        <v>411448</v>
+        <v>395417</v>
       </c>
       <c r="AZ11" s="14" t="n">
         <v>1324620</v>
@@ -7961,7 +7961,7 @@
         <v>1286174</v>
       </c>
       <c r="BC11" s="14" t="n">
-        <v>-637230</v>
+        <v>-637844</v>
       </c>
       <c r="BD11" s="14" t="n">
         <v>1344171</v>
@@ -7979,7 +7979,7 @@
         <v>1493343</v>
       </c>
       <c r="BI11" s="14" t="n">
-        <v>-573655</v>
+        <v>-572446</v>
       </c>
     </row>
     <row r="12">
@@ -7989,184 +7989,184 @@
         </is>
       </c>
       <c r="B12" s="14" t="n">
-        <v>3373640</v>
+        <v>3437000</v>
       </c>
       <c r="C12" s="14" t="n">
-        <v>3343220</v>
+        <v>3371980</v>
       </c>
       <c r="D12" s="14" t="n">
-        <v>3140342</v>
+        <v>3276620</v>
       </c>
       <c r="E12" s="14" t="n">
-        <v>2943824</v>
+        <v>3106702</v>
       </c>
       <c r="F12" s="14" t="n">
-        <v>2725087</v>
+        <v>2851324</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>2545165</v>
+        <v>2653954</v>
       </c>
       <c r="H12" s="14" t="n">
-        <v>2405367</v>
+        <v>2360255</v>
       </c>
       <c r="I12" s="14" t="n">
-        <v>2135713</v>
+        <v>2119812</v>
       </c>
       <c r="J12" s="14" t="n">
-        <v>1986359</v>
+        <v>1945564</v>
       </c>
       <c r="K12" s="14" t="n">
-        <v>1895241</v>
+        <v>1838476</v>
       </c>
       <c r="L12" s="14" t="n">
-        <v>1646535</v>
+        <v>1572643</v>
       </c>
       <c r="M12" s="14" t="n">
-        <v>1608013</v>
+        <v>1523840</v>
       </c>
       <c r="N12" s="14" t="n">
-        <v>1388344</v>
+        <v>1304170</v>
       </c>
       <c r="O12" s="14" t="n">
-        <v>1380692</v>
+        <v>1354925</v>
       </c>
       <c r="P12" s="14" t="n">
-        <v>1256273</v>
+        <v>1172099</v>
       </c>
       <c r="Q12" s="14" t="n">
-        <v>1127176</v>
+        <v>1194798</v>
       </c>
       <c r="R12" s="14" t="n">
-        <v>1135907</v>
+        <v>1051733</v>
       </c>
       <c r="S12" s="14" t="n">
-        <v>993430</v>
+        <v>985348</v>
       </c>
       <c r="T12" s="14" t="n">
-        <v>739219</v>
+        <v>674027</v>
       </c>
       <c r="U12" s="14" t="n">
-        <v>12603429</v>
+        <v>12709989</v>
       </c>
       <c r="V12" s="14" t="n">
-        <v>12526498</v>
+        <v>12633059</v>
       </c>
       <c r="W12" s="14" t="n">
-        <v>12455933</v>
+        <v>12511858</v>
       </c>
       <c r="X12" s="14" t="n">
-        <v>12452641</v>
+        <v>12490844</v>
       </c>
       <c r="Y12" s="14" t="n">
-        <v>12399276</v>
+        <v>12385151</v>
       </c>
       <c r="Z12" s="14" t="n">
-        <v>12353203</v>
+        <v>12292585</v>
       </c>
       <c r="AA12" s="14" t="n">
-        <v>11838841</v>
+        <v>11772605</v>
       </c>
       <c r="AB12" s="14" t="n">
-        <v>11784038</v>
+        <v>11700221</v>
       </c>
       <c r="AC12" s="14" t="n">
-        <v>11618559</v>
+        <v>11565135</v>
       </c>
       <c r="AD12" s="14" t="n">
-        <v>11596311</v>
+        <v>11524457</v>
       </c>
       <c r="AE12" s="14" t="n">
-        <v>11423055</v>
+        <v>11416079</v>
       </c>
       <c r="AF12" s="14" t="n">
-        <v>11322812</v>
+        <v>11250359</v>
       </c>
       <c r="AG12" s="14" t="n">
-        <v>11020276</v>
+        <v>10999871</v>
       </c>
       <c r="AH12" s="14" t="n">
-        <v>10709989</v>
+        <v>10625096</v>
       </c>
       <c r="AI12" s="14" t="n">
-        <v>10770908</v>
+        <v>10703457</v>
       </c>
       <c r="AJ12" s="14" t="n">
-        <v>10940608</v>
+        <v>10855715</v>
       </c>
       <c r="AK12" s="14" t="n">
-        <v>10957155</v>
+        <v>10884803</v>
       </c>
       <c r="AL12" s="14" t="n">
-        <v>11101330</v>
+        <v>11028978</v>
       </c>
       <c r="AM12" s="14" t="n">
-        <v>10951522</v>
+        <v>10879171</v>
       </c>
       <c r="AN12" s="14" t="n">
-        <v>11551987</v>
+        <v>11479635</v>
       </c>
       <c r="AO12" s="14" t="n">
-        <v>11941335</v>
+        <v>11868983</v>
       </c>
       <c r="AP12" s="14" t="n">
-        <v>12512850</v>
+        <v>12458316</v>
       </c>
       <c r="AQ12" s="14" t="n">
-        <v>12536977</v>
+        <v>12474895</v>
       </c>
       <c r="AR12" s="14" t="n">
-        <v>13094064</v>
+        <v>13077738</v>
       </c>
       <c r="AS12" s="14" t="n">
-        <v>13363745</v>
+        <v>13301664</v>
       </c>
       <c r="AT12" s="14" t="n">
-        <v>13849798</v>
+        <v>13821386</v>
       </c>
       <c r="AU12" s="14" t="n">
-        <v>14166185</v>
+        <v>14104104</v>
       </c>
       <c r="AV12" s="14" t="n">
-        <v>14661797</v>
+        <v>14642934</v>
       </c>
       <c r="AW12" s="14" t="n">
-        <v>14225133</v>
+        <v>14164499</v>
       </c>
       <c r="AX12" s="14" t="n">
-        <v>14591001</v>
+        <v>14546399</v>
       </c>
       <c r="AY12" s="14" t="n">
-        <v>15002449</v>
+        <v>14941815</v>
       </c>
       <c r="AZ12" s="14" t="n">
-        <v>16327069</v>
+        <v>16266435</v>
       </c>
       <c r="BA12" s="14" t="n">
-        <v>17392447</v>
+        <v>17331813</v>
       </c>
       <c r="BB12" s="14" t="n">
-        <v>18678621</v>
+        <v>18617987</v>
       </c>
       <c r="BC12" s="14" t="n">
-        <v>18041391</v>
+        <v>17980143</v>
       </c>
       <c r="BD12" s="14" t="n">
-        <v>19385562</v>
+        <v>19324313</v>
       </c>
       <c r="BE12" s="14" t="n">
-        <v>20561289</v>
+        <v>20500041</v>
       </c>
       <c r="BF12" s="14" t="n">
-        <v>21980046</v>
+        <v>21918798</v>
       </c>
       <c r="BG12" s="14" t="n">
-        <v>23210548</v>
+        <v>23149300</v>
       </c>
       <c r="BH12" s="14" t="n">
-        <v>24703892</v>
+        <v>24642643</v>
       </c>
       <c r="BI12" s="14" t="n">
-        <v>24130237</v>
+        <v>24070197</v>
       </c>
     </row>
     <row r="13">
@@ -8188,172 +8188,172 @@
         <v>0</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>29400</v>
+        <v>0</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>28097</v>
+        <v>0</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>25891</v>
+        <v>27947</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>22783</v>
+        <v>25440</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>18771</v>
+        <v>21880</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>43257</v>
+        <v>46667</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>37440</v>
+        <v>41000</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>30720</v>
+        <v>34280</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>50743</v>
+        <v>54303</v>
       </c>
       <c r="O13" s="12" t="n">
-        <v>40450</v>
+        <v>44010</v>
       </c>
       <c r="P13" s="12" t="n">
-        <v>58640</v>
+        <v>62200</v>
       </c>
       <c r="Q13" s="12" t="n">
-        <v>46513</v>
+        <v>50073</v>
       </c>
       <c r="R13" s="12" t="n">
-        <v>62870</v>
+        <v>66430</v>
       </c>
       <c r="S13" s="12" t="n">
-        <v>78310</v>
+        <v>52470</v>
       </c>
       <c r="T13" s="12" t="n">
-        <v>62953</v>
+        <v>66513</v>
       </c>
       <c r="U13" s="12" t="n">
-        <v>75600</v>
+        <v>79160</v>
       </c>
       <c r="V13" s="12" t="n">
-        <v>86850</v>
+        <v>90410</v>
       </c>
       <c r="W13" s="12" t="n">
-        <v>96703</v>
+        <v>70863</v>
       </c>
       <c r="X13" s="12" t="n">
-        <v>105160</v>
+        <v>79320</v>
       </c>
       <c r="Y13" s="12" t="n">
-        <v>112220</v>
+        <v>96180</v>
       </c>
       <c r="Z13" s="12" t="n">
-        <v>113350</v>
+        <v>97310</v>
       </c>
       <c r="AA13" s="12" t="n">
-        <v>112580</v>
+        <v>106340</v>
       </c>
       <c r="AB13" s="12" t="n">
-        <v>109910</v>
+        <v>113470</v>
       </c>
       <c r="AC13" s="12" t="n">
-        <v>124940</v>
+        <v>128500</v>
       </c>
       <c r="AD13" s="12" t="n">
-        <v>147870</v>
+        <v>151430</v>
       </c>
       <c r="AE13" s="12" t="n">
-        <v>168900</v>
+        <v>172460</v>
       </c>
       <c r="AF13" s="12" t="n">
-        <v>173030</v>
+        <v>176590</v>
       </c>
       <c r="AG13" s="12" t="n">
-        <v>185060</v>
+        <v>178820</v>
       </c>
       <c r="AH13" s="12" t="n">
-        <v>185390</v>
+        <v>188950</v>
       </c>
       <c r="AI13" s="12" t="n">
-        <v>213220</v>
+        <v>206980</v>
       </c>
       <c r="AJ13" s="12" t="n">
-        <v>229350</v>
+        <v>232910</v>
       </c>
       <c r="AK13" s="12" t="n">
-        <v>253380</v>
+        <v>256940</v>
       </c>
       <c r="AL13" s="12" t="n">
-        <v>257142</v>
+        <v>260702</v>
       </c>
       <c r="AM13" s="12" t="n">
-        <v>268834</v>
+        <v>272394</v>
       </c>
       <c r="AN13" s="12" t="n">
-        <v>268855</v>
+        <v>272415</v>
       </c>
       <c r="AO13" s="12" t="n">
-        <v>276805</v>
+        <v>280365</v>
       </c>
       <c r="AP13" s="12" t="n">
-        <v>282884</v>
+        <v>286444</v>
       </c>
       <c r="AQ13" s="12" t="n">
-        <v>287092</v>
+        <v>290652</v>
       </c>
       <c r="AR13" s="12" t="n">
-        <v>289430</v>
+        <v>292990</v>
       </c>
       <c r="AS13" s="12" t="n">
-        <v>299697</v>
+        <v>303257</v>
       </c>
       <c r="AT13" s="12" t="n">
-        <v>308092</v>
+        <v>301852</v>
       </c>
       <c r="AU13" s="12" t="n">
-        <v>344017</v>
+        <v>347577</v>
       </c>
       <c r="AV13" s="12" t="n">
-        <v>378072</v>
+        <v>381632</v>
       </c>
       <c r="AW13" s="12" t="n">
-        <v>420055</v>
+        <v>423615</v>
       </c>
       <c r="AX13" s="12" t="n">
-        <v>426490</v>
+        <v>420250</v>
       </c>
       <c r="AY13" s="12" t="n">
-        <v>421553</v>
+        <v>425113</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>434642</v>
+        <v>438202</v>
       </c>
       <c r="BA13" s="12" t="n">
-        <v>436359</v>
+        <v>439919</v>
       </c>
       <c r="BB13" s="12" t="n">
-        <v>436503</v>
+        <v>440063</v>
       </c>
       <c r="BC13" s="12" t="n">
-        <v>444874</v>
+        <v>448434</v>
       </c>
       <c r="BD13" s="12" t="n">
-        <v>451672</v>
+        <v>455232</v>
       </c>
       <c r="BE13" s="12" t="n">
-        <v>456897</v>
+        <v>460457</v>
       </c>
       <c r="BF13" s="12" t="n">
-        <v>460549</v>
+        <v>464109</v>
       </c>
       <c r="BG13" s="12" t="n">
-        <v>462628</v>
+        <v>466188</v>
       </c>
       <c r="BH13" s="12" t="n">
-        <v>463134</v>
+        <v>466694</v>
       </c>
       <c r="BI13" s="12" t="n">
-        <v>462068</v>
+        <v>465628</v>
       </c>
     </row>
     <row r="14">
@@ -8375,172 +8375,172 @@
         <v>0</v>
       </c>
       <c r="F14" s="13" t="n">
-        <v>287476</v>
+        <v>0</v>
       </c>
       <c r="G14" s="13" t="n">
-        <v>274736</v>
+        <v>0</v>
       </c>
       <c r="H14" s="13" t="n">
-        <v>253169</v>
+        <v>273265</v>
       </c>
       <c r="I14" s="13" t="n">
-        <v>222773</v>
+        <v>248754</v>
       </c>
       <c r="J14" s="13" t="n">
-        <v>183549</v>
+        <v>213944</v>
       </c>
       <c r="K14" s="13" t="n">
-        <v>422972</v>
+        <v>456311</v>
       </c>
       <c r="L14" s="13" t="n">
-        <v>366091</v>
+        <v>400901</v>
       </c>
       <c r="M14" s="13" t="n">
-        <v>300383</v>
+        <v>335193</v>
       </c>
       <c r="N14" s="13" t="n">
-        <v>466053</v>
+        <v>505298</v>
       </c>
       <c r="O14" s="13" t="n">
-        <v>371513</v>
+        <v>409517</v>
       </c>
       <c r="P14" s="13" t="n">
-        <v>525911</v>
+        <v>565039</v>
       </c>
       <c r="Q14" s="13" t="n">
-        <v>417153</v>
+        <v>454877</v>
       </c>
       <c r="R14" s="13" t="n">
-        <v>567487</v>
+        <v>603662</v>
       </c>
       <c r="S14" s="13" t="n">
-        <v>708791</v>
+        <v>476805</v>
       </c>
       <c r="T14" s="13" t="n">
-        <v>569797</v>
+        <v>604541</v>
       </c>
       <c r="U14" s="13" t="n">
-        <v>685473</v>
+        <v>719565</v>
       </c>
       <c r="V14" s="13" t="n">
-        <v>788217</v>
+        <v>821883</v>
       </c>
       <c r="W14" s="13" t="n">
-        <v>878132</v>
+        <v>644191</v>
       </c>
       <c r="X14" s="13" t="n">
-        <v>955264</v>
+        <v>721106</v>
       </c>
       <c r="Y14" s="13" t="n">
-        <v>1019642</v>
+        <v>874419</v>
       </c>
       <c r="Z14" s="13" t="n">
-        <v>1008163</v>
+        <v>867719</v>
       </c>
       <c r="AA14" s="13" t="n">
-        <v>985209</v>
+        <v>930815</v>
       </c>
       <c r="AB14" s="13" t="n">
-        <v>949943</v>
+        <v>980793</v>
       </c>
       <c r="AC14" s="13" t="n">
-        <v>1065318</v>
+        <v>1099189</v>
       </c>
       <c r="AD14" s="13" t="n">
-        <v>1256977</v>
+        <v>1290913</v>
       </c>
       <c r="AE14" s="13" t="n">
-        <v>1433420</v>
+        <v>1467114</v>
       </c>
       <c r="AF14" s="13" t="n">
-        <v>1466956</v>
+        <v>1500185</v>
       </c>
       <c r="AG14" s="13" t="n">
-        <v>1567781</v>
+        <v>1517599</v>
       </c>
       <c r="AH14" s="13" t="n">
-        <v>1569947</v>
+        <v>1602223</v>
       </c>
       <c r="AI14" s="13" t="n">
-        <v>1804977</v>
+        <v>1753983</v>
       </c>
       <c r="AJ14" s="13" t="n">
-        <v>1941186</v>
+        <v>1972805</v>
       </c>
       <c r="AK14" s="13" t="n">
-        <v>2144324</v>
+        <v>2175695</v>
       </c>
       <c r="AL14" s="13" t="n">
-        <v>2127137</v>
+        <v>2170199</v>
       </c>
       <c r="AM14" s="13" t="n">
-        <v>2188062</v>
+        <v>2236460</v>
       </c>
       <c r="AN14" s="13" t="n">
-        <v>2167762</v>
+        <v>2216416</v>
       </c>
       <c r="AO14" s="13" t="n">
-        <v>2216580</v>
+        <v>2264099</v>
       </c>
       <c r="AP14" s="13" t="n">
-        <v>2285550</v>
+        <v>2323522</v>
       </c>
       <c r="AQ14" s="13" t="n">
-        <v>2332813</v>
+        <v>2365302</v>
       </c>
       <c r="AR14" s="13" t="n">
-        <v>2360541</v>
+        <v>2390003</v>
       </c>
       <c r="AS14" s="13" t="n">
-        <v>2450628</v>
+        <v>2478441</v>
       </c>
       <c r="AT14" s="13" t="n">
-        <v>2523350</v>
+        <v>2470063</v>
       </c>
       <c r="AU14" s="13" t="n">
-        <v>2820951</v>
+        <v>2847846</v>
       </c>
       <c r="AV14" s="13" t="n">
-        <v>3102220</v>
+        <v>3129173</v>
       </c>
       <c r="AW14" s="13" t="n">
-        <v>3448090</v>
+        <v>3475218</v>
       </c>
       <c r="AX14" s="13" t="n">
-        <v>3434053</v>
+        <v>3401360</v>
       </c>
       <c r="AY14" s="13" t="n">
-        <v>3353400</v>
+        <v>3403276</v>
       </c>
       <c r="AZ14" s="13" t="n">
-        <v>3425999</v>
+        <v>3478338</v>
       </c>
       <c r="BA14" s="13" t="n">
-        <v>3420637</v>
+        <v>3471639</v>
       </c>
       <c r="BB14" s="13" t="n">
-        <v>3453577</v>
+        <v>3490840</v>
       </c>
       <c r="BC14" s="13" t="n">
-        <v>3542313</v>
+        <v>3571717</v>
       </c>
       <c r="BD14" s="13" t="n">
-        <v>3611015</v>
+        <v>3636545</v>
       </c>
       <c r="BE14" s="13" t="n">
-        <v>3662302</v>
+        <v>3686202</v>
       </c>
       <c r="BF14" s="13" t="n">
-        <v>3697825</v>
+        <v>3721324</v>
       </c>
       <c r="BG14" s="13" t="n">
-        <v>3718641</v>
+        <v>3742380</v>
       </c>
       <c r="BH14" s="13" t="n">
-        <v>3725435</v>
+        <v>3749714</v>
       </c>
       <c r="BI14" s="13" t="n">
-        <v>3718657</v>
+        <v>3743583</v>
       </c>
     </row>
     <row r="15">
@@ -8565,22 +8565,22 @@
         <v>0</v>
       </c>
       <c r="G15" s="13" t="n">
-        <v>25178</v>
+        <v>0</v>
       </c>
       <c r="H15" s="13" t="n">
-        <v>50357</v>
+        <v>29375</v>
       </c>
       <c r="I15" s="13" t="n">
-        <v>75535</v>
+        <v>58750</v>
       </c>
       <c r="J15" s="13" t="n">
-        <v>100714</v>
+        <v>88124</v>
       </c>
       <c r="K15" s="13" t="n">
-        <v>125892</v>
+        <v>117499</v>
       </c>
       <c r="L15" s="13" t="n">
-        <v>151071</v>
+        <v>146874</v>
       </c>
       <c r="M15" s="13" t="n">
         <v>176249</v>
@@ -8801,13 +8801,13 @@
         </is>
       </c>
       <c r="B5" s="12" t="n">
-        <v>12636</v>
+        <v>11034</v>
       </c>
       <c r="C5" s="12" t="n">
-        <v>28080</v>
+        <v>24520</v>
       </c>
       <c r="D5" s="12" t="n">
-        <v>43524</v>
+        <v>38006</v>
       </c>
     </row>
     <row r="6">
@@ -8849,13 +8849,13 @@
         </is>
       </c>
       <c r="B8" s="13" t="n">
-        <v>300769.92</v>
+        <v>262433.43</v>
       </c>
       <c r="C8" s="13" t="n">
-        <v>711040</v>
+        <v>620410</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>1135175.36</v>
+        <v>990484.5649999999</v>
       </c>
     </row>
     <row r="9">
@@ -8897,13 +8897,13 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>0.5841</v>
+        <v>0.5838</v>
       </c>
       <c r="C11" s="8" t="n">
         <v>0.6719000000000001</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>0.6956</v>
+        <v>0.6954</v>
       </c>
     </row>
     <row r="12">
@@ -8913,13 +8913,13 @@
         </is>
       </c>
       <c r="B12" s="13" t="n">
-        <v>210275.1833</v>
+        <v>204661.8055</v>
       </c>
       <c r="C12" s="13" t="n">
-        <v>13353196.9556</v>
+        <v>13350995.4564</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>26818444.8704</v>
+        <v>26811460.7425</v>
       </c>
     </row>
     <row r="13">
@@ -8929,13 +8929,13 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>0.0119</v>
+        <v>0.0116</v>
       </c>
       <c r="C13" s="8" t="n">
         <v>0.306</v>
       </c>
       <c r="D13" s="8" t="n">
-        <v>0.391</v>
+        <v>0.3909</v>
       </c>
     </row>
     <row r="14">
@@ -8945,13 +8945,13 @@
         </is>
       </c>
       <c r="B14" s="13" t="n">
-        <v>-5094797.0875</v>
+        <v>-5116360.2475</v>
       </c>
       <c r="C14" s="13" t="n">
-        <v>18298295.4026</v>
+        <v>18254314.5811</v>
       </c>
       <c r="D14" s="13" t="n">
-        <v>46170557.4812</v>
+        <v>46109341.8032</v>
       </c>
     </row>
     <row r="15">
@@ -8977,13 +8977,13 @@
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>7717074.4142</v>
+        <v>7752567.734</v>
       </c>
       <c r="C16" s="13" t="n">
-        <v>4790011.3534</v>
+        <v>4874904.3651</v>
       </c>
       <c r="D16" s="13" t="n">
-        <v>2703007.3995</v>
+        <v>2798324.8512</v>
       </c>
     </row>
     <row r="17">
@@ -9009,13 +9009,13 @@
         </is>
       </c>
       <c r="B18" s="13" t="n">
-        <v>1295155.6191</v>
+        <v>1259662.2993</v>
       </c>
       <c r="C18" s="13" t="n">
-        <v>739218.8665</v>
+        <v>674027.0365</v>
       </c>
       <c r="D18" s="13" t="n">
-        <v>1035191.4611</v>
+        <v>990261.4608</v>
       </c>
     </row>
     <row r="19">
@@ -9025,13 +9025,13 @@
         </is>
       </c>
       <c r="B19" s="13" t="n">
-        <v>8737278.4871</v>
+        <v>8702112.9256</v>
       </c>
       <c r="C19" s="13" t="n">
-        <v>24130236.9414</v>
+        <v>24070197.3733</v>
       </c>
       <c r="D19" s="13" t="n">
-        <v>41261862.2519</v>
+        <v>41179779.1137</v>
       </c>
     </row>
   </sheetData>
@@ -9223,7 +9223,7 @@
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>528408</v>
+        <v>523602</v>
       </c>
       <c r="C15" t="inlineStr"/>
     </row>
@@ -9234,7 +9234,7 @@
         </is>
       </c>
       <c r="B16" s="14" t="n">
-        <v>2125884</v>
+        <v>2121078</v>
       </c>
     </row>
     <row r="17">
@@ -9244,13 +9244,13 @@
         </is>
       </c>
       <c r="B17" s="14" t="n">
-        <v>1374116</v>
+        <v>1378922</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Note: the base case dips to its lowest cash balance in month 19 at R739,219. The growth round must be closed before then, not started then.</t>
+          <t>Note: the base case dips to its lowest cash balance in month 19 at R674,027. The growth round must be closed before then, not started then.</t>
         </is>
       </c>
     </row>
@@ -9268,7 +9268,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J54"/>
+  <dimension ref="A1:J53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9344,10 +9344,10 @@
     </row>
     <row r="4">
       <c r="A4" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B4" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C4" s="12" t="n">
         <v>30000</v>
@@ -9504,10 +9504,10 @@
     </row>
     <row r="9">
       <c r="A9" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B9" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>30000</v>
@@ -9600,10 +9600,10 @@
     </row>
     <row r="12">
       <c r="A12" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B12" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C12" s="12" t="n">
         <v>30000</v>
@@ -9632,31 +9632,31 @@
     </row>
     <row r="13">
       <c r="A13" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B13" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C13" s="12" t="n">
-        <v>30000</v>
+        <v>40000</v>
       </c>
       <c r="D13" s="13" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="E13" s="13" t="n">
-        <v>194688</v>
+        <v>259584</v>
       </c>
       <c r="F13" s="13" t="n">
-        <v>14541</v>
+        <v>19389</v>
       </c>
       <c r="G13" s="13" t="n">
-        <v>973</v>
+        <v>1298</v>
       </c>
       <c r="H13" s="13" t="n">
-        <v>48672</v>
+        <v>64896</v>
       </c>
       <c r="I13" s="13" t="n">
-        <v>8438</v>
+        <v>11250</v>
       </c>
       <c r="J13" s="6" t="n">
         <v>8.91</v>
@@ -9664,10 +9664,10 @@
     </row>
     <row r="14">
       <c r="A14" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B14" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C14" s="12" t="n">
         <v>30000</v>
@@ -9676,51 +9676,51 @@
         <v>0.22</v>
       </c>
       <c r="E14" s="13" t="n">
-        <v>194688</v>
+        <v>177216</v>
       </c>
       <c r="F14" s="13" t="n">
         <v>14541</v>
       </c>
       <c r="G14" s="13" t="n">
-        <v>973</v>
+        <v>886</v>
       </c>
       <c r="H14" s="13" t="n">
-        <v>48672</v>
+        <v>44304</v>
       </c>
       <c r="I14" s="13" t="n">
         <v>8438</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>8.91</v>
+        <v>8.18</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B15" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C15" s="12" t="n">
-        <v>30000</v>
+        <v>40000</v>
       </c>
       <c r="D15" s="13" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="E15" s="13" t="n">
-        <v>177216</v>
+        <v>236288</v>
       </c>
       <c r="F15" s="13" t="n">
-        <v>14541</v>
+        <v>19389</v>
       </c>
       <c r="G15" s="13" t="n">
-        <v>886</v>
+        <v>1181</v>
       </c>
       <c r="H15" s="13" t="n">
-        <v>44304</v>
+        <v>59072</v>
       </c>
       <c r="I15" s="13" t="n">
-        <v>8438</v>
+        <v>11250</v>
       </c>
       <c r="J15" s="6" t="n">
         <v>8.18</v>
@@ -9728,31 +9728,31 @@
     </row>
     <row r="16">
       <c r="A16" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B16" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C16" s="12" t="n">
-        <v>30000</v>
+        <v>40000</v>
       </c>
       <c r="D16" s="13" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="E16" s="13" t="n">
-        <v>177216</v>
+        <v>236288</v>
       </c>
       <c r="F16" s="13" t="n">
-        <v>14541</v>
+        <v>19389</v>
       </c>
       <c r="G16" s="13" t="n">
-        <v>886</v>
+        <v>1181</v>
       </c>
       <c r="H16" s="13" t="n">
-        <v>44304</v>
+        <v>59072</v>
       </c>
       <c r="I16" s="13" t="n">
-        <v>8438</v>
+        <v>11250</v>
       </c>
       <c r="J16" s="6" t="n">
         <v>8.18</v>
@@ -9760,31 +9760,31 @@
     </row>
     <row r="17">
       <c r="A17" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B17" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C17" s="12" t="n">
-        <v>30000</v>
+        <v>50000</v>
       </c>
       <c r="D17" s="13" t="n">
-        <v>0.22</v>
+        <v>0.37</v>
       </c>
       <c r="E17" s="13" t="n">
-        <v>177216</v>
+        <v>295360</v>
       </c>
       <c r="F17" s="13" t="n">
-        <v>14541</v>
+        <v>24236</v>
       </c>
       <c r="G17" s="13" t="n">
-        <v>886</v>
+        <v>1477</v>
       </c>
       <c r="H17" s="13" t="n">
-        <v>44304</v>
+        <v>73840</v>
       </c>
       <c r="I17" s="13" t="n">
-        <v>8438</v>
+        <v>14062</v>
       </c>
       <c r="J17" s="6" t="n">
         <v>8.18</v>
@@ -9792,42 +9792,42 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B18" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C18" s="12" t="n">
-        <v>50000</v>
+        <v>60000</v>
       </c>
       <c r="D18" s="13" t="n">
-        <v>0.37</v>
+        <v>0.45</v>
       </c>
       <c r="E18" s="13" t="n">
-        <v>295360</v>
+        <v>368609</v>
       </c>
       <c r="F18" s="13" t="n">
-        <v>24236</v>
+        <v>22405</v>
       </c>
       <c r="G18" s="13" t="n">
-        <v>1477</v>
+        <v>1843</v>
       </c>
       <c r="H18" s="13" t="n">
-        <v>73840</v>
+        <v>92152</v>
       </c>
       <c r="I18" s="13" t="n">
-        <v>14062</v>
+        <v>12500</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>8.18</v>
+        <v>8.289999999999999</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B19" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C19" s="12" t="n">
         <v>60000</v>
@@ -9856,10 +9856,10 @@
     </row>
     <row r="20">
       <c r="A20" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B20" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C20" s="12" t="n">
         <v>60000</v>
@@ -9888,10 +9888,10 @@
     </row>
     <row r="21">
       <c r="A21" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B21" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C21" s="12" t="n">
         <v>60000</v>
@@ -9920,10 +9920,10 @@
     </row>
     <row r="22">
       <c r="A22" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B22" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C22" s="12" t="n">
         <v>70000</v>
@@ -9952,31 +9952,31 @@
     </row>
     <row r="23">
       <c r="A23" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B23" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C23" s="12" t="n">
-        <v>60000</v>
+        <v>80000</v>
       </c>
       <c r="D23" s="13" t="n">
-        <v>0.45</v>
+        <v>0.6</v>
       </c>
       <c r="E23" s="13" t="n">
-        <v>368609</v>
+        <v>491479</v>
       </c>
       <c r="F23" s="13" t="n">
-        <v>22405</v>
+        <v>29873</v>
       </c>
       <c r="G23" s="13" t="n">
-        <v>1843</v>
+        <v>2457</v>
       </c>
       <c r="H23" s="13" t="n">
-        <v>92152</v>
+        <v>122870</v>
       </c>
       <c r="I23" s="13" t="n">
-        <v>12500</v>
+        <v>16667</v>
       </c>
       <c r="J23" s="6" t="n">
         <v>8.289999999999999</v>
@@ -9984,10 +9984,10 @@
     </row>
     <row r="24">
       <c r="A24" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B24" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C24" s="12" t="n">
         <v>90000</v>
@@ -10016,31 +10016,31 @@
     </row>
     <row r="25">
       <c r="A25" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B25" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C25" s="12" t="n">
-        <v>80000</v>
+        <v>90000</v>
       </c>
       <c r="D25" s="13" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="E25" s="13" t="n">
-        <v>491479</v>
+        <v>552914</v>
       </c>
       <c r="F25" s="13" t="n">
-        <v>29873</v>
+        <v>33607</v>
       </c>
       <c r="G25" s="13" t="n">
-        <v>2457</v>
+        <v>2765</v>
       </c>
       <c r="H25" s="13" t="n">
-        <v>122870</v>
+        <v>138228</v>
       </c>
       <c r="I25" s="13" t="n">
-        <v>16667</v>
+        <v>18750</v>
       </c>
       <c r="J25" s="6" t="n">
         <v>8.289999999999999</v>
@@ -10048,10 +10048,10 @@
     </row>
     <row r="26">
       <c r="A26" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B26" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C26" s="12" t="n">
         <v>90000</v>
@@ -10060,51 +10060,51 @@
         <v>0.67</v>
       </c>
       <c r="E26" s="13" t="n">
-        <v>552914</v>
+        <v>513976</v>
       </c>
       <c r="F26" s="13" t="n">
         <v>33607</v>
       </c>
       <c r="G26" s="13" t="n">
-        <v>2765</v>
+        <v>2570</v>
       </c>
       <c r="H26" s="13" t="n">
-        <v>138228</v>
+        <v>128494</v>
       </c>
       <c r="I26" s="13" t="n">
         <v>18750</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>8.289999999999999</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B27" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C27" s="12" t="n">
-        <v>90000</v>
+        <v>100000</v>
       </c>
       <c r="D27" s="13" t="n">
-        <v>0.67</v>
+        <v>0.74</v>
       </c>
       <c r="E27" s="13" t="n">
-        <v>513976</v>
+        <v>571085</v>
       </c>
       <c r="F27" s="13" t="n">
-        <v>33607</v>
+        <v>37341</v>
       </c>
       <c r="G27" s="13" t="n">
-        <v>2570</v>
+        <v>2855</v>
       </c>
       <c r="H27" s="13" t="n">
-        <v>128494</v>
+        <v>142771</v>
       </c>
       <c r="I27" s="13" t="n">
-        <v>18750</v>
+        <v>20833</v>
       </c>
       <c r="J27" s="6" t="n">
         <v>7.75</v>
@@ -10112,31 +10112,31 @@
     </row>
     <row r="28">
       <c r="A28" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B28" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C28" s="12" t="n">
-        <v>100000</v>
+        <v>90000</v>
       </c>
       <c r="D28" s="13" t="n">
-        <v>0.74</v>
+        <v>0.67</v>
       </c>
       <c r="E28" s="13" t="n">
-        <v>571085</v>
+        <v>513976</v>
       </c>
       <c r="F28" s="13" t="n">
-        <v>37341</v>
+        <v>33607</v>
       </c>
       <c r="G28" s="13" t="n">
-        <v>2855</v>
+        <v>2570</v>
       </c>
       <c r="H28" s="13" t="n">
-        <v>142771</v>
+        <v>128494</v>
       </c>
       <c r="I28" s="13" t="n">
-        <v>20833</v>
+        <v>18750</v>
       </c>
       <c r="J28" s="6" t="n">
         <v>7.75</v>
@@ -10144,31 +10144,31 @@
     </row>
     <row r="29">
       <c r="A29" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B29" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C29" s="12" t="n">
-        <v>90000</v>
+        <v>100000</v>
       </c>
       <c r="D29" s="13" t="n">
-        <v>0.67</v>
+        <v>0.74</v>
       </c>
       <c r="E29" s="13" t="n">
-        <v>513976</v>
+        <v>571085</v>
       </c>
       <c r="F29" s="13" t="n">
-        <v>33607</v>
+        <v>37341</v>
       </c>
       <c r="G29" s="13" t="n">
-        <v>2570</v>
+        <v>2855</v>
       </c>
       <c r="H29" s="13" t="n">
-        <v>128494</v>
+        <v>142771</v>
       </c>
       <c r="I29" s="13" t="n">
-        <v>18750</v>
+        <v>20833</v>
       </c>
       <c r="J29" s="6" t="n">
         <v>7.75</v>
@@ -10176,10 +10176,10 @@
     </row>
     <row r="30">
       <c r="A30" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B30" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C30" s="12" t="n">
         <v>100000</v>
@@ -10188,30 +10188,30 @@
         <v>0.74</v>
       </c>
       <c r="E30" s="13" t="n">
-        <v>571085</v>
+        <v>593928</v>
       </c>
       <c r="F30" s="13" t="n">
-        <v>37341</v>
+        <v>38835</v>
       </c>
       <c r="G30" s="13" t="n">
-        <v>2855</v>
+        <v>2970</v>
       </c>
       <c r="H30" s="13" t="n">
-        <v>142771</v>
+        <v>148482</v>
       </c>
       <c r="I30" s="13" t="n">
         <v>20833</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>7.75</v>
+        <v>8.050000000000001</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B31" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C31" s="12" t="n">
         <v>100000</v>
@@ -10240,10 +10240,10 @@
     </row>
     <row r="32">
       <c r="A32" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B32" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C32" s="12" t="n">
         <v>100000</v>
@@ -10272,31 +10272,31 @@
     </row>
     <row r="33">
       <c r="A33" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B33" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C33" s="12" t="n">
-        <v>100000</v>
+        <v>110000</v>
       </c>
       <c r="D33" s="13" t="n">
-        <v>0.74</v>
+        <v>0.82</v>
       </c>
       <c r="E33" s="13" t="n">
-        <v>593928</v>
+        <v>653321</v>
       </c>
       <c r="F33" s="13" t="n">
-        <v>38835</v>
+        <v>42718</v>
       </c>
       <c r="G33" s="13" t="n">
-        <v>2970</v>
+        <v>3267</v>
       </c>
       <c r="H33" s="13" t="n">
-        <v>148482</v>
+        <v>163330</v>
       </c>
       <c r="I33" s="13" t="n">
-        <v>20833</v>
+        <v>22917</v>
       </c>
       <c r="J33" s="6" t="n">
         <v>8.050000000000001</v>
@@ -10304,31 +10304,31 @@
     </row>
     <row r="34">
       <c r="A34" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B34" s="12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C34" s="12" t="n">
-        <v>110000</v>
+        <v>100000</v>
       </c>
       <c r="D34" s="13" t="n">
-        <v>0.82</v>
+        <v>0.74</v>
       </c>
       <c r="E34" s="13" t="n">
-        <v>653321</v>
+        <v>593928</v>
       </c>
       <c r="F34" s="13" t="n">
-        <v>42718</v>
+        <v>38835</v>
       </c>
       <c r="G34" s="13" t="n">
-        <v>3267</v>
+        <v>2970</v>
       </c>
       <c r="H34" s="13" t="n">
-        <v>163330</v>
+        <v>148482</v>
       </c>
       <c r="I34" s="13" t="n">
-        <v>22917</v>
+        <v>20833</v>
       </c>
       <c r="J34" s="6" t="n">
         <v>8.050000000000001</v>
@@ -10336,31 +10336,31 @@
     </row>
     <row r="35">
       <c r="A35" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B35" s="12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C35" s="12" t="n">
-        <v>110000</v>
+        <v>150000</v>
       </c>
       <c r="D35" s="13" t="n">
-        <v>0.82</v>
+        <v>1.12</v>
       </c>
       <c r="E35" s="13" t="n">
-        <v>653321</v>
+        <v>890892</v>
       </c>
       <c r="F35" s="13" t="n">
-        <v>42718</v>
+        <v>58252</v>
       </c>
       <c r="G35" s="13" t="n">
-        <v>3267</v>
+        <v>4454</v>
       </c>
       <c r="H35" s="13" t="n">
-        <v>163330</v>
+        <v>222723</v>
       </c>
       <c r="I35" s="13" t="n">
-        <v>22917</v>
+        <v>31250</v>
       </c>
       <c r="J35" s="6" t="n">
         <v>8.050000000000001</v>
@@ -10368,10 +10368,10 @@
     </row>
     <row r="36">
       <c r="A36" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B36" s="12" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C36" s="12" t="n">
         <v>140000</v>
@@ -10400,31 +10400,31 @@
     </row>
     <row r="37">
       <c r="A37" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B37" s="12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C37" s="12" t="n">
-        <v>140000</v>
+        <v>150000</v>
       </c>
       <c r="D37" s="13" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="E37" s="13" t="n">
-        <v>831499</v>
+        <v>890892</v>
       </c>
       <c r="F37" s="13" t="n">
-        <v>54368</v>
+        <v>58252</v>
       </c>
       <c r="G37" s="13" t="n">
-        <v>4157</v>
+        <v>4454</v>
       </c>
       <c r="H37" s="13" t="n">
-        <v>207875</v>
+        <v>222723</v>
       </c>
       <c r="I37" s="13" t="n">
-        <v>29167</v>
+        <v>31250</v>
       </c>
       <c r="J37" s="6" t="n">
         <v>8.050000000000001</v>
@@ -10432,42 +10432,42 @@
     </row>
     <row r="38">
       <c r="A38" s="12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B38" s="12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C38" s="12" t="n">
-        <v>150000</v>
+        <v>140000</v>
       </c>
       <c r="D38" s="13" t="n">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="E38" s="13" t="n">
-        <v>890892</v>
+        <v>781106</v>
       </c>
       <c r="F38" s="13" t="n">
-        <v>58252</v>
+        <v>54368</v>
       </c>
       <c r="G38" s="13" t="n">
-        <v>4454</v>
+        <v>3906</v>
       </c>
       <c r="H38" s="13" t="n">
-        <v>222723</v>
+        <v>195276</v>
       </c>
       <c r="I38" s="13" t="n">
-        <v>31250</v>
+        <v>29167</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>8.050000000000001</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B39" s="12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C39" s="12" t="n">
         <v>150000</v>
@@ -10496,31 +10496,31 @@
     </row>
     <row r="40">
       <c r="A40" s="12" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B40" s="12" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C40" s="12" t="n">
-        <v>140000</v>
+        <v>160000</v>
       </c>
       <c r="D40" s="13" t="n">
-        <v>1.04</v>
+        <v>1.19</v>
       </c>
       <c r="E40" s="13" t="n">
-        <v>781106</v>
+        <v>892692</v>
       </c>
       <c r="F40" s="13" t="n">
-        <v>54368</v>
+        <v>62135</v>
       </c>
       <c r="G40" s="13" t="n">
-        <v>3906</v>
+        <v>4463</v>
       </c>
       <c r="H40" s="13" t="n">
-        <v>195276</v>
+        <v>223173</v>
       </c>
       <c r="I40" s="13" t="n">
-        <v>29167</v>
+        <v>33333</v>
       </c>
       <c r="J40" s="6" t="n">
         <v>7.6</v>
@@ -10528,31 +10528,31 @@
     </row>
     <row r="41">
       <c r="A41" s="12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B41" s="12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C41" s="12" t="n">
-        <v>160000</v>
+        <v>150000</v>
       </c>
       <c r="D41" s="13" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="E41" s="13" t="n">
-        <v>892692</v>
+        <v>836899</v>
       </c>
       <c r="F41" s="13" t="n">
-        <v>62135</v>
+        <v>58252</v>
       </c>
       <c r="G41" s="13" t="n">
-        <v>4463</v>
+        <v>4184</v>
       </c>
       <c r="H41" s="13" t="n">
-        <v>223173</v>
+        <v>209225</v>
       </c>
       <c r="I41" s="13" t="n">
-        <v>33333</v>
+        <v>31250</v>
       </c>
       <c r="J41" s="6" t="n">
         <v>7.6</v>
@@ -10560,10 +10560,10 @@
     </row>
     <row r="42">
       <c r="A42" s="12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B42" s="12" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C42" s="12" t="n">
         <v>150000</v>
@@ -10572,51 +10572,51 @@
         <v>1.12</v>
       </c>
       <c r="E42" s="13" t="n">
-        <v>836899</v>
+        <v>870375</v>
       </c>
       <c r="F42" s="13" t="n">
-        <v>58252</v>
+        <v>60582</v>
       </c>
       <c r="G42" s="13" t="n">
-        <v>4184</v>
+        <v>4352</v>
       </c>
       <c r="H42" s="13" t="n">
-        <v>209225</v>
+        <v>217594</v>
       </c>
       <c r="I42" s="13" t="n">
         <v>31250</v>
       </c>
       <c r="J42" s="6" t="n">
-        <v>7.6</v>
+        <v>7.89</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B43" s="12" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C43" s="12" t="n">
-        <v>150000</v>
+        <v>160000</v>
       </c>
       <c r="D43" s="13" t="n">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="E43" s="13" t="n">
-        <v>870375</v>
+        <v>928400</v>
       </c>
       <c r="F43" s="13" t="n">
-        <v>60582</v>
+        <v>64621</v>
       </c>
       <c r="G43" s="13" t="n">
-        <v>4352</v>
+        <v>4642</v>
       </c>
       <c r="H43" s="13" t="n">
-        <v>217594</v>
+        <v>232100</v>
       </c>
       <c r="I43" s="13" t="n">
-        <v>31250</v>
+        <v>33333</v>
       </c>
       <c r="J43" s="6" t="n">
         <v>7.89</v>
@@ -10624,10 +10624,10 @@
     </row>
     <row r="44">
       <c r="A44" s="12" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B44" s="12" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C44" s="12" t="n">
         <v>160000</v>
@@ -10656,10 +10656,10 @@
     </row>
     <row r="45">
       <c r="A45" s="12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B45" s="12" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C45" s="12" t="n">
         <v>160000</v>
@@ -10688,10 +10688,10 @@
     </row>
     <row r="46">
       <c r="A46" s="12" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B46" s="12" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C46" s="12" t="n">
         <v>160000</v>
@@ -10720,10 +10720,10 @@
     </row>
     <row r="47">
       <c r="A47" s="12" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B47" s="12" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C47" s="12" t="n">
         <v>160000</v>
@@ -10752,10 +10752,10 @@
     </row>
     <row r="48">
       <c r="A48" s="12" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B48" s="12" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C48" s="12" t="n">
         <v>160000</v>
@@ -10784,10 +10784,10 @@
     </row>
     <row r="49">
       <c r="A49" s="12" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B49" s="12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C49" s="12" t="n">
         <v>160000</v>
@@ -10816,10 +10816,10 @@
     </row>
     <row r="50">
       <c r="A50" s="12" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B50" s="12" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C50" s="12" t="n">
         <v>160000</v>
@@ -10848,10 +10848,10 @@
     </row>
     <row r="51">
       <c r="A51" s="12" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B51" s="12" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C51" s="12" t="n">
         <v>160000</v>
@@ -10880,10 +10880,10 @@
     </row>
     <row r="52">
       <c r="A52" s="12" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B52" s="12" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C52" s="12" t="n">
         <v>160000</v>
@@ -10912,10 +10912,10 @@
     </row>
     <row r="53">
       <c r="A53" s="12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B53" s="12" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C53" s="12" t="n">
         <v>160000</v>
@@ -10939,38 +10939,6 @@
         <v>33333</v>
       </c>
       <c r="J53" s="6" t="n">
-        <v>7.89</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="12" t="n">
-        <v>60</v>
-      </c>
-      <c r="B54" s="12" t="n">
-        <v>64</v>
-      </c>
-      <c r="C54" s="12" t="n">
-        <v>160000</v>
-      </c>
-      <c r="D54" s="13" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="E54" s="13" t="n">
-        <v>928400</v>
-      </c>
-      <c r="F54" s="13" t="n">
-        <v>64621</v>
-      </c>
-      <c r="G54" s="13" t="n">
-        <v>4642</v>
-      </c>
-      <c r="H54" s="13" t="n">
-        <v>232100</v>
-      </c>
-      <c r="I54" s="13" t="n">
-        <v>33333</v>
-      </c>
-      <c r="J54" s="6" t="n">
         <v>7.89</v>
       </c>
     </row>

--- a/finance/outputs/mulligan-mints-5yr-model.xlsx
+++ b/finance/outputs/mulligan-mints-5yr-model.xlsx
@@ -512,7 +512,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>0.44</v>
+        <v>0.465</v>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
         </is>
       </c>
       <c r="B14" s="8" t="n">
-        <v>0.31</v>
+        <v>0.328</v>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         </is>
       </c>
       <c r="B30" s="8" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.44</v>
+        <v>0.465</v>
       </c>
     </row>
     <row r="6">
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>7.04</v>
+        <v>7.44</v>
       </c>
     </row>
     <row r="7">
@@ -1109,7 +1109,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>0.0352</v>
+        <v>0.0372</v>
       </c>
     </row>
     <row r="9">
@@ -1119,7 +1119,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>1.76</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="10">
@@ -1139,7 +1139,7 @@
         </is>
       </c>
       <c r="B11" s="9" t="n">
-        <v>9.3888</v>
+        <v>9.8908</v>
       </c>
     </row>
     <row r="12">
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="B12" s="9" t="n">
-        <v>9.580399999999999</v>
+        <v>10.0926</v>
       </c>
     </row>
     <row r="14">
@@ -1209,13 +1209,13 @@
         <v>24.25</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>9.580399999999999</v>
+        <v>10.0926</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>14.6696</v>
+        <v>14.1574</v>
       </c>
       <c r="E15" s="8" t="n">
-        <v>0.6049</v>
+        <v>0.5838</v>
       </c>
       <c r="F15" s="6" t="n">
         <v>1.35</v>
@@ -1224,10 +1224,10 @@
         <v>0.7275</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>12.5921</v>
+        <v>12.0799</v>
       </c>
       <c r="I15" s="8" t="n">
-        <v>0.5193</v>
+        <v>0.4981</v>
       </c>
     </row>
     <row r="16">
@@ -1240,13 +1240,13 @@
         <v>24.25</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>9.580399999999999</v>
+        <v>10.0926</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>14.6696</v>
+        <v>14.1574</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>0.6049</v>
+        <v>0.5838</v>
       </c>
       <c r="F16" s="6" t="n">
         <v>1.35</v>
@@ -1255,10 +1255,10 @@
         <v>0.7275</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>12.5921</v>
+        <v>12.0799</v>
       </c>
       <c r="I16" s="8" t="n">
-        <v>0.5193</v>
+        <v>0.4981</v>
       </c>
     </row>
     <row r="17">
@@ -1271,13 +1271,13 @@
         <v>35</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>9.580399999999999</v>
+        <v>10.0926</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>25.4196</v>
+        <v>24.9074</v>
       </c>
       <c r="E17" s="8" t="n">
-        <v>0.7262999999999999</v>
+        <v>0.7116</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>1.35</v>
@@ -1286,10 +1286,10 @@
         <v>0</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>24.0696</v>
+        <v>23.5574</v>
       </c>
       <c r="I17" s="8" t="n">
-        <v>0.6877</v>
+        <v>0.6731</v>
       </c>
     </row>
     <row r="18">
@@ -1302,13 +1302,13 @@
         <v>21</v>
       </c>
       <c r="C18" s="6" t="n">
-        <v>9.580399999999999</v>
+        <v>10.0926</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>11.4196</v>
+        <v>10.9074</v>
       </c>
       <c r="E18" s="8" t="n">
-        <v>0.5438</v>
+        <v>0.5194</v>
       </c>
       <c r="F18" s="6" t="n">
         <v>1.35</v>
@@ -1317,10 +1317,10 @@
         <v>0</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>10.0696</v>
+        <v>9.557399999999999</v>
       </c>
       <c r="I18" s="8" t="n">
-        <v>0.4795</v>
+        <v>0.4551</v>
       </c>
     </row>
     <row r="19">
@@ -1333,13 +1333,13 @@
         <v>15.5</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>9.580399999999999</v>
+        <v>10.0926</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>5.9196</v>
+        <v>5.4074</v>
       </c>
       <c r="E19" s="8" t="n">
-        <v>0.3819</v>
+        <v>0.3489</v>
       </c>
       <c r="F19" s="6" t="n">
         <v>0.45</v>
@@ -1348,10 +1348,10 @@
         <v>0</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>5.4696</v>
+        <v>4.9574</v>
       </c>
       <c r="I19" s="8" t="n">
-        <v>0.3529</v>
+        <v>0.3198</v>
       </c>
     </row>
     <row r="22">
@@ -1371,21 +1371,21 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Contribution per direct tin: R12.59.</t>
+          <t>Contribution per direct tin: R12.08.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>At the month-12 cost base, break-even is 14,758 tins/month including marketing (9,728 excluding it).</t>
+          <t>At the month-12 cost base, break-even is 15,384 tins/month including marketing (10,141 excluding it).</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>At 38 tins per outlet per month that is ~388 active outlets. The year-1 plan exits with ~250. Break-even therefore lands early in year 2, not in year 1 —</t>
+          <t>At 38 tins per outlet per month that is ~405 active outlets. The year-1 plan exits with ~250. Break-even therefore lands early in year 2, not in year 1 —</t>
         </is>
       </c>
     </row>
@@ -1665,19 +1665,19 @@
         </is>
       </c>
       <c r="B14" s="13" t="n">
-        <v>239759</v>
+        <v>252319</v>
       </c>
       <c r="C14" s="13" t="n">
-        <v>1668464</v>
+        <v>1754714</v>
       </c>
       <c r="D14" s="13" t="n">
-        <v>4733781</v>
+        <v>4979515</v>
       </c>
       <c r="E14" s="13" t="n">
-        <v>9292997</v>
+        <v>9786134</v>
       </c>
       <c r="F14" s="13" t="n">
-        <v>14316698</v>
+        <v>15082333</v>
       </c>
     </row>
     <row r="15">
@@ -1687,19 +1687,19 @@
         </is>
       </c>
       <c r="B15" s="14" t="n">
-        <v>380651</v>
+        <v>368091</v>
       </c>
       <c r="C15" s="14" t="n">
-        <v>3041842</v>
+        <v>2955592</v>
       </c>
       <c r="D15" s="14" t="n">
-        <v>8547358</v>
+        <v>8301624</v>
       </c>
       <c r="E15" s="14" t="n">
-        <v>17487620</v>
+        <v>16994483</v>
       </c>
       <c r="F15" s="14" t="n">
-        <v>29316830</v>
+        <v>28551195</v>
       </c>
     </row>
     <row r="17">
@@ -1885,19 +1885,19 @@
         </is>
       </c>
       <c r="B26" s="14" t="n">
-        <v>-1469043</v>
+        <v>-1481603</v>
       </c>
       <c r="C26" s="14" t="n">
-        <v>-329370</v>
+        <v>-415620</v>
       </c>
       <c r="D26" s="14" t="n">
-        <v>785777</v>
+        <v>540043</v>
       </c>
       <c r="E26" s="14" t="n">
-        <v>5915955</v>
+        <v>5422818</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>13350995</v>
+        <v>12585360</v>
       </c>
     </row>
     <row r="27">
@@ -1910,16 +1910,16 @@
         <v>0</v>
       </c>
       <c r="C27" s="13" t="n">
-        <v>4474</v>
+        <v>2813</v>
       </c>
       <c r="D27" s="13" t="n">
-        <v>76824</v>
+        <v>65683</v>
       </c>
       <c r="E27" s="13" t="n">
-        <v>1242599</v>
+        <v>1029226</v>
       </c>
       <c r="F27" s="13" t="n">
-        <v>3604769</v>
+        <v>3398047</v>
       </c>
     </row>
     <row r="28">
@@ -1929,19 +1929,19 @@
         </is>
       </c>
       <c r="B28" s="14" t="n">
-        <v>-1469043</v>
+        <v>-1481603</v>
       </c>
       <c r="C28" s="14" t="n">
-        <v>-333843</v>
+        <v>-418433</v>
       </c>
       <c r="D28" s="14" t="n">
-        <v>708953</v>
+        <v>474360</v>
       </c>
       <c r="E28" s="14" t="n">
-        <v>4673356</v>
+        <v>4393592</v>
       </c>
       <c r="F28" s="14" t="n">
-        <v>9746227</v>
+        <v>9187313</v>
       </c>
     </row>
     <row r="29">
@@ -1951,19 +1951,19 @@
         </is>
       </c>
       <c r="B29" s="15" t="n">
-        <v>0.6135481417512721</v>
+        <v>0.5933030701083921</v>
       </c>
       <c r="C29" s="15" t="n">
-        <v>0.645784443789404</v>
+        <v>0.6274734175140196</v>
       </c>
       <c r="D29" s="15" t="n">
-        <v>0.6435711697296859</v>
+        <v>0.625068707708304</v>
       </c>
       <c r="E29" s="15" t="n">
-        <v>0.652995397221382</v>
+        <v>0.6345814642268531</v>
       </c>
       <c r="F29" s="15" t="n">
-        <v>0.6718876899395222</v>
+        <v>0.6543407335484146</v>
       </c>
     </row>
     <row r="30">
@@ -1973,19 +1973,19 @@
         </is>
       </c>
       <c r="B30" s="15" t="n">
-        <v>-2.367858186322099</v>
+        <v>-2.388103257964979</v>
       </c>
       <c r="C30" s="15" t="n">
-        <v>-0.06992532543544379</v>
+        <v>-0.08823635171082821</v>
       </c>
       <c r="D30" s="15" t="n">
-        <v>0.059164879782049</v>
+        <v>0.04066241776066723</v>
       </c>
       <c r="E30" s="15" t="n">
-        <v>0.2209043472902747</v>
+        <v>0.2024904142957458</v>
       </c>
       <c r="F30" s="15" t="n">
-        <v>0.3059801973479503</v>
+        <v>0.2884332409568427</v>
       </c>
     </row>
     <row r="33">
@@ -2211,19 +2211,19 @@
         </is>
       </c>
       <c r="B44" s="13" t="n">
-        <v>115850</v>
+        <v>121954</v>
       </c>
       <c r="C44" s="13" t="n">
-        <v>882160</v>
+        <v>928667</v>
       </c>
       <c r="D44" s="13" t="n">
-        <v>2535480</v>
+        <v>2667577</v>
       </c>
       <c r="E44" s="13" t="n">
-        <v>4922897</v>
+        <v>5177811</v>
       </c>
       <c r="F44" s="13" t="n">
-        <v>7365261</v>
+        <v>7757908</v>
       </c>
     </row>
     <row r="45">
@@ -2233,19 +2233,19 @@
         </is>
       </c>
       <c r="B45" s="14" t="n">
-        <v>146584</v>
+        <v>140480</v>
       </c>
       <c r="C45" s="14" t="n">
-        <v>1110300</v>
+        <v>1063792</v>
       </c>
       <c r="D45" s="14" t="n">
-        <v>3082442</v>
+        <v>2950345</v>
       </c>
       <c r="E45" s="14" t="n">
-        <v>6236104</v>
+        <v>5981190</v>
       </c>
       <c r="F45" s="14" t="n">
-        <v>10330321</v>
+        <v>9937674</v>
       </c>
     </row>
     <row r="47">
@@ -2431,19 +2431,19 @@
         </is>
       </c>
       <c r="B56" s="14" t="n">
-        <v>-998519</v>
+        <v>-1004623</v>
       </c>
       <c r="C56" s="14" t="n">
-        <v>-1143766</v>
+        <v>-1190274</v>
       </c>
       <c r="D56" s="14" t="n">
-        <v>-1894501</v>
+        <v>-2026599</v>
       </c>
       <c r="E56" s="14" t="n">
-        <v>-1284236</v>
+        <v>-1539150</v>
       </c>
       <c r="F56" s="14" t="n">
-        <v>204662</v>
+        <v>-187985</v>
       </c>
     </row>
     <row r="57">
@@ -2465,7 +2465,7 @@
         <v>0</v>
       </c>
       <c r="F57" s="13" t="n">
-        <v>16325</v>
+        <v>3784</v>
       </c>
     </row>
     <row r="58">
@@ -2475,19 +2475,19 @@
         </is>
       </c>
       <c r="B58" s="14" t="n">
-        <v>-998519</v>
+        <v>-1004623</v>
       </c>
       <c r="C58" s="14" t="n">
-        <v>-1143766</v>
+        <v>-1190274</v>
       </c>
       <c r="D58" s="14" t="n">
-        <v>-1894501</v>
+        <v>-2026599</v>
       </c>
       <c r="E58" s="14" t="n">
-        <v>-1284236</v>
+        <v>-1539150</v>
       </c>
       <c r="F58" s="14" t="n">
-        <v>188337</v>
+        <v>-191770</v>
       </c>
     </row>
     <row r="59">
@@ -2497,19 +2497,19 @@
         </is>
       </c>
       <c r="B59" s="15" t="n">
-        <v>0.558556469019252</v>
+        <v>0.5352961739401985</v>
       </c>
       <c r="C59" s="15" t="n">
-        <v>0.5572507935931791</v>
+        <v>0.533909016040454</v>
       </c>
       <c r="D59" s="15" t="n">
-        <v>0.5486801495635067</v>
+        <v>0.525166543485751</v>
       </c>
       <c r="E59" s="15" t="n">
-        <v>0.5588407144215103</v>
+        <v>0.5359969287707608</v>
       </c>
       <c r="F59" s="15" t="n">
-        <v>0.5837796536514781</v>
+        <v>0.5615906764315536</v>
       </c>
     </row>
     <row r="60">
@@ -2519,19 +2519,19 @@
         </is>
       </c>
       <c r="B60" s="15" t="n">
-        <v>-3.80484701543774</v>
+        <v>-3.828107310516793</v>
       </c>
       <c r="C60" s="15" t="n">
-        <v>-0.5740474665265493</v>
+        <v>-0.5973892440792741</v>
       </c>
       <c r="D60" s="15" t="n">
-        <v>-0.3372245210720815</v>
+        <v>-0.3607381271498373</v>
       </c>
       <c r="E60" s="15" t="n">
-        <v>-0.1150851883626193</v>
+        <v>-0.1379289740133689</v>
       </c>
       <c r="F60" s="15" t="n">
-        <v>0.01156570054106826</v>
+        <v>-0.01062327667885635</v>
       </c>
     </row>
     <row r="63">
@@ -2757,19 +2757,19 @@
         </is>
       </c>
       <c r="B74" s="13" t="n">
-        <v>354494</v>
+        <v>372989</v>
       </c>
       <c r="C74" s="13" t="n">
-        <v>2467118</v>
+        <v>2594076</v>
       </c>
       <c r="D74" s="13" t="n">
-        <v>6575706</v>
+        <v>6921975</v>
       </c>
       <c r="E74" s="13" t="n">
-        <v>12940289</v>
+        <v>13628737</v>
       </c>
       <c r="F74" s="13" t="n">
-        <v>20888303</v>
+        <v>22001865</v>
       </c>
     </row>
     <row r="75">
@@ -2779,19 +2779,19 @@
         </is>
       </c>
       <c r="B75" s="14" t="n">
-        <v>635991</v>
+        <v>617496</v>
       </c>
       <c r="C75" s="14" t="n">
-        <v>5052885</v>
+        <v>4925927</v>
       </c>
       <c r="D75" s="14" t="n">
-        <v>14627633</v>
+        <v>14281364</v>
       </c>
       <c r="E75" s="14" t="n">
-        <v>29576366</v>
+        <v>28887917</v>
       </c>
       <c r="F75" s="14" t="n">
-        <v>47698924</v>
+        <v>46585363</v>
       </c>
     </row>
     <row r="77">
@@ -2977,19 +2977,19 @@
         </is>
       </c>
       <c r="B86" s="14" t="n">
-        <v>-1404559</v>
+        <v>-1423054</v>
       </c>
       <c r="C86" s="14" t="n">
-        <v>973633</v>
+        <v>846675</v>
       </c>
       <c r="D86" s="14" t="n">
-        <v>5039724</v>
+        <v>4693455</v>
       </c>
       <c r="E86" s="14" t="n">
-        <v>14689083</v>
+        <v>14000634</v>
       </c>
       <c r="F86" s="14" t="n">
-        <v>26811461</v>
+        <v>25697899</v>
       </c>
     </row>
     <row r="87">
@@ -3002,16 +3002,16 @@
         <v>0</v>
       </c>
       <c r="C87" s="13" t="n">
-        <v>57684</v>
+        <v>51400</v>
       </c>
       <c r="D87" s="13" t="n">
-        <v>1186692</v>
+        <v>1060210</v>
       </c>
       <c r="E87" s="13" t="n">
-        <v>3966052</v>
+        <v>3780171</v>
       </c>
       <c r="F87" s="13" t="n">
-        <v>7239094</v>
+        <v>6938433</v>
       </c>
     </row>
     <row r="88">
@@ -3021,19 +3021,19 @@
         </is>
       </c>
       <c r="B88" s="14" t="n">
-        <v>-1404559</v>
+        <v>-1423054</v>
       </c>
       <c r="C88" s="14" t="n">
-        <v>915949</v>
+        <v>795275</v>
       </c>
       <c r="D88" s="14" t="n">
-        <v>3853032</v>
+        <v>3633244</v>
       </c>
       <c r="E88" s="14" t="n">
-        <v>10723031</v>
+        <v>10220463</v>
       </c>
       <c r="F88" s="14" t="n">
-        <v>19572366</v>
+        <v>18759466</v>
       </c>
     </row>
     <row r="89">
@@ -3043,19 +3043,19 @@
         </is>
       </c>
       <c r="B89" s="15" t="n">
-        <v>0.6421007813563169</v>
+        <v>0.6234281424623985</v>
       </c>
       <c r="C89" s="15" t="n">
-        <v>0.6719258876704935</v>
+        <v>0.6550432234115678</v>
       </c>
       <c r="D89" s="15" t="n">
-        <v>0.6898740512262032</v>
+        <v>0.6735431686603511</v>
       </c>
       <c r="E89" s="15" t="n">
-        <v>0.6956418890480596</v>
+        <v>0.6794494427463789</v>
       </c>
       <c r="F89" s="15" t="n">
-        <v>0.6954490796935608</v>
+        <v>0.6792133819191508</v>
       </c>
     </row>
     <row r="90">
@@ -3065,19 +3065,19 @@
         </is>
       </c>
       <c r="B90" s="15" t="n">
-        <v>-1.418051924758795</v>
+        <v>-1.436724563652714</v>
       </c>
       <c r="C90" s="15" t="n">
-        <v>0.1294723720768652</v>
+        <v>0.1125897078179395</v>
       </c>
       <c r="D90" s="15" t="n">
-        <v>0.2376853898255194</v>
+        <v>0.2213545072596676</v>
       </c>
       <c r="E90" s="15" t="n">
-        <v>0.3454900948687904</v>
+        <v>0.3292976485671098</v>
       </c>
       <c r="F90" s="15" t="n">
-        <v>0.3909104048173726</v>
+        <v>0.3746747070429626</v>
       </c>
     </row>
   </sheetData>
@@ -3873,166 +3873,166 @@
         <v>0</v>
       </c>
       <c r="H6" s="13" t="n">
-        <v>14211</v>
+        <v>14955</v>
       </c>
       <c r="I6" s="13" t="n">
-        <v>24510</v>
+        <v>25794</v>
       </c>
       <c r="J6" s="13" t="n">
-        <v>34810</v>
+        <v>36634</v>
       </c>
       <c r="K6" s="13" t="n">
-        <v>45110</v>
+        <v>47473</v>
       </c>
       <c r="L6" s="13" t="n">
-        <v>55409</v>
+        <v>58312</v>
       </c>
       <c r="M6" s="13" t="n">
-        <v>65709</v>
+        <v>69151</v>
       </c>
       <c r="N6" s="13" t="n">
-        <v>87251</v>
+        <v>91788</v>
       </c>
       <c r="O6" s="13" t="n">
-        <v>95780</v>
+        <v>100761</v>
       </c>
       <c r="P6" s="13" t="n">
-        <v>101834</v>
+        <v>107110</v>
       </c>
       <c r="Q6" s="13" t="n">
-        <v>110161</v>
+        <v>115868</v>
       </c>
       <c r="R6" s="13" t="n">
-        <v>118527</v>
+        <v>124657</v>
       </c>
       <c r="S6" s="13" t="n">
-        <v>126857</v>
+        <v>133418</v>
       </c>
       <c r="T6" s="13" t="n">
-        <v>139577</v>
+        <v>146787</v>
       </c>
       <c r="U6" s="13" t="n">
-        <v>152288</v>
+        <v>160150</v>
       </c>
       <c r="V6" s="13" t="n">
-        <v>164995</v>
+        <v>173510</v>
       </c>
       <c r="W6" s="13" t="n">
-        <v>177691</v>
+        <v>186862</v>
       </c>
       <c r="X6" s="13" t="n">
-        <v>190398</v>
+        <v>200222</v>
       </c>
       <c r="Y6" s="13" t="n">
-        <v>203104</v>
+        <v>213581</v>
       </c>
       <c r="Z6" s="13" t="n">
-        <v>252085</v>
+        <v>265060</v>
       </c>
       <c r="AA6" s="13" t="n">
-        <v>264084</v>
+        <v>277647</v>
       </c>
       <c r="AB6" s="13" t="n">
-        <v>277201</v>
+        <v>291417</v>
       </c>
       <c r="AC6" s="13" t="n">
-        <v>290579</v>
+        <v>305462</v>
       </c>
       <c r="AD6" s="13" t="n">
-        <v>305785</v>
+        <v>321558</v>
       </c>
       <c r="AE6" s="13" t="n">
-        <v>321309</v>
+        <v>337954</v>
       </c>
       <c r="AF6" s="13" t="n">
-        <v>464438</v>
+        <v>488566</v>
       </c>
       <c r="AG6" s="13" t="n">
-        <v>480095</v>
+        <v>505089</v>
       </c>
       <c r="AH6" s="13" t="n">
-        <v>495803</v>
+        <v>521659</v>
       </c>
       <c r="AI6" s="13" t="n">
-        <v>511586</v>
+        <v>538300</v>
       </c>
       <c r="AJ6" s="13" t="n">
-        <v>527442</v>
+        <v>555011</v>
       </c>
       <c r="AK6" s="13" t="n">
-        <v>543373</v>
+        <v>571792</v>
       </c>
       <c r="AL6" s="13" t="n">
-        <v>702894</v>
+        <v>739818</v>
       </c>
       <c r="AM6" s="13" t="n">
-        <v>708624</v>
+        <v>745984</v>
       </c>
       <c r="AN6" s="13" t="n">
-        <v>717441</v>
+        <v>755357</v>
       </c>
       <c r="AO6" s="13" t="n">
-        <v>727203</v>
+        <v>765710</v>
       </c>
       <c r="AP6" s="13" t="n">
-        <v>745625</v>
+        <v>785178</v>
       </c>
       <c r="AQ6" s="13" t="n">
-        <v>763268</v>
+        <v>803807</v>
       </c>
       <c r="AR6" s="13" t="n">
-        <v>780346</v>
+        <v>821832</v>
       </c>
       <c r="AS6" s="13" t="n">
-        <v>797115</v>
+        <v>839524</v>
       </c>
       <c r="AT6" s="13" t="n">
-        <v>813426</v>
+        <v>856723</v>
       </c>
       <c r="AU6" s="13" t="n">
-        <v>829788</v>
+        <v>873978</v>
       </c>
       <c r="AV6" s="13" t="n">
-        <v>845740</v>
+        <v>890793</v>
       </c>
       <c r="AW6" s="13" t="n">
-        <v>861527</v>
+        <v>907430</v>
       </c>
       <c r="AX6" s="13" t="n">
-        <v>1137681</v>
+        <v>1198357</v>
       </c>
       <c r="AY6" s="13" t="n">
-        <v>1137893</v>
+        <v>1198630</v>
       </c>
       <c r="AZ6" s="13" t="n">
-        <v>1140736</v>
+        <v>1201663</v>
       </c>
       <c r="BA6" s="13" t="n">
-        <v>1146509</v>
+        <v>1207771</v>
       </c>
       <c r="BB6" s="13" t="n">
-        <v>1164951</v>
+        <v>1227236</v>
       </c>
       <c r="BC6" s="13" t="n">
-        <v>1182219</v>
+        <v>1245458</v>
       </c>
       <c r="BD6" s="13" t="n">
-        <v>1198268</v>
+        <v>1262387</v>
       </c>
       <c r="BE6" s="13" t="n">
-        <v>1213439</v>
+        <v>1278386</v>
       </c>
       <c r="BF6" s="13" t="n">
-        <v>1227973</v>
+        <v>1293710</v>
       </c>
       <c r="BG6" s="13" t="n">
-        <v>1242040</v>
+        <v>1308539</v>
       </c>
       <c r="BH6" s="13" t="n">
-        <v>1255762</v>
+        <v>1323003</v>
       </c>
       <c r="BI6" s="13" t="n">
-        <v>1269227</v>
+        <v>1337193</v>
       </c>
     </row>
     <row r="7">
@@ -4060,166 +4060,166 @@
         <v>0</v>
       </c>
       <c r="H7" s="13" t="n">
-        <v>25333</v>
+        <v>24588</v>
       </c>
       <c r="I7" s="13" t="n">
-        <v>40576</v>
+        <v>39292</v>
       </c>
       <c r="J7" s="13" t="n">
-        <v>55820</v>
+        <v>53996</v>
       </c>
       <c r="K7" s="13" t="n">
-        <v>71064</v>
+        <v>68701</v>
       </c>
       <c r="L7" s="13" t="n">
-        <v>86308</v>
+        <v>83405</v>
       </c>
       <c r="M7" s="13" t="n">
-        <v>101551</v>
+        <v>98109</v>
       </c>
       <c r="N7" s="13" t="n">
-        <v>161456</v>
+        <v>156919</v>
       </c>
       <c r="O7" s="13" t="n">
-        <v>175708</v>
+        <v>170727</v>
       </c>
       <c r="P7" s="13" t="n">
-        <v>192435</v>
+        <v>187160</v>
       </c>
       <c r="Q7" s="13" t="n">
-        <v>206889</v>
+        <v>201182</v>
       </c>
       <c r="R7" s="13" t="n">
-        <v>221304</v>
+        <v>215175</v>
       </c>
       <c r="S7" s="13" t="n">
-        <v>235756</v>
+        <v>229195</v>
       </c>
       <c r="T7" s="13" t="n">
-        <v>256401</v>
+        <v>249191</v>
       </c>
       <c r="U7" s="13" t="n">
-        <v>277055</v>
+        <v>269193</v>
       </c>
       <c r="V7" s="13" t="n">
-        <v>297714</v>
+        <v>289198</v>
       </c>
       <c r="W7" s="13" t="n">
-        <v>318382</v>
+        <v>309212</v>
       </c>
       <c r="X7" s="13" t="n">
-        <v>339041</v>
+        <v>329217</v>
       </c>
       <c r="Y7" s="13" t="n">
-        <v>359700</v>
+        <v>349223</v>
       </c>
       <c r="Z7" s="13" t="n">
-        <v>477745</v>
+        <v>464770</v>
       </c>
       <c r="AA7" s="13" t="n">
-        <v>510976</v>
+        <v>497413</v>
       </c>
       <c r="AB7" s="13" t="n">
-        <v>543089</v>
+        <v>528873</v>
       </c>
       <c r="AC7" s="13" t="n">
-        <v>574941</v>
+        <v>560058</v>
       </c>
       <c r="AD7" s="13" t="n">
-        <v>604965</v>
+        <v>589193</v>
       </c>
       <c r="AE7" s="13" t="n">
-        <v>634672</v>
+        <v>618027</v>
       </c>
       <c r="AF7" s="13" t="n">
-        <v>793104</v>
+        <v>768976</v>
       </c>
       <c r="AG7" s="13" t="n">
-        <v>822678</v>
+        <v>797684</v>
       </c>
       <c r="AH7" s="13" t="n">
-        <v>852200</v>
+        <v>826344</v>
       </c>
       <c r="AI7" s="13" t="n">
-        <v>881647</v>
+        <v>854933</v>
       </c>
       <c r="AJ7" s="13" t="n">
-        <v>911021</v>
+        <v>883452</v>
       </c>
       <c r="AK7" s="13" t="n">
-        <v>940320</v>
+        <v>911901</v>
       </c>
       <c r="AL7" s="13" t="n">
-        <v>1284075</v>
+        <v>1247151</v>
       </c>
       <c r="AM7" s="13" t="n">
-        <v>1322844</v>
+        <v>1285485</v>
       </c>
       <c r="AN7" s="13" t="n">
-        <v>1358528</v>
+        <v>1320612</v>
       </c>
       <c r="AO7" s="13" t="n">
-        <v>1393266</v>
+        <v>1354758</v>
       </c>
       <c r="AP7" s="13" t="n">
-        <v>1419343</v>
+        <v>1379790</v>
       </c>
       <c r="AQ7" s="13" t="n">
-        <v>1446201</v>
+        <v>1405661</v>
       </c>
       <c r="AR7" s="13" t="n">
-        <v>1473622</v>
+        <v>1432136</v>
       </c>
       <c r="AS7" s="13" t="n">
-        <v>1501352</v>
+        <v>1458944</v>
       </c>
       <c r="AT7" s="13" t="n">
-        <v>1529542</v>
+        <v>1486245</v>
       </c>
       <c r="AU7" s="13" t="n">
-        <v>1557679</v>
+        <v>1513489</v>
       </c>
       <c r="AV7" s="13" t="n">
-        <v>1586227</v>
+        <v>1541175</v>
       </c>
       <c r="AW7" s="13" t="n">
-        <v>1614940</v>
+        <v>1569037</v>
       </c>
       <c r="AX7" s="13" t="n">
-        <v>2285900</v>
+        <v>2225224</v>
       </c>
       <c r="AY7" s="13" t="n">
-        <v>2324332</v>
+        <v>2263595</v>
       </c>
       <c r="AZ7" s="13" t="n">
-        <v>2360134</v>
+        <v>2299207</v>
       </c>
       <c r="BA7" s="13" t="n">
-        <v>2393006</v>
+        <v>2331744</v>
       </c>
       <c r="BB7" s="13" t="n">
-        <v>2413209</v>
+        <v>2350924</v>
       </c>
       <c r="BC7" s="13" t="n">
-        <v>2434586</v>
+        <v>2371347</v>
       </c>
       <c r="BD7" s="13" t="n">
-        <v>2457182</v>
+        <v>2393063</v>
       </c>
       <c r="BE7" s="13" t="n">
-        <v>2480656</v>
+        <v>2415709</v>
       </c>
       <c r="BF7" s="13" t="n">
-        <v>2504766</v>
+        <v>2439029</v>
       </c>
       <c r="BG7" s="13" t="n">
-        <v>2529344</v>
+        <v>2462845</v>
       </c>
       <c r="BH7" s="13" t="n">
-        <v>2554267</v>
+        <v>2487027</v>
       </c>
       <c r="BI7" s="13" t="n">
-        <v>2579447</v>
+        <v>2511481</v>
       </c>
     </row>
     <row r="8">
@@ -5743,166 +5743,166 @@
         <v>-157500</v>
       </c>
       <c r="H16" s="14" t="n">
-        <v>-223229</v>
+        <v>-223974</v>
       </c>
       <c r="I16" s="14" t="n">
-        <v>-150174</v>
+        <v>-151458</v>
       </c>
       <c r="J16" s="14" t="n">
-        <v>-137118</v>
+        <v>-138942</v>
       </c>
       <c r="K16" s="14" t="n">
-        <v>-124063</v>
+        <v>-126426</v>
       </c>
       <c r="L16" s="14" t="n">
-        <v>-111007</v>
+        <v>-113910</v>
       </c>
       <c r="M16" s="14" t="n">
-        <v>-97952</v>
+        <v>-101394</v>
       </c>
       <c r="N16" s="14" t="n">
-        <v>-25576</v>
+        <v>-30113</v>
       </c>
       <c r="O16" s="14" t="n">
-        <v>-48506</v>
+        <v>-53487</v>
       </c>
       <c r="P16" s="14" t="n">
-        <v>-37161</v>
+        <v>-42437</v>
       </c>
       <c r="Q16" s="14" t="n">
-        <v>-28090</v>
+        <v>-33797</v>
       </c>
       <c r="R16" s="14" t="n">
-        <v>-19057</v>
+        <v>-25186</v>
       </c>
       <c r="S16" s="14" t="n">
-        <v>-37548</v>
+        <v>-44108</v>
       </c>
       <c r="T16" s="14" t="n">
-        <v>-204612</v>
+        <v>-211823</v>
       </c>
       <c r="U16" s="14" t="n">
-        <v>-11668</v>
+        <v>-19530</v>
       </c>
       <c r="V16" s="14" t="n">
-        <v>1281</v>
+        <v>-7235</v>
       </c>
       <c r="W16" s="14" t="n">
-        <v>14240</v>
+        <v>5069</v>
       </c>
       <c r="X16" s="14" t="n">
-        <v>27189</v>
+        <v>17365</v>
       </c>
       <c r="Y16" s="14" t="n">
-        <v>40138</v>
+        <v>29661</v>
       </c>
       <c r="Z16" s="14" t="n">
-        <v>52510</v>
+        <v>39535</v>
       </c>
       <c r="AA16" s="14" t="n">
-        <v>-374041</v>
+        <v>-387604</v>
       </c>
       <c r="AB16" s="14" t="n">
-        <v>62335</v>
+        <v>48119</v>
       </c>
       <c r="AC16" s="14" t="n">
-        <v>84405</v>
+        <v>69522</v>
       </c>
       <c r="AD16" s="14" t="n">
-        <v>104647</v>
+        <v>88875</v>
       </c>
       <c r="AE16" s="14" t="n">
-        <v>124572</v>
+        <v>107927</v>
       </c>
       <c r="AF16" s="14" t="n">
-        <v>147622</v>
+        <v>123494</v>
       </c>
       <c r="AG16" s="14" t="n">
-        <v>167414</v>
+        <v>142420</v>
       </c>
       <c r="AH16" s="14" t="n">
-        <v>-262846</v>
+        <v>-288702</v>
       </c>
       <c r="AI16" s="14" t="n">
-        <v>206820</v>
+        <v>180105</v>
       </c>
       <c r="AJ16" s="14" t="n">
-        <v>226411</v>
+        <v>198842</v>
       </c>
       <c r="AK16" s="14" t="n">
-        <v>245928</v>
+        <v>217509</v>
       </c>
       <c r="AL16" s="14" t="n">
-        <v>450129</v>
+        <v>413204</v>
       </c>
       <c r="AM16" s="14" t="n">
-        <v>160114</v>
+        <v>122754</v>
       </c>
       <c r="AN16" s="14" t="n">
-        <v>507014</v>
+        <v>469098</v>
       </c>
       <c r="AO16" s="14" t="n">
-        <v>459126</v>
+        <v>420618</v>
       </c>
       <c r="AP16" s="14" t="n">
-        <v>476419</v>
+        <v>436866</v>
       </c>
       <c r="AQ16" s="14" t="n">
-        <v>494493</v>
+        <v>453953</v>
       </c>
       <c r="AR16" s="14" t="n">
-        <v>513130</v>
+        <v>471645</v>
       </c>
       <c r="AS16" s="14" t="n">
-        <v>532077</v>
+        <v>489669</v>
       </c>
       <c r="AT16" s="14" t="n">
-        <v>551484</v>
+        <v>508186</v>
       </c>
       <c r="AU16" s="14" t="n">
-        <v>570837</v>
+        <v>526647</v>
       </c>
       <c r="AV16" s="14" t="n">
-        <v>590601</v>
+        <v>545549</v>
       </c>
       <c r="AW16" s="14" t="n">
-        <v>610531</v>
+        <v>564628</v>
       </c>
       <c r="AX16" s="14" t="n">
-        <v>1051542</v>
+        <v>990865</v>
       </c>
       <c r="AY16" s="14" t="n">
-        <v>1082825</v>
+        <v>1022089</v>
       </c>
       <c r="AZ16" s="14" t="n">
-        <v>1111479</v>
+        <v>1050552</v>
       </c>
       <c r="BA16" s="14" t="n">
-        <v>1061454</v>
+        <v>1000192</v>
       </c>
       <c r="BB16" s="14" t="n">
-        <v>1074508</v>
+        <v>1012223</v>
       </c>
       <c r="BC16" s="14" t="n">
-        <v>1088737</v>
+        <v>1025498</v>
       </c>
       <c r="BD16" s="14" t="n">
-        <v>1104185</v>
+        <v>1040066</v>
       </c>
       <c r="BE16" s="14" t="n">
-        <v>1120510</v>
+        <v>1055563</v>
       </c>
       <c r="BF16" s="14" t="n">
-        <v>1137472</v>
+        <v>1071735</v>
       </c>
       <c r="BG16" s="14" t="n">
-        <v>1154901</v>
+        <v>1088402</v>
       </c>
       <c r="BH16" s="14" t="n">
-        <v>1172676</v>
+        <v>1105435</v>
       </c>
       <c r="BI16" s="14" t="n">
-        <v>1190707</v>
+        <v>1122741</v>
       </c>
     </row>
     <row r="17">
@@ -6686,178 +6686,178 @@
         <v>0</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>63360</v>
+        <v>111600</v>
       </c>
       <c r="E5" s="13" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>162878</v>
+        <v>126698</v>
       </c>
       <c r="G5" s="13" t="n">
-        <v>63360</v>
+        <v>111600</v>
       </c>
       <c r="H5" s="13" t="n">
         <v>0</v>
       </c>
       <c r="I5" s="13" t="n">
-        <v>162878</v>
+        <v>126698</v>
       </c>
       <c r="J5" s="13" t="n">
-        <v>56160</v>
+        <v>98880</v>
       </c>
       <c r="K5" s="13" t="n">
         <v>0</v>
       </c>
       <c r="L5" s="13" t="n">
-        <v>202118</v>
+        <v>212731</v>
       </c>
       <c r="M5" s="13" t="n">
         <v>0</v>
       </c>
       <c r="N5" s="13" t="n">
-        <v>204365</v>
+        <v>216686</v>
       </c>
       <c r="O5" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P5" s="13" t="n">
-        <v>210203</v>
+        <v>221240</v>
       </c>
       <c r="Q5" s="13" t="n">
-        <v>58406</v>
+        <v>102835</v>
       </c>
       <c r="R5" s="13" t="n">
-        <v>210203</v>
+        <v>221240</v>
       </c>
       <c r="S5" s="13" t="n">
-        <v>151796</v>
+        <v>118405</v>
       </c>
       <c r="T5" s="13" t="n">
-        <v>210203</v>
+        <v>221240</v>
       </c>
       <c r="U5" s="13" t="n">
-        <v>77875</v>
+        <v>137114</v>
       </c>
       <c r="V5" s="13" t="n">
-        <v>204961</v>
+        <v>212005</v>
       </c>
       <c r="W5" s="13" t="n">
-        <v>273282</v>
+        <v>282673</v>
       </c>
       <c r="X5" s="13" t="n">
-        <v>210365</v>
+        <v>233877</v>
       </c>
       <c r="Y5" s="13" t="n">
-        <v>274580</v>
+        <v>301437</v>
       </c>
       <c r="Z5" s="13" t="n">
-        <v>296554</v>
+        <v>340125</v>
       </c>
       <c r="AA5" s="13" t="n">
-        <v>343047</v>
+        <v>376484</v>
       </c>
       <c r="AB5" s="13" t="n">
-        <v>392857</v>
+        <v>413727</v>
       </c>
       <c r="AC5" s="13" t="n">
-        <v>392857</v>
+        <v>413727</v>
       </c>
       <c r="AD5" s="13" t="n">
-        <v>411287</v>
+        <v>446175</v>
       </c>
       <c r="AE5" s="13" t="n">
-        <v>429718</v>
+        <v>478623</v>
       </c>
       <c r="AF5" s="13" t="n">
-        <v>495194</v>
+        <v>547578</v>
       </c>
       <c r="AG5" s="13" t="n">
-        <v>542240</v>
+        <v>584085</v>
       </c>
       <c r="AH5" s="13" t="n">
-        <v>577604</v>
+        <v>600344</v>
       </c>
       <c r="AI5" s="13" t="n">
-        <v>594737</v>
+        <v>630542</v>
       </c>
       <c r="AJ5" s="13" t="n">
-        <v>550153</v>
+        <v>579894</v>
       </c>
       <c r="AK5" s="13" t="n">
-        <v>611281</v>
+        <v>644326</v>
       </c>
       <c r="AL5" s="13" t="n">
-        <v>574139</v>
+        <v>622171</v>
       </c>
       <c r="AM5" s="13" t="n">
-        <v>618134</v>
+        <v>656406</v>
       </c>
       <c r="AN5" s="13" t="n">
-        <v>635732</v>
+        <v>670099</v>
       </c>
       <c r="AO5" s="13" t="n">
-        <v>653550</v>
+        <v>701505</v>
       </c>
       <c r="AP5" s="13" t="n">
-        <v>635732</v>
+        <v>670099</v>
       </c>
       <c r="AQ5" s="13" t="n">
-        <v>770577</v>
+        <v>862734</v>
       </c>
       <c r="AR5" s="13" t="n">
-        <v>707004</v>
+        <v>795724</v>
       </c>
       <c r="AS5" s="13" t="n">
-        <v>953599</v>
+        <v>1005149</v>
       </c>
       <c r="AT5" s="13" t="n">
-        <v>874907</v>
+        <v>911682</v>
       </c>
       <c r="AU5" s="13" t="n">
-        <v>937401</v>
+        <v>976802</v>
       </c>
       <c r="AV5" s="13" t="n">
-        <v>872855</v>
+        <v>943994</v>
       </c>
       <c r="AW5" s="13" t="n">
-        <v>899335</v>
+        <v>948172</v>
       </c>
       <c r="AX5" s="13" t="n">
-        <v>952596</v>
+        <v>999577</v>
       </c>
       <c r="AY5" s="13" t="n">
-        <v>926785</v>
+        <v>996579</v>
       </c>
       <c r="AZ5" s="13" t="n">
-        <v>952716</v>
+        <v>1016796</v>
       </c>
       <c r="BA5" s="13" t="n">
-        <v>997663</v>
+        <v>1051839</v>
       </c>
       <c r="BB5" s="13" t="n">
-        <v>997663</v>
+        <v>1051839</v>
       </c>
       <c r="BC5" s="13" t="n">
-        <v>997663</v>
+        <v>1051839</v>
       </c>
       <c r="BD5" s="13" t="n">
-        <v>997663</v>
+        <v>1051839</v>
       </c>
       <c r="BE5" s="13" t="n">
-        <v>997663</v>
+        <v>1051839</v>
       </c>
       <c r="BF5" s="13" t="n">
-        <v>997663</v>
+        <v>1051839</v>
       </c>
       <c r="BG5" s="13" t="n">
-        <v>997663</v>
+        <v>1051839</v>
       </c>
       <c r="BH5" s="13" t="n">
-        <v>997663</v>
+        <v>1051839</v>
       </c>
       <c r="BI5" s="13" t="n">
-        <v>997663</v>
+        <v>1051839</v>
       </c>
     </row>
     <row r="6">
@@ -6885,7 +6885,7 @@
         <v>0</v>
       </c>
       <c r="H6" s="13" t="n">
-        <v>61238</v>
+        <v>64238</v>
       </c>
       <c r="I6" s="13" t="n">
         <v>0</v>
@@ -6894,7 +6894,7 @@
         <v>0</v>
       </c>
       <c r="K6" s="13" t="n">
-        <v>61238</v>
+        <v>64238</v>
       </c>
       <c r="L6" s="13" t="n">
         <v>0</v>
@@ -6903,148 +6903,148 @@
         <v>0</v>
       </c>
       <c r="N6" s="13" t="n">
+        <v>57878</v>
+      </c>
+      <c r="O6" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="13" t="n">
+        <v>57878</v>
+      </c>
+      <c r="Q6" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="13" t="n">
+        <v>59855</v>
+      </c>
+      <c r="S6" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" s="13" t="n">
+        <v>59855</v>
+      </c>
+      <c r="U6" s="13" t="n">
+        <v>59855</v>
+      </c>
+      <c r="V6" s="13" t="n">
+        <v>59855</v>
+      </c>
+      <c r="W6" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="13" t="n">
+        <v>59855</v>
+      </c>
+      <c r="Y6" s="13" t="n">
+        <v>79807</v>
+      </c>
+      <c r="Z6" s="13" t="n">
         <v>55238</v>
       </c>
-      <c r="O6" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="13" t="n">
-        <v>55238</v>
-      </c>
-      <c r="Q6" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" s="13" t="n">
-        <v>57110</v>
-      </c>
-      <c r="S6" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" s="13" t="n">
-        <v>57110</v>
-      </c>
-      <c r="U6" s="13" t="n">
-        <v>57110</v>
-      </c>
-      <c r="V6" s="13" t="n">
-        <v>57110</v>
-      </c>
-      <c r="W6" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" s="13" t="n">
-        <v>57110</v>
-      </c>
-      <c r="Y6" s="13" t="n">
-        <v>76146</v>
-      </c>
-      <c r="Z6" s="13" t="n">
-        <v>52742</v>
-      </c>
       <c r="AA6" s="13" t="n">
-        <v>70322</v>
+        <v>73650</v>
       </c>
       <c r="AB6" s="13" t="n">
-        <v>70322</v>
+        <v>73650</v>
       </c>
       <c r="AC6" s="13" t="n">
-        <v>87902</v>
+        <v>92062</v>
       </c>
       <c r="AD6" s="13" t="n">
-        <v>104652</v>
+        <v>109844</v>
       </c>
       <c r="AE6" s="13" t="n">
-        <v>104652</v>
+        <v>109844</v>
       </c>
       <c r="AF6" s="13" t="n">
-        <v>104652</v>
+        <v>109844</v>
       </c>
       <c r="AG6" s="13" t="n">
-        <v>104652</v>
+        <v>109844</v>
       </c>
       <c r="AH6" s="13" t="n">
-        <v>122094</v>
+        <v>128151</v>
       </c>
       <c r="AI6" s="13" t="n">
-        <v>139536</v>
+        <v>146459</v>
       </c>
       <c r="AJ6" s="13" t="n">
-        <v>156978</v>
+        <v>164766</v>
       </c>
       <c r="AK6" s="13" t="n">
-        <v>156978</v>
+        <v>164766</v>
       </c>
       <c r="AL6" s="13" t="n">
-        <v>147244</v>
+        <v>154642</v>
       </c>
       <c r="AM6" s="13" t="n">
-        <v>163605</v>
+        <v>171825</v>
       </c>
       <c r="AN6" s="13" t="n">
-        <v>147244</v>
+        <v>154642</v>
       </c>
       <c r="AO6" s="13" t="n">
-        <v>163605</v>
+        <v>171825</v>
       </c>
       <c r="AP6" s="13" t="n">
-        <v>169315</v>
+        <v>177864</v>
       </c>
       <c r="AQ6" s="13" t="n">
-        <v>169315</v>
+        <v>177864</v>
       </c>
       <c r="AR6" s="13" t="n">
-        <v>169315</v>
+        <v>177864</v>
       </c>
       <c r="AS6" s="13" t="n">
-        <v>186247</v>
+        <v>195651</v>
       </c>
       <c r="AT6" s="13" t="n">
-        <v>169315</v>
+        <v>177864</v>
       </c>
       <c r="AU6" s="13" t="n">
-        <v>253973</v>
+        <v>266797</v>
       </c>
       <c r="AV6" s="13" t="n">
-        <v>237042</v>
+        <v>249010</v>
       </c>
       <c r="AW6" s="13" t="n">
-        <v>253973</v>
+        <v>266797</v>
       </c>
       <c r="AX6" s="13" t="n">
-        <v>224443</v>
+        <v>235782</v>
       </c>
       <c r="AY6" s="13" t="n">
-        <v>240475</v>
+        <v>252623</v>
       </c>
       <c r="AZ6" s="13" t="n">
-        <v>256506</v>
+        <v>269465</v>
       </c>
       <c r="BA6" s="13" t="n">
-        <v>240475</v>
+        <v>252623</v>
       </c>
       <c r="BB6" s="13" t="n">
-        <v>248844</v>
+        <v>261478</v>
       </c>
       <c r="BC6" s="13" t="n">
-        <v>265433</v>
+        <v>278910</v>
       </c>
       <c r="BD6" s="13" t="n">
-        <v>265433</v>
+        <v>278910</v>
       </c>
       <c r="BE6" s="13" t="n">
-        <v>265433</v>
+        <v>278910</v>
       </c>
       <c r="BF6" s="13" t="n">
-        <v>265433</v>
+        <v>278910</v>
       </c>
       <c r="BG6" s="13" t="n">
-        <v>265433</v>
+        <v>278910</v>
       </c>
       <c r="BH6" s="13" t="n">
-        <v>265433</v>
+        <v>278910</v>
       </c>
       <c r="BI6" s="13" t="n">
-        <v>265433</v>
+        <v>278910</v>
       </c>
     </row>
     <row r="7">
@@ -7262,13 +7262,13 @@
         <v>0</v>
       </c>
       <c r="I8" s="13" t="n">
-        <v>67710</v>
+        <v>70140</v>
       </c>
       <c r="J8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="K8" s="13" t="n">
-        <v>45052</v>
+        <v>47482</v>
       </c>
       <c r="L8" s="13" t="n">
         <v>0</v>
@@ -7280,145 +7280,145 @@
         <v>0</v>
       </c>
       <c r="O8" s="13" t="n">
-        <v>-11044</v>
+        <v>-8905</v>
       </c>
       <c r="P8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="Q8" s="13" t="n">
-        <v>-22326</v>
+        <v>-20187</v>
       </c>
       <c r="R8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="S8" s="13" t="n">
-        <v>-32091</v>
+        <v>-29867</v>
       </c>
       <c r="T8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="U8" s="13" t="n">
-        <v>16466</v>
+        <v>20914</v>
       </c>
       <c r="V8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="W8" s="13" t="n">
-        <v>-63719</v>
+        <v>-61495</v>
       </c>
       <c r="X8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="Y8" s="13" t="n">
-        <v>-27615</v>
+        <v>-22426</v>
       </c>
       <c r="Z8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="AA8" s="13" t="n">
-        <v>-27892</v>
+        <v>-23175</v>
       </c>
       <c r="AB8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="AC8" s="13" t="n">
-        <v>-87355</v>
+        <v>-81290</v>
       </c>
       <c r="AD8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="AE8" s="13" t="n">
-        <v>-68364</v>
+        <v>-59954</v>
       </c>
       <c r="AF8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="AG8" s="13" t="n">
-        <v>-79956</v>
+        <v>-71546</v>
       </c>
       <c r="AH8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="AI8" s="13" t="n">
-        <v>-4522</v>
+        <v>5992</v>
       </c>
       <c r="AJ8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="AK8" s="13" t="n">
-        <v>-50587</v>
+        <v>-37971</v>
       </c>
       <c r="AL8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="AM8" s="13" t="n">
-        <v>-79715</v>
+        <v>-67064</v>
       </c>
       <c r="AN8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="AO8" s="13" t="n">
-        <v>-145485</v>
+        <v>-132834</v>
       </c>
       <c r="AP8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="AQ8" s="13" t="n">
-        <v>-147239</v>
+        <v>-133390</v>
       </c>
       <c r="AR8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="AS8" s="13" t="n">
-        <v>-157782</v>
+        <v>-143240</v>
       </c>
       <c r="AT8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="AU8" s="13" t="n">
-        <v>-132244</v>
+        <v>-114933</v>
       </c>
       <c r="AV8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="AW8" s="13" t="n">
-        <v>-106706</v>
+        <v>-86625</v>
       </c>
       <c r="AX8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="AY8" s="13" t="n">
-        <v>-194657</v>
+        <v>-175632</v>
       </c>
       <c r="AZ8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="BA8" s="13" t="n">
-        <v>-191873</v>
+        <v>-171536</v>
       </c>
       <c r="BB8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="BC8" s="13" t="n">
-        <v>-197675</v>
+        <v>-176525</v>
       </c>
       <c r="BD8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="BE8" s="13" t="n">
-        <v>-205737</v>
+        <v>-183904</v>
       </c>
       <c r="BF8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="BG8" s="13" t="n">
-        <v>-225549</v>
+        <v>-203716</v>
       </c>
       <c r="BH8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="BI8" s="13" t="n">
-        <v>-245361</v>
+        <v>-223528</v>
       </c>
     </row>
     <row r="9">
@@ -7497,7 +7497,7 @@
         <v>0</v>
       </c>
       <c r="Y9" s="13" t="n">
-        <v>-4474</v>
+        <v>-2813</v>
       </c>
       <c r="Z9" s="13" t="n">
         <v>0</v>
@@ -7515,7 +7515,7 @@
         <v>0</v>
       </c>
       <c r="AE9" s="13" t="n">
-        <v>-23137</v>
+        <v>-19115</v>
       </c>
       <c r="AF9" s="13" t="n">
         <v>0</v>
@@ -7533,7 +7533,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="13" t="n">
-        <v>-53687</v>
+        <v>-46568</v>
       </c>
       <c r="AL9" s="13" t="n">
         <v>0</v>
@@ -7551,7 +7551,7 @@
         <v>0</v>
       </c>
       <c r="AQ9" s="13" t="n">
-        <v>-333060</v>
+        <v>-190519</v>
       </c>
       <c r="AR9" s="13" t="n">
         <v>0</v>
@@ -7569,7 +7569,7 @@
         <v>0</v>
       </c>
       <c r="AW9" s="13" t="n">
-        <v>-909538</v>
+        <v>-838707</v>
       </c>
       <c r="AX9" s="13" t="n">
         <v>0</v>
@@ -7587,7 +7587,7 @@
         <v>0</v>
       </c>
       <c r="BC9" s="13" t="n">
-        <v>-1747047</v>
+        <v>-1647383</v>
       </c>
       <c r="BD9" s="13" t="n">
         <v>0</v>
@@ -7605,7 +7605,7 @@
         <v>0</v>
       </c>
       <c r="BI9" s="13" t="n">
-        <v>-1857722</v>
+        <v>-1750664</v>
       </c>
     </row>
     <row r="10">
@@ -7808,178 +7808,178 @@
         <v>-65020</v>
       </c>
       <c r="D11" s="14" t="n">
-        <v>-95360</v>
+        <v>-143600</v>
       </c>
       <c r="E11" s="14" t="n">
         <v>-169918</v>
       </c>
       <c r="F11" s="14" t="n">
-        <v>-255378</v>
+        <v>-219198</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-197370</v>
+        <v>-245610</v>
       </c>
       <c r="H11" s="14" t="n">
-        <v>-293699</v>
+        <v>-296699</v>
       </c>
       <c r="I11" s="14" t="n">
-        <v>-240443</v>
+        <v>-201833</v>
       </c>
       <c r="J11" s="14" t="n">
-        <v>-174249</v>
+        <v>-216969</v>
       </c>
       <c r="K11" s="14" t="n">
-        <v>-107087</v>
+        <v>-107657</v>
       </c>
       <c r="L11" s="14" t="n">
-        <v>-265834</v>
+        <v>-276446</v>
       </c>
       <c r="M11" s="14" t="n">
         <v>-48803</v>
       </c>
       <c r="N11" s="14" t="n">
-        <v>-219670</v>
+        <v>-234632</v>
       </c>
       <c r="O11" s="14" t="n">
-        <v>50755</v>
+        <v>52894</v>
       </c>
       <c r="P11" s="14" t="n">
-        <v>-182825</v>
+        <v>-196503</v>
       </c>
       <c r="Q11" s="14" t="n">
-        <v>22699</v>
+        <v>-19592</v>
       </c>
       <c r="R11" s="14" t="n">
-        <v>-143065</v>
+        <v>-156848</v>
       </c>
       <c r="S11" s="14" t="n">
-        <v>-66385</v>
+        <v>-30770</v>
       </c>
       <c r="T11" s="14" t="n">
-        <v>-311321</v>
+        <v>-325104</v>
       </c>
       <c r="U11" s="14" t="n">
-        <v>12035962</v>
+        <v>11978426</v>
       </c>
       <c r="V11" s="14" t="n">
-        <v>-76930</v>
+        <v>-86720</v>
       </c>
       <c r="W11" s="14" t="n">
-        <v>-121200</v>
+        <v>-128368</v>
       </c>
       <c r="X11" s="14" t="n">
-        <v>-21014</v>
+        <v>-47272</v>
       </c>
       <c r="Y11" s="14" t="n">
-        <v>-105693</v>
+        <v>-129361</v>
       </c>
       <c r="Z11" s="14" t="n">
-        <v>-92566</v>
+        <v>-138633</v>
       </c>
       <c r="AA11" s="14" t="n">
-        <v>-519980</v>
+        <v>-552027</v>
       </c>
       <c r="AB11" s="14" t="n">
-        <v>-72383</v>
+        <v>-96582</v>
       </c>
       <c r="AC11" s="14" t="n">
-        <v>-135086</v>
+        <v>-154051</v>
       </c>
       <c r="AD11" s="14" t="n">
-        <v>-40679</v>
+        <v>-80758</v>
       </c>
       <c r="AE11" s="14" t="n">
-        <v>-108378</v>
+        <v>-150042</v>
       </c>
       <c r="AF11" s="14" t="n">
-        <v>-165720</v>
+        <v>-223295</v>
       </c>
       <c r="AG11" s="14" t="n">
-        <v>-250489</v>
+        <v>-289115</v>
       </c>
       <c r="AH11" s="14" t="n">
-        <v>-374775</v>
+        <v>-403571</v>
       </c>
       <c r="AI11" s="14" t="n">
-        <v>78362</v>
+        <v>46147</v>
       </c>
       <c r="AJ11" s="14" t="n">
-        <v>152257</v>
+        <v>114729</v>
       </c>
       <c r="AK11" s="14" t="n">
-        <v>29089</v>
+        <v>7990</v>
       </c>
       <c r="AL11" s="14" t="n">
-        <v>144175</v>
+        <v>88744</v>
       </c>
       <c r="AM11" s="14" t="n">
-        <v>-149808</v>
+        <v>-183649</v>
       </c>
       <c r="AN11" s="14" t="n">
-        <v>600464</v>
+        <v>558699</v>
       </c>
       <c r="AO11" s="14" t="n">
-        <v>389349</v>
+        <v>345824</v>
       </c>
       <c r="AP11" s="14" t="n">
-        <v>589332</v>
+        <v>546416</v>
       </c>
       <c r="AQ11" s="14" t="n">
-        <v>16579</v>
+        <v>72264</v>
       </c>
       <c r="AR11" s="14" t="n">
-        <v>602843</v>
+        <v>505574</v>
       </c>
       <c r="AS11" s="14" t="n">
-        <v>223926</v>
+        <v>177513</v>
       </c>
       <c r="AT11" s="14" t="n">
-        <v>519722</v>
+        <v>474398</v>
       </c>
       <c r="AU11" s="14" t="n">
-        <v>282718</v>
+        <v>247804</v>
       </c>
       <c r="AV11" s="14" t="n">
-        <v>538830</v>
+        <v>455723</v>
       </c>
       <c r="AW11" s="14" t="n">
-        <v>-478435</v>
+        <v>-449183</v>
       </c>
       <c r="AX11" s="14" t="n">
-        <v>381900</v>
+        <v>323580</v>
       </c>
       <c r="AY11" s="14" t="n">
-        <v>395417</v>
+        <v>332499</v>
       </c>
       <c r="AZ11" s="14" t="n">
-        <v>1324620</v>
+        <v>1247582</v>
       </c>
       <c r="BA11" s="14" t="n">
-        <v>1065377</v>
+        <v>1019389</v>
       </c>
       <c r="BB11" s="14" t="n">
-        <v>1286174</v>
+        <v>1219363</v>
       </c>
       <c r="BC11" s="14" t="n">
-        <v>-637844</v>
+        <v>-584684</v>
       </c>
       <c r="BD11" s="14" t="n">
-        <v>1344171</v>
+        <v>1276517</v>
       </c>
       <c r="BE11" s="14" t="n">
-        <v>1175727</v>
+        <v>1129906</v>
       </c>
       <c r="BF11" s="14" t="n">
-        <v>1418757</v>
+        <v>1351104</v>
       </c>
       <c r="BG11" s="14" t="n">
-        <v>1230502</v>
+        <v>1184681</v>
       </c>
       <c r="BH11" s="14" t="n">
-        <v>1493343</v>
+        <v>1425690</v>
       </c>
       <c r="BI11" s="14" t="n">
-        <v>-572446</v>
+        <v>-511209</v>
       </c>
     </row>
     <row r="12">
@@ -7995,178 +7995,178 @@
         <v>3371980</v>
       </c>
       <c r="D12" s="14" t="n">
-        <v>3276620</v>
+        <v>3228380</v>
       </c>
       <c r="E12" s="14" t="n">
-        <v>3106702</v>
+        <v>3058462</v>
       </c>
       <c r="F12" s="14" t="n">
-        <v>2851324</v>
+        <v>2839264</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>2653954</v>
+        <v>2593654</v>
       </c>
       <c r="H12" s="14" t="n">
-        <v>2360255</v>
+        <v>2296955</v>
       </c>
       <c r="I12" s="14" t="n">
-        <v>2119812</v>
+        <v>2095122</v>
       </c>
       <c r="J12" s="14" t="n">
-        <v>1945564</v>
+        <v>1878154</v>
       </c>
       <c r="K12" s="14" t="n">
-        <v>1838476</v>
+        <v>1770496</v>
       </c>
       <c r="L12" s="14" t="n">
-        <v>1572643</v>
+        <v>1494050</v>
       </c>
       <c r="M12" s="14" t="n">
-        <v>1523840</v>
+        <v>1445247</v>
       </c>
       <c r="N12" s="14" t="n">
-        <v>1304170</v>
+        <v>1210615</v>
       </c>
       <c r="O12" s="14" t="n">
-        <v>1354925</v>
+        <v>1263509</v>
       </c>
       <c r="P12" s="14" t="n">
-        <v>1172099</v>
+        <v>1067006</v>
       </c>
       <c r="Q12" s="14" t="n">
-        <v>1194798</v>
+        <v>1047414</v>
       </c>
       <c r="R12" s="14" t="n">
-        <v>1051733</v>
+        <v>890566</v>
       </c>
       <c r="S12" s="14" t="n">
-        <v>985348</v>
+        <v>859797</v>
       </c>
       <c r="T12" s="14" t="n">
-        <v>674027</v>
+        <v>534693</v>
       </c>
       <c r="U12" s="14" t="n">
-        <v>12709989</v>
+        <v>12513119</v>
       </c>
       <c r="V12" s="14" t="n">
-        <v>12633059</v>
+        <v>12426399</v>
       </c>
       <c r="W12" s="14" t="n">
-        <v>12511858</v>
+        <v>12298031</v>
       </c>
       <c r="X12" s="14" t="n">
-        <v>12490844</v>
+        <v>12250759</v>
       </c>
       <c r="Y12" s="14" t="n">
-        <v>12385151</v>
+        <v>12121398</v>
       </c>
       <c r="Z12" s="14" t="n">
-        <v>12292585</v>
+        <v>11982765</v>
       </c>
       <c r="AA12" s="14" t="n">
-        <v>11772605</v>
+        <v>11430738</v>
       </c>
       <c r="AB12" s="14" t="n">
-        <v>11700221</v>
+        <v>11334157</v>
       </c>
       <c r="AC12" s="14" t="n">
-        <v>11565135</v>
+        <v>11180105</v>
       </c>
       <c r="AD12" s="14" t="n">
-        <v>11524457</v>
+        <v>11099347</v>
       </c>
       <c r="AE12" s="14" t="n">
-        <v>11416079</v>
+        <v>10949305</v>
       </c>
       <c r="AF12" s="14" t="n">
-        <v>11250359</v>
+        <v>10726009</v>
       </c>
       <c r="AG12" s="14" t="n">
-        <v>10999871</v>
+        <v>10436895</v>
       </c>
       <c r="AH12" s="14" t="n">
-        <v>10625096</v>
+        <v>10033323</v>
       </c>
       <c r="AI12" s="14" t="n">
-        <v>10703457</v>
+        <v>10079470</v>
       </c>
       <c r="AJ12" s="14" t="n">
-        <v>10855715</v>
+        <v>10194200</v>
       </c>
       <c r="AK12" s="14" t="n">
-        <v>10884803</v>
+        <v>10202190</v>
       </c>
       <c r="AL12" s="14" t="n">
-        <v>11028978</v>
+        <v>10290935</v>
       </c>
       <c r="AM12" s="14" t="n">
-        <v>10879171</v>
+        <v>10107286</v>
       </c>
       <c r="AN12" s="14" t="n">
-        <v>11479635</v>
+        <v>10665985</v>
       </c>
       <c r="AO12" s="14" t="n">
-        <v>11868983</v>
+        <v>11011809</v>
       </c>
       <c r="AP12" s="14" t="n">
-        <v>12458316</v>
+        <v>11558226</v>
       </c>
       <c r="AQ12" s="14" t="n">
-        <v>12474895</v>
+        <v>11630490</v>
       </c>
       <c r="AR12" s="14" t="n">
-        <v>13077738</v>
+        <v>12136064</v>
       </c>
       <c r="AS12" s="14" t="n">
-        <v>13301664</v>
+        <v>12313577</v>
       </c>
       <c r="AT12" s="14" t="n">
-        <v>13821386</v>
+        <v>12787975</v>
       </c>
       <c r="AU12" s="14" t="n">
-        <v>14104104</v>
+        <v>13035779</v>
       </c>
       <c r="AV12" s="14" t="n">
-        <v>14642934</v>
+        <v>13491503</v>
       </c>
       <c r="AW12" s="14" t="n">
-        <v>14164499</v>
+        <v>13042320</v>
       </c>
       <c r="AX12" s="14" t="n">
-        <v>14546399</v>
+        <v>13365899</v>
       </c>
       <c r="AY12" s="14" t="n">
-        <v>14941815</v>
+        <v>13698398</v>
       </c>
       <c r="AZ12" s="14" t="n">
-        <v>16266435</v>
+        <v>14945980</v>
       </c>
       <c r="BA12" s="14" t="n">
-        <v>17331813</v>
+        <v>15965369</v>
       </c>
       <c r="BB12" s="14" t="n">
-        <v>18617987</v>
+        <v>17184732</v>
       </c>
       <c r="BC12" s="14" t="n">
-        <v>17980143</v>
+        <v>16600048</v>
       </c>
       <c r="BD12" s="14" t="n">
-        <v>19324313</v>
+        <v>17876566</v>
       </c>
       <c r="BE12" s="14" t="n">
-        <v>20500041</v>
+        <v>19006472</v>
       </c>
       <c r="BF12" s="14" t="n">
-        <v>21918798</v>
+        <v>20357576</v>
       </c>
       <c r="BG12" s="14" t="n">
-        <v>23149300</v>
+        <v>21542256</v>
       </c>
       <c r="BH12" s="14" t="n">
-        <v>24642643</v>
+        <v>22967946</v>
       </c>
       <c r="BI12" s="14" t="n">
-        <v>24070197</v>
+        <v>22456737</v>
       </c>
     </row>
     <row r="13">
@@ -8381,166 +8381,166 @@
         <v>0</v>
       </c>
       <c r="H14" s="13" t="n">
-        <v>273265</v>
+        <v>287580</v>
       </c>
       <c r="I14" s="13" t="n">
-        <v>248754</v>
+        <v>261786</v>
       </c>
       <c r="J14" s="13" t="n">
-        <v>213944</v>
+        <v>225152</v>
       </c>
       <c r="K14" s="13" t="n">
-        <v>456311</v>
+        <v>480215</v>
       </c>
       <c r="L14" s="13" t="n">
-        <v>400901</v>
+        <v>421903</v>
       </c>
       <c r="M14" s="13" t="n">
-        <v>335193</v>
+        <v>352752</v>
       </c>
       <c r="N14" s="13" t="n">
-        <v>505298</v>
+        <v>531573</v>
       </c>
       <c r="O14" s="13" t="n">
-        <v>409517</v>
+        <v>430812</v>
       </c>
       <c r="P14" s="13" t="n">
-        <v>565039</v>
+        <v>594311</v>
       </c>
       <c r="Q14" s="13" t="n">
-        <v>454877</v>
+        <v>478442</v>
       </c>
       <c r="R14" s="13" t="n">
-        <v>603662</v>
+        <v>634881</v>
       </c>
       <c r="S14" s="13" t="n">
-        <v>476805</v>
+        <v>501463</v>
       </c>
       <c r="T14" s="13" t="n">
-        <v>604541</v>
+        <v>635771</v>
       </c>
       <c r="U14" s="13" t="n">
-        <v>719565</v>
+        <v>756716</v>
       </c>
       <c r="V14" s="13" t="n">
-        <v>821883</v>
+        <v>864301</v>
       </c>
       <c r="W14" s="13" t="n">
-        <v>644191</v>
+        <v>677439</v>
       </c>
       <c r="X14" s="13" t="n">
-        <v>721106</v>
+        <v>758312</v>
       </c>
       <c r="Y14" s="13" t="n">
-        <v>874419</v>
+        <v>919525</v>
       </c>
       <c r="Z14" s="13" t="n">
-        <v>867719</v>
+        <v>912380</v>
       </c>
       <c r="AA14" s="13" t="n">
-        <v>930815</v>
+        <v>978620</v>
       </c>
       <c r="AB14" s="13" t="n">
-        <v>980793</v>
+        <v>1031090</v>
       </c>
       <c r="AC14" s="13" t="n">
-        <v>1099189</v>
+        <v>1155486</v>
       </c>
       <c r="AD14" s="13" t="n">
-        <v>1290913</v>
+        <v>1357500</v>
       </c>
       <c r="AE14" s="13" t="n">
-        <v>1467114</v>
+        <v>1543117</v>
       </c>
       <c r="AF14" s="13" t="n">
-        <v>1500185</v>
+        <v>1578122</v>
       </c>
       <c r="AG14" s="13" t="n">
-        <v>1517599</v>
+        <v>1596605</v>
       </c>
       <c r="AH14" s="13" t="n">
-        <v>1602223</v>
+        <v>1685779</v>
       </c>
       <c r="AI14" s="13" t="n">
-        <v>1753983</v>
+        <v>1845574</v>
       </c>
       <c r="AJ14" s="13" t="n">
-        <v>1972805</v>
+        <v>2075921</v>
       </c>
       <c r="AK14" s="13" t="n">
-        <v>2175695</v>
+        <v>2289486</v>
       </c>
       <c r="AL14" s="13" t="n">
-        <v>2170199</v>
+        <v>2284203</v>
       </c>
       <c r="AM14" s="13" t="n">
-        <v>2236460</v>
+        <v>2354370</v>
       </c>
       <c r="AN14" s="13" t="n">
-        <v>2216416</v>
+        <v>2333549</v>
       </c>
       <c r="AO14" s="13" t="n">
-        <v>2264099</v>
+        <v>2383990</v>
       </c>
       <c r="AP14" s="13" t="n">
-        <v>2323522</v>
+        <v>2446776</v>
       </c>
       <c r="AQ14" s="13" t="n">
-        <v>2365302</v>
+        <v>2490932</v>
       </c>
       <c r="AR14" s="13" t="n">
-        <v>2390003</v>
+        <v>2517063</v>
       </c>
       <c r="AS14" s="13" t="n">
-        <v>2478441</v>
+        <v>2610300</v>
       </c>
       <c r="AT14" s="13" t="n">
-        <v>2470063</v>
+        <v>2601540</v>
       </c>
       <c r="AU14" s="13" t="n">
-        <v>2847846</v>
+        <v>2999508</v>
       </c>
       <c r="AV14" s="13" t="n">
-        <v>3129173</v>
+        <v>3295864</v>
       </c>
       <c r="AW14" s="13" t="n">
-        <v>3475218</v>
+        <v>3660380</v>
       </c>
       <c r="AX14" s="13" t="n">
-        <v>3401360</v>
+        <v>3582765</v>
       </c>
       <c r="AY14" s="13" t="n">
-        <v>3403276</v>
+        <v>3584931</v>
       </c>
       <c r="AZ14" s="13" t="n">
-        <v>3478338</v>
+        <v>3664117</v>
       </c>
       <c r="BA14" s="13" t="n">
-        <v>3471639</v>
+        <v>3657141</v>
       </c>
       <c r="BB14" s="13" t="n">
-        <v>3490840</v>
+        <v>3677482</v>
       </c>
       <c r="BC14" s="13" t="n">
-        <v>3571717</v>
+        <v>3762773</v>
       </c>
       <c r="BD14" s="13" t="n">
-        <v>3636545</v>
+        <v>3831136</v>
       </c>
       <c r="BE14" s="13" t="n">
-        <v>3686202</v>
+        <v>3883499</v>
       </c>
       <c r="BF14" s="13" t="n">
-        <v>3721324</v>
+        <v>3920538</v>
       </c>
       <c r="BG14" s="13" t="n">
-        <v>3742380</v>
+        <v>3942748</v>
       </c>
       <c r="BH14" s="13" t="n">
-        <v>3749714</v>
+        <v>3950494</v>
       </c>
       <c r="BI14" s="13" t="n">
-        <v>3743583</v>
+        <v>3944050</v>
       </c>
     </row>
     <row r="15">
@@ -8897,13 +8897,13 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>0.5838</v>
+        <v>0.5616</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>0.6719000000000001</v>
+        <v>0.6543</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>0.6954</v>
+        <v>0.6792</v>
       </c>
     </row>
     <row r="12">
@@ -8913,13 +8913,13 @@
         </is>
       </c>
       <c r="B12" s="13" t="n">
-        <v>204661.8055</v>
+        <v>-187985.0665</v>
       </c>
       <c r="C12" s="13" t="n">
-        <v>13350995.4564</v>
+        <v>12585359.8464</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>26811460.7425</v>
+        <v>25697899.2508</v>
       </c>
     </row>
     <row r="13">
@@ -8929,13 +8929,13 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>0.0116</v>
+        <v>-0.0106</v>
       </c>
       <c r="C13" s="8" t="n">
-        <v>0.306</v>
+        <v>0.2884</v>
       </c>
       <c r="D13" s="8" t="n">
-        <v>0.3909</v>
+        <v>0.3747</v>
       </c>
     </row>
     <row r="14">
@@ -8945,13 +8945,13 @@
         </is>
       </c>
       <c r="B14" s="13" t="n">
-        <v>-5116360.2475</v>
+        <v>-5948630.3696</v>
       </c>
       <c r="C14" s="13" t="n">
-        <v>18254314.5811</v>
+        <v>16650997.9337</v>
       </c>
       <c r="D14" s="13" t="n">
-        <v>46109341.8032</v>
+        <v>43815609.7748</v>
       </c>
     </row>
     <row r="15">
@@ -8961,7 +8961,7 @@
         </is>
       </c>
       <c r="B15" s="17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C15" s="17" t="n">
         <v>3</v>
@@ -8977,13 +8977,13 @@
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>7752567.734</v>
+        <v>8518384.9835</v>
       </c>
       <c r="C16" s="13" t="n">
-        <v>4874904.3651</v>
+        <v>5466676.8275</v>
       </c>
       <c r="D16" s="13" t="n">
-        <v>2798324.8512</v>
+        <v>3315789.8417</v>
       </c>
     </row>
     <row r="17">
@@ -8999,7 +8999,7 @@
         <v>33</v>
       </c>
       <c r="D17" s="17" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18">
@@ -9009,13 +9009,13 @@
         </is>
       </c>
       <c r="B18" s="13" t="n">
-        <v>1259662.2993</v>
+        <v>1150466.5233</v>
       </c>
       <c r="C18" s="13" t="n">
-        <v>674027.0365</v>
+        <v>534692.9245</v>
       </c>
       <c r="D18" s="13" t="n">
-        <v>990261.4608</v>
+        <v>742581.1740999999</v>
       </c>
     </row>
     <row r="19">
@@ -9025,13 +9025,13 @@
         </is>
       </c>
       <c r="B19" s="13" t="n">
-        <v>8702112.9256</v>
+        <v>7658055.007</v>
       </c>
       <c r="C19" s="13" t="n">
-        <v>24070197.3733</v>
+        <v>22456737.3838</v>
       </c>
       <c r="D19" s="13" t="n">
-        <v>41179779.1137</v>
+        <v>38836848.6968</v>
       </c>
     </row>
   </sheetData>
@@ -9163,7 +9163,7 @@
         </is>
       </c>
       <c r="B11" s="13" t="n">
-        <v>226238</v>
+        <v>238298</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -9178,7 +9178,7 @@
         </is>
       </c>
       <c r="B12" s="13" t="n">
-        <v>61238</v>
+        <v>64238</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -9234,7 +9234,7 @@
         </is>
       </c>
       <c r="B16" s="14" t="n">
-        <v>2121078</v>
+        <v>2136138</v>
       </c>
     </row>
     <row r="17">
@@ -9244,13 +9244,13 @@
         </is>
       </c>
       <c r="B17" s="14" t="n">
-        <v>1378922</v>
+        <v>1363862</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Note: the base case dips to its lowest cash balance in month 19 at R674,027. The growth round must be closed before then, not started then.</t>
+          <t>Note: the base case dips to its lowest cash balance in month 19 at R534,693. The growth round must be closed before then, not started then.</t>
         </is>
       </c>
     </row>
@@ -9356,22 +9356,22 @@
         <v>0.22</v>
       </c>
       <c r="E4" s="13" t="n">
-        <v>211200</v>
+        <v>223200</v>
       </c>
       <c r="F4" s="13" t="n">
         <v>13982</v>
       </c>
       <c r="G4" s="13" t="n">
-        <v>1056</v>
+        <v>1116</v>
       </c>
       <c r="H4" s="13" t="n">
-        <v>52800</v>
+        <v>55800</v>
       </c>
       <c r="I4" s="13" t="n">
         <v>8438</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>9.58</v>
+        <v>10.08</v>
       </c>
     </row>
     <row r="5">
@@ -9388,22 +9388,22 @@
         <v>0.22</v>
       </c>
       <c r="E5" s="13" t="n">
-        <v>211200</v>
+        <v>223200</v>
       </c>
       <c r="F5" s="13" t="n">
         <v>13982</v>
       </c>
       <c r="G5" s="13" t="n">
-        <v>1056</v>
+        <v>1116</v>
       </c>
       <c r="H5" s="13" t="n">
-        <v>52800</v>
+        <v>55800</v>
       </c>
       <c r="I5" s="13" t="n">
         <v>8438</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>9.58</v>
+        <v>10.08</v>
       </c>
     </row>
     <row r="6">
@@ -9420,22 +9420,22 @@
         <v>0.22</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>187200</v>
+        <v>197760</v>
       </c>
       <c r="F6" s="13" t="n">
         <v>13982</v>
       </c>
       <c r="G6" s="13" t="n">
-        <v>936</v>
+        <v>989</v>
       </c>
       <c r="H6" s="13" t="n">
-        <v>46800</v>
+        <v>49440</v>
       </c>
       <c r="I6" s="13" t="n">
         <v>8438</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>8.58</v>
+        <v>9.02</v>
       </c>
     </row>
     <row r="7">
@@ -9452,22 +9452,22 @@
         <v>0.22</v>
       </c>
       <c r="E7" s="13" t="n">
-        <v>187200</v>
+        <v>197760</v>
       </c>
       <c r="F7" s="13" t="n">
         <v>13982</v>
       </c>
       <c r="G7" s="13" t="n">
-        <v>936</v>
+        <v>989</v>
       </c>
       <c r="H7" s="13" t="n">
-        <v>46800</v>
+        <v>49440</v>
       </c>
       <c r="I7" s="13" t="n">
         <v>8438</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>8.58</v>
+        <v>9.02</v>
       </c>
     </row>
     <row r="8">
@@ -9484,22 +9484,22 @@
         <v>0.22</v>
       </c>
       <c r="E8" s="13" t="n">
-        <v>194688</v>
+        <v>205670</v>
       </c>
       <c r="F8" s="13" t="n">
         <v>14541</v>
       </c>
       <c r="G8" s="13" t="n">
-        <v>973</v>
+        <v>1028</v>
       </c>
       <c r="H8" s="13" t="n">
-        <v>48672</v>
+        <v>51418</v>
       </c>
       <c r="I8" s="13" t="n">
         <v>8438</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>8.91</v>
+        <v>9.369999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -9516,22 +9516,22 @@
         <v>0.22</v>
       </c>
       <c r="E9" s="13" t="n">
-        <v>194688</v>
+        <v>205670</v>
       </c>
       <c r="F9" s="13" t="n">
         <v>14541</v>
       </c>
       <c r="G9" s="13" t="n">
-        <v>973</v>
+        <v>1028</v>
       </c>
       <c r="H9" s="13" t="n">
-        <v>48672</v>
+        <v>51418</v>
       </c>
       <c r="I9" s="13" t="n">
         <v>8438</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>8.91</v>
+        <v>9.369999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -9548,22 +9548,22 @@
         <v>0.22</v>
       </c>
       <c r="E10" s="13" t="n">
-        <v>194688</v>
+        <v>205670</v>
       </c>
       <c r="F10" s="13" t="n">
         <v>14541</v>
       </c>
       <c r="G10" s="13" t="n">
-        <v>973</v>
+        <v>1028</v>
       </c>
       <c r="H10" s="13" t="n">
-        <v>48672</v>
+        <v>51418</v>
       </c>
       <c r="I10" s="13" t="n">
         <v>8438</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>8.91</v>
+        <v>9.369999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -9580,22 +9580,22 @@
         <v>0.22</v>
       </c>
       <c r="E11" s="13" t="n">
-        <v>194688</v>
+        <v>205670</v>
       </c>
       <c r="F11" s="13" t="n">
         <v>14541</v>
       </c>
       <c r="G11" s="13" t="n">
-        <v>973</v>
+        <v>1028</v>
       </c>
       <c r="H11" s="13" t="n">
-        <v>48672</v>
+        <v>51418</v>
       </c>
       <c r="I11" s="13" t="n">
         <v>8438</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>8.91</v>
+        <v>9.369999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -9612,22 +9612,22 @@
         <v>0.22</v>
       </c>
       <c r="E12" s="13" t="n">
-        <v>194688</v>
+        <v>205670</v>
       </c>
       <c r="F12" s="13" t="n">
         <v>14541</v>
       </c>
       <c r="G12" s="13" t="n">
-        <v>973</v>
+        <v>1028</v>
       </c>
       <c r="H12" s="13" t="n">
-        <v>48672</v>
+        <v>51418</v>
       </c>
       <c r="I12" s="13" t="n">
         <v>8438</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>8.91</v>
+        <v>9.369999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -9644,22 +9644,22 @@
         <v>0.3</v>
       </c>
       <c r="E13" s="13" t="n">
-        <v>259584</v>
+        <v>274227</v>
       </c>
       <c r="F13" s="13" t="n">
         <v>19389</v>
       </c>
       <c r="G13" s="13" t="n">
-        <v>1298</v>
+        <v>1371</v>
       </c>
       <c r="H13" s="13" t="n">
-        <v>64896</v>
+        <v>68557</v>
       </c>
       <c r="I13" s="13" t="n">
         <v>11250</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>8.91</v>
+        <v>9.369999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -9676,22 +9676,22 @@
         <v>0.22</v>
       </c>
       <c r="E14" s="13" t="n">
-        <v>177216</v>
+        <v>187200</v>
       </c>
       <c r="F14" s="13" t="n">
         <v>14541</v>
       </c>
       <c r="G14" s="13" t="n">
-        <v>886</v>
+        <v>936</v>
       </c>
       <c r="H14" s="13" t="n">
-        <v>44304</v>
+        <v>46800</v>
       </c>
       <c r="I14" s="13" t="n">
         <v>8438</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>8.18</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="15">
@@ -9708,22 +9708,22 @@
         <v>0.3</v>
       </c>
       <c r="E15" s="13" t="n">
-        <v>236288</v>
+        <v>249600</v>
       </c>
       <c r="F15" s="13" t="n">
         <v>19389</v>
       </c>
       <c r="G15" s="13" t="n">
-        <v>1181</v>
+        <v>1248</v>
       </c>
       <c r="H15" s="13" t="n">
-        <v>59072</v>
+        <v>62400</v>
       </c>
       <c r="I15" s="13" t="n">
         <v>11250</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>8.18</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="16">
@@ -9740,22 +9740,22 @@
         <v>0.3</v>
       </c>
       <c r="E16" s="13" t="n">
-        <v>236288</v>
+        <v>249600</v>
       </c>
       <c r="F16" s="13" t="n">
         <v>19389</v>
       </c>
       <c r="G16" s="13" t="n">
-        <v>1181</v>
+        <v>1248</v>
       </c>
       <c r="H16" s="13" t="n">
-        <v>59072</v>
+        <v>62400</v>
       </c>
       <c r="I16" s="13" t="n">
         <v>11250</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>8.18</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="17">
@@ -9772,22 +9772,22 @@
         <v>0.37</v>
       </c>
       <c r="E17" s="13" t="n">
-        <v>295360</v>
+        <v>312000</v>
       </c>
       <c r="F17" s="13" t="n">
         <v>24236</v>
       </c>
       <c r="G17" s="13" t="n">
-        <v>1477</v>
+        <v>1560</v>
       </c>
       <c r="H17" s="13" t="n">
-        <v>73840</v>
+        <v>78000</v>
       </c>
       <c r="I17" s="13" t="n">
         <v>14062</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>8.18</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="18">
@@ -9804,22 +9804,22 @@
         <v>0.45</v>
       </c>
       <c r="E18" s="13" t="n">
-        <v>368609</v>
+        <v>389376</v>
       </c>
       <c r="F18" s="13" t="n">
         <v>22405</v>
       </c>
       <c r="G18" s="13" t="n">
-        <v>1843</v>
+        <v>1947</v>
       </c>
       <c r="H18" s="13" t="n">
-        <v>92152</v>
+        <v>97344</v>
       </c>
       <c r="I18" s="13" t="n">
         <v>12500</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>8.289999999999999</v>
+        <v>8.73</v>
       </c>
     </row>
     <row r="19">
@@ -9836,22 +9836,22 @@
         <v>0.45</v>
       </c>
       <c r="E19" s="13" t="n">
-        <v>368609</v>
+        <v>389376</v>
       </c>
       <c r="F19" s="13" t="n">
         <v>22405</v>
       </c>
       <c r="G19" s="13" t="n">
-        <v>1843</v>
+        <v>1947</v>
       </c>
       <c r="H19" s="13" t="n">
-        <v>92152</v>
+        <v>97344</v>
       </c>
       <c r="I19" s="13" t="n">
         <v>12500</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>8.289999999999999</v>
+        <v>8.73</v>
       </c>
     </row>
     <row r="20">
@@ -9868,22 +9868,22 @@
         <v>0.45</v>
       </c>
       <c r="E20" s="13" t="n">
-        <v>368609</v>
+        <v>389376</v>
       </c>
       <c r="F20" s="13" t="n">
         <v>22405</v>
       </c>
       <c r="G20" s="13" t="n">
-        <v>1843</v>
+        <v>1947</v>
       </c>
       <c r="H20" s="13" t="n">
-        <v>92152</v>
+        <v>97344</v>
       </c>
       <c r="I20" s="13" t="n">
         <v>12500</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>8.289999999999999</v>
+        <v>8.73</v>
       </c>
     </row>
     <row r="21">
@@ -9900,22 +9900,22 @@
         <v>0.45</v>
       </c>
       <c r="E21" s="13" t="n">
-        <v>368609</v>
+        <v>389376</v>
       </c>
       <c r="F21" s="13" t="n">
         <v>22405</v>
       </c>
       <c r="G21" s="13" t="n">
-        <v>1843</v>
+        <v>1947</v>
       </c>
       <c r="H21" s="13" t="n">
-        <v>92152</v>
+        <v>97344</v>
       </c>
       <c r="I21" s="13" t="n">
         <v>12500</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>8.289999999999999</v>
+        <v>8.73</v>
       </c>
     </row>
     <row r="22">
@@ -9932,22 +9932,22 @@
         <v>0.52</v>
       </c>
       <c r="E22" s="13" t="n">
-        <v>430044</v>
+        <v>454272</v>
       </c>
       <c r="F22" s="13" t="n">
         <v>26139</v>
       </c>
       <c r="G22" s="13" t="n">
-        <v>2150</v>
+        <v>2271</v>
       </c>
       <c r="H22" s="13" t="n">
-        <v>107511</v>
+        <v>113568</v>
       </c>
       <c r="I22" s="13" t="n">
         <v>14583</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>8.289999999999999</v>
+        <v>8.73</v>
       </c>
     </row>
     <row r="23">
@@ -9964,22 +9964,22 @@
         <v>0.6</v>
       </c>
       <c r="E23" s="13" t="n">
-        <v>491479</v>
+        <v>519168</v>
       </c>
       <c r="F23" s="13" t="n">
         <v>29873</v>
       </c>
       <c r="G23" s="13" t="n">
-        <v>2457</v>
+        <v>2596</v>
       </c>
       <c r="H23" s="13" t="n">
-        <v>122870</v>
+        <v>129792</v>
       </c>
       <c r="I23" s="13" t="n">
         <v>16667</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>8.289999999999999</v>
+        <v>8.73</v>
       </c>
     </row>
     <row r="24">
@@ -9996,22 +9996,22 @@
         <v>0.67</v>
       </c>
       <c r="E24" s="13" t="n">
-        <v>552914</v>
+        <v>584064</v>
       </c>
       <c r="F24" s="13" t="n">
         <v>33607</v>
       </c>
       <c r="G24" s="13" t="n">
-        <v>2765</v>
+        <v>2920</v>
       </c>
       <c r="H24" s="13" t="n">
-        <v>138228</v>
+        <v>146016</v>
       </c>
       <c r="I24" s="13" t="n">
         <v>18750</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>8.289999999999999</v>
+        <v>8.73</v>
       </c>
     </row>
     <row r="25">
@@ -10028,22 +10028,22 @@
         <v>0.67</v>
       </c>
       <c r="E25" s="13" t="n">
-        <v>552914</v>
+        <v>584064</v>
       </c>
       <c r="F25" s="13" t="n">
         <v>33607</v>
       </c>
       <c r="G25" s="13" t="n">
-        <v>2765</v>
+        <v>2920</v>
       </c>
       <c r="H25" s="13" t="n">
-        <v>138228</v>
+        <v>146016</v>
       </c>
       <c r="I25" s="13" t="n">
         <v>18750</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>8.289999999999999</v>
+        <v>8.73</v>
       </c>
     </row>
     <row r="26">
@@ -10060,22 +10060,22 @@
         <v>0.67</v>
       </c>
       <c r="E26" s="13" t="n">
-        <v>513976</v>
+        <v>543569</v>
       </c>
       <c r="F26" s="13" t="n">
         <v>33607</v>
       </c>
       <c r="G26" s="13" t="n">
-        <v>2570</v>
+        <v>2718</v>
       </c>
       <c r="H26" s="13" t="n">
-        <v>128494</v>
+        <v>135892</v>
       </c>
       <c r="I26" s="13" t="n">
         <v>18750</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>7.75</v>
+        <v>8.16</v>
       </c>
     </row>
     <row r="27">
@@ -10092,22 +10092,22 @@
         <v>0.74</v>
       </c>
       <c r="E27" s="13" t="n">
-        <v>571085</v>
+        <v>603965</v>
       </c>
       <c r="F27" s="13" t="n">
         <v>37341</v>
       </c>
       <c r="G27" s="13" t="n">
-        <v>2855</v>
+        <v>3020</v>
       </c>
       <c r="H27" s="13" t="n">
-        <v>142771</v>
+        <v>150991</v>
       </c>
       <c r="I27" s="13" t="n">
         <v>20833</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>7.75</v>
+        <v>8.16</v>
       </c>
     </row>
     <row r="28">
@@ -10124,22 +10124,22 @@
         <v>0.67</v>
       </c>
       <c r="E28" s="13" t="n">
-        <v>513976</v>
+        <v>543569</v>
       </c>
       <c r="F28" s="13" t="n">
         <v>33607</v>
       </c>
       <c r="G28" s="13" t="n">
-        <v>2570</v>
+        <v>2718</v>
       </c>
       <c r="H28" s="13" t="n">
-        <v>128494</v>
+        <v>135892</v>
       </c>
       <c r="I28" s="13" t="n">
         <v>18750</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>7.75</v>
+        <v>8.16</v>
       </c>
     </row>
     <row r="29">
@@ -10156,22 +10156,22 @@
         <v>0.74</v>
       </c>
       <c r="E29" s="13" t="n">
-        <v>571085</v>
+        <v>603965</v>
       </c>
       <c r="F29" s="13" t="n">
         <v>37341</v>
       </c>
       <c r="G29" s="13" t="n">
-        <v>2855</v>
+        <v>3020</v>
       </c>
       <c r="H29" s="13" t="n">
-        <v>142771</v>
+        <v>150991</v>
       </c>
       <c r="I29" s="13" t="n">
         <v>20833</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>7.75</v>
+        <v>8.16</v>
       </c>
     </row>
     <row r="30">
@@ -10188,22 +10188,22 @@
         <v>0.74</v>
       </c>
       <c r="E30" s="13" t="n">
-        <v>593928</v>
+        <v>628124</v>
       </c>
       <c r="F30" s="13" t="n">
         <v>38835</v>
       </c>
       <c r="G30" s="13" t="n">
-        <v>2970</v>
+        <v>3141</v>
       </c>
       <c r="H30" s="13" t="n">
-        <v>148482</v>
+        <v>157031</v>
       </c>
       <c r="I30" s="13" t="n">
         <v>20833</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>8.050000000000001</v>
+        <v>8.48</v>
       </c>
     </row>
     <row r="31">
@@ -10220,22 +10220,22 @@
         <v>0.74</v>
       </c>
       <c r="E31" s="13" t="n">
-        <v>593928</v>
+        <v>628124</v>
       </c>
       <c r="F31" s="13" t="n">
         <v>38835</v>
       </c>
       <c r="G31" s="13" t="n">
-        <v>2970</v>
+        <v>3141</v>
       </c>
       <c r="H31" s="13" t="n">
-        <v>148482</v>
+        <v>157031</v>
       </c>
       <c r="I31" s="13" t="n">
         <v>20833</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>8.050000000000001</v>
+        <v>8.48</v>
       </c>
     </row>
     <row r="32">
@@ -10252,22 +10252,22 @@
         <v>0.74</v>
       </c>
       <c r="E32" s="13" t="n">
-        <v>593928</v>
+        <v>628124</v>
       </c>
       <c r="F32" s="13" t="n">
         <v>38835</v>
       </c>
       <c r="G32" s="13" t="n">
-        <v>2970</v>
+        <v>3141</v>
       </c>
       <c r="H32" s="13" t="n">
-        <v>148482</v>
+        <v>157031</v>
       </c>
       <c r="I32" s="13" t="n">
         <v>20833</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>8.050000000000001</v>
+        <v>8.48</v>
       </c>
     </row>
     <row r="33">
@@ -10284,22 +10284,22 @@
         <v>0.82</v>
       </c>
       <c r="E33" s="13" t="n">
-        <v>653321</v>
+        <v>690936</v>
       </c>
       <c r="F33" s="13" t="n">
         <v>42718</v>
       </c>
       <c r="G33" s="13" t="n">
-        <v>3267</v>
+        <v>3455</v>
       </c>
       <c r="H33" s="13" t="n">
-        <v>163330</v>
+        <v>172734</v>
       </c>
       <c r="I33" s="13" t="n">
         <v>22917</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>8.050000000000001</v>
+        <v>8.48</v>
       </c>
     </row>
     <row r="34">
@@ -10316,22 +10316,22 @@
         <v>0.74</v>
       </c>
       <c r="E34" s="13" t="n">
-        <v>593928</v>
+        <v>628124</v>
       </c>
       <c r="F34" s="13" t="n">
         <v>38835</v>
       </c>
       <c r="G34" s="13" t="n">
-        <v>2970</v>
+        <v>3141</v>
       </c>
       <c r="H34" s="13" t="n">
-        <v>148482</v>
+        <v>157031</v>
       </c>
       <c r="I34" s="13" t="n">
         <v>20833</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>8.050000000000001</v>
+        <v>8.48</v>
       </c>
     </row>
     <row r="35">
@@ -10348,22 +10348,22 @@
         <v>1.12</v>
       </c>
       <c r="E35" s="13" t="n">
-        <v>890892</v>
+        <v>942186</v>
       </c>
       <c r="F35" s="13" t="n">
         <v>58252</v>
       </c>
       <c r="G35" s="13" t="n">
-        <v>4454</v>
+        <v>4711</v>
       </c>
       <c r="H35" s="13" t="n">
-        <v>222723</v>
+        <v>235547</v>
       </c>
       <c r="I35" s="13" t="n">
         <v>31250</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>8.050000000000001</v>
+        <v>8.48</v>
       </c>
     </row>
     <row r="36">
@@ -10380,22 +10380,22 @@
         <v>1.04</v>
       </c>
       <c r="E36" s="13" t="n">
-        <v>831499</v>
+        <v>879374</v>
       </c>
       <c r="F36" s="13" t="n">
         <v>54368</v>
       </c>
       <c r="G36" s="13" t="n">
-        <v>4157</v>
+        <v>4397</v>
       </c>
       <c r="H36" s="13" t="n">
-        <v>207875</v>
+        <v>219843</v>
       </c>
       <c r="I36" s="13" t="n">
         <v>29167</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>8.050000000000001</v>
+        <v>8.48</v>
       </c>
     </row>
     <row r="37">
@@ -10412,22 +10412,22 @@
         <v>1.12</v>
       </c>
       <c r="E37" s="13" t="n">
-        <v>890892</v>
+        <v>942186</v>
       </c>
       <c r="F37" s="13" t="n">
         <v>58252</v>
       </c>
       <c r="G37" s="13" t="n">
-        <v>4454</v>
+        <v>4711</v>
       </c>
       <c r="H37" s="13" t="n">
-        <v>222723</v>
+        <v>235547</v>
       </c>
       <c r="I37" s="13" t="n">
         <v>31250</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>8.050000000000001</v>
+        <v>8.48</v>
       </c>
     </row>
     <row r="38">
@@ -10444,22 +10444,22 @@
         <v>1.04</v>
       </c>
       <c r="E38" s="13" t="n">
-        <v>781106</v>
+        <v>826460</v>
       </c>
       <c r="F38" s="13" t="n">
         <v>54368</v>
       </c>
       <c r="G38" s="13" t="n">
-        <v>3906</v>
+        <v>4132</v>
       </c>
       <c r="H38" s="13" t="n">
-        <v>195276</v>
+        <v>206615</v>
       </c>
       <c r="I38" s="13" t="n">
         <v>29167</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>7.6</v>
+        <v>8.01</v>
       </c>
     </row>
     <row r="39">
@@ -10476,22 +10476,22 @@
         <v>1.12</v>
       </c>
       <c r="E39" s="13" t="n">
-        <v>836899</v>
+        <v>885493</v>
       </c>
       <c r="F39" s="13" t="n">
         <v>58252</v>
       </c>
       <c r="G39" s="13" t="n">
-        <v>4184</v>
+        <v>4427</v>
       </c>
       <c r="H39" s="13" t="n">
-        <v>209225</v>
+        <v>221373</v>
       </c>
       <c r="I39" s="13" t="n">
         <v>31250</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>7.6</v>
+        <v>8.01</v>
       </c>
     </row>
     <row r="40">
@@ -10508,22 +10508,22 @@
         <v>1.19</v>
       </c>
       <c r="E40" s="13" t="n">
-        <v>892692</v>
+        <v>944526</v>
       </c>
       <c r="F40" s="13" t="n">
         <v>62135</v>
       </c>
       <c r="G40" s="13" t="n">
-        <v>4463</v>
+        <v>4723</v>
       </c>
       <c r="H40" s="13" t="n">
-        <v>223173</v>
+        <v>236131</v>
       </c>
       <c r="I40" s="13" t="n">
         <v>33333</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>7.6</v>
+        <v>8.01</v>
       </c>
     </row>
     <row r="41">
@@ -10540,22 +10540,22 @@
         <v>1.12</v>
       </c>
       <c r="E41" s="13" t="n">
-        <v>836899</v>
+        <v>885493</v>
       </c>
       <c r="F41" s="13" t="n">
         <v>58252</v>
       </c>
       <c r="G41" s="13" t="n">
-        <v>4184</v>
+        <v>4427</v>
       </c>
       <c r="H41" s="13" t="n">
-        <v>209225</v>
+        <v>221373</v>
       </c>
       <c r="I41" s="13" t="n">
         <v>31250</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>7.6</v>
+        <v>8.01</v>
       </c>
     </row>
     <row r="42">
@@ -10572,22 +10572,22 @@
         <v>1.12</v>
       </c>
       <c r="E42" s="13" t="n">
-        <v>870375</v>
+        <v>920913</v>
       </c>
       <c r="F42" s="13" t="n">
         <v>60582</v>
       </c>
       <c r="G42" s="13" t="n">
-        <v>4352</v>
+        <v>4605</v>
       </c>
       <c r="H42" s="13" t="n">
-        <v>217594</v>
+        <v>230228</v>
       </c>
       <c r="I42" s="13" t="n">
         <v>31250</v>
       </c>
       <c r="J42" s="6" t="n">
-        <v>7.89</v>
+        <v>8.32</v>
       </c>
     </row>
     <row r="43">
@@ -10604,22 +10604,22 @@
         <v>1.19</v>
       </c>
       <c r="E43" s="13" t="n">
-        <v>928400</v>
+        <v>982307</v>
       </c>
       <c r="F43" s="13" t="n">
         <v>64621</v>
       </c>
       <c r="G43" s="13" t="n">
-        <v>4642</v>
+        <v>4912</v>
       </c>
       <c r="H43" s="13" t="n">
-        <v>232100</v>
+        <v>245577</v>
       </c>
       <c r="I43" s="13" t="n">
         <v>33333</v>
       </c>
       <c r="J43" s="6" t="n">
-        <v>7.89</v>
+        <v>8.32</v>
       </c>
     </row>
     <row r="44">
@@ -10636,22 +10636,22 @@
         <v>1.19</v>
       </c>
       <c r="E44" s="13" t="n">
-        <v>928400</v>
+        <v>982307</v>
       </c>
       <c r="F44" s="13" t="n">
         <v>64621</v>
       </c>
       <c r="G44" s="13" t="n">
-        <v>4642</v>
+        <v>4912</v>
       </c>
       <c r="H44" s="13" t="n">
-        <v>232100</v>
+        <v>245577</v>
       </c>
       <c r="I44" s="13" t="n">
         <v>33333</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>7.89</v>
+        <v>8.32</v>
       </c>
     </row>
     <row r="45">
@@ -10668,22 +10668,22 @@
         <v>1.19</v>
       </c>
       <c r="E45" s="13" t="n">
-        <v>928400</v>
+        <v>982307</v>
       </c>
       <c r="F45" s="13" t="n">
         <v>64621</v>
       </c>
       <c r="G45" s="13" t="n">
-        <v>4642</v>
+        <v>4912</v>
       </c>
       <c r="H45" s="13" t="n">
-        <v>232100</v>
+        <v>245577</v>
       </c>
       <c r="I45" s="13" t="n">
         <v>33333</v>
       </c>
       <c r="J45" s="6" t="n">
-        <v>7.89</v>
+        <v>8.32</v>
       </c>
     </row>
     <row r="46">
@@ -10700,22 +10700,22 @@
         <v>1.19</v>
       </c>
       <c r="E46" s="13" t="n">
-        <v>928400</v>
+        <v>982307</v>
       </c>
       <c r="F46" s="13" t="n">
         <v>64621</v>
       </c>
       <c r="G46" s="13" t="n">
-        <v>4642</v>
+        <v>4912</v>
       </c>
       <c r="H46" s="13" t="n">
-        <v>232100</v>
+        <v>245577</v>
       </c>
       <c r="I46" s="13" t="n">
         <v>33333</v>
       </c>
       <c r="J46" s="6" t="n">
-        <v>7.89</v>
+        <v>8.32</v>
       </c>
     </row>
     <row r="47">
@@ -10732,22 +10732,22 @@
         <v>1.19</v>
       </c>
       <c r="E47" s="13" t="n">
-        <v>928400</v>
+        <v>982307</v>
       </c>
       <c r="F47" s="13" t="n">
         <v>64621</v>
       </c>
       <c r="G47" s="13" t="n">
-        <v>4642</v>
+        <v>4912</v>
       </c>
       <c r="H47" s="13" t="n">
-        <v>232100</v>
+        <v>245577</v>
       </c>
       <c r="I47" s="13" t="n">
         <v>33333</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>7.89</v>
+        <v>8.32</v>
       </c>
     </row>
     <row r="48">
@@ -10764,22 +10764,22 @@
         <v>1.19</v>
       </c>
       <c r="E48" s="13" t="n">
-        <v>928400</v>
+        <v>982307</v>
       </c>
       <c r="F48" s="13" t="n">
         <v>64621</v>
       </c>
       <c r="G48" s="13" t="n">
-        <v>4642</v>
+        <v>4912</v>
       </c>
       <c r="H48" s="13" t="n">
-        <v>232100</v>
+        <v>245577</v>
       </c>
       <c r="I48" s="13" t="n">
         <v>33333</v>
       </c>
       <c r="J48" s="6" t="n">
-        <v>7.89</v>
+        <v>8.32</v>
       </c>
     </row>
     <row r="49">
@@ -10796,22 +10796,22 @@
         <v>1.19</v>
       </c>
       <c r="E49" s="13" t="n">
-        <v>928400</v>
+        <v>982307</v>
       </c>
       <c r="F49" s="13" t="n">
         <v>64621</v>
       </c>
       <c r="G49" s="13" t="n">
-        <v>4642</v>
+        <v>4912</v>
       </c>
       <c r="H49" s="13" t="n">
-        <v>232100</v>
+        <v>245577</v>
       </c>
       <c r="I49" s="13" t="n">
         <v>33333</v>
       </c>
       <c r="J49" s="6" t="n">
-        <v>7.89</v>
+        <v>8.32</v>
       </c>
     </row>
     <row r="50">
@@ -10828,22 +10828,22 @@
         <v>1.19</v>
       </c>
       <c r="E50" s="13" t="n">
-        <v>928400</v>
+        <v>982307</v>
       </c>
       <c r="F50" s="13" t="n">
         <v>64621</v>
       </c>
       <c r="G50" s="13" t="n">
-        <v>4642</v>
+        <v>4912</v>
       </c>
       <c r="H50" s="13" t="n">
-        <v>232100</v>
+        <v>245577</v>
       </c>
       <c r="I50" s="13" t="n">
         <v>33333</v>
       </c>
       <c r="J50" s="6" t="n">
-        <v>7.89</v>
+        <v>8.32</v>
       </c>
     </row>
     <row r="51">
@@ -10860,22 +10860,22 @@
         <v>1.19</v>
       </c>
       <c r="E51" s="13" t="n">
-        <v>928400</v>
+        <v>982307</v>
       </c>
       <c r="F51" s="13" t="n">
         <v>64621</v>
       </c>
       <c r="G51" s="13" t="n">
-        <v>4642</v>
+        <v>4912</v>
       </c>
       <c r="H51" s="13" t="n">
-        <v>232100</v>
+        <v>245577</v>
       </c>
       <c r="I51" s="13" t="n">
         <v>33333</v>
       </c>
       <c r="J51" s="6" t="n">
-        <v>7.89</v>
+        <v>8.32</v>
       </c>
     </row>
     <row r="52">
@@ -10892,22 +10892,22 @@
         <v>1.19</v>
       </c>
       <c r="E52" s="13" t="n">
-        <v>928400</v>
+        <v>982307</v>
       </c>
       <c r="F52" s="13" t="n">
         <v>64621</v>
       </c>
       <c r="G52" s="13" t="n">
-        <v>4642</v>
+        <v>4912</v>
       </c>
       <c r="H52" s="13" t="n">
-        <v>232100</v>
+        <v>245577</v>
       </c>
       <c r="I52" s="13" t="n">
         <v>33333</v>
       </c>
       <c r="J52" s="6" t="n">
-        <v>7.89</v>
+        <v>8.32</v>
       </c>
     </row>
     <row r="53">
@@ -10924,22 +10924,22 @@
         <v>1.19</v>
       </c>
       <c r="E53" s="13" t="n">
-        <v>928400</v>
+        <v>982307</v>
       </c>
       <c r="F53" s="13" t="n">
         <v>64621</v>
       </c>
       <c r="G53" s="13" t="n">
-        <v>4642</v>
+        <v>4912</v>
       </c>
       <c r="H53" s="13" t="n">
-        <v>232100</v>
+        <v>245577</v>
       </c>
       <c r="I53" s="13" t="n">
         <v>33333</v>
       </c>
       <c r="J53" s="6" t="n">
-        <v>7.89</v>
+        <v>8.32</v>
       </c>
     </row>
   </sheetData>

--- a/finance/outputs/mulligan-mints-5yr-model.xlsx
+++ b/finance/outputs/mulligan-mints-5yr-model.xlsx
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="B33" s="6" t="n">
-        <v>30000</v>
+        <v>68832</v>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
@@ -1665,19 +1665,19 @@
         </is>
       </c>
       <c r="B14" s="13" t="n">
-        <v>252319</v>
+        <v>247471</v>
       </c>
       <c r="C14" s="13" t="n">
-        <v>1754714</v>
+        <v>1720121</v>
       </c>
       <c r="D14" s="13" t="n">
-        <v>4979515</v>
+        <v>4954704</v>
       </c>
       <c r="E14" s="13" t="n">
-        <v>9786134</v>
+        <v>9791147</v>
       </c>
       <c r="F14" s="13" t="n">
-        <v>15082333</v>
+        <v>15075852</v>
       </c>
     </row>
     <row r="15">
@@ -1687,19 +1687,19 @@
         </is>
       </c>
       <c r="B15" s="14" t="n">
-        <v>368091</v>
+        <v>372939</v>
       </c>
       <c r="C15" s="14" t="n">
-        <v>2955592</v>
+        <v>2990185</v>
       </c>
       <c r="D15" s="14" t="n">
-        <v>8301624</v>
+        <v>8326436</v>
       </c>
       <c r="E15" s="14" t="n">
-        <v>16994483</v>
+        <v>16989470</v>
       </c>
       <c r="F15" s="14" t="n">
-        <v>28551195</v>
+        <v>28557676</v>
       </c>
     </row>
     <row r="17">
@@ -1885,19 +1885,19 @@
         </is>
       </c>
       <c r="B26" s="14" t="n">
-        <v>-1481603</v>
+        <v>-1476755</v>
       </c>
       <c r="C26" s="14" t="n">
-        <v>-415620</v>
+        <v>-381027</v>
       </c>
       <c r="D26" s="14" t="n">
-        <v>540043</v>
+        <v>564854</v>
       </c>
       <c r="E26" s="14" t="n">
-        <v>5422818</v>
+        <v>5417805</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>12585360</v>
+        <v>12591842</v>
       </c>
     </row>
     <row r="27">
@@ -1910,16 +1910,16 @@
         <v>0</v>
       </c>
       <c r="C27" s="13" t="n">
-        <v>2813</v>
+        <v>3450</v>
       </c>
       <c r="D27" s="13" t="n">
-        <v>65683</v>
+        <v>66689</v>
       </c>
       <c r="E27" s="13" t="n">
-        <v>1029226</v>
+        <v>1043578</v>
       </c>
       <c r="F27" s="13" t="n">
-        <v>3398047</v>
+        <v>3399797</v>
       </c>
     </row>
     <row r="28">
@@ -1929,19 +1929,19 @@
         </is>
       </c>
       <c r="B28" s="14" t="n">
-        <v>-1481603</v>
+        <v>-1476755</v>
       </c>
       <c r="C28" s="14" t="n">
-        <v>-418433</v>
+        <v>-384477</v>
       </c>
       <c r="D28" s="14" t="n">
-        <v>474360</v>
+        <v>498165</v>
       </c>
       <c r="E28" s="14" t="n">
-        <v>4393592</v>
+        <v>4374228</v>
       </c>
       <c r="F28" s="14" t="n">
-        <v>9187313</v>
+        <v>9192044</v>
       </c>
     </row>
     <row r="29">
@@ -1951,19 +1951,19 @@
         </is>
       </c>
       <c r="B29" s="15" t="n">
-        <v>0.5933030701083921</v>
+        <v>0.6011167805283284</v>
       </c>
       <c r="C29" s="15" t="n">
-        <v>0.6274734175140196</v>
+        <v>0.6348175085046985</v>
       </c>
       <c r="D29" s="15" t="n">
-        <v>0.625068707708304</v>
+        <v>0.6269368489213979</v>
       </c>
       <c r="E29" s="15" t="n">
-        <v>0.6345814642268531</v>
+        <v>0.6343942855449126</v>
       </c>
       <c r="F29" s="15" t="n">
-        <v>0.6543407335484146</v>
+        <v>0.6544892822205781</v>
       </c>
     </row>
     <row r="30">
@@ -1973,19 +1973,19 @@
         </is>
       </c>
       <c r="B30" s="15" t="n">
-        <v>-2.388103257964979</v>
+        <v>-2.380289547545043</v>
       </c>
       <c r="C30" s="15" t="n">
-        <v>-0.08823635171082821</v>
+        <v>-0.08089226072014925</v>
       </c>
       <c r="D30" s="15" t="n">
-        <v>0.04066241776066723</v>
+        <v>0.04253055897376109</v>
       </c>
       <c r="E30" s="15" t="n">
-        <v>0.2024904142957458</v>
+        <v>0.2023032356138051</v>
       </c>
       <c r="F30" s="15" t="n">
-        <v>0.2884332409568427</v>
+        <v>0.288581789629006</v>
       </c>
     </row>
     <row r="33">
@@ -2211,19 +2211,19 @@
         </is>
       </c>
       <c r="B44" s="13" t="n">
-        <v>121954</v>
+        <v>119772</v>
       </c>
       <c r="C44" s="13" t="n">
-        <v>928667</v>
+        <v>910205</v>
       </c>
       <c r="D44" s="13" t="n">
-        <v>2667577</v>
+        <v>2590869</v>
       </c>
       <c r="E44" s="13" t="n">
-        <v>5177811</v>
+        <v>5075026</v>
       </c>
       <c r="F44" s="13" t="n">
-        <v>7757908</v>
+        <v>7749745</v>
       </c>
     </row>
     <row r="45">
@@ -2233,19 +2233,19 @@
         </is>
       </c>
       <c r="B45" s="14" t="n">
-        <v>140480</v>
+        <v>142661</v>
       </c>
       <c r="C45" s="14" t="n">
-        <v>1063792</v>
+        <v>1082255</v>
       </c>
       <c r="D45" s="14" t="n">
-        <v>2950345</v>
+        <v>3027053</v>
       </c>
       <c r="E45" s="14" t="n">
-        <v>5981190</v>
+        <v>6083975</v>
       </c>
       <c r="F45" s="14" t="n">
-        <v>9937674</v>
+        <v>9945837</v>
       </c>
     </row>
     <row r="47">
@@ -2431,19 +2431,19 @@
         </is>
       </c>
       <c r="B56" s="14" t="n">
-        <v>-1004623</v>
+        <v>-1002442</v>
       </c>
       <c r="C56" s="14" t="n">
-        <v>-1190274</v>
+        <v>-1171811</v>
       </c>
       <c r="D56" s="14" t="n">
-        <v>-2026599</v>
+        <v>-1949890</v>
       </c>
       <c r="E56" s="14" t="n">
-        <v>-1539150</v>
+        <v>-1436365</v>
       </c>
       <c r="F56" s="14" t="n">
-        <v>-187985</v>
+        <v>-179822</v>
       </c>
     </row>
     <row r="57">
@@ -2465,7 +2465,7 @@
         <v>0</v>
       </c>
       <c r="F57" s="13" t="n">
-        <v>3784</v>
+        <v>3801</v>
       </c>
     </row>
     <row r="58">
@@ -2475,19 +2475,19 @@
         </is>
       </c>
       <c r="B58" s="14" t="n">
-        <v>-1004623</v>
+        <v>-1002442</v>
       </c>
       <c r="C58" s="14" t="n">
-        <v>-1190274</v>
+        <v>-1171811</v>
       </c>
       <c r="D58" s="14" t="n">
-        <v>-2026599</v>
+        <v>-1949890</v>
       </c>
       <c r="E58" s="14" t="n">
-        <v>-1539150</v>
+        <v>-1436365</v>
       </c>
       <c r="F58" s="14" t="n">
-        <v>-191770</v>
+        <v>-183623</v>
       </c>
     </row>
     <row r="59">
@@ -2497,19 +2497,19 @@
         </is>
       </c>
       <c r="B59" s="15" t="n">
-        <v>0.5352961739401985</v>
+        <v>0.5436086318337477</v>
       </c>
       <c r="C59" s="15" t="n">
-        <v>0.533909016040454</v>
+        <v>0.5431751999202683</v>
       </c>
       <c r="D59" s="15" t="n">
-        <v>0.525166543485751</v>
+        <v>0.5388207681016494</v>
       </c>
       <c r="E59" s="15" t="n">
-        <v>0.5359969287707608</v>
+        <v>0.5452078447280476</v>
       </c>
       <c r="F59" s="15" t="n">
-        <v>0.5615906764315536</v>
+        <v>0.5620519832877421</v>
       </c>
     </row>
     <row r="60">
@@ -2519,19 +2519,19 @@
         </is>
       </c>
       <c r="B60" s="15" t="n">
-        <v>-3.828107310516793</v>
+        <v>-3.819794852623244</v>
       </c>
       <c r="C60" s="15" t="n">
-        <v>-0.5973892440792741</v>
+        <v>-0.5881230601994599</v>
       </c>
       <c r="D60" s="15" t="n">
-        <v>-0.3607381271498373</v>
+        <v>-0.3470839025339391</v>
       </c>
       <c r="E60" s="15" t="n">
-        <v>-0.1379289740133689</v>
+        <v>-0.1287180580560819</v>
       </c>
       <c r="F60" s="15" t="n">
-        <v>-0.01062327667885635</v>
+        <v>-0.01016196982266782</v>
       </c>
     </row>
     <row r="63">
@@ -2757,19 +2757,19 @@
         </is>
       </c>
       <c r="B74" s="13" t="n">
-        <v>372989</v>
+        <v>365475</v>
       </c>
       <c r="C74" s="13" t="n">
-        <v>2594076</v>
+        <v>2572658</v>
       </c>
       <c r="D74" s="13" t="n">
-        <v>6921975</v>
+        <v>6895442</v>
       </c>
       <c r="E74" s="13" t="n">
-        <v>13628737</v>
+        <v>13626049</v>
       </c>
       <c r="F74" s="13" t="n">
-        <v>22001865</v>
+        <v>21998909</v>
       </c>
     </row>
     <row r="75">
@@ -2779,19 +2779,19 @@
         </is>
       </c>
       <c r="B75" s="14" t="n">
-        <v>617496</v>
+        <v>625010</v>
       </c>
       <c r="C75" s="14" t="n">
-        <v>4925927</v>
+        <v>4947346</v>
       </c>
       <c r="D75" s="14" t="n">
-        <v>14281364</v>
+        <v>14307897</v>
       </c>
       <c r="E75" s="14" t="n">
-        <v>28887917</v>
+        <v>28890606</v>
       </c>
       <c r="F75" s="14" t="n">
-        <v>46585363</v>
+        <v>46588318</v>
       </c>
     </row>
     <row r="77">
@@ -2977,19 +2977,19 @@
         </is>
       </c>
       <c r="B86" s="14" t="n">
-        <v>-1423054</v>
+        <v>-1415540</v>
       </c>
       <c r="C86" s="14" t="n">
-        <v>846675</v>
+        <v>868093</v>
       </c>
       <c r="D86" s="14" t="n">
-        <v>4693455</v>
+        <v>4719988</v>
       </c>
       <c r="E86" s="14" t="n">
-        <v>14000634</v>
+        <v>14003323</v>
       </c>
       <c r="F86" s="14" t="n">
-        <v>25697899</v>
+        <v>25700855</v>
       </c>
     </row>
     <row r="87">
@@ -3002,16 +3002,16 @@
         <v>0</v>
       </c>
       <c r="C87" s="13" t="n">
-        <v>51400</v>
+        <v>52437</v>
       </c>
       <c r="D87" s="13" t="n">
-        <v>1060210</v>
+        <v>1074149</v>
       </c>
       <c r="E87" s="13" t="n">
-        <v>3780171</v>
+        <v>3780897</v>
       </c>
       <c r="F87" s="13" t="n">
-        <v>6938433</v>
+        <v>6939231</v>
       </c>
     </row>
     <row r="88">
@@ -3021,19 +3021,19 @@
         </is>
       </c>
       <c r="B88" s="14" t="n">
-        <v>-1423054</v>
+        <v>-1415540</v>
       </c>
       <c r="C88" s="14" t="n">
-        <v>795275</v>
+        <v>815657</v>
       </c>
       <c r="D88" s="14" t="n">
-        <v>3633244</v>
+        <v>3645838</v>
       </c>
       <c r="E88" s="14" t="n">
-        <v>10220463</v>
+        <v>10222426</v>
       </c>
       <c r="F88" s="14" t="n">
-        <v>18759466</v>
+        <v>18761624</v>
       </c>
     </row>
     <row r="89">
@@ -3043,19 +3043,19 @@
         </is>
       </c>
       <c r="B89" s="15" t="n">
-        <v>0.6234281424623985</v>
+        <v>0.6310142690836957</v>
       </c>
       <c r="C89" s="15" t="n">
-        <v>0.6550432234115678</v>
+        <v>0.6578914137895946</v>
       </c>
       <c r="D89" s="15" t="n">
-        <v>0.6735431686603511</v>
+        <v>0.6747945311402928</v>
       </c>
       <c r="E89" s="15" t="n">
-        <v>0.6794494427463789</v>
+        <v>0.6795126721619584</v>
       </c>
       <c r="F89" s="15" t="n">
-        <v>0.6792133819191508</v>
+        <v>0.6792564755072882</v>
       </c>
     </row>
     <row r="90">
@@ -3065,19 +3065,19 @@
         </is>
       </c>
       <c r="B90" s="15" t="n">
-        <v>-1.436724563652714</v>
+        <v>-1.429138437031417</v>
       </c>
       <c r="C90" s="15" t="n">
-        <v>0.1125897078179395</v>
+        <v>0.1154378981959662</v>
       </c>
       <c r="D90" s="15" t="n">
-        <v>0.2213545072596676</v>
+        <v>0.2226058697396092</v>
       </c>
       <c r="E90" s="15" t="n">
-        <v>0.3292976485671098</v>
+        <v>0.3293608779826894</v>
       </c>
       <c r="F90" s="15" t="n">
-        <v>0.3746747070429626</v>
+        <v>0.3747178006311001</v>
       </c>
     </row>
   </sheetData>
@@ -3873,166 +3873,166 @@
         <v>0</v>
       </c>
       <c r="H6" s="13" t="n">
-        <v>14955</v>
+        <v>14668</v>
       </c>
       <c r="I6" s="13" t="n">
-        <v>25794</v>
+        <v>25299</v>
       </c>
       <c r="J6" s="13" t="n">
-        <v>36634</v>
+        <v>35930</v>
       </c>
       <c r="K6" s="13" t="n">
-        <v>47473</v>
+        <v>46561</v>
       </c>
       <c r="L6" s="13" t="n">
-        <v>58312</v>
+        <v>57192</v>
       </c>
       <c r="M6" s="13" t="n">
-        <v>69151</v>
+        <v>67822</v>
       </c>
       <c r="N6" s="13" t="n">
-        <v>91788</v>
+        <v>88413</v>
       </c>
       <c r="O6" s="13" t="n">
-        <v>100761</v>
+        <v>97056</v>
       </c>
       <c r="P6" s="13" t="n">
-        <v>107110</v>
+        <v>105700</v>
       </c>
       <c r="Q6" s="13" t="n">
-        <v>115868</v>
+        <v>114343</v>
       </c>
       <c r="R6" s="13" t="n">
-        <v>124657</v>
+        <v>122986</v>
       </c>
       <c r="S6" s="13" t="n">
-        <v>133418</v>
+        <v>131083</v>
       </c>
       <c r="T6" s="13" t="n">
-        <v>146787</v>
+        <v>144198</v>
       </c>
       <c r="U6" s="13" t="n">
-        <v>160150</v>
+        <v>157313</v>
       </c>
       <c r="V6" s="13" t="n">
-        <v>173510</v>
+        <v>170158</v>
       </c>
       <c r="W6" s="13" t="n">
-        <v>186862</v>
+        <v>183252</v>
       </c>
       <c r="X6" s="13" t="n">
-        <v>200222</v>
+        <v>196346</v>
       </c>
       <c r="Y6" s="13" t="n">
-        <v>213581</v>
+        <v>209274</v>
       </c>
       <c r="Z6" s="13" t="n">
-        <v>265060</v>
+        <v>264825</v>
       </c>
       <c r="AA6" s="13" t="n">
-        <v>277647</v>
+        <v>273008</v>
       </c>
       <c r="AB6" s="13" t="n">
-        <v>291417</v>
+        <v>290201</v>
       </c>
       <c r="AC6" s="13" t="n">
-        <v>305462</v>
+        <v>301088</v>
       </c>
       <c r="AD6" s="13" t="n">
-        <v>321558</v>
+        <v>318406</v>
       </c>
       <c r="AE6" s="13" t="n">
-        <v>337954</v>
+        <v>335566</v>
       </c>
       <c r="AF6" s="13" t="n">
-        <v>488566</v>
+        <v>485985</v>
       </c>
       <c r="AG6" s="13" t="n">
-        <v>505089</v>
+        <v>503076</v>
       </c>
       <c r="AH6" s="13" t="n">
-        <v>521659</v>
+        <v>520125</v>
       </c>
       <c r="AI6" s="13" t="n">
-        <v>538300</v>
+        <v>537144</v>
       </c>
       <c r="AJ6" s="13" t="n">
-        <v>555011</v>
+        <v>554141</v>
       </c>
       <c r="AK6" s="13" t="n">
-        <v>571792</v>
+        <v>571140</v>
       </c>
       <c r="AL6" s="13" t="n">
-        <v>739818</v>
+        <v>739522</v>
       </c>
       <c r="AM6" s="13" t="n">
-        <v>745984</v>
+        <v>746821</v>
       </c>
       <c r="AN6" s="13" t="n">
-        <v>755357</v>
+        <v>756067</v>
       </c>
       <c r="AO6" s="13" t="n">
-        <v>765710</v>
+        <v>766762</v>
       </c>
       <c r="AP6" s="13" t="n">
-        <v>785178</v>
+        <v>785749</v>
       </c>
       <c r="AQ6" s="13" t="n">
-        <v>803807</v>
+        <v>804545</v>
       </c>
       <c r="AR6" s="13" t="n">
-        <v>821832</v>
+        <v>822243</v>
       </c>
       <c r="AS6" s="13" t="n">
-        <v>839524</v>
+        <v>839874</v>
       </c>
       <c r="AT6" s="13" t="n">
-        <v>856723</v>
+        <v>857086</v>
       </c>
       <c r="AU6" s="13" t="n">
-        <v>873978</v>
+        <v>874128</v>
       </c>
       <c r="AV6" s="13" t="n">
-        <v>890793</v>
+        <v>890885</v>
       </c>
       <c r="AW6" s="13" t="n">
-        <v>907430</v>
+        <v>907466</v>
       </c>
       <c r="AX6" s="13" t="n">
-        <v>1198357</v>
+        <v>1196442</v>
       </c>
       <c r="AY6" s="13" t="n">
-        <v>1198630</v>
+        <v>1198264</v>
       </c>
       <c r="AZ6" s="13" t="n">
-        <v>1201663</v>
+        <v>1201390</v>
       </c>
       <c r="BA6" s="13" t="n">
-        <v>1207771</v>
+        <v>1207227</v>
       </c>
       <c r="BB6" s="13" t="n">
-        <v>1227236</v>
+        <v>1226284</v>
       </c>
       <c r="BC6" s="13" t="n">
-        <v>1245458</v>
+        <v>1244759</v>
       </c>
       <c r="BD6" s="13" t="n">
-        <v>1262387</v>
+        <v>1261868</v>
       </c>
       <c r="BE6" s="13" t="n">
-        <v>1278386</v>
+        <v>1277997</v>
       </c>
       <c r="BF6" s="13" t="n">
-        <v>1293710</v>
+        <v>1293416</v>
       </c>
       <c r="BG6" s="13" t="n">
-        <v>1308539</v>
+        <v>1308314</v>
       </c>
       <c r="BH6" s="13" t="n">
-        <v>1323003</v>
+        <v>1322829</v>
       </c>
       <c r="BI6" s="13" t="n">
-        <v>1337193</v>
+        <v>1337059</v>
       </c>
     </row>
     <row r="7">
@@ -4060,166 +4060,166 @@
         <v>0</v>
       </c>
       <c r="H7" s="13" t="n">
-        <v>24588</v>
+        <v>24875</v>
       </c>
       <c r="I7" s="13" t="n">
-        <v>39292</v>
+        <v>39788</v>
       </c>
       <c r="J7" s="13" t="n">
-        <v>53996</v>
+        <v>54700</v>
       </c>
       <c r="K7" s="13" t="n">
-        <v>68701</v>
+        <v>69613</v>
       </c>
       <c r="L7" s="13" t="n">
-        <v>83405</v>
+        <v>84525</v>
       </c>
       <c r="M7" s="13" t="n">
-        <v>98109</v>
+        <v>99438</v>
       </c>
       <c r="N7" s="13" t="n">
-        <v>156919</v>
+        <v>160294</v>
       </c>
       <c r="O7" s="13" t="n">
-        <v>170727</v>
+        <v>174432</v>
       </c>
       <c r="P7" s="13" t="n">
-        <v>187160</v>
+        <v>188570</v>
       </c>
       <c r="Q7" s="13" t="n">
-        <v>201182</v>
+        <v>202708</v>
       </c>
       <c r="R7" s="13" t="n">
-        <v>215175</v>
+        <v>216846</v>
       </c>
       <c r="S7" s="13" t="n">
-        <v>229195</v>
+        <v>231529</v>
       </c>
       <c r="T7" s="13" t="n">
-        <v>249191</v>
+        <v>251780</v>
       </c>
       <c r="U7" s="13" t="n">
-        <v>269193</v>
+        <v>272031</v>
       </c>
       <c r="V7" s="13" t="n">
-        <v>289198</v>
+        <v>292551</v>
       </c>
       <c r="W7" s="13" t="n">
-        <v>309212</v>
+        <v>312822</v>
       </c>
       <c r="X7" s="13" t="n">
-        <v>329217</v>
+        <v>333093</v>
       </c>
       <c r="Y7" s="13" t="n">
-        <v>349223</v>
+        <v>353530</v>
       </c>
       <c r="Z7" s="13" t="n">
-        <v>464770</v>
+        <v>465005</v>
       </c>
       <c r="AA7" s="13" t="n">
-        <v>497413</v>
+        <v>502052</v>
       </c>
       <c r="AB7" s="13" t="n">
-        <v>528873</v>
+        <v>530089</v>
       </c>
       <c r="AC7" s="13" t="n">
-        <v>560058</v>
+        <v>564432</v>
       </c>
       <c r="AD7" s="13" t="n">
-        <v>589193</v>
+        <v>592345</v>
       </c>
       <c r="AE7" s="13" t="n">
-        <v>618027</v>
+        <v>620415</v>
       </c>
       <c r="AF7" s="13" t="n">
-        <v>768976</v>
+        <v>771558</v>
       </c>
       <c r="AG7" s="13" t="n">
-        <v>797684</v>
+        <v>799697</v>
       </c>
       <c r="AH7" s="13" t="n">
-        <v>826344</v>
+        <v>827878</v>
       </c>
       <c r="AI7" s="13" t="n">
-        <v>854933</v>
+        <v>856089</v>
       </c>
       <c r="AJ7" s="13" t="n">
-        <v>883452</v>
+        <v>884322</v>
       </c>
       <c r="AK7" s="13" t="n">
-        <v>911901</v>
+        <v>912554</v>
       </c>
       <c r="AL7" s="13" t="n">
-        <v>1247151</v>
+        <v>1247447</v>
       </c>
       <c r="AM7" s="13" t="n">
-        <v>1285485</v>
+        <v>1284648</v>
       </c>
       <c r="AN7" s="13" t="n">
-        <v>1320612</v>
+        <v>1319902</v>
       </c>
       <c r="AO7" s="13" t="n">
-        <v>1354758</v>
+        <v>1353707</v>
       </c>
       <c r="AP7" s="13" t="n">
-        <v>1379790</v>
+        <v>1379220</v>
       </c>
       <c r="AQ7" s="13" t="n">
-        <v>1405661</v>
+        <v>1404923</v>
       </c>
       <c r="AR7" s="13" t="n">
-        <v>1432136</v>
+        <v>1431725</v>
       </c>
       <c r="AS7" s="13" t="n">
-        <v>1458944</v>
+        <v>1458594</v>
       </c>
       <c r="AT7" s="13" t="n">
-        <v>1486245</v>
+        <v>1485881</v>
       </c>
       <c r="AU7" s="13" t="n">
-        <v>1513489</v>
+        <v>1513339</v>
       </c>
       <c r="AV7" s="13" t="n">
-        <v>1541175</v>
+        <v>1541082</v>
       </c>
       <c r="AW7" s="13" t="n">
-        <v>1569037</v>
+        <v>1569001</v>
       </c>
       <c r="AX7" s="13" t="n">
-        <v>2225224</v>
+        <v>2227139</v>
       </c>
       <c r="AY7" s="13" t="n">
-        <v>2263595</v>
+        <v>2263961</v>
       </c>
       <c r="AZ7" s="13" t="n">
-        <v>2299207</v>
+        <v>2299480</v>
       </c>
       <c r="BA7" s="13" t="n">
-        <v>2331744</v>
+        <v>2332288</v>
       </c>
       <c r="BB7" s="13" t="n">
-        <v>2350924</v>
+        <v>2351876</v>
       </c>
       <c r="BC7" s="13" t="n">
-        <v>2371347</v>
+        <v>2372045</v>
       </c>
       <c r="BD7" s="13" t="n">
-        <v>2393063</v>
+        <v>2393581</v>
       </c>
       <c r="BE7" s="13" t="n">
-        <v>2415709</v>
+        <v>2416097</v>
       </c>
       <c r="BF7" s="13" t="n">
-        <v>2439029</v>
+        <v>2439324</v>
       </c>
       <c r="BG7" s="13" t="n">
-        <v>2462845</v>
+        <v>2463070</v>
       </c>
       <c r="BH7" s="13" t="n">
-        <v>2487027</v>
+        <v>2487200</v>
       </c>
       <c r="BI7" s="13" t="n">
-        <v>2511481</v>
+        <v>2511615</v>
       </c>
     </row>
     <row r="8">
@@ -5743,166 +5743,166 @@
         <v>-157500</v>
       </c>
       <c r="H16" s="14" t="n">
-        <v>-223974</v>
+        <v>-223686</v>
       </c>
       <c r="I16" s="14" t="n">
-        <v>-151458</v>
+        <v>-150962</v>
       </c>
       <c r="J16" s="14" t="n">
-        <v>-138942</v>
+        <v>-138238</v>
       </c>
       <c r="K16" s="14" t="n">
-        <v>-126426</v>
+        <v>-125514</v>
       </c>
       <c r="L16" s="14" t="n">
-        <v>-113910</v>
+        <v>-112790</v>
       </c>
       <c r="M16" s="14" t="n">
-        <v>-101394</v>
+        <v>-100066</v>
       </c>
       <c r="N16" s="14" t="n">
-        <v>-30113</v>
+        <v>-26738</v>
       </c>
       <c r="O16" s="14" t="n">
-        <v>-53487</v>
+        <v>-49782</v>
       </c>
       <c r="P16" s="14" t="n">
-        <v>-42437</v>
+        <v>-41027</v>
       </c>
       <c r="Q16" s="14" t="n">
-        <v>-33797</v>
+        <v>-32271</v>
       </c>
       <c r="R16" s="14" t="n">
-        <v>-25186</v>
+        <v>-23516</v>
       </c>
       <c r="S16" s="14" t="n">
-        <v>-44108</v>
+        <v>-41774</v>
       </c>
       <c r="T16" s="14" t="n">
-        <v>-211823</v>
+        <v>-209233</v>
       </c>
       <c r="U16" s="14" t="n">
-        <v>-19530</v>
+        <v>-16692</v>
       </c>
       <c r="V16" s="14" t="n">
-        <v>-7235</v>
+        <v>-3882</v>
       </c>
       <c r="W16" s="14" t="n">
-        <v>5069</v>
+        <v>8679</v>
       </c>
       <c r="X16" s="14" t="n">
-        <v>17365</v>
+        <v>21241</v>
       </c>
       <c r="Y16" s="14" t="n">
-        <v>29661</v>
+        <v>33968</v>
       </c>
       <c r="Z16" s="14" t="n">
-        <v>39535</v>
+        <v>39770</v>
       </c>
       <c r="AA16" s="14" t="n">
-        <v>-387604</v>
+        <v>-382965</v>
       </c>
       <c r="AB16" s="14" t="n">
-        <v>48119</v>
+        <v>49335</v>
       </c>
       <c r="AC16" s="14" t="n">
-        <v>69522</v>
+        <v>73896</v>
       </c>
       <c r="AD16" s="14" t="n">
-        <v>88875</v>
+        <v>92027</v>
       </c>
       <c r="AE16" s="14" t="n">
-        <v>107927</v>
+        <v>110315</v>
       </c>
       <c r="AF16" s="14" t="n">
-        <v>123494</v>
+        <v>126076</v>
       </c>
       <c r="AG16" s="14" t="n">
-        <v>142420</v>
+        <v>144433</v>
       </c>
       <c r="AH16" s="14" t="n">
-        <v>-288702</v>
+        <v>-287168</v>
       </c>
       <c r="AI16" s="14" t="n">
-        <v>180105</v>
+        <v>181261</v>
       </c>
       <c r="AJ16" s="14" t="n">
-        <v>198842</v>
+        <v>199712</v>
       </c>
       <c r="AK16" s="14" t="n">
-        <v>217509</v>
+        <v>218162</v>
       </c>
       <c r="AL16" s="14" t="n">
-        <v>413204</v>
+        <v>413501</v>
       </c>
       <c r="AM16" s="14" t="n">
-        <v>122754</v>
+        <v>121918</v>
       </c>
       <c r="AN16" s="14" t="n">
-        <v>469098</v>
+        <v>468388</v>
       </c>
       <c r="AO16" s="14" t="n">
-        <v>420618</v>
+        <v>419566</v>
       </c>
       <c r="AP16" s="14" t="n">
-        <v>436866</v>
+        <v>436296</v>
       </c>
       <c r="AQ16" s="14" t="n">
-        <v>453953</v>
+        <v>453216</v>
       </c>
       <c r="AR16" s="14" t="n">
-        <v>471645</v>
+        <v>471234</v>
       </c>
       <c r="AS16" s="14" t="n">
-        <v>489669</v>
+        <v>489319</v>
       </c>
       <c r="AT16" s="14" t="n">
-        <v>508186</v>
+        <v>507823</v>
       </c>
       <c r="AU16" s="14" t="n">
-        <v>526647</v>
+        <v>526497</v>
       </c>
       <c r="AV16" s="14" t="n">
-        <v>545549</v>
+        <v>545457</v>
       </c>
       <c r="AW16" s="14" t="n">
-        <v>564628</v>
+        <v>564592</v>
       </c>
       <c r="AX16" s="14" t="n">
-        <v>990865</v>
+        <v>992781</v>
       </c>
       <c r="AY16" s="14" t="n">
-        <v>1022089</v>
+        <v>1022454</v>
       </c>
       <c r="AZ16" s="14" t="n">
-        <v>1050552</v>
+        <v>1050825</v>
       </c>
       <c r="BA16" s="14" t="n">
-        <v>1000192</v>
+        <v>1000736</v>
       </c>
       <c r="BB16" s="14" t="n">
-        <v>1012223</v>
+        <v>1013176</v>
       </c>
       <c r="BC16" s="14" t="n">
-        <v>1025498</v>
+        <v>1026196</v>
       </c>
       <c r="BD16" s="14" t="n">
-        <v>1040066</v>
+        <v>1040584</v>
       </c>
       <c r="BE16" s="14" t="n">
-        <v>1055563</v>
+        <v>1055951</v>
       </c>
       <c r="BF16" s="14" t="n">
-        <v>1071735</v>
+        <v>1072029</v>
       </c>
       <c r="BG16" s="14" t="n">
-        <v>1088402</v>
+        <v>1088627</v>
       </c>
       <c r="BH16" s="14" t="n">
-        <v>1105435</v>
+        <v>1105608</v>
       </c>
       <c r="BI16" s="14" t="n">
-        <v>1122741</v>
+        <v>1122875</v>
       </c>
     </row>
     <row r="17">
@@ -6686,178 +6686,178 @@
         <v>0</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>111600</v>
+        <v>256055</v>
       </c>
       <c r="E5" s="13" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>126698</v>
+        <v>282379</v>
       </c>
       <c r="G5" s="13" t="n">
-        <v>111600</v>
+        <v>0</v>
       </c>
       <c r="H5" s="13" t="n">
         <v>0</v>
       </c>
       <c r="I5" s="13" t="n">
-        <v>126698</v>
+        <v>0</v>
       </c>
       <c r="J5" s="13" t="n">
-        <v>98880</v>
+        <v>226870</v>
       </c>
       <c r="K5" s="13" t="n">
         <v>0</v>
       </c>
       <c r="L5" s="13" t="n">
-        <v>212731</v>
+        <v>252902</v>
       </c>
       <c r="M5" s="13" t="n">
         <v>0</v>
       </c>
       <c r="N5" s="13" t="n">
-        <v>216686</v>
+        <v>0</v>
       </c>
       <c r="O5" s="13" t="n">
-        <v>0</v>
+        <v>235945</v>
       </c>
       <c r="P5" s="13" t="n">
-        <v>221240</v>
+        <v>0</v>
       </c>
       <c r="Q5" s="13" t="n">
-        <v>102835</v>
+        <v>263018</v>
       </c>
       <c r="R5" s="13" t="n">
-        <v>221240</v>
+        <v>235945</v>
       </c>
       <c r="S5" s="13" t="n">
-        <v>118405</v>
+        <v>0</v>
       </c>
       <c r="T5" s="13" t="n">
-        <v>221240</v>
+        <v>263018</v>
       </c>
       <c r="U5" s="13" t="n">
-        <v>137114</v>
+        <v>235945</v>
       </c>
       <c r="V5" s="13" t="n">
-        <v>212005</v>
+        <v>0</v>
       </c>
       <c r="W5" s="13" t="n">
-        <v>282673</v>
+        <v>477774</v>
       </c>
       <c r="X5" s="13" t="n">
-        <v>233877</v>
+        <v>0</v>
       </c>
       <c r="Y5" s="13" t="n">
-        <v>301437</v>
+        <v>456373</v>
       </c>
       <c r="Z5" s="13" t="n">
-        <v>340125</v>
+        <v>223346</v>
       </c>
       <c r="AA5" s="13" t="n">
-        <v>376484</v>
+        <v>464963</v>
       </c>
       <c r="AB5" s="13" t="n">
-        <v>413727</v>
+        <v>474628</v>
       </c>
       <c r="AC5" s="13" t="n">
-        <v>413727</v>
+        <v>474628</v>
       </c>
       <c r="AD5" s="13" t="n">
-        <v>446175</v>
+        <v>474628</v>
       </c>
       <c r="AE5" s="13" t="n">
-        <v>478623</v>
+        <v>474628</v>
       </c>
       <c r="AF5" s="13" t="n">
-        <v>547578</v>
+        <v>474628</v>
       </c>
       <c r="AG5" s="13" t="n">
-        <v>584085</v>
+        <v>549077</v>
       </c>
       <c r="AH5" s="13" t="n">
-        <v>600344</v>
+        <v>528430</v>
       </c>
       <c r="AI5" s="13" t="n">
-        <v>630542</v>
+        <v>612190</v>
       </c>
       <c r="AJ5" s="13" t="n">
-        <v>579894</v>
+        <v>591337</v>
       </c>
       <c r="AK5" s="13" t="n">
-        <v>644326</v>
+        <v>591337</v>
       </c>
       <c r="AL5" s="13" t="n">
-        <v>622171</v>
+        <v>602423</v>
       </c>
       <c r="AM5" s="13" t="n">
-        <v>656406</v>
+        <v>674481</v>
       </c>
       <c r="AN5" s="13" t="n">
-        <v>670099</v>
+        <v>614990</v>
       </c>
       <c r="AO5" s="13" t="n">
-        <v>701505</v>
+        <v>768738</v>
       </c>
       <c r="AP5" s="13" t="n">
-        <v>670099</v>
+        <v>687049</v>
       </c>
       <c r="AQ5" s="13" t="n">
-        <v>862734</v>
+        <v>840796</v>
       </c>
       <c r="AR5" s="13" t="n">
-        <v>795724</v>
+        <v>840796</v>
       </c>
       <c r="AS5" s="13" t="n">
-        <v>1005149</v>
+        <v>922485</v>
       </c>
       <c r="AT5" s="13" t="n">
-        <v>911682</v>
+        <v>964193</v>
       </c>
       <c r="AU5" s="13" t="n">
-        <v>976802</v>
+        <v>896470</v>
       </c>
       <c r="AV5" s="13" t="n">
-        <v>943994</v>
+        <v>1015227</v>
       </c>
       <c r="AW5" s="13" t="n">
-        <v>948172</v>
+        <v>937917</v>
       </c>
       <c r="AX5" s="13" t="n">
-        <v>999577</v>
+        <v>963758</v>
       </c>
       <c r="AY5" s="13" t="n">
-        <v>996579</v>
+        <v>1034189</v>
       </c>
       <c r="AZ5" s="13" t="n">
-        <v>1016796</v>
+        <v>975434</v>
       </c>
       <c r="BA5" s="13" t="n">
-        <v>1051839</v>
+        <v>1055836</v>
       </c>
       <c r="BB5" s="13" t="n">
-        <v>1051839</v>
+        <v>1055836</v>
       </c>
       <c r="BC5" s="13" t="n">
-        <v>1051839</v>
+        <v>1055836</v>
       </c>
       <c r="BD5" s="13" t="n">
-        <v>1051839</v>
+        <v>1055836</v>
       </c>
       <c r="BE5" s="13" t="n">
-        <v>1051839</v>
+        <v>1055836</v>
       </c>
       <c r="BF5" s="13" t="n">
-        <v>1051839</v>
+        <v>1055836</v>
       </c>
       <c r="BG5" s="13" t="n">
-        <v>1051839</v>
+        <v>1055836</v>
       </c>
       <c r="BH5" s="13" t="n">
-        <v>1051839</v>
+        <v>1055836</v>
       </c>
       <c r="BI5" s="13" t="n">
-        <v>1051839</v>
+        <v>1055836</v>
       </c>
     </row>
     <row r="6">
@@ -6885,7 +6885,7 @@
         <v>0</v>
       </c>
       <c r="H6" s="13" t="n">
-        <v>64238</v>
+        <v>142368</v>
       </c>
       <c r="I6" s="13" t="n">
         <v>0</v>
@@ -6894,7 +6894,7 @@
         <v>0</v>
       </c>
       <c r="K6" s="13" t="n">
-        <v>64238</v>
+        <v>0</v>
       </c>
       <c r="L6" s="13" t="n">
         <v>0</v>
@@ -6903,148 +6903,148 @@
         <v>0</v>
       </c>
       <c r="N6" s="13" t="n">
-        <v>57878</v>
+        <v>127775</v>
       </c>
       <c r="O6" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P6" s="13" t="n">
-        <v>57878</v>
+        <v>0</v>
       </c>
       <c r="Q6" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R6" s="13" t="n">
-        <v>59855</v>
+        <v>0</v>
       </c>
       <c r="S6" s="13" t="n">
-        <v>0</v>
+        <v>132313</v>
       </c>
       <c r="T6" s="13" t="n">
-        <v>59855</v>
+        <v>0</v>
       </c>
       <c r="U6" s="13" t="n">
-        <v>59855</v>
+        <v>0</v>
       </c>
       <c r="V6" s="13" t="n">
-        <v>59855</v>
+        <v>132313</v>
       </c>
       <c r="W6" s="13" t="n">
         <v>0</v>
       </c>
       <c r="X6" s="13" t="n">
-        <v>59855</v>
+        <v>0</v>
       </c>
       <c r="Y6" s="13" t="n">
-        <v>79807</v>
+        <v>132313</v>
       </c>
       <c r="Z6" s="13" t="n">
-        <v>55238</v>
+        <v>0</v>
       </c>
       <c r="AA6" s="13" t="n">
-        <v>73650</v>
+        <v>121718</v>
       </c>
       <c r="AB6" s="13" t="n">
-        <v>73650</v>
+        <v>0</v>
       </c>
       <c r="AC6" s="13" t="n">
-        <v>92062</v>
+        <v>121718</v>
       </c>
       <c r="AD6" s="13" t="n">
-        <v>109844</v>
+        <v>126013</v>
       </c>
       <c r="AE6" s="13" t="n">
-        <v>109844</v>
+        <v>126013</v>
       </c>
       <c r="AF6" s="13" t="n">
-        <v>109844</v>
+        <v>126013</v>
       </c>
       <c r="AG6" s="13" t="n">
-        <v>109844</v>
+        <v>126013</v>
       </c>
       <c r="AH6" s="13" t="n">
-        <v>128151</v>
+        <v>126013</v>
       </c>
       <c r="AI6" s="13" t="n">
-        <v>146459</v>
+        <v>126013</v>
       </c>
       <c r="AJ6" s="13" t="n">
-        <v>164766</v>
+        <v>126013</v>
       </c>
       <c r="AK6" s="13" t="n">
-        <v>164766</v>
+        <v>168017</v>
       </c>
       <c r="AL6" s="13" t="n">
-        <v>154642</v>
+        <v>157694</v>
       </c>
       <c r="AM6" s="13" t="n">
-        <v>171825</v>
+        <v>157694</v>
       </c>
       <c r="AN6" s="13" t="n">
-        <v>154642</v>
+        <v>157694</v>
       </c>
       <c r="AO6" s="13" t="n">
-        <v>171825</v>
+        <v>157694</v>
       </c>
       <c r="AP6" s="13" t="n">
-        <v>177864</v>
+        <v>163237</v>
       </c>
       <c r="AQ6" s="13" t="n">
-        <v>177864</v>
+        <v>204046</v>
       </c>
       <c r="AR6" s="13" t="n">
-        <v>177864</v>
+        <v>163237</v>
       </c>
       <c r="AS6" s="13" t="n">
-        <v>195651</v>
+        <v>204046</v>
       </c>
       <c r="AT6" s="13" t="n">
-        <v>177864</v>
+        <v>204046</v>
       </c>
       <c r="AU6" s="13" t="n">
-        <v>266797</v>
+        <v>244855</v>
       </c>
       <c r="AV6" s="13" t="n">
-        <v>249010</v>
+        <v>244855</v>
       </c>
       <c r="AW6" s="13" t="n">
-        <v>266797</v>
+        <v>244855</v>
       </c>
       <c r="AX6" s="13" t="n">
-        <v>235782</v>
+        <v>270489</v>
       </c>
       <c r="AY6" s="13" t="n">
-        <v>252623</v>
+        <v>231848</v>
       </c>
       <c r="AZ6" s="13" t="n">
-        <v>269465</v>
+        <v>270489</v>
       </c>
       <c r="BA6" s="13" t="n">
-        <v>252623</v>
+        <v>270489</v>
       </c>
       <c r="BB6" s="13" t="n">
-        <v>261478</v>
+        <v>239974</v>
       </c>
       <c r="BC6" s="13" t="n">
-        <v>278910</v>
+        <v>279970</v>
       </c>
       <c r="BD6" s="13" t="n">
-        <v>278910</v>
+        <v>279970</v>
       </c>
       <c r="BE6" s="13" t="n">
-        <v>278910</v>
+        <v>279970</v>
       </c>
       <c r="BF6" s="13" t="n">
-        <v>278910</v>
+        <v>279970</v>
       </c>
       <c r="BG6" s="13" t="n">
-        <v>278910</v>
+        <v>279970</v>
       </c>
       <c r="BH6" s="13" t="n">
-        <v>278910</v>
+        <v>279970</v>
       </c>
       <c r="BI6" s="13" t="n">
-        <v>278910</v>
+        <v>279970</v>
       </c>
     </row>
     <row r="7">
@@ -7262,13 +7262,13 @@
         <v>0</v>
       </c>
       <c r="I8" s="13" t="n">
-        <v>70140</v>
+        <v>128645</v>
       </c>
       <c r="J8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="K8" s="13" t="n">
-        <v>47482</v>
+        <v>2284</v>
       </c>
       <c r="L8" s="13" t="n">
         <v>0</v>
@@ -7280,145 +7280,145 @@
         <v>0</v>
       </c>
       <c r="O8" s="13" t="n">
-        <v>-8905</v>
+        <v>42931</v>
       </c>
       <c r="P8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="Q8" s="13" t="n">
-        <v>-20187</v>
+        <v>-60234</v>
       </c>
       <c r="R8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="S8" s="13" t="n">
-        <v>-29867</v>
+        <v>24042</v>
       </c>
       <c r="T8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="U8" s="13" t="n">
-        <v>20914</v>
+        <v>-62382</v>
       </c>
       <c r="V8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="W8" s="13" t="n">
-        <v>-61495</v>
+        <v>-7586</v>
       </c>
       <c r="X8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="Y8" s="13" t="n">
-        <v>-22426</v>
+        <v>-24047</v>
       </c>
       <c r="Z8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="AA8" s="13" t="n">
-        <v>-23175</v>
+        <v>-24651</v>
       </c>
       <c r="AB8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="AC8" s="13" t="n">
-        <v>-81290</v>
+        <v>-108038</v>
       </c>
       <c r="AD8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="AE8" s="13" t="n">
-        <v>-59954</v>
+        <v>-36741</v>
       </c>
       <c r="AF8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="AG8" s="13" t="n">
-        <v>-71546</v>
+        <v>-48333</v>
       </c>
       <c r="AH8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="AI8" s="13" t="n">
-        <v>5992</v>
+        <v>-10220</v>
       </c>
       <c r="AJ8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="AK8" s="13" t="n">
-        <v>-37971</v>
+        <v>-63455</v>
       </c>
       <c r="AL8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="AM8" s="13" t="n">
-        <v>-67064</v>
+        <v>-74950</v>
       </c>
       <c r="AN8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="AO8" s="13" t="n">
-        <v>-132834</v>
+        <v>-140720</v>
       </c>
       <c r="AP8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="AQ8" s="13" t="n">
-        <v>-133390</v>
+        <v>-125127</v>
       </c>
       <c r="AR8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="AS8" s="13" t="n">
-        <v>-143240</v>
+        <v>-147697</v>
       </c>
       <c r="AT8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="AU8" s="13" t="n">
-        <v>-114933</v>
+        <v>-111900</v>
       </c>
       <c r="AV8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="AW8" s="13" t="n">
-        <v>-86625</v>
+        <v>-105287</v>
       </c>
       <c r="AX8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="AY8" s="13" t="n">
-        <v>-175632</v>
+        <v>-165744</v>
       </c>
       <c r="AZ8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="BA8" s="13" t="n">
-        <v>-171536</v>
+        <v>-158128</v>
       </c>
       <c r="BB8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="BC8" s="13" t="n">
-        <v>-176525</v>
+        <v>-191105</v>
       </c>
       <c r="BD8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="BE8" s="13" t="n">
-        <v>-183904</v>
+        <v>-182393</v>
       </c>
       <c r="BF8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="BG8" s="13" t="n">
-        <v>-203716</v>
+        <v>-202204</v>
       </c>
       <c r="BH8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="BI8" s="13" t="n">
-        <v>-223528</v>
+        <v>-222016</v>
       </c>
     </row>
     <row r="9">
@@ -7497,7 +7497,7 @@
         <v>0</v>
       </c>
       <c r="Y9" s="13" t="n">
-        <v>-2813</v>
+        <v>-3450</v>
       </c>
       <c r="Z9" s="13" t="n">
         <v>0</v>
@@ -7515,7 +7515,7 @@
         <v>0</v>
       </c>
       <c r="AE9" s="13" t="n">
-        <v>-19115</v>
+        <v>-19729</v>
       </c>
       <c r="AF9" s="13" t="n">
         <v>0</v>
@@ -7533,7 +7533,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="13" t="n">
-        <v>-46568</v>
+        <v>-46961</v>
       </c>
       <c r="AL9" s="13" t="n">
         <v>0</v>
@@ -7551,7 +7551,7 @@
         <v>0</v>
       </c>
       <c r="AQ9" s="13" t="n">
-        <v>-190519</v>
+        <v>-205249</v>
       </c>
       <c r="AR9" s="13" t="n">
         <v>0</v>
@@ -7569,7 +7569,7 @@
         <v>0</v>
       </c>
       <c r="AW9" s="13" t="n">
-        <v>-838707</v>
+        <v>-838329</v>
       </c>
       <c r="AX9" s="13" t="n">
         <v>0</v>
@@ -7587,7 +7587,7 @@
         <v>0</v>
       </c>
       <c r="BC9" s="13" t="n">
-        <v>-1647383</v>
+        <v>-1648665</v>
       </c>
       <c r="BD9" s="13" t="n">
         <v>0</v>
@@ -7605,7 +7605,7 @@
         <v>0</v>
       </c>
       <c r="BI9" s="13" t="n">
-        <v>-1750664</v>
+        <v>-1751132</v>
       </c>
     </row>
     <row r="10">
@@ -7808,178 +7808,178 @@
         <v>-65020</v>
       </c>
       <c r="D11" s="14" t="n">
-        <v>-143600</v>
+        <v>-288055</v>
       </c>
       <c r="E11" s="14" t="n">
         <v>-169918</v>
       </c>
       <c r="F11" s="14" t="n">
-        <v>-219198</v>
+        <v>-374879</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-245610</v>
+        <v>-134010</v>
       </c>
       <c r="H11" s="14" t="n">
-        <v>-296699</v>
+        <v>-374829</v>
       </c>
       <c r="I11" s="14" t="n">
-        <v>-201833</v>
+        <v>-16631</v>
       </c>
       <c r="J11" s="14" t="n">
-        <v>-216969</v>
+        <v>-344959</v>
       </c>
       <c r="K11" s="14" t="n">
-        <v>-107657</v>
+        <v>-88618</v>
       </c>
       <c r="L11" s="14" t="n">
-        <v>-276446</v>
+        <v>-316618</v>
       </c>
       <c r="M11" s="14" t="n">
         <v>-48803</v>
       </c>
       <c r="N11" s="14" t="n">
-        <v>-234632</v>
+        <v>-87843</v>
       </c>
       <c r="O11" s="14" t="n">
-        <v>52894</v>
+        <v>-131215</v>
       </c>
       <c r="P11" s="14" t="n">
-        <v>-196503</v>
+        <v>82615</v>
       </c>
       <c r="Q11" s="14" t="n">
-        <v>-19592</v>
+        <v>-219821</v>
       </c>
       <c r="R11" s="14" t="n">
-        <v>-156848</v>
+        <v>-111698</v>
       </c>
       <c r="S11" s="14" t="n">
-        <v>-30770</v>
+        <v>9232</v>
       </c>
       <c r="T11" s="14" t="n">
-        <v>-325104</v>
+        <v>-307027</v>
       </c>
       <c r="U11" s="14" t="n">
-        <v>11978426</v>
+        <v>11856153</v>
       </c>
       <c r="V11" s="14" t="n">
-        <v>-86720</v>
+        <v>52828</v>
       </c>
       <c r="W11" s="14" t="n">
-        <v>-128368</v>
+        <v>-269560</v>
       </c>
       <c r="X11" s="14" t="n">
-        <v>-47272</v>
+        <v>246461</v>
       </c>
       <c r="Y11" s="14" t="n">
-        <v>-129361</v>
+        <v>-339062</v>
       </c>
       <c r="Z11" s="14" t="n">
-        <v>-138633</v>
+        <v>33383</v>
       </c>
       <c r="AA11" s="14" t="n">
-        <v>-552027</v>
+        <v>-690051</v>
       </c>
       <c r="AB11" s="14" t="n">
-        <v>-96582</v>
+        <v>-83833</v>
       </c>
       <c r="AC11" s="14" t="n">
-        <v>-154051</v>
+        <v>-271355</v>
       </c>
       <c r="AD11" s="14" t="n">
-        <v>-80758</v>
+        <v>-125380</v>
       </c>
       <c r="AE11" s="14" t="n">
-        <v>-150042</v>
+        <v>-139616</v>
       </c>
       <c r="AF11" s="14" t="n">
-        <v>-223295</v>
+        <v>-166514</v>
       </c>
       <c r="AG11" s="14" t="n">
-        <v>-289115</v>
+        <v>-247063</v>
       </c>
       <c r="AH11" s="14" t="n">
-        <v>-403571</v>
+        <v>-329519</v>
       </c>
       <c r="AI11" s="14" t="n">
-        <v>46147</v>
+        <v>68733</v>
       </c>
       <c r="AJ11" s="14" t="n">
-        <v>114729</v>
+        <v>142039</v>
       </c>
       <c r="AK11" s="14" t="n">
-        <v>7990</v>
+        <v>31852</v>
       </c>
       <c r="AL11" s="14" t="n">
-        <v>88744</v>
+        <v>105441</v>
       </c>
       <c r="AM11" s="14" t="n">
-        <v>-183649</v>
+        <v>-195479</v>
       </c>
       <c r="AN11" s="14" t="n">
-        <v>558699</v>
+        <v>610756</v>
       </c>
       <c r="AO11" s="14" t="n">
-        <v>345824</v>
+        <v>284837</v>
       </c>
       <c r="AP11" s="14" t="n">
-        <v>546416</v>
+        <v>544094</v>
       </c>
       <c r="AQ11" s="14" t="n">
-        <v>72264</v>
+        <v>61553</v>
       </c>
       <c r="AR11" s="14" t="n">
-        <v>505574</v>
+        <v>475129</v>
       </c>
       <c r="AS11" s="14" t="n">
-        <v>177513</v>
+        <v>247325</v>
       </c>
       <c r="AT11" s="14" t="n">
-        <v>474398</v>
+        <v>395706</v>
       </c>
       <c r="AU11" s="14" t="n">
-        <v>247804</v>
+        <v>353110</v>
       </c>
       <c r="AV11" s="14" t="n">
-        <v>455723</v>
+        <v>388645</v>
       </c>
       <c r="AW11" s="14" t="n">
-        <v>-449183</v>
+        <v>-435269</v>
       </c>
       <c r="AX11" s="14" t="n">
-        <v>323580</v>
+        <v>324692</v>
       </c>
       <c r="AY11" s="14" t="n">
-        <v>332499</v>
+        <v>325553</v>
       </c>
       <c r="AZ11" s="14" t="n">
-        <v>1247582</v>
+        <v>1287920</v>
       </c>
       <c r="BA11" s="14" t="n">
-        <v>1019389</v>
+        <v>1010934</v>
       </c>
       <c r="BB11" s="14" t="n">
-        <v>1219363</v>
+        <v>1236870</v>
       </c>
       <c r="BC11" s="14" t="n">
-        <v>-584684</v>
+        <v>-605603</v>
       </c>
       <c r="BD11" s="14" t="n">
-        <v>1276517</v>
+        <v>1271461</v>
       </c>
       <c r="BE11" s="14" t="n">
-        <v>1129906</v>
+        <v>1126361</v>
       </c>
       <c r="BF11" s="14" t="n">
-        <v>1351104</v>
+        <v>1346047</v>
       </c>
       <c r="BG11" s="14" t="n">
-        <v>1184681</v>
+        <v>1181136</v>
       </c>
       <c r="BH11" s="14" t="n">
-        <v>1425690</v>
+        <v>1420633</v>
       </c>
       <c r="BI11" s="14" t="n">
-        <v>-511209</v>
+        <v>-515222</v>
       </c>
     </row>
     <row r="12">
@@ -7995,178 +7995,178 @@
         <v>3371980</v>
       </c>
       <c r="D12" s="14" t="n">
-        <v>3228380</v>
+        <v>3083925</v>
       </c>
       <c r="E12" s="14" t="n">
-        <v>3058462</v>
+        <v>2914007</v>
       </c>
       <c r="F12" s="14" t="n">
-        <v>2839264</v>
+        <v>2539128</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>2593654</v>
+        <v>2405118</v>
       </c>
       <c r="H12" s="14" t="n">
-        <v>2296955</v>
+        <v>2030289</v>
       </c>
       <c r="I12" s="14" t="n">
-        <v>2095122</v>
+        <v>2013659</v>
       </c>
       <c r="J12" s="14" t="n">
-        <v>1878154</v>
+        <v>1668700</v>
       </c>
       <c r="K12" s="14" t="n">
-        <v>1770496</v>
+        <v>1580082</v>
       </c>
       <c r="L12" s="14" t="n">
-        <v>1494050</v>
+        <v>1263464</v>
       </c>
       <c r="M12" s="14" t="n">
-        <v>1445247</v>
+        <v>1214661</v>
       </c>
       <c r="N12" s="14" t="n">
-        <v>1210615</v>
+        <v>1126818</v>
       </c>
       <c r="O12" s="14" t="n">
-        <v>1263509</v>
+        <v>995603</v>
       </c>
       <c r="P12" s="14" t="n">
-        <v>1067006</v>
+        <v>1078218</v>
       </c>
       <c r="Q12" s="14" t="n">
-        <v>1047414</v>
+        <v>858396</v>
       </c>
       <c r="R12" s="14" t="n">
-        <v>890566</v>
+        <v>746698</v>
       </c>
       <c r="S12" s="14" t="n">
-        <v>859797</v>
+        <v>755931</v>
       </c>
       <c r="T12" s="14" t="n">
-        <v>534693</v>
+        <v>448904</v>
       </c>
       <c r="U12" s="14" t="n">
-        <v>12513119</v>
+        <v>12305056</v>
       </c>
       <c r="V12" s="14" t="n">
-        <v>12426399</v>
+        <v>12357884</v>
       </c>
       <c r="W12" s="14" t="n">
-        <v>12298031</v>
+        <v>12088325</v>
       </c>
       <c r="X12" s="14" t="n">
-        <v>12250759</v>
+        <v>12334785</v>
       </c>
       <c r="Y12" s="14" t="n">
-        <v>12121398</v>
+        <v>11995724</v>
       </c>
       <c r="Z12" s="14" t="n">
-        <v>11982765</v>
+        <v>12029107</v>
       </c>
       <c r="AA12" s="14" t="n">
-        <v>11430738</v>
+        <v>11339056</v>
       </c>
       <c r="AB12" s="14" t="n">
-        <v>11334157</v>
+        <v>11255224</v>
       </c>
       <c r="AC12" s="14" t="n">
-        <v>11180105</v>
+        <v>10983869</v>
       </c>
       <c r="AD12" s="14" t="n">
-        <v>11099347</v>
+        <v>10858488</v>
       </c>
       <c r="AE12" s="14" t="n">
-        <v>10949305</v>
+        <v>10718872</v>
       </c>
       <c r="AF12" s="14" t="n">
-        <v>10726009</v>
+        <v>10552358</v>
       </c>
       <c r="AG12" s="14" t="n">
-        <v>10436895</v>
+        <v>10305295</v>
       </c>
       <c r="AH12" s="14" t="n">
-        <v>10033323</v>
+        <v>9975775</v>
       </c>
       <c r="AI12" s="14" t="n">
-        <v>10079470</v>
+        <v>10044508</v>
       </c>
       <c r="AJ12" s="14" t="n">
-        <v>10194200</v>
+        <v>10186548</v>
       </c>
       <c r="AK12" s="14" t="n">
-        <v>10202190</v>
+        <v>10218399</v>
       </c>
       <c r="AL12" s="14" t="n">
-        <v>10290935</v>
+        <v>10323840</v>
       </c>
       <c r="AM12" s="14" t="n">
-        <v>10107286</v>
+        <v>10128361</v>
       </c>
       <c r="AN12" s="14" t="n">
-        <v>10665985</v>
+        <v>10739118</v>
       </c>
       <c r="AO12" s="14" t="n">
-        <v>11011809</v>
+        <v>11023954</v>
       </c>
       <c r="AP12" s="14" t="n">
-        <v>11558226</v>
+        <v>11568049</v>
       </c>
       <c r="AQ12" s="14" t="n">
-        <v>11630490</v>
+        <v>11629601</v>
       </c>
       <c r="AR12" s="14" t="n">
-        <v>12136064</v>
+        <v>12104730</v>
       </c>
       <c r="AS12" s="14" t="n">
-        <v>12313577</v>
+        <v>12352055</v>
       </c>
       <c r="AT12" s="14" t="n">
-        <v>12787975</v>
+        <v>12747761</v>
       </c>
       <c r="AU12" s="14" t="n">
-        <v>13035779</v>
+        <v>13100871</v>
       </c>
       <c r="AV12" s="14" t="n">
-        <v>13491503</v>
+        <v>13489516</v>
       </c>
       <c r="AW12" s="14" t="n">
-        <v>13042320</v>
+        <v>13054247</v>
       </c>
       <c r="AX12" s="14" t="n">
-        <v>13365899</v>
+        <v>13378939</v>
       </c>
       <c r="AY12" s="14" t="n">
-        <v>13698398</v>
+        <v>13704492</v>
       </c>
       <c r="AZ12" s="14" t="n">
-        <v>14945980</v>
+        <v>14992412</v>
       </c>
       <c r="BA12" s="14" t="n">
-        <v>15965369</v>
+        <v>16003346</v>
       </c>
       <c r="BB12" s="14" t="n">
-        <v>17184732</v>
+        <v>17240216</v>
       </c>
       <c r="BC12" s="14" t="n">
-        <v>16600048</v>
+        <v>16634613</v>
       </c>
       <c r="BD12" s="14" t="n">
-        <v>17876566</v>
+        <v>17906073</v>
       </c>
       <c r="BE12" s="14" t="n">
-        <v>19006472</v>
+        <v>19032435</v>
       </c>
       <c r="BF12" s="14" t="n">
-        <v>20357576</v>
+        <v>20378481</v>
       </c>
       <c r="BG12" s="14" t="n">
-        <v>21542256</v>
+        <v>21559617</v>
       </c>
       <c r="BH12" s="14" t="n">
-        <v>22967946</v>
+        <v>22980250</v>
       </c>
       <c r="BI12" s="14" t="n">
-        <v>22456737</v>
+        <v>22465028</v>
       </c>
     </row>
     <row r="13">
@@ -8194,166 +8194,166 @@
         <v>0</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>27947</v>
+        <v>66002</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>25440</v>
+        <v>63495</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>21880</v>
+        <v>59935</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>46667</v>
+        <v>55322</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>41000</v>
+        <v>49655</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>34280</v>
+        <v>42935</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>54303</v>
+        <v>101014</v>
       </c>
       <c r="O13" s="12" t="n">
-        <v>44010</v>
+        <v>90721</v>
       </c>
       <c r="P13" s="12" t="n">
-        <v>62200</v>
+        <v>79511</v>
       </c>
       <c r="Q13" s="12" t="n">
-        <v>50073</v>
+        <v>67384</v>
       </c>
       <c r="R13" s="12" t="n">
-        <v>66430</v>
+        <v>54341</v>
       </c>
       <c r="S13" s="12" t="n">
-        <v>52470</v>
+        <v>107836</v>
       </c>
       <c r="T13" s="12" t="n">
-        <v>66513</v>
+        <v>92479</v>
       </c>
       <c r="U13" s="12" t="n">
-        <v>79160</v>
+        <v>75726</v>
       </c>
       <c r="V13" s="12" t="n">
-        <v>90410</v>
+        <v>125031</v>
       </c>
       <c r="W13" s="12" t="n">
-        <v>70863</v>
+        <v>105485</v>
       </c>
       <c r="X13" s="12" t="n">
-        <v>79320</v>
+        <v>84541</v>
       </c>
       <c r="Y13" s="12" t="n">
-        <v>96180</v>
+        <v>129657</v>
       </c>
       <c r="Z13" s="12" t="n">
-        <v>97310</v>
+        <v>101387</v>
       </c>
       <c r="AA13" s="12" t="n">
-        <v>106340</v>
+        <v>138672</v>
       </c>
       <c r="AB13" s="12" t="n">
-        <v>113470</v>
+        <v>106602</v>
       </c>
       <c r="AC13" s="12" t="n">
-        <v>128500</v>
+        <v>140088</v>
       </c>
       <c r="AD13" s="12" t="n">
-        <v>151430</v>
+        <v>171673</v>
       </c>
       <c r="AE13" s="12" t="n">
-        <v>172460</v>
+        <v>201358</v>
       </c>
       <c r="AF13" s="12" t="n">
-        <v>176590</v>
+        <v>214144</v>
       </c>
       <c r="AG13" s="12" t="n">
-        <v>178820</v>
+        <v>225029</v>
       </c>
       <c r="AH13" s="12" t="n">
-        <v>188950</v>
+        <v>234014</v>
       </c>
       <c r="AI13" s="12" t="n">
-        <v>206980</v>
+        <v>241100</v>
       </c>
       <c r="AJ13" s="12" t="n">
-        <v>232910</v>
+        <v>246285</v>
       </c>
       <c r="AK13" s="12" t="n">
-        <v>256940</v>
+        <v>272056</v>
       </c>
       <c r="AL13" s="12" t="n">
-        <v>260702</v>
+        <v>277558</v>
       </c>
       <c r="AM13" s="12" t="n">
-        <v>272394</v>
+        <v>281191</v>
       </c>
       <c r="AN13" s="12" t="n">
-        <v>272415</v>
+        <v>282952</v>
       </c>
       <c r="AO13" s="12" t="n">
-        <v>280365</v>
+        <v>282842</v>
       </c>
       <c r="AP13" s="12" t="n">
-        <v>286444</v>
+        <v>280862</v>
       </c>
       <c r="AQ13" s="12" t="n">
-        <v>290652</v>
+        <v>299496</v>
       </c>
       <c r="AR13" s="12" t="n">
-        <v>292990</v>
+        <v>293774</v>
       </c>
       <c r="AS13" s="12" t="n">
-        <v>303257</v>
+        <v>308666</v>
       </c>
       <c r="AT13" s="12" t="n">
-        <v>301852</v>
+        <v>321688</v>
       </c>
       <c r="AU13" s="12" t="n">
-        <v>347577</v>
+        <v>355323</v>
       </c>
       <c r="AV13" s="12" t="n">
-        <v>381632</v>
+        <v>387088</v>
       </c>
       <c r="AW13" s="12" t="n">
-        <v>423615</v>
+        <v>416982</v>
       </c>
       <c r="AX13" s="12" t="n">
-        <v>420250</v>
+        <v>433814</v>
       </c>
       <c r="AY13" s="12" t="n">
-        <v>425113</v>
+        <v>426587</v>
       </c>
       <c r="AZ13" s="12" t="n">
-        <v>438202</v>
+        <v>440272</v>
       </c>
       <c r="BA13" s="12" t="n">
-        <v>439919</v>
+        <v>452385</v>
       </c>
       <c r="BB13" s="12" t="n">
-        <v>440063</v>
+        <v>440439</v>
       </c>
       <c r="BC13" s="12" t="n">
-        <v>448434</v>
+        <v>449406</v>
       </c>
       <c r="BD13" s="12" t="n">
-        <v>455232</v>
+        <v>456800</v>
       </c>
       <c r="BE13" s="12" t="n">
-        <v>460457</v>
+        <v>462621</v>
       </c>
       <c r="BF13" s="12" t="n">
-        <v>464109</v>
+        <v>466868</v>
       </c>
       <c r="BG13" s="12" t="n">
-        <v>466188</v>
+        <v>469543</v>
       </c>
       <c r="BH13" s="12" t="n">
-        <v>466694</v>
+        <v>470646</v>
       </c>
       <c r="BI13" s="12" t="n">
-        <v>465628</v>
+        <v>470175</v>
       </c>
     </row>
     <row r="14">
@@ -8381,166 +8381,166 @@
         <v>0</v>
       </c>
       <c r="H14" s="13" t="n">
-        <v>287580</v>
+        <v>666134</v>
       </c>
       <c r="I14" s="13" t="n">
-        <v>261786</v>
+        <v>640835</v>
       </c>
       <c r="J14" s="13" t="n">
-        <v>225152</v>
+        <v>604905</v>
       </c>
       <c r="K14" s="13" t="n">
-        <v>480215</v>
+        <v>558344</v>
       </c>
       <c r="L14" s="13" t="n">
-        <v>421903</v>
+        <v>501153</v>
       </c>
       <c r="M14" s="13" t="n">
-        <v>352752</v>
+        <v>433330</v>
       </c>
       <c r="N14" s="13" t="n">
-        <v>531573</v>
+        <v>952465</v>
       </c>
       <c r="O14" s="13" t="n">
-        <v>430812</v>
+        <v>855409</v>
       </c>
       <c r="P14" s="13" t="n">
-        <v>594311</v>
+        <v>749710</v>
       </c>
       <c r="Q14" s="13" t="n">
-        <v>478442</v>
+        <v>635367</v>
       </c>
       <c r="R14" s="13" t="n">
-        <v>634881</v>
+        <v>512381</v>
       </c>
       <c r="S14" s="13" t="n">
-        <v>501463</v>
+        <v>1012573</v>
       </c>
       <c r="T14" s="13" t="n">
-        <v>635771</v>
+        <v>868375</v>
       </c>
       <c r="U14" s="13" t="n">
-        <v>756716</v>
+        <v>711063</v>
       </c>
       <c r="V14" s="13" t="n">
-        <v>864301</v>
+        <v>1172181</v>
       </c>
       <c r="W14" s="13" t="n">
-        <v>677439</v>
+        <v>988929</v>
       </c>
       <c r="X14" s="13" t="n">
-        <v>758312</v>
+        <v>792584</v>
       </c>
       <c r="Y14" s="13" t="n">
-        <v>919525</v>
+        <v>1214585</v>
       </c>
       <c r="Z14" s="13" t="n">
-        <v>912380</v>
+        <v>949761</v>
       </c>
       <c r="AA14" s="13" t="n">
-        <v>978620</v>
+        <v>1254844</v>
       </c>
       <c r="AB14" s="13" t="n">
-        <v>1031090</v>
+        <v>964642</v>
       </c>
       <c r="AC14" s="13" t="n">
-        <v>1155486</v>
+        <v>1241645</v>
       </c>
       <c r="AD14" s="13" t="n">
-        <v>1357500</v>
+        <v>1523881</v>
       </c>
       <c r="AE14" s="13" t="n">
-        <v>1543117</v>
+        <v>1788957</v>
       </c>
       <c r="AF14" s="13" t="n">
-        <v>1578122</v>
+        <v>1903613</v>
       </c>
       <c r="AG14" s="13" t="n">
-        <v>1596605</v>
+        <v>2001178</v>
       </c>
       <c r="AH14" s="13" t="n">
-        <v>1685779</v>
+        <v>2081694</v>
       </c>
       <c r="AI14" s="13" t="n">
-        <v>1845574</v>
+        <v>2145192</v>
       </c>
       <c r="AJ14" s="13" t="n">
-        <v>2075921</v>
+        <v>2191692</v>
       </c>
       <c r="AK14" s="13" t="n">
-        <v>2289486</v>
+        <v>2421407</v>
       </c>
       <c r="AL14" s="13" t="n">
-        <v>2284203</v>
+        <v>2430916</v>
       </c>
       <c r="AM14" s="13" t="n">
-        <v>2354370</v>
+        <v>2433126</v>
       </c>
       <c r="AN14" s="13" t="n">
-        <v>2333549</v>
+        <v>2426090</v>
       </c>
       <c r="AO14" s="13" t="n">
-        <v>2383990</v>
+        <v>2408359</v>
       </c>
       <c r="AP14" s="13" t="n">
-        <v>2446776</v>
+        <v>2400837</v>
       </c>
       <c r="AQ14" s="13" t="n">
-        <v>2490932</v>
+        <v>2569077</v>
       </c>
       <c r="AR14" s="13" t="n">
-        <v>2517063</v>
+        <v>2525061</v>
       </c>
       <c r="AS14" s="13" t="n">
-        <v>2610300</v>
+        <v>2657971</v>
       </c>
       <c r="AT14" s="13" t="n">
-        <v>2601540</v>
+        <v>2773668</v>
       </c>
       <c r="AU14" s="13" t="n">
-        <v>2999508</v>
+        <v>3066880</v>
       </c>
       <c r="AV14" s="13" t="n">
-        <v>3295864</v>
+        <v>3343336</v>
       </c>
       <c r="AW14" s="13" t="n">
-        <v>3660380</v>
+        <v>3603211</v>
       </c>
       <c r="AX14" s="13" t="n">
-        <v>3582765</v>
+        <v>3692485</v>
       </c>
       <c r="AY14" s="13" t="n">
-        <v>3584931</v>
+        <v>3596263</v>
       </c>
       <c r="AZ14" s="13" t="n">
-        <v>3664117</v>
+        <v>3680588</v>
       </c>
       <c r="BA14" s="13" t="n">
-        <v>3657141</v>
+        <v>3759077</v>
       </c>
       <c r="BB14" s="13" t="n">
-        <v>3677482</v>
+        <v>3677770</v>
       </c>
       <c r="BC14" s="13" t="n">
-        <v>3762773</v>
+        <v>3768816</v>
       </c>
       <c r="BD14" s="13" t="n">
-        <v>3831136</v>
+        <v>3842754</v>
       </c>
       <c r="BE14" s="13" t="n">
-        <v>3883499</v>
+        <v>3900563</v>
       </c>
       <c r="BF14" s="13" t="n">
-        <v>3920538</v>
+        <v>3942953</v>
       </c>
       <c r="BG14" s="13" t="n">
-        <v>3942748</v>
+        <v>3970444</v>
       </c>
       <c r="BH14" s="13" t="n">
-        <v>3950494</v>
+        <v>3983421</v>
       </c>
       <c r="BI14" s="13" t="n">
-        <v>3944050</v>
+        <v>3982167</v>
       </c>
     </row>
     <row r="15">
@@ -8897,13 +8897,13 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>0.5616</v>
+        <v>0.5621</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>0.6543</v>
+        <v>0.6545</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>0.6792</v>
+        <v>0.6793</v>
       </c>
     </row>
     <row r="12">
@@ -8913,13 +8913,13 @@
         </is>
       </c>
       <c r="B12" s="13" t="n">
-        <v>-187985.0665</v>
+        <v>-179821.973</v>
       </c>
       <c r="C12" s="13" t="n">
-        <v>12585359.8464</v>
+        <v>12591841.549</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>25697899.2508</v>
+        <v>25700854.9205</v>
       </c>
     </row>
     <row r="13">
@@ -8929,10 +8929,10 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>-0.0106</v>
+        <v>-0.0102</v>
       </c>
       <c r="C13" s="8" t="n">
-        <v>0.2884</v>
+        <v>0.2886</v>
       </c>
       <c r="D13" s="8" t="n">
         <v>0.3747</v>
@@ -8945,13 +8945,13 @@
         </is>
       </c>
       <c r="B14" s="13" t="n">
-        <v>-5948630.3696</v>
+        <v>-5740330.3275</v>
       </c>
       <c r="C14" s="13" t="n">
-        <v>16650997.9337</v>
+        <v>16716718.5383</v>
       </c>
       <c r="D14" s="13" t="n">
-        <v>43815609.7748</v>
+        <v>43876719.1528</v>
       </c>
     </row>
     <row r="15">
@@ -8977,13 +8977,13 @@
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>8518384.9835</v>
+        <v>8601290.9364</v>
       </c>
       <c r="C16" s="13" t="n">
-        <v>5466676.8275</v>
+        <v>5524224.698</v>
       </c>
       <c r="D16" s="13" t="n">
-        <v>3315789.8417</v>
+        <v>3336675.2557</v>
       </c>
     </row>
     <row r="17">
@@ -8999,7 +8999,7 @@
         <v>33</v>
       </c>
       <c r="D17" s="17" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18">
@@ -9009,13 +9009,13 @@
         </is>
       </c>
       <c r="B18" s="13" t="n">
-        <v>1150466.5233</v>
+        <v>1000258.3102</v>
       </c>
       <c r="C18" s="13" t="n">
-        <v>534692.9245</v>
+        <v>448903.5758</v>
       </c>
       <c r="D18" s="13" t="n">
-        <v>742581.1740999999</v>
+        <v>553890.0669</v>
       </c>
     </row>
     <row r="19">
@@ -9025,13 +9025,13 @@
         </is>
       </c>
       <c r="B19" s="13" t="n">
-        <v>7658055.007</v>
+        <v>7824302.2724</v>
       </c>
       <c r="C19" s="13" t="n">
-        <v>22456737.3838</v>
+        <v>22465028.1213</v>
       </c>
       <c r="D19" s="13" t="n">
-        <v>38836848.6968</v>
+        <v>38888197.2137</v>
       </c>
     </row>
   </sheetData>
@@ -9163,11 +9163,11 @@
         </is>
       </c>
       <c r="B11" s="13" t="n">
-        <v>238298</v>
+        <v>538434</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>30,000 tins</t>
+          <t>68,832 tins</t>
         </is>
       </c>
     </row>
@@ -9178,7 +9178,7 @@
         </is>
       </c>
       <c r="B12" s="13" t="n">
-        <v>64238</v>
+        <v>142368</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -9234,7 +9234,7 @@
         </is>
       </c>
       <c r="B16" s="14" t="n">
-        <v>2136138</v>
+        <v>2514404</v>
       </c>
     </row>
     <row r="17">
@@ -9244,13 +9244,13 @@
         </is>
       </c>
       <c r="B17" s="14" t="n">
-        <v>1363862</v>
+        <v>985596</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Note: the base case dips to its lowest cash balance in month 19 at R534,693. The growth round must be closed before then, not started then.</t>
+          <t>Note: the base case dips to its lowest cash balance in month 19 at R448,904. The growth round must be closed before then, not started then.</t>
         </is>
       </c>
     </row>
@@ -9268,7 +9268,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J53"/>
+  <dimension ref="A1:J46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9350,473 +9350,473 @@
         <v>7</v>
       </c>
       <c r="C4" s="12" t="n">
-        <v>30000</v>
+        <v>68832</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>0.22</v>
+        <v>0.51</v>
       </c>
       <c r="E4" s="13" t="n">
-        <v>223200</v>
+        <v>512110</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>13982</v>
+        <v>23763</v>
       </c>
       <c r="G4" s="13" t="n">
-        <v>1116</v>
+        <v>2561</v>
       </c>
       <c r="H4" s="13" t="n">
-        <v>55800</v>
+        <v>128028</v>
       </c>
       <c r="I4" s="13" t="n">
-        <v>8438</v>
+        <v>14340</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>10.08</v>
+        <v>9.890000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B5" s="12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C5" s="12" t="n">
-        <v>30000</v>
+        <v>68832</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>0.22</v>
+        <v>0.51</v>
       </c>
       <c r="E5" s="13" t="n">
-        <v>223200</v>
+        <v>453741</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>13982</v>
+        <v>23763</v>
       </c>
       <c r="G5" s="13" t="n">
-        <v>1116</v>
+        <v>2269</v>
       </c>
       <c r="H5" s="13" t="n">
-        <v>55800</v>
+        <v>113435</v>
       </c>
       <c r="I5" s="13" t="n">
-        <v>8438</v>
+        <v>14340</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>10.08</v>
+        <v>8.83</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="12" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="B6" s="12" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C6" s="12" t="n">
-        <v>30000</v>
+        <v>68832</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>0.22</v>
+        <v>0.51</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>197760</v>
+        <v>471890</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>13982</v>
+        <v>24714</v>
       </c>
       <c r="G6" s="13" t="n">
-        <v>989</v>
+        <v>2359</v>
       </c>
       <c r="H6" s="13" t="n">
-        <v>49440</v>
+        <v>117973</v>
       </c>
       <c r="I6" s="13" t="n">
-        <v>8438</v>
+        <v>14340</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>9.02</v>
+        <v>9.17</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B7" s="12" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C7" s="12" t="n">
-        <v>30000</v>
+        <v>68832</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>0.22</v>
+        <v>0.51</v>
       </c>
       <c r="E7" s="13" t="n">
-        <v>197760</v>
+        <v>471890</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>13982</v>
+        <v>24714</v>
       </c>
       <c r="G7" s="13" t="n">
-        <v>989</v>
+        <v>2359</v>
       </c>
       <c r="H7" s="13" t="n">
-        <v>49440</v>
+        <v>117973</v>
       </c>
       <c r="I7" s="13" t="n">
-        <v>8438</v>
+        <v>14340</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>9.02</v>
+        <v>9.17</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="12" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="B8" s="12" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C8" s="12" t="n">
-        <v>30000</v>
+        <v>68832</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>0.22</v>
+        <v>0.51</v>
       </c>
       <c r="E8" s="13" t="n">
-        <v>205670</v>
+        <v>471890</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>14541</v>
+        <v>24714</v>
       </c>
       <c r="G8" s="13" t="n">
-        <v>1028</v>
+        <v>2359</v>
       </c>
       <c r="H8" s="13" t="n">
-        <v>51418</v>
+        <v>117973</v>
       </c>
       <c r="I8" s="13" t="n">
-        <v>8438</v>
+        <v>14340</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>9.369999999999999</v>
+        <v>9.17</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B9" s="12" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C9" s="12" t="n">
-        <v>30000</v>
+        <v>68832</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>0.22</v>
+        <v>0.51</v>
       </c>
       <c r="E9" s="13" t="n">
-        <v>205670</v>
+        <v>429512</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>14541</v>
+        <v>24714</v>
       </c>
       <c r="G9" s="13" t="n">
-        <v>1028</v>
+        <v>2148</v>
       </c>
       <c r="H9" s="13" t="n">
-        <v>51418</v>
+        <v>107378</v>
       </c>
       <c r="I9" s="13" t="n">
-        <v>8438</v>
+        <v>14340</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>9.369999999999999</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="12" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B10" s="12" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="C10" s="12" t="n">
-        <v>30000</v>
+        <v>68832</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>0.22</v>
+        <v>0.51</v>
       </c>
       <c r="E10" s="13" t="n">
-        <v>205670</v>
+        <v>429512</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>14541</v>
+        <v>24714</v>
       </c>
       <c r="G10" s="13" t="n">
-        <v>1028</v>
+        <v>2148</v>
       </c>
       <c r="H10" s="13" t="n">
-        <v>51418</v>
+        <v>107378</v>
       </c>
       <c r="I10" s="13" t="n">
-        <v>8438</v>
+        <v>14340</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>9.369999999999999</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="B11" s="12" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="C11" s="12" t="n">
-        <v>30000</v>
+        <v>68832</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>0.22</v>
+        <v>0.51</v>
       </c>
       <c r="E11" s="13" t="n">
-        <v>205670</v>
+        <v>446692</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>14541</v>
+        <v>25703</v>
       </c>
       <c r="G11" s="13" t="n">
-        <v>1028</v>
+        <v>2233</v>
       </c>
       <c r="H11" s="13" t="n">
-        <v>51418</v>
+        <v>111673</v>
       </c>
       <c r="I11" s="13" t="n">
-        <v>8438</v>
+        <v>14340</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>9.369999999999999</v>
+        <v>8.73</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="12" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="B12" s="12" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C12" s="12" t="n">
-        <v>30000</v>
+        <v>68832</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>0.22</v>
+        <v>0.51</v>
       </c>
       <c r="E12" s="13" t="n">
-        <v>205670</v>
+        <v>446692</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>14541</v>
+        <v>25703</v>
       </c>
       <c r="G12" s="13" t="n">
-        <v>1028</v>
+        <v>2233</v>
       </c>
       <c r="H12" s="13" t="n">
-        <v>51418</v>
+        <v>111673</v>
       </c>
       <c r="I12" s="13" t="n">
-        <v>8438</v>
+        <v>14340</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>9.369999999999999</v>
+        <v>8.73</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="B13" s="12" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C13" s="12" t="n">
-        <v>40000</v>
+        <v>68832</v>
       </c>
       <c r="D13" s="13" t="n">
-        <v>0.3</v>
+        <v>0.51</v>
       </c>
       <c r="E13" s="13" t="n">
-        <v>274227</v>
+        <v>446692</v>
       </c>
       <c r="F13" s="13" t="n">
-        <v>19389</v>
+        <v>25703</v>
       </c>
       <c r="G13" s="13" t="n">
-        <v>1371</v>
+        <v>2233</v>
       </c>
       <c r="H13" s="13" t="n">
-        <v>68557</v>
+        <v>111673</v>
       </c>
       <c r="I13" s="13" t="n">
-        <v>11250</v>
+        <v>14340</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>9.369999999999999</v>
+        <v>8.73</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="B14" s="12" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C14" s="12" t="n">
-        <v>30000</v>
+        <v>68832</v>
       </c>
       <c r="D14" s="13" t="n">
-        <v>0.22</v>
+        <v>0.51</v>
       </c>
       <c r="E14" s="13" t="n">
-        <v>187200</v>
+        <v>446692</v>
       </c>
       <c r="F14" s="13" t="n">
-        <v>14541</v>
+        <v>25703</v>
       </c>
       <c r="G14" s="13" t="n">
-        <v>936</v>
+        <v>2233</v>
       </c>
       <c r="H14" s="13" t="n">
-        <v>46800</v>
+        <v>111673</v>
       </c>
       <c r="I14" s="13" t="n">
-        <v>8438</v>
+        <v>14340</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>8.6</v>
+        <v>8.73</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="B15" s="12" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="C15" s="12" t="n">
-        <v>40000</v>
+        <v>68832</v>
       </c>
       <c r="D15" s="13" t="n">
-        <v>0.3</v>
+        <v>0.51</v>
       </c>
       <c r="E15" s="13" t="n">
-        <v>249600</v>
+        <v>446692</v>
       </c>
       <c r="F15" s="13" t="n">
-        <v>19389</v>
+        <v>25703</v>
       </c>
       <c r="G15" s="13" t="n">
-        <v>1248</v>
+        <v>2233</v>
       </c>
       <c r="H15" s="13" t="n">
-        <v>62400</v>
+        <v>111673</v>
       </c>
       <c r="I15" s="13" t="n">
-        <v>11250</v>
+        <v>14340</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>8.6</v>
+        <v>8.73</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="B16" s="12" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C16" s="12" t="n">
-        <v>40000</v>
+        <v>68832</v>
       </c>
       <c r="D16" s="13" t="n">
-        <v>0.3</v>
+        <v>0.51</v>
       </c>
       <c r="E16" s="13" t="n">
-        <v>249600</v>
+        <v>446692</v>
       </c>
       <c r="F16" s="13" t="n">
-        <v>19389</v>
+        <v>25703</v>
       </c>
       <c r="G16" s="13" t="n">
-        <v>1248</v>
+        <v>2233</v>
       </c>
       <c r="H16" s="13" t="n">
-        <v>62400</v>
+        <v>111673</v>
       </c>
       <c r="I16" s="13" t="n">
-        <v>11250</v>
+        <v>14340</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>8.6</v>
+        <v>8.73</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="12" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="B17" s="12" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C17" s="12" t="n">
-        <v>50000</v>
+        <v>68832</v>
       </c>
       <c r="D17" s="13" t="n">
-        <v>0.37</v>
+        <v>0.51</v>
       </c>
       <c r="E17" s="13" t="n">
-        <v>312000</v>
+        <v>446692</v>
       </c>
       <c r="F17" s="13" t="n">
-        <v>24236</v>
+        <v>25703</v>
       </c>
       <c r="G17" s="13" t="n">
-        <v>1560</v>
+        <v>2233</v>
       </c>
       <c r="H17" s="13" t="n">
-        <v>78000</v>
+        <v>111673</v>
       </c>
       <c r="I17" s="13" t="n">
-        <v>14062</v>
+        <v>14340</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>8.6</v>
+        <v>8.73</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="B18" s="12" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="C18" s="12" t="n">
-        <v>60000</v>
+        <v>91776</v>
       </c>
       <c r="D18" s="13" t="n">
-        <v>0.45</v>
+        <v>0.68</v>
       </c>
       <c r="E18" s="13" t="n">
-        <v>389376</v>
+        <v>595590</v>
       </c>
       <c r="F18" s="13" t="n">
-        <v>22405</v>
+        <v>34270</v>
       </c>
       <c r="G18" s="13" t="n">
-        <v>1947</v>
+        <v>2978</v>
       </c>
       <c r="H18" s="13" t="n">
-        <v>97344</v>
+        <v>148897</v>
       </c>
       <c r="I18" s="13" t="n">
-        <v>12500</v>
+        <v>19120</v>
       </c>
       <c r="J18" s="6" t="n">
         <v>8.73</v>
@@ -9824,383 +9824,383 @@
     </row>
     <row r="19">
       <c r="A19" s="12" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="B19" s="12" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="C19" s="12" t="n">
-        <v>60000</v>
+        <v>91776</v>
       </c>
       <c r="D19" s="13" t="n">
-        <v>0.45</v>
+        <v>0.68</v>
       </c>
       <c r="E19" s="13" t="n">
-        <v>389376</v>
+        <v>554295</v>
       </c>
       <c r="F19" s="13" t="n">
-        <v>22405</v>
+        <v>34270</v>
       </c>
       <c r="G19" s="13" t="n">
-        <v>1947</v>
+        <v>2771</v>
       </c>
       <c r="H19" s="13" t="n">
-        <v>97344</v>
+        <v>138574</v>
       </c>
       <c r="I19" s="13" t="n">
-        <v>12500</v>
+        <v>19120</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>8.73</v>
+        <v>8.16</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="B20" s="12" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="C20" s="12" t="n">
-        <v>60000</v>
+        <v>91776</v>
       </c>
       <c r="D20" s="13" t="n">
-        <v>0.45</v>
+        <v>0.68</v>
       </c>
       <c r="E20" s="13" t="n">
-        <v>389376</v>
+        <v>554295</v>
       </c>
       <c r="F20" s="13" t="n">
-        <v>22405</v>
+        <v>34270</v>
       </c>
       <c r="G20" s="13" t="n">
-        <v>1947</v>
+        <v>2771</v>
       </c>
       <c r="H20" s="13" t="n">
-        <v>97344</v>
+        <v>138574</v>
       </c>
       <c r="I20" s="13" t="n">
-        <v>12500</v>
+        <v>19120</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>8.73</v>
+        <v>8.16</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="B21" s="12" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="C21" s="12" t="n">
-        <v>60000</v>
+        <v>91776</v>
       </c>
       <c r="D21" s="13" t="n">
-        <v>0.45</v>
+        <v>0.68</v>
       </c>
       <c r="E21" s="13" t="n">
-        <v>389376</v>
+        <v>554295</v>
       </c>
       <c r="F21" s="13" t="n">
-        <v>22405</v>
+        <v>34270</v>
       </c>
       <c r="G21" s="13" t="n">
-        <v>1947</v>
+        <v>2771</v>
       </c>
       <c r="H21" s="13" t="n">
-        <v>97344</v>
+        <v>138574</v>
       </c>
       <c r="I21" s="13" t="n">
-        <v>12500</v>
+        <v>19120</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>8.73</v>
+        <v>8.16</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="B22" s="12" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="C22" s="12" t="n">
-        <v>70000</v>
+        <v>91776</v>
       </c>
       <c r="D22" s="13" t="n">
-        <v>0.52</v>
+        <v>0.68</v>
       </c>
       <c r="E22" s="13" t="n">
-        <v>454272</v>
+        <v>554295</v>
       </c>
       <c r="F22" s="13" t="n">
-        <v>26139</v>
+        <v>34270</v>
       </c>
       <c r="G22" s="13" t="n">
-        <v>2271</v>
+        <v>2771</v>
       </c>
       <c r="H22" s="13" t="n">
-        <v>113568</v>
+        <v>138574</v>
       </c>
       <c r="I22" s="13" t="n">
-        <v>14583</v>
+        <v>19120</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>8.73</v>
+        <v>8.16</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="12" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="B23" s="12" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C23" s="12" t="n">
-        <v>80000</v>
+        <v>91776</v>
       </c>
       <c r="D23" s="13" t="n">
-        <v>0.6</v>
+        <v>0.68</v>
       </c>
       <c r="E23" s="13" t="n">
-        <v>519168</v>
+        <v>576467</v>
       </c>
       <c r="F23" s="13" t="n">
-        <v>29873</v>
+        <v>35641</v>
       </c>
       <c r="G23" s="13" t="n">
-        <v>2596</v>
+        <v>2882</v>
       </c>
       <c r="H23" s="13" t="n">
-        <v>129792</v>
+        <v>144117</v>
       </c>
       <c r="I23" s="13" t="n">
-        <v>16667</v>
+        <v>19120</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>8.73</v>
+        <v>8.48</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B24" s="12" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="C24" s="12" t="n">
-        <v>90000</v>
+        <v>114720</v>
       </c>
       <c r="D24" s="13" t="n">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="E24" s="13" t="n">
-        <v>584064</v>
+        <v>720584</v>
       </c>
       <c r="F24" s="13" t="n">
-        <v>33607</v>
+        <v>44551</v>
       </c>
       <c r="G24" s="13" t="n">
-        <v>2920</v>
+        <v>3603</v>
       </c>
       <c r="H24" s="13" t="n">
-        <v>146016</v>
+        <v>180146</v>
       </c>
       <c r="I24" s="13" t="n">
-        <v>18750</v>
+        <v>23900</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>8.73</v>
+        <v>8.48</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="12" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="B25" s="12" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="C25" s="12" t="n">
-        <v>90000</v>
+        <v>91776</v>
       </c>
       <c r="D25" s="13" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="E25" s="13" t="n">
-        <v>584064</v>
+        <v>576467</v>
       </c>
       <c r="F25" s="13" t="n">
-        <v>33607</v>
+        <v>35641</v>
       </c>
       <c r="G25" s="13" t="n">
-        <v>2920</v>
+        <v>2882</v>
       </c>
       <c r="H25" s="13" t="n">
-        <v>146016</v>
+        <v>144117</v>
       </c>
       <c r="I25" s="13" t="n">
-        <v>18750</v>
+        <v>19120</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>8.73</v>
+        <v>8.48</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="B26" s="12" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="C26" s="12" t="n">
-        <v>90000</v>
+        <v>114720</v>
       </c>
       <c r="D26" s="13" t="n">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="E26" s="13" t="n">
-        <v>543569</v>
+        <v>720584</v>
       </c>
       <c r="F26" s="13" t="n">
-        <v>33607</v>
+        <v>44551</v>
       </c>
       <c r="G26" s="13" t="n">
-        <v>2718</v>
+        <v>3603</v>
       </c>
       <c r="H26" s="13" t="n">
-        <v>135892</v>
+        <v>180146</v>
       </c>
       <c r="I26" s="13" t="n">
-        <v>18750</v>
+        <v>23900</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>8.16</v>
+        <v>8.48</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="12" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="B27" s="12" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="C27" s="12" t="n">
-        <v>100000</v>
+        <v>114720</v>
       </c>
       <c r="D27" s="13" t="n">
-        <v>0.74</v>
+        <v>0.85</v>
       </c>
       <c r="E27" s="13" t="n">
-        <v>603965</v>
+        <v>720584</v>
       </c>
       <c r="F27" s="13" t="n">
-        <v>37341</v>
+        <v>44551</v>
       </c>
       <c r="G27" s="13" t="n">
-        <v>3020</v>
+        <v>3603</v>
       </c>
       <c r="H27" s="13" t="n">
-        <v>150991</v>
+        <v>180146</v>
       </c>
       <c r="I27" s="13" t="n">
-        <v>20833</v>
+        <v>23900</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>8.16</v>
+        <v>8.48</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B28" s="12" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="C28" s="12" t="n">
-        <v>90000</v>
+        <v>137664</v>
       </c>
       <c r="D28" s="13" t="n">
-        <v>0.67</v>
+        <v>1.02</v>
       </c>
       <c r="E28" s="13" t="n">
-        <v>543569</v>
+        <v>864701</v>
       </c>
       <c r="F28" s="13" t="n">
-        <v>33607</v>
+        <v>53461</v>
       </c>
       <c r="G28" s="13" t="n">
-        <v>2718</v>
+        <v>4324</v>
       </c>
       <c r="H28" s="13" t="n">
-        <v>135892</v>
+        <v>216175</v>
       </c>
       <c r="I28" s="13" t="n">
-        <v>18750</v>
+        <v>28680</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>8.16</v>
+        <v>8.48</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="12" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="B29" s="12" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="C29" s="12" t="n">
-        <v>100000</v>
+        <v>137664</v>
       </c>
       <c r="D29" s="13" t="n">
-        <v>0.74</v>
+        <v>1.02</v>
       </c>
       <c r="E29" s="13" t="n">
-        <v>603965</v>
+        <v>864701</v>
       </c>
       <c r="F29" s="13" t="n">
-        <v>37341</v>
+        <v>53461</v>
       </c>
       <c r="G29" s="13" t="n">
-        <v>3020</v>
+        <v>4324</v>
       </c>
       <c r="H29" s="13" t="n">
-        <v>150991</v>
+        <v>216175</v>
       </c>
       <c r="I29" s="13" t="n">
-        <v>20833</v>
+        <v>28680</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>8.16</v>
+        <v>8.48</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="12" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B30" s="12" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="C30" s="12" t="n">
-        <v>100000</v>
+        <v>137664</v>
       </c>
       <c r="D30" s="13" t="n">
-        <v>0.74</v>
+        <v>1.02</v>
       </c>
       <c r="E30" s="13" t="n">
-        <v>628124</v>
+        <v>864701</v>
       </c>
       <c r="F30" s="13" t="n">
-        <v>38835</v>
+        <v>53461</v>
       </c>
       <c r="G30" s="13" t="n">
-        <v>3141</v>
+        <v>4324</v>
       </c>
       <c r="H30" s="13" t="n">
-        <v>157031</v>
+        <v>216175</v>
       </c>
       <c r="I30" s="13" t="n">
-        <v>20833</v>
+        <v>28680</v>
       </c>
       <c r="J30" s="6" t="n">
         <v>8.48</v>
@@ -10208,383 +10208,383 @@
     </row>
     <row r="31">
       <c r="A31" s="12" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B31" s="12" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C31" s="12" t="n">
-        <v>100000</v>
+        <v>160608</v>
       </c>
       <c r="D31" s="13" t="n">
-        <v>0.74</v>
+        <v>1.2</v>
       </c>
       <c r="E31" s="13" t="n">
-        <v>628124</v>
+        <v>948115</v>
       </c>
       <c r="F31" s="13" t="n">
-        <v>38835</v>
+        <v>62371</v>
       </c>
       <c r="G31" s="13" t="n">
-        <v>3141</v>
+        <v>4741</v>
       </c>
       <c r="H31" s="13" t="n">
-        <v>157031</v>
+        <v>237029</v>
       </c>
       <c r="I31" s="13" t="n">
-        <v>20833</v>
+        <v>33460</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>8.48</v>
+        <v>8.01</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="12" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="B32" s="12" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="C32" s="12" t="n">
-        <v>100000</v>
+        <v>137664</v>
       </c>
       <c r="D32" s="13" t="n">
-        <v>0.74</v>
+        <v>1.02</v>
       </c>
       <c r="E32" s="13" t="n">
-        <v>628124</v>
+        <v>812670</v>
       </c>
       <c r="F32" s="13" t="n">
-        <v>38835</v>
+        <v>53461</v>
       </c>
       <c r="G32" s="13" t="n">
-        <v>3141</v>
+        <v>4063</v>
       </c>
       <c r="H32" s="13" t="n">
-        <v>157031</v>
+        <v>203168</v>
       </c>
       <c r="I32" s="13" t="n">
-        <v>20833</v>
+        <v>28680</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>8.48</v>
+        <v>8.01</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="12" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B33" s="12" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="C33" s="12" t="n">
-        <v>110000</v>
+        <v>160608</v>
       </c>
       <c r="D33" s="13" t="n">
-        <v>0.82</v>
+        <v>1.2</v>
       </c>
       <c r="E33" s="13" t="n">
-        <v>690936</v>
+        <v>948115</v>
       </c>
       <c r="F33" s="13" t="n">
-        <v>42718</v>
+        <v>62371</v>
       </c>
       <c r="G33" s="13" t="n">
-        <v>3455</v>
+        <v>4741</v>
       </c>
       <c r="H33" s="13" t="n">
-        <v>172734</v>
+        <v>237029</v>
       </c>
       <c r="I33" s="13" t="n">
-        <v>22917</v>
+        <v>33460</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>8.48</v>
+        <v>8.01</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="12" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="B34" s="12" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="C34" s="12" t="n">
-        <v>100000</v>
+        <v>160608</v>
       </c>
       <c r="D34" s="13" t="n">
-        <v>0.74</v>
+        <v>1.2</v>
       </c>
       <c r="E34" s="13" t="n">
-        <v>628124</v>
+        <v>948115</v>
       </c>
       <c r="F34" s="13" t="n">
-        <v>38835</v>
+        <v>62371</v>
       </c>
       <c r="G34" s="13" t="n">
-        <v>3141</v>
+        <v>4741</v>
       </c>
       <c r="H34" s="13" t="n">
-        <v>157031</v>
+        <v>237029</v>
       </c>
       <c r="I34" s="13" t="n">
-        <v>20833</v>
+        <v>33460</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>8.48</v>
+        <v>8.01</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="12" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B35" s="12" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C35" s="12" t="n">
-        <v>150000</v>
+        <v>137664</v>
       </c>
       <c r="D35" s="13" t="n">
-        <v>1.12</v>
+        <v>1.02</v>
       </c>
       <c r="E35" s="13" t="n">
-        <v>942186</v>
+        <v>845177</v>
       </c>
       <c r="F35" s="13" t="n">
-        <v>58252</v>
+        <v>55600</v>
       </c>
       <c r="G35" s="13" t="n">
-        <v>4711</v>
+        <v>4226</v>
       </c>
       <c r="H35" s="13" t="n">
-        <v>235547</v>
+        <v>211294</v>
       </c>
       <c r="I35" s="13" t="n">
-        <v>31250</v>
+        <v>28680</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>8.48</v>
+        <v>8.32</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="12" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="B36" s="12" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="C36" s="12" t="n">
-        <v>140000</v>
+        <v>160608</v>
       </c>
       <c r="D36" s="13" t="n">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="E36" s="13" t="n">
-        <v>879374</v>
+        <v>986040</v>
       </c>
       <c r="F36" s="13" t="n">
-        <v>54368</v>
+        <v>64866</v>
       </c>
       <c r="G36" s="13" t="n">
-        <v>4397</v>
+        <v>4930</v>
       </c>
       <c r="H36" s="13" t="n">
-        <v>219843</v>
+        <v>246510</v>
       </c>
       <c r="I36" s="13" t="n">
-        <v>29167</v>
+        <v>33460</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>8.48</v>
+        <v>8.32</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="12" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B37" s="12" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="C37" s="12" t="n">
-        <v>150000</v>
+        <v>160608</v>
       </c>
       <c r="D37" s="13" t="n">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="E37" s="13" t="n">
-        <v>942186</v>
+        <v>986040</v>
       </c>
       <c r="F37" s="13" t="n">
-        <v>58252</v>
+        <v>64866</v>
       </c>
       <c r="G37" s="13" t="n">
-        <v>4711</v>
+        <v>4930</v>
       </c>
       <c r="H37" s="13" t="n">
-        <v>235547</v>
+        <v>246510</v>
       </c>
       <c r="I37" s="13" t="n">
-        <v>31250</v>
+        <v>33460</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>8.48</v>
+        <v>8.32</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="12" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B38" s="12" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C38" s="12" t="n">
-        <v>140000</v>
+        <v>160608</v>
       </c>
       <c r="D38" s="13" t="n">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="E38" s="13" t="n">
-        <v>826460</v>
+        <v>986040</v>
       </c>
       <c r="F38" s="13" t="n">
-        <v>54368</v>
+        <v>64866</v>
       </c>
       <c r="G38" s="13" t="n">
-        <v>4132</v>
+        <v>4930</v>
       </c>
       <c r="H38" s="13" t="n">
-        <v>206615</v>
+        <v>246510</v>
       </c>
       <c r="I38" s="13" t="n">
-        <v>29167</v>
+        <v>33460</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>8.01</v>
+        <v>8.32</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="12" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B39" s="12" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="C39" s="12" t="n">
-        <v>150000</v>
+        <v>160608</v>
       </c>
       <c r="D39" s="13" t="n">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="E39" s="13" t="n">
-        <v>885493</v>
+        <v>986040</v>
       </c>
       <c r="F39" s="13" t="n">
-        <v>58252</v>
+        <v>64866</v>
       </c>
       <c r="G39" s="13" t="n">
-        <v>4427</v>
+        <v>4930</v>
       </c>
       <c r="H39" s="13" t="n">
-        <v>221373</v>
+        <v>246510</v>
       </c>
       <c r="I39" s="13" t="n">
-        <v>31250</v>
+        <v>33460</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>8.01</v>
+        <v>8.32</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="12" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B40" s="12" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="C40" s="12" t="n">
-        <v>160000</v>
+        <v>160608</v>
       </c>
       <c r="D40" s="13" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="E40" s="13" t="n">
-        <v>944526</v>
+        <v>986040</v>
       </c>
       <c r="F40" s="13" t="n">
-        <v>62135</v>
+        <v>64866</v>
       </c>
       <c r="G40" s="13" t="n">
-        <v>4723</v>
+        <v>4930</v>
       </c>
       <c r="H40" s="13" t="n">
-        <v>236131</v>
+        <v>246510</v>
       </c>
       <c r="I40" s="13" t="n">
-        <v>33333</v>
+        <v>33460</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>8.01</v>
+        <v>8.32</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="12" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B41" s="12" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="C41" s="12" t="n">
-        <v>150000</v>
+        <v>160608</v>
       </c>
       <c r="D41" s="13" t="n">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="E41" s="13" t="n">
-        <v>885493</v>
+        <v>986040</v>
       </c>
       <c r="F41" s="13" t="n">
-        <v>58252</v>
+        <v>64866</v>
       </c>
       <c r="G41" s="13" t="n">
-        <v>4427</v>
+        <v>4930</v>
       </c>
       <c r="H41" s="13" t="n">
-        <v>221373</v>
+        <v>246510</v>
       </c>
       <c r="I41" s="13" t="n">
-        <v>31250</v>
+        <v>33460</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>8.01</v>
+        <v>8.32</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="12" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B42" s="12" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="C42" s="12" t="n">
-        <v>150000</v>
+        <v>160608</v>
       </c>
       <c r="D42" s="13" t="n">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="E42" s="13" t="n">
-        <v>920913</v>
+        <v>986040</v>
       </c>
       <c r="F42" s="13" t="n">
-        <v>60582</v>
+        <v>64866</v>
       </c>
       <c r="G42" s="13" t="n">
-        <v>4605</v>
+        <v>4930</v>
       </c>
       <c r="H42" s="13" t="n">
-        <v>230228</v>
+        <v>246510</v>
       </c>
       <c r="I42" s="13" t="n">
-        <v>31250</v>
+        <v>33460</v>
       </c>
       <c r="J42" s="6" t="n">
         <v>8.32</v>
@@ -10592,31 +10592,31 @@
     </row>
     <row r="43">
       <c r="A43" s="12" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B43" s="12" t="n">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="C43" s="12" t="n">
-        <v>160000</v>
+        <v>160608</v>
       </c>
       <c r="D43" s="13" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="E43" s="13" t="n">
-        <v>982307</v>
+        <v>986040</v>
       </c>
       <c r="F43" s="13" t="n">
-        <v>64621</v>
+        <v>64866</v>
       </c>
       <c r="G43" s="13" t="n">
-        <v>4912</v>
+        <v>4930</v>
       </c>
       <c r="H43" s="13" t="n">
-        <v>245577</v>
+        <v>246510</v>
       </c>
       <c r="I43" s="13" t="n">
-        <v>33333</v>
+        <v>33460</v>
       </c>
       <c r="J43" s="6" t="n">
         <v>8.32</v>
@@ -10624,31 +10624,31 @@
     </row>
     <row r="44">
       <c r="A44" s="12" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B44" s="12" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="C44" s="12" t="n">
-        <v>160000</v>
+        <v>160608</v>
       </c>
       <c r="D44" s="13" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="E44" s="13" t="n">
-        <v>982307</v>
+        <v>986040</v>
       </c>
       <c r="F44" s="13" t="n">
-        <v>64621</v>
+        <v>64866</v>
       </c>
       <c r="G44" s="13" t="n">
-        <v>4912</v>
+        <v>4930</v>
       </c>
       <c r="H44" s="13" t="n">
-        <v>245577</v>
+        <v>246510</v>
       </c>
       <c r="I44" s="13" t="n">
-        <v>33333</v>
+        <v>33460</v>
       </c>
       <c r="J44" s="6" t="n">
         <v>8.32</v>
@@ -10656,31 +10656,31 @@
     </row>
     <row r="45">
       <c r="A45" s="12" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="B45" s="12" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="C45" s="12" t="n">
-        <v>160000</v>
+        <v>160608</v>
       </c>
       <c r="D45" s="13" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="E45" s="13" t="n">
-        <v>982307</v>
+        <v>986040</v>
       </c>
       <c r="F45" s="13" t="n">
-        <v>64621</v>
+        <v>64866</v>
       </c>
       <c r="G45" s="13" t="n">
-        <v>4912</v>
+        <v>4930</v>
       </c>
       <c r="H45" s="13" t="n">
-        <v>245577</v>
+        <v>246510</v>
       </c>
       <c r="I45" s="13" t="n">
-        <v>33333</v>
+        <v>33460</v>
       </c>
       <c r="J45" s="6" t="n">
         <v>8.32</v>
@@ -10688,257 +10688,33 @@
     </row>
     <row r="46">
       <c r="A46" s="12" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="B46" s="12" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="C46" s="12" t="n">
-        <v>160000</v>
+        <v>160608</v>
       </c>
       <c r="D46" s="13" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="E46" s="13" t="n">
-        <v>982307</v>
+        <v>986040</v>
       </c>
       <c r="F46" s="13" t="n">
-        <v>64621</v>
+        <v>64866</v>
       </c>
       <c r="G46" s="13" t="n">
-        <v>4912</v>
+        <v>4930</v>
       </c>
       <c r="H46" s="13" t="n">
-        <v>245577</v>
+        <v>246510</v>
       </c>
       <c r="I46" s="13" t="n">
-        <v>33333</v>
+        <v>33460</v>
       </c>
       <c r="J46" s="6" t="n">
-        <v>8.32</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="12" t="n">
-        <v>54</v>
-      </c>
-      <c r="B47" s="12" t="n">
-        <v>58</v>
-      </c>
-      <c r="C47" s="12" t="n">
-        <v>160000</v>
-      </c>
-      <c r="D47" s="13" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="E47" s="13" t="n">
-        <v>982307</v>
-      </c>
-      <c r="F47" s="13" t="n">
-        <v>64621</v>
-      </c>
-      <c r="G47" s="13" t="n">
-        <v>4912</v>
-      </c>
-      <c r="H47" s="13" t="n">
-        <v>245577</v>
-      </c>
-      <c r="I47" s="13" t="n">
-        <v>33333</v>
-      </c>
-      <c r="J47" s="6" t="n">
-        <v>8.32</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="12" t="n">
-        <v>55</v>
-      </c>
-      <c r="B48" s="12" t="n">
-        <v>59</v>
-      </c>
-      <c r="C48" s="12" t="n">
-        <v>160000</v>
-      </c>
-      <c r="D48" s="13" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="E48" s="13" t="n">
-        <v>982307</v>
-      </c>
-      <c r="F48" s="13" t="n">
-        <v>64621</v>
-      </c>
-      <c r="G48" s="13" t="n">
-        <v>4912</v>
-      </c>
-      <c r="H48" s="13" t="n">
-        <v>245577</v>
-      </c>
-      <c r="I48" s="13" t="n">
-        <v>33333</v>
-      </c>
-      <c r="J48" s="6" t="n">
-        <v>8.32</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="12" t="n">
-        <v>56</v>
-      </c>
-      <c r="B49" s="12" t="n">
-        <v>60</v>
-      </c>
-      <c r="C49" s="12" t="n">
-        <v>160000</v>
-      </c>
-      <c r="D49" s="13" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="E49" s="13" t="n">
-        <v>982307</v>
-      </c>
-      <c r="F49" s="13" t="n">
-        <v>64621</v>
-      </c>
-      <c r="G49" s="13" t="n">
-        <v>4912</v>
-      </c>
-      <c r="H49" s="13" t="n">
-        <v>245577</v>
-      </c>
-      <c r="I49" s="13" t="n">
-        <v>33333</v>
-      </c>
-      <c r="J49" s="6" t="n">
-        <v>8.32</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="12" t="n">
-        <v>57</v>
-      </c>
-      <c r="B50" s="12" t="n">
-        <v>61</v>
-      </c>
-      <c r="C50" s="12" t="n">
-        <v>160000</v>
-      </c>
-      <c r="D50" s="13" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="E50" s="13" t="n">
-        <v>982307</v>
-      </c>
-      <c r="F50" s="13" t="n">
-        <v>64621</v>
-      </c>
-      <c r="G50" s="13" t="n">
-        <v>4912</v>
-      </c>
-      <c r="H50" s="13" t="n">
-        <v>245577</v>
-      </c>
-      <c r="I50" s="13" t="n">
-        <v>33333</v>
-      </c>
-      <c r="J50" s="6" t="n">
-        <v>8.32</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="12" t="n">
-        <v>58</v>
-      </c>
-      <c r="B51" s="12" t="n">
-        <v>62</v>
-      </c>
-      <c r="C51" s="12" t="n">
-        <v>160000</v>
-      </c>
-      <c r="D51" s="13" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="E51" s="13" t="n">
-        <v>982307</v>
-      </c>
-      <c r="F51" s="13" t="n">
-        <v>64621</v>
-      </c>
-      <c r="G51" s="13" t="n">
-        <v>4912</v>
-      </c>
-      <c r="H51" s="13" t="n">
-        <v>245577</v>
-      </c>
-      <c r="I51" s="13" t="n">
-        <v>33333</v>
-      </c>
-      <c r="J51" s="6" t="n">
-        <v>8.32</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="12" t="n">
-        <v>59</v>
-      </c>
-      <c r="B52" s="12" t="n">
-        <v>63</v>
-      </c>
-      <c r="C52" s="12" t="n">
-        <v>160000</v>
-      </c>
-      <c r="D52" s="13" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="E52" s="13" t="n">
-        <v>982307</v>
-      </c>
-      <c r="F52" s="13" t="n">
-        <v>64621</v>
-      </c>
-      <c r="G52" s="13" t="n">
-        <v>4912</v>
-      </c>
-      <c r="H52" s="13" t="n">
-        <v>245577</v>
-      </c>
-      <c r="I52" s="13" t="n">
-        <v>33333</v>
-      </c>
-      <c r="J52" s="6" t="n">
-        <v>8.32</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="12" t="n">
-        <v>60</v>
-      </c>
-      <c r="B53" s="12" t="n">
-        <v>64</v>
-      </c>
-      <c r="C53" s="12" t="n">
-        <v>160000</v>
-      </c>
-      <c r="D53" s="13" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="E53" s="13" t="n">
-        <v>982307</v>
-      </c>
-      <c r="F53" s="13" t="n">
-        <v>64621</v>
-      </c>
-      <c r="G53" s="13" t="n">
-        <v>4912</v>
-      </c>
-      <c r="H53" s="13" t="n">
-        <v>245577</v>
-      </c>
-      <c r="I53" s="13" t="n">
-        <v>33333</v>
-      </c>
-      <c r="J53" s="6" t="n">
         <v>8.32</v>
       </c>
     </row>

--- a/finance/outputs/mulligan-mints-5yr-model.xlsx
+++ b/finance/outputs/mulligan-mints-5yr-model.xlsx
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="B33" s="6" t="n">
-        <v>68832</v>
+        <v>22944</v>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
@@ -1665,19 +1665,19 @@
         </is>
       </c>
       <c r="B14" s="13" t="n">
-        <v>247471</v>
+        <v>252319</v>
       </c>
       <c r="C14" s="13" t="n">
-        <v>1720121</v>
+        <v>1765211</v>
       </c>
       <c r="D14" s="13" t="n">
-        <v>4954704</v>
+        <v>4989372</v>
       </c>
       <c r="E14" s="13" t="n">
-        <v>9791147</v>
+        <v>9796628</v>
       </c>
       <c r="F14" s="13" t="n">
-        <v>15075852</v>
+        <v>15076083</v>
       </c>
     </row>
     <row r="15">
@@ -1687,19 +1687,19 @@
         </is>
       </c>
       <c r="B15" s="14" t="n">
-        <v>372939</v>
+        <v>368091</v>
       </c>
       <c r="C15" s="14" t="n">
-        <v>2990185</v>
+        <v>2945095</v>
       </c>
       <c r="D15" s="14" t="n">
-        <v>8326436</v>
+        <v>8291767</v>
       </c>
       <c r="E15" s="14" t="n">
-        <v>16989470</v>
+        <v>16983989</v>
       </c>
       <c r="F15" s="14" t="n">
-        <v>28557676</v>
+        <v>28557445</v>
       </c>
     </row>
     <row r="17">
@@ -1841,7 +1841,7 @@
         </is>
       </c>
       <c r="B23" s="13" t="n">
-        <v>408000</v>
+        <v>388000</v>
       </c>
       <c r="C23" s="13" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         </is>
       </c>
       <c r="B24" s="14" t="n">
-        <v>1849694</v>
+        <v>1829694</v>
       </c>
       <c r="C24" s="14" t="n">
         <v>3371212</v>
@@ -1885,19 +1885,19 @@
         </is>
       </c>
       <c r="B26" s="14" t="n">
-        <v>-1476755</v>
+        <v>-1461603</v>
       </c>
       <c r="C26" s="14" t="n">
-        <v>-381027</v>
+        <v>-426117</v>
       </c>
       <c r="D26" s="14" t="n">
-        <v>564854</v>
+        <v>530186</v>
       </c>
       <c r="E26" s="14" t="n">
-        <v>5417805</v>
+        <v>5412324</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>12591842</v>
+        <v>12591610</v>
       </c>
     </row>
     <row r="27">
@@ -1910,16 +1910,16 @@
         <v>0</v>
       </c>
       <c r="C27" s="13" t="n">
-        <v>3450</v>
+        <v>2778</v>
       </c>
       <c r="D27" s="13" t="n">
-        <v>66689</v>
+        <v>65290</v>
       </c>
       <c r="E27" s="13" t="n">
-        <v>1043578</v>
+        <v>1026725</v>
       </c>
       <c r="F27" s="13" t="n">
-        <v>3399797</v>
+        <v>3399735</v>
       </c>
     </row>
     <row r="28">
@@ -1929,19 +1929,19 @@
         </is>
       </c>
       <c r="B28" s="14" t="n">
-        <v>-1476755</v>
+        <v>-1461603</v>
       </c>
       <c r="C28" s="14" t="n">
-        <v>-384477</v>
+        <v>-428895</v>
       </c>
       <c r="D28" s="14" t="n">
-        <v>498165</v>
+        <v>464896</v>
       </c>
       <c r="E28" s="14" t="n">
-        <v>4374228</v>
+        <v>4385599</v>
       </c>
       <c r="F28" s="14" t="n">
-        <v>9192044</v>
+        <v>9191875</v>
       </c>
     </row>
     <row r="29">
@@ -1951,19 +1951,19 @@
         </is>
       </c>
       <c r="B29" s="15" t="n">
-        <v>0.6011167805283284</v>
+        <v>0.593303070108392</v>
       </c>
       <c r="C29" s="15" t="n">
-        <v>0.6348175085046985</v>
+        <v>0.6252449339150132</v>
       </c>
       <c r="D29" s="15" t="n">
-        <v>0.6269368489213979</v>
+        <v>0.6243264960928632</v>
       </c>
       <c r="E29" s="15" t="n">
-        <v>0.6343942855449126</v>
+        <v>0.6341896151101259</v>
       </c>
       <c r="F29" s="15" t="n">
-        <v>0.6544892822205781</v>
+        <v>0.6544839772955371</v>
       </c>
     </row>
     <row r="30">
@@ -1973,19 +1973,19 @@
         </is>
       </c>
       <c r="B30" s="15" t="n">
-        <v>-2.380289547545043</v>
+        <v>-2.355866511297452</v>
       </c>
       <c r="C30" s="15" t="n">
-        <v>-0.08089226072014925</v>
+        <v>-0.09046483530983451</v>
       </c>
       <c r="D30" s="15" t="n">
-        <v>0.04253055897376109</v>
+        <v>0.03992020614522623</v>
       </c>
       <c r="E30" s="15" t="n">
-        <v>0.2023032356138051</v>
+        <v>0.2020985651790186</v>
       </c>
       <c r="F30" s="15" t="n">
-        <v>0.288581789629006</v>
+        <v>0.2885764847039652</v>
       </c>
     </row>
     <row r="33">
@@ -2211,19 +2211,19 @@
         </is>
       </c>
       <c r="B44" s="13" t="n">
-        <v>119772</v>
+        <v>121954</v>
       </c>
       <c r="C44" s="13" t="n">
-        <v>910205</v>
+        <v>925382</v>
       </c>
       <c r="D44" s="13" t="n">
-        <v>2590869</v>
+        <v>2657361</v>
       </c>
       <c r="E44" s="13" t="n">
-        <v>5075026</v>
+        <v>5185833</v>
       </c>
       <c r="F44" s="13" t="n">
-        <v>7749745</v>
+        <v>7759367</v>
       </c>
     </row>
     <row r="45">
@@ -2233,19 +2233,19 @@
         </is>
       </c>
       <c r="B45" s="14" t="n">
-        <v>142661</v>
+        <v>140480</v>
       </c>
       <c r="C45" s="14" t="n">
-        <v>1082255</v>
+        <v>1067077</v>
       </c>
       <c r="D45" s="14" t="n">
-        <v>3027053</v>
+        <v>2960561</v>
       </c>
       <c r="E45" s="14" t="n">
-        <v>6083975</v>
+        <v>5973168</v>
       </c>
       <c r="F45" s="14" t="n">
-        <v>9945837</v>
+        <v>9936216</v>
       </c>
     </row>
     <row r="47">
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="B53" s="13" t="n">
-        <v>408000</v>
+        <v>388000</v>
       </c>
       <c r="C53" s="13" t="n">
         <v>0</v>
@@ -2409,7 +2409,7 @@
         </is>
       </c>
       <c r="B54" s="14" t="n">
-        <v>1145103</v>
+        <v>1125103</v>
       </c>
       <c r="C54" s="14" t="n">
         <v>2254066</v>
@@ -2431,19 +2431,19 @@
         </is>
       </c>
       <c r="B56" s="14" t="n">
-        <v>-1002442</v>
+        <v>-984623</v>
       </c>
       <c r="C56" s="14" t="n">
-        <v>-1171811</v>
+        <v>-1186989</v>
       </c>
       <c r="D56" s="14" t="n">
-        <v>-1949890</v>
+        <v>-2016383</v>
       </c>
       <c r="E56" s="14" t="n">
-        <v>-1436365</v>
+        <v>-1547172</v>
       </c>
       <c r="F56" s="14" t="n">
-        <v>-179822</v>
+        <v>-189443</v>
       </c>
     </row>
     <row r="57">
@@ -2465,7 +2465,7 @@
         <v>0</v>
       </c>
       <c r="F57" s="13" t="n">
-        <v>3801</v>
+        <v>3676</v>
       </c>
     </row>
     <row r="58">
@@ -2475,19 +2475,19 @@
         </is>
       </c>
       <c r="B58" s="14" t="n">
-        <v>-1002442</v>
+        <v>-984623</v>
       </c>
       <c r="C58" s="14" t="n">
-        <v>-1171811</v>
+        <v>-1186989</v>
       </c>
       <c r="D58" s="14" t="n">
-        <v>-1949890</v>
+        <v>-2016383</v>
       </c>
       <c r="E58" s="14" t="n">
-        <v>-1436365</v>
+        <v>-1547172</v>
       </c>
       <c r="F58" s="14" t="n">
-        <v>-183623</v>
+        <v>-193120</v>
       </c>
     </row>
     <row r="59">
@@ -2497,19 +2497,19 @@
         </is>
       </c>
       <c r="B59" s="15" t="n">
-        <v>0.5436086318337477</v>
+        <v>0.5352961739401985</v>
       </c>
       <c r="C59" s="15" t="n">
-        <v>0.5431751999202683</v>
+        <v>0.5355578376499529</v>
       </c>
       <c r="D59" s="15" t="n">
-        <v>0.5388207681016494</v>
+        <v>0.5269850089444209</v>
       </c>
       <c r="E59" s="15" t="n">
-        <v>0.5452078447280476</v>
+        <v>0.5352779821328782</v>
       </c>
       <c r="F59" s="15" t="n">
-        <v>0.5620519832877421</v>
+        <v>0.5615082689949957</v>
       </c>
     </row>
     <row r="60">
@@ -2519,19 +2519,19 @@
         </is>
       </c>
       <c r="B60" s="15" t="n">
-        <v>-3.819794852623244</v>
+        <v>-3.751897507520277</v>
       </c>
       <c r="C60" s="15" t="n">
-        <v>-0.5881230601994599</v>
+        <v>-0.5957404224697753</v>
       </c>
       <c r="D60" s="15" t="n">
-        <v>-0.3470839025339391</v>
+        <v>-0.3589196616911676</v>
       </c>
       <c r="E60" s="15" t="n">
-        <v>-0.1287180580560819</v>
+        <v>-0.1386479206512514</v>
       </c>
       <c r="F60" s="15" t="n">
-        <v>-0.01016196982266782</v>
+        <v>-0.01070568411541408</v>
       </c>
     </row>
     <row r="63">
@@ -2757,19 +2757,19 @@
         </is>
       </c>
       <c r="B74" s="13" t="n">
-        <v>365475</v>
+        <v>372989</v>
       </c>
       <c r="C74" s="13" t="n">
-        <v>2572658</v>
+        <v>2594799</v>
       </c>
       <c r="D74" s="13" t="n">
-        <v>6895442</v>
+        <v>6944339</v>
       </c>
       <c r="E74" s="13" t="n">
-        <v>13626049</v>
+        <v>13628243</v>
       </c>
       <c r="F74" s="13" t="n">
-        <v>21998909</v>
+        <v>21998999</v>
       </c>
     </row>
     <row r="75">
@@ -2779,19 +2779,19 @@
         </is>
       </c>
       <c r="B75" s="14" t="n">
-        <v>625010</v>
+        <v>617496</v>
       </c>
       <c r="C75" s="14" t="n">
-        <v>4947346</v>
+        <v>4925204</v>
       </c>
       <c r="D75" s="14" t="n">
-        <v>14307897</v>
+        <v>14258999</v>
       </c>
       <c r="E75" s="14" t="n">
-        <v>28890606</v>
+        <v>28888412</v>
       </c>
       <c r="F75" s="14" t="n">
-        <v>46588318</v>
+        <v>46588228</v>
       </c>
     </row>
     <row r="77">
@@ -2933,7 +2933,7 @@
         </is>
       </c>
       <c r="B83" s="13" t="n">
-        <v>408000</v>
+        <v>388000</v>
       </c>
       <c r="C83" s="13" t="n">
         <v>0</v>
@@ -2955,7 +2955,7 @@
         </is>
       </c>
       <c r="B84" s="14" t="n">
-        <v>2040549</v>
+        <v>2020549</v>
       </c>
       <c r="C84" s="14" t="n">
         <v>4079252</v>
@@ -2977,19 +2977,19 @@
         </is>
       </c>
       <c r="B86" s="14" t="n">
-        <v>-1415540</v>
+        <v>-1403054</v>
       </c>
       <c r="C86" s="14" t="n">
-        <v>868093</v>
+        <v>845952</v>
       </c>
       <c r="D86" s="14" t="n">
-        <v>4719988</v>
+        <v>4671090</v>
       </c>
       <c r="E86" s="14" t="n">
-        <v>14003323</v>
+        <v>14001129</v>
       </c>
       <c r="F86" s="14" t="n">
-        <v>25700855</v>
+        <v>25700765</v>
       </c>
     </row>
     <row r="87">
@@ -3002,16 +3002,16 @@
         <v>0</v>
       </c>
       <c r="C87" s="13" t="n">
-        <v>52437</v>
+        <v>51359</v>
       </c>
       <c r="D87" s="13" t="n">
-        <v>1074149</v>
+        <v>1059418</v>
       </c>
       <c r="E87" s="13" t="n">
-        <v>3780897</v>
+        <v>3780305</v>
       </c>
       <c r="F87" s="13" t="n">
-        <v>6939231</v>
+        <v>6939207</v>
       </c>
     </row>
     <row r="88">
@@ -3021,19 +3021,19 @@
         </is>
       </c>
       <c r="B88" s="14" t="n">
-        <v>-1415540</v>
+        <v>-1403054</v>
       </c>
       <c r="C88" s="14" t="n">
-        <v>815657</v>
+        <v>794593</v>
       </c>
       <c r="D88" s="14" t="n">
-        <v>3645838</v>
+        <v>3611672</v>
       </c>
       <c r="E88" s="14" t="n">
-        <v>10222426</v>
+        <v>10220824</v>
       </c>
       <c r="F88" s="14" t="n">
-        <v>18761624</v>
+        <v>18761558</v>
       </c>
     </row>
     <row r="89">
@@ -3043,19 +3043,19 @@
         </is>
       </c>
       <c r="B89" s="15" t="n">
-        <v>0.6310142690836957</v>
+        <v>0.6234281424623985</v>
       </c>
       <c r="C89" s="15" t="n">
-        <v>0.6578914137895946</v>
+        <v>0.6549471112262671</v>
       </c>
       <c r="D89" s="15" t="n">
-        <v>0.6747945311402928</v>
+        <v>0.6724884021143732</v>
       </c>
       <c r="E89" s="15" t="n">
-        <v>0.6795126721619584</v>
+        <v>0.6794610631616296</v>
       </c>
       <c r="F89" s="15" t="n">
-        <v>0.6792564755072882</v>
+        <v>0.6792551645258191</v>
       </c>
     </row>
     <row r="90">
@@ -3065,19 +3065,19 @@
         </is>
       </c>
       <c r="B90" s="15" t="n">
-        <v>-1.429138437031417</v>
+        <v>-1.416532426685895</v>
       </c>
       <c r="C90" s="15" t="n">
-        <v>0.1154378981959662</v>
+        <v>0.1124935956326389</v>
       </c>
       <c r="D90" s="15" t="n">
-        <v>0.2226058697396092</v>
+        <v>0.2202997407136895</v>
       </c>
       <c r="E90" s="15" t="n">
-        <v>0.3293608779826894</v>
+        <v>0.3293092689823605</v>
       </c>
       <c r="F90" s="15" t="n">
-        <v>0.3747178006311001</v>
+        <v>0.3747164896496309</v>
       </c>
     </row>
   </sheetData>
@@ -3873,166 +3873,166 @@
         <v>0</v>
       </c>
       <c r="H6" s="13" t="n">
-        <v>14668</v>
+        <v>14955</v>
       </c>
       <c r="I6" s="13" t="n">
-        <v>25299</v>
+        <v>25794</v>
       </c>
       <c r="J6" s="13" t="n">
-        <v>35930</v>
+        <v>36634</v>
       </c>
       <c r="K6" s="13" t="n">
-        <v>46561</v>
+        <v>47473</v>
       </c>
       <c r="L6" s="13" t="n">
-        <v>57192</v>
+        <v>58312</v>
       </c>
       <c r="M6" s="13" t="n">
-        <v>67822</v>
+        <v>69151</v>
       </c>
       <c r="N6" s="13" t="n">
-        <v>88413</v>
+        <v>96489</v>
       </c>
       <c r="O6" s="13" t="n">
-        <v>97056</v>
+        <v>101437</v>
       </c>
       <c r="P6" s="13" t="n">
-        <v>105700</v>
+        <v>108068</v>
       </c>
       <c r="Q6" s="13" t="n">
-        <v>114343</v>
+        <v>116905</v>
       </c>
       <c r="R6" s="13" t="n">
-        <v>122986</v>
+        <v>125397</v>
       </c>
       <c r="S6" s="13" t="n">
-        <v>131083</v>
+        <v>133994</v>
       </c>
       <c r="T6" s="13" t="n">
-        <v>144198</v>
+        <v>147249</v>
       </c>
       <c r="U6" s="13" t="n">
-        <v>157313</v>
+        <v>160529</v>
       </c>
       <c r="V6" s="13" t="n">
-        <v>170158</v>
+        <v>173825</v>
       </c>
       <c r="W6" s="13" t="n">
-        <v>183252</v>
+        <v>187132</v>
       </c>
       <c r="X6" s="13" t="n">
-        <v>196346</v>
+        <v>200447</v>
       </c>
       <c r="Y6" s="13" t="n">
-        <v>209274</v>
+        <v>213738</v>
       </c>
       <c r="Z6" s="13" t="n">
-        <v>264825</v>
+        <v>266576</v>
       </c>
       <c r="AA6" s="13" t="n">
-        <v>273008</v>
+        <v>278402</v>
       </c>
       <c r="AB6" s="13" t="n">
-        <v>290201</v>
+        <v>293568</v>
       </c>
       <c r="AC6" s="13" t="n">
-        <v>301088</v>
+        <v>303272</v>
       </c>
       <c r="AD6" s="13" t="n">
-        <v>318406</v>
+        <v>321842</v>
       </c>
       <c r="AE6" s="13" t="n">
-        <v>335566</v>
+        <v>338088</v>
       </c>
       <c r="AF6" s="13" t="n">
-        <v>485985</v>
+        <v>488661</v>
       </c>
       <c r="AG6" s="13" t="n">
-        <v>503076</v>
+        <v>507511</v>
       </c>
       <c r="AH6" s="13" t="n">
-        <v>520125</v>
+        <v>523487</v>
       </c>
       <c r="AI6" s="13" t="n">
-        <v>537144</v>
+        <v>539548</v>
       </c>
       <c r="AJ6" s="13" t="n">
-        <v>554141</v>
+        <v>555929</v>
       </c>
       <c r="AK6" s="13" t="n">
-        <v>571140</v>
+        <v>572489</v>
       </c>
       <c r="AL6" s="13" t="n">
-        <v>739522</v>
+        <v>740856</v>
       </c>
       <c r="AM6" s="13" t="n">
-        <v>746821</v>
+        <v>747851</v>
       </c>
       <c r="AN6" s="13" t="n">
-        <v>756067</v>
+        <v>756864</v>
       </c>
       <c r="AO6" s="13" t="n">
-        <v>766762</v>
+        <v>767379</v>
       </c>
       <c r="AP6" s="13" t="n">
-        <v>785749</v>
+        <v>786227</v>
       </c>
       <c r="AQ6" s="13" t="n">
-        <v>804545</v>
+        <v>804894</v>
       </c>
       <c r="AR6" s="13" t="n">
-        <v>822243</v>
+        <v>822517</v>
       </c>
       <c r="AS6" s="13" t="n">
-        <v>839874</v>
+        <v>840076</v>
       </c>
       <c r="AT6" s="13" t="n">
-        <v>857086</v>
+        <v>857237</v>
       </c>
       <c r="AU6" s="13" t="n">
-        <v>874128</v>
+        <v>874237</v>
       </c>
       <c r="AV6" s="13" t="n">
-        <v>890885</v>
+        <v>890965</v>
       </c>
       <c r="AW6" s="13" t="n">
-        <v>907466</v>
+        <v>907526</v>
       </c>
       <c r="AX6" s="13" t="n">
-        <v>1196442</v>
+        <v>1196500</v>
       </c>
       <c r="AY6" s="13" t="n">
-        <v>1198264</v>
+        <v>1198310</v>
       </c>
       <c r="AZ6" s="13" t="n">
-        <v>1201390</v>
+        <v>1201424</v>
       </c>
       <c r="BA6" s="13" t="n">
-        <v>1207227</v>
+        <v>1207252</v>
       </c>
       <c r="BB6" s="13" t="n">
-        <v>1226284</v>
+        <v>1226303</v>
       </c>
       <c r="BC6" s="13" t="n">
-        <v>1244759</v>
+        <v>1244774</v>
       </c>
       <c r="BD6" s="13" t="n">
-        <v>1261868</v>
+        <v>1261879</v>
       </c>
       <c r="BE6" s="13" t="n">
-        <v>1277997</v>
+        <v>1278005</v>
       </c>
       <c r="BF6" s="13" t="n">
-        <v>1293416</v>
+        <v>1293422</v>
       </c>
       <c r="BG6" s="13" t="n">
-        <v>1308314</v>
+        <v>1308319</v>
       </c>
       <c r="BH6" s="13" t="n">
-        <v>1322829</v>
+        <v>1322833</v>
       </c>
       <c r="BI6" s="13" t="n">
-        <v>1337059</v>
+        <v>1337062</v>
       </c>
     </row>
     <row r="7">
@@ -4060,166 +4060,166 @@
         <v>0</v>
       </c>
       <c r="H7" s="13" t="n">
-        <v>24875</v>
+        <v>24588</v>
       </c>
       <c r="I7" s="13" t="n">
-        <v>39788</v>
+        <v>39292</v>
       </c>
       <c r="J7" s="13" t="n">
-        <v>54700</v>
+        <v>53996</v>
       </c>
       <c r="K7" s="13" t="n">
-        <v>69613</v>
+        <v>68701</v>
       </c>
       <c r="L7" s="13" t="n">
-        <v>84525</v>
+        <v>83405</v>
       </c>
       <c r="M7" s="13" t="n">
-        <v>99438</v>
+        <v>98109</v>
       </c>
       <c r="N7" s="13" t="n">
-        <v>160294</v>
+        <v>152218</v>
       </c>
       <c r="O7" s="13" t="n">
-        <v>174432</v>
+        <v>170051</v>
       </c>
       <c r="P7" s="13" t="n">
-        <v>188570</v>
+        <v>186201</v>
       </c>
       <c r="Q7" s="13" t="n">
-        <v>202708</v>
+        <v>200145</v>
       </c>
       <c r="R7" s="13" t="n">
-        <v>216846</v>
+        <v>214434</v>
       </c>
       <c r="S7" s="13" t="n">
-        <v>231529</v>
+        <v>228619</v>
       </c>
       <c r="T7" s="13" t="n">
-        <v>251780</v>
+        <v>248729</v>
       </c>
       <c r="U7" s="13" t="n">
-        <v>272031</v>
+        <v>268815</v>
       </c>
       <c r="V7" s="13" t="n">
-        <v>292551</v>
+        <v>288884</v>
       </c>
       <c r="W7" s="13" t="n">
-        <v>312822</v>
+        <v>308942</v>
       </c>
       <c r="X7" s="13" t="n">
-        <v>333093</v>
+        <v>328992</v>
       </c>
       <c r="Y7" s="13" t="n">
-        <v>353530</v>
+        <v>349066</v>
       </c>
       <c r="Z7" s="13" t="n">
-        <v>465005</v>
+        <v>463253</v>
       </c>
       <c r="AA7" s="13" t="n">
-        <v>502052</v>
+        <v>496658</v>
       </c>
       <c r="AB7" s="13" t="n">
-        <v>530089</v>
+        <v>526722</v>
       </c>
       <c r="AC7" s="13" t="n">
-        <v>564432</v>
+        <v>562248</v>
       </c>
       <c r="AD7" s="13" t="n">
-        <v>592345</v>
+        <v>588909</v>
       </c>
       <c r="AE7" s="13" t="n">
-        <v>620415</v>
+        <v>617893</v>
       </c>
       <c r="AF7" s="13" t="n">
-        <v>771558</v>
+        <v>768882</v>
       </c>
       <c r="AG7" s="13" t="n">
-        <v>799697</v>
+        <v>795262</v>
       </c>
       <c r="AH7" s="13" t="n">
-        <v>827878</v>
+        <v>824516</v>
       </c>
       <c r="AI7" s="13" t="n">
-        <v>856089</v>
+        <v>853685</v>
       </c>
       <c r="AJ7" s="13" t="n">
-        <v>884322</v>
+        <v>882535</v>
       </c>
       <c r="AK7" s="13" t="n">
-        <v>912554</v>
+        <v>911205</v>
       </c>
       <c r="AL7" s="13" t="n">
-        <v>1247447</v>
+        <v>1246113</v>
       </c>
       <c r="AM7" s="13" t="n">
-        <v>1284648</v>
+        <v>1283618</v>
       </c>
       <c r="AN7" s="13" t="n">
-        <v>1319902</v>
+        <v>1319104</v>
       </c>
       <c r="AO7" s="13" t="n">
-        <v>1353707</v>
+        <v>1353089</v>
       </c>
       <c r="AP7" s="13" t="n">
-        <v>1379220</v>
+        <v>1378741</v>
       </c>
       <c r="AQ7" s="13" t="n">
-        <v>1404923</v>
+        <v>1404575</v>
       </c>
       <c r="AR7" s="13" t="n">
-        <v>1431725</v>
+        <v>1431451</v>
       </c>
       <c r="AS7" s="13" t="n">
-        <v>1458594</v>
+        <v>1458392</v>
       </c>
       <c r="AT7" s="13" t="n">
-        <v>1485881</v>
+        <v>1485731</v>
       </c>
       <c r="AU7" s="13" t="n">
-        <v>1513339</v>
+        <v>1513231</v>
       </c>
       <c r="AV7" s="13" t="n">
-        <v>1541082</v>
+        <v>1541002</v>
       </c>
       <c r="AW7" s="13" t="n">
-        <v>1569001</v>
+        <v>1568941</v>
       </c>
       <c r="AX7" s="13" t="n">
-        <v>2227139</v>
+        <v>2227080</v>
       </c>
       <c r="AY7" s="13" t="n">
-        <v>2263961</v>
+        <v>2263916</v>
       </c>
       <c r="AZ7" s="13" t="n">
-        <v>2299480</v>
+        <v>2299447</v>
       </c>
       <c r="BA7" s="13" t="n">
-        <v>2332288</v>
+        <v>2332263</v>
       </c>
       <c r="BB7" s="13" t="n">
-        <v>2351876</v>
+        <v>2351857</v>
       </c>
       <c r="BC7" s="13" t="n">
-        <v>2372045</v>
+        <v>2372031</v>
       </c>
       <c r="BD7" s="13" t="n">
-        <v>2393581</v>
+        <v>2393571</v>
       </c>
       <c r="BE7" s="13" t="n">
-        <v>2416097</v>
+        <v>2416089</v>
       </c>
       <c r="BF7" s="13" t="n">
-        <v>2439324</v>
+        <v>2439318</v>
       </c>
       <c r="BG7" s="13" t="n">
-        <v>2463070</v>
+        <v>2463065</v>
       </c>
       <c r="BH7" s="13" t="n">
-        <v>2487200</v>
+        <v>2487196</v>
       </c>
       <c r="BI7" s="13" t="n">
-        <v>2511615</v>
+        <v>2511612</v>
       </c>
     </row>
     <row r="8">
@@ -5354,7 +5354,7 @@
         <v>63000</v>
       </c>
       <c r="C14" s="13" t="n">
-        <v>85000</v>
+        <v>65000</v>
       </c>
       <c r="D14" s="13" t="n">
         <v>32000</v>
@@ -5541,7 +5541,7 @@
         <v>63000</v>
       </c>
       <c r="C15" s="13" t="n">
-        <v>85000</v>
+        <v>65000</v>
       </c>
       <c r="D15" s="13" t="n">
         <v>32000</v>
@@ -5728,7 +5728,7 @@
         <v>-63000</v>
       </c>
       <c r="C16" s="14" t="n">
-        <v>-85000</v>
+        <v>-65000</v>
       </c>
       <c r="D16" s="14" t="n">
         <v>-32000</v>
@@ -5743,166 +5743,166 @@
         <v>-157500</v>
       </c>
       <c r="H16" s="14" t="n">
-        <v>-223686</v>
+        <v>-223974</v>
       </c>
       <c r="I16" s="14" t="n">
-        <v>-150962</v>
+        <v>-151458</v>
       </c>
       <c r="J16" s="14" t="n">
-        <v>-138238</v>
+        <v>-138942</v>
       </c>
       <c r="K16" s="14" t="n">
-        <v>-125514</v>
+        <v>-126426</v>
       </c>
       <c r="L16" s="14" t="n">
-        <v>-112790</v>
+        <v>-113910</v>
       </c>
       <c r="M16" s="14" t="n">
-        <v>-100066</v>
+        <v>-101394</v>
       </c>
       <c r="N16" s="14" t="n">
-        <v>-26738</v>
+        <v>-34814</v>
       </c>
       <c r="O16" s="14" t="n">
-        <v>-49782</v>
+        <v>-54163</v>
       </c>
       <c r="P16" s="14" t="n">
-        <v>-41027</v>
+        <v>-43396</v>
       </c>
       <c r="Q16" s="14" t="n">
-        <v>-32271</v>
+        <v>-34834</v>
       </c>
       <c r="R16" s="14" t="n">
-        <v>-23516</v>
+        <v>-25927</v>
       </c>
       <c r="S16" s="14" t="n">
-        <v>-41774</v>
+        <v>-44685</v>
       </c>
       <c r="T16" s="14" t="n">
-        <v>-209233</v>
+        <v>-212284</v>
       </c>
       <c r="U16" s="14" t="n">
-        <v>-16692</v>
+        <v>-19908</v>
       </c>
       <c r="V16" s="14" t="n">
-        <v>-3882</v>
+        <v>-7549</v>
       </c>
       <c r="W16" s="14" t="n">
-        <v>8679</v>
+        <v>4799</v>
       </c>
       <c r="X16" s="14" t="n">
-        <v>21241</v>
+        <v>17139</v>
       </c>
       <c r="Y16" s="14" t="n">
-        <v>33968</v>
+        <v>29504</v>
       </c>
       <c r="Z16" s="14" t="n">
-        <v>39770</v>
+        <v>38019</v>
       </c>
       <c r="AA16" s="14" t="n">
-        <v>-382965</v>
+        <v>-388359</v>
       </c>
       <c r="AB16" s="14" t="n">
-        <v>49335</v>
+        <v>45968</v>
       </c>
       <c r="AC16" s="14" t="n">
-        <v>73896</v>
+        <v>71712</v>
       </c>
       <c r="AD16" s="14" t="n">
-        <v>92027</v>
+        <v>88591</v>
       </c>
       <c r="AE16" s="14" t="n">
-        <v>110315</v>
+        <v>107793</v>
       </c>
       <c r="AF16" s="14" t="n">
-        <v>126076</v>
+        <v>123400</v>
       </c>
       <c r="AG16" s="14" t="n">
-        <v>144433</v>
+        <v>139998</v>
       </c>
       <c r="AH16" s="14" t="n">
-        <v>-287168</v>
+        <v>-290530</v>
       </c>
       <c r="AI16" s="14" t="n">
-        <v>181261</v>
+        <v>178857</v>
       </c>
       <c r="AJ16" s="14" t="n">
-        <v>199712</v>
+        <v>197925</v>
       </c>
       <c r="AK16" s="14" t="n">
-        <v>218162</v>
+        <v>216813</v>
       </c>
       <c r="AL16" s="14" t="n">
-        <v>413501</v>
+        <v>412167</v>
       </c>
       <c r="AM16" s="14" t="n">
-        <v>121918</v>
+        <v>120888</v>
       </c>
       <c r="AN16" s="14" t="n">
-        <v>468388</v>
+        <v>467591</v>
       </c>
       <c r="AO16" s="14" t="n">
-        <v>419566</v>
+        <v>418949</v>
       </c>
       <c r="AP16" s="14" t="n">
-        <v>436296</v>
+        <v>435817</v>
       </c>
       <c r="AQ16" s="14" t="n">
-        <v>453216</v>
+        <v>452867</v>
       </c>
       <c r="AR16" s="14" t="n">
-        <v>471234</v>
+        <v>470960</v>
       </c>
       <c r="AS16" s="14" t="n">
-        <v>489319</v>
+        <v>489117</v>
       </c>
       <c r="AT16" s="14" t="n">
-        <v>507823</v>
+        <v>507672</v>
       </c>
       <c r="AU16" s="14" t="n">
-        <v>526497</v>
+        <v>526389</v>
       </c>
       <c r="AV16" s="14" t="n">
-        <v>545457</v>
+        <v>545377</v>
       </c>
       <c r="AW16" s="14" t="n">
-        <v>564592</v>
+        <v>564532</v>
       </c>
       <c r="AX16" s="14" t="n">
-        <v>992781</v>
+        <v>992722</v>
       </c>
       <c r="AY16" s="14" t="n">
-        <v>1022454</v>
+        <v>1022409</v>
       </c>
       <c r="AZ16" s="14" t="n">
-        <v>1050825</v>
+        <v>1050791</v>
       </c>
       <c r="BA16" s="14" t="n">
-        <v>1000736</v>
+        <v>1000711</v>
       </c>
       <c r="BB16" s="14" t="n">
-        <v>1013176</v>
+        <v>1013156</v>
       </c>
       <c r="BC16" s="14" t="n">
-        <v>1026196</v>
+        <v>1026182</v>
       </c>
       <c r="BD16" s="14" t="n">
-        <v>1040584</v>
+        <v>1040573</v>
       </c>
       <c r="BE16" s="14" t="n">
-        <v>1055951</v>
+        <v>1055943</v>
       </c>
       <c r="BF16" s="14" t="n">
-        <v>1072029</v>
+        <v>1072023</v>
       </c>
       <c r="BG16" s="14" t="n">
-        <v>1088627</v>
+        <v>1088622</v>
       </c>
       <c r="BH16" s="14" t="n">
-        <v>1105608</v>
+        <v>1105605</v>
       </c>
       <c r="BI16" s="14" t="n">
-        <v>1122875</v>
+        <v>1122872</v>
       </c>
     </row>
     <row r="17">
@@ -6686,97 +6686,97 @@
         <v>0</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>256055</v>
+        <v>85352</v>
       </c>
       <c r="E5" s="13" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>282379</v>
+        <v>182250</v>
       </c>
       <c r="G5" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H5" s="13" t="n">
-        <v>0</v>
+        <v>96899</v>
       </c>
       <c r="I5" s="13" t="n">
-        <v>0</v>
+        <v>85352</v>
       </c>
       <c r="J5" s="13" t="n">
-        <v>226870</v>
+        <v>0</v>
       </c>
       <c r="K5" s="13" t="n">
-        <v>0</v>
+        <v>172522</v>
       </c>
       <c r="L5" s="13" t="n">
-        <v>252902</v>
+        <v>75623</v>
       </c>
       <c r="M5" s="13" t="n">
-        <v>0</v>
+        <v>87073</v>
       </c>
       <c r="N5" s="13" t="n">
-        <v>0</v>
+        <v>165722</v>
       </c>
       <c r="O5" s="13" t="n">
-        <v>235945</v>
+        <v>78648</v>
       </c>
       <c r="P5" s="13" t="n">
-        <v>0</v>
+        <v>169204</v>
       </c>
       <c r="Q5" s="13" t="n">
-        <v>263018</v>
+        <v>169204</v>
       </c>
       <c r="R5" s="13" t="n">
-        <v>235945</v>
+        <v>169204</v>
       </c>
       <c r="S5" s="13" t="n">
-        <v>0</v>
+        <v>169204</v>
       </c>
       <c r="T5" s="13" t="n">
-        <v>263018</v>
+        <v>169204</v>
       </c>
       <c r="U5" s="13" t="n">
-        <v>235945</v>
+        <v>247853</v>
       </c>
       <c r="V5" s="13" t="n">
-        <v>0</v>
+        <v>162141</v>
       </c>
       <c r="W5" s="13" t="n">
-        <v>477774</v>
+        <v>324283</v>
       </c>
       <c r="X5" s="13" t="n">
-        <v>0</v>
+        <v>155008</v>
       </c>
       <c r="Y5" s="13" t="n">
-        <v>456373</v>
+        <v>381601</v>
       </c>
       <c r="Z5" s="13" t="n">
-        <v>223346</v>
+        <v>232320</v>
       </c>
       <c r="AA5" s="13" t="n">
         <v>464963</v>
       </c>
       <c r="AB5" s="13" t="n">
-        <v>474628</v>
+        <v>396865</v>
       </c>
       <c r="AC5" s="13" t="n">
-        <v>474628</v>
+        <v>400179</v>
       </c>
       <c r="AD5" s="13" t="n">
         <v>474628</v>
       </c>
       <c r="AE5" s="13" t="n">
-        <v>474628</v>
+        <v>471313</v>
       </c>
       <c r="AF5" s="13" t="n">
-        <v>474628</v>
+        <v>549077</v>
       </c>
       <c r="AG5" s="13" t="n">
-        <v>549077</v>
+        <v>632838</v>
       </c>
       <c r="AH5" s="13" t="n">
-        <v>528430</v>
+        <v>612190</v>
       </c>
       <c r="AI5" s="13" t="n">
         <v>612190</v>
@@ -6885,13 +6885,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="13" t="n">
-        <v>142368</v>
+        <v>49129</v>
       </c>
       <c r="I6" s="13" t="n">
         <v>0</v>
       </c>
       <c r="J6" s="13" t="n">
-        <v>0</v>
+        <v>49129</v>
       </c>
       <c r="K6" s="13" t="n">
         <v>0</v>
@@ -6900,58 +6900,58 @@
         <v>0</v>
       </c>
       <c r="M6" s="13" t="n">
-        <v>0</v>
+        <v>49129</v>
       </c>
       <c r="N6" s="13" t="n">
-        <v>127775</v>
+        <v>0</v>
       </c>
       <c r="O6" s="13" t="n">
-        <v>0</v>
+        <v>44265</v>
       </c>
       <c r="P6" s="13" t="n">
-        <v>0</v>
+        <v>44265</v>
       </c>
       <c r="Q6" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R6" s="13" t="n">
-        <v>0</v>
+        <v>45777</v>
       </c>
       <c r="S6" s="13" t="n">
-        <v>132313</v>
+        <v>45777</v>
       </c>
       <c r="T6" s="13" t="n">
-        <v>0</v>
+        <v>45777</v>
       </c>
       <c r="U6" s="13" t="n">
-        <v>0</v>
+        <v>45777</v>
       </c>
       <c r="V6" s="13" t="n">
-        <v>132313</v>
+        <v>45777</v>
       </c>
       <c r="W6" s="13" t="n">
-        <v>0</v>
+        <v>45777</v>
       </c>
       <c r="X6" s="13" t="n">
-        <v>0</v>
+        <v>45777</v>
       </c>
       <c r="Y6" s="13" t="n">
-        <v>132313</v>
+        <v>91554</v>
       </c>
       <c r="Z6" s="13" t="n">
-        <v>0</v>
+        <v>42246</v>
       </c>
       <c r="AA6" s="13" t="n">
-        <v>121718</v>
+        <v>84491</v>
       </c>
       <c r="AB6" s="13" t="n">
-        <v>0</v>
+        <v>42246</v>
       </c>
       <c r="AC6" s="13" t="n">
         <v>121718</v>
       </c>
       <c r="AD6" s="13" t="n">
-        <v>126013</v>
+        <v>87355</v>
       </c>
       <c r="AE6" s="13" t="n">
         <v>126013</v>
@@ -6960,16 +6960,16 @@
         <v>126013</v>
       </c>
       <c r="AG6" s="13" t="n">
-        <v>126013</v>
+        <v>87355</v>
       </c>
       <c r="AH6" s="13" t="n">
         <v>126013</v>
       </c>
       <c r="AI6" s="13" t="n">
-        <v>126013</v>
+        <v>168017</v>
       </c>
       <c r="AJ6" s="13" t="n">
-        <v>126013</v>
+        <v>168017</v>
       </c>
       <c r="AK6" s="13" t="n">
         <v>168017</v>
@@ -7057,7 +7057,7 @@
         <v>63000</v>
       </c>
       <c r="C7" s="13" t="n">
-        <v>85000</v>
+        <v>65000</v>
       </c>
       <c r="D7" s="13" t="n">
         <v>32000</v>
@@ -7244,7 +7244,7 @@
         <v>0</v>
       </c>
       <c r="C8" s="13" t="n">
-        <v>19980</v>
+        <v>17280</v>
       </c>
       <c r="D8" s="13" t="n">
         <v>0</v>
@@ -7262,49 +7262,49 @@
         <v>0</v>
       </c>
       <c r="I8" s="13" t="n">
-        <v>128645</v>
+        <v>59510</v>
       </c>
       <c r="J8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="K8" s="13" t="n">
-        <v>2284</v>
+        <v>36852</v>
       </c>
       <c r="L8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="M8" s="13" t="n">
-        <v>-12274</v>
+        <v>22293</v>
       </c>
       <c r="N8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O8" s="13" t="n">
-        <v>42931</v>
+        <v>-18324</v>
       </c>
       <c r="P8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="Q8" s="13" t="n">
-        <v>-60234</v>
+        <v>-29606</v>
       </c>
       <c r="R8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="S8" s="13" t="n">
-        <v>24042</v>
+        <v>-7811</v>
       </c>
       <c r="T8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="U8" s="13" t="n">
-        <v>-62382</v>
+        <v>1323</v>
       </c>
       <c r="V8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="W8" s="13" t="n">
-        <v>-7586</v>
+        <v>-39438</v>
       </c>
       <c r="X8" s="13" t="n">
         <v>0</v>
@@ -7322,31 +7322,31 @@
         <v>0</v>
       </c>
       <c r="AC8" s="13" t="n">
-        <v>-108038</v>
+        <v>-79046</v>
       </c>
       <c r="AD8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="AE8" s="13" t="n">
-        <v>-36741</v>
+        <v>-66892</v>
       </c>
       <c r="AF8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="AG8" s="13" t="n">
-        <v>-48333</v>
+        <v>-78484</v>
       </c>
       <c r="AH8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="AI8" s="13" t="n">
-        <v>-10220</v>
+        <v>19932</v>
       </c>
       <c r="AJ8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="AK8" s="13" t="n">
-        <v>-63455</v>
+        <v>-33303</v>
       </c>
       <c r="AL8" s="13" t="n">
         <v>0</v>
@@ -7497,7 +7497,7 @@
         <v>0</v>
       </c>
       <c r="Y9" s="13" t="n">
-        <v>-3450</v>
+        <v>-2778</v>
       </c>
       <c r="Z9" s="13" t="n">
         <v>0</v>
@@ -7515,7 +7515,7 @@
         <v>0</v>
       </c>
       <c r="AE9" s="13" t="n">
-        <v>-19729</v>
+        <v>-19012</v>
       </c>
       <c r="AF9" s="13" t="n">
         <v>0</v>
@@ -7533,7 +7533,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="13" t="n">
-        <v>-46961</v>
+        <v>-46278</v>
       </c>
       <c r="AL9" s="13" t="n">
         <v>0</v>
@@ -7551,7 +7551,7 @@
         <v>0</v>
       </c>
       <c r="AQ9" s="13" t="n">
-        <v>-205249</v>
+        <v>-188633</v>
       </c>
       <c r="AR9" s="13" t="n">
         <v>0</v>
@@ -7569,7 +7569,7 @@
         <v>0</v>
       </c>
       <c r="AW9" s="13" t="n">
-        <v>-838329</v>
+        <v>-838093</v>
       </c>
       <c r="AX9" s="13" t="n">
         <v>0</v>
@@ -7587,7 +7587,7 @@
         <v>0</v>
       </c>
       <c r="BC9" s="13" t="n">
-        <v>-1648665</v>
+        <v>-1648612</v>
       </c>
       <c r="BD9" s="13" t="n">
         <v>0</v>
@@ -7605,7 +7605,7 @@
         <v>0</v>
       </c>
       <c r="BI9" s="13" t="n">
-        <v>-1751132</v>
+        <v>-1751122</v>
       </c>
     </row>
     <row r="10">
@@ -7805,109 +7805,109 @@
         <v>3437000</v>
       </c>
       <c r="C11" s="14" t="n">
-        <v>-65020</v>
+        <v>-47720</v>
       </c>
       <c r="D11" s="14" t="n">
-        <v>-288055</v>
+        <v>-117352</v>
       </c>
       <c r="E11" s="14" t="n">
         <v>-169918</v>
       </c>
       <c r="F11" s="14" t="n">
-        <v>-374879</v>
+        <v>-274750</v>
       </c>
       <c r="G11" s="14" t="n">
         <v>-134010</v>
       </c>
       <c r="H11" s="14" t="n">
-        <v>-374829</v>
+        <v>-378489</v>
       </c>
       <c r="I11" s="14" t="n">
-        <v>-16631</v>
+        <v>-171117</v>
       </c>
       <c r="J11" s="14" t="n">
-        <v>-344959</v>
+        <v>-167217</v>
       </c>
       <c r="K11" s="14" t="n">
-        <v>-88618</v>
+        <v>-226573</v>
       </c>
       <c r="L11" s="14" t="n">
-        <v>-316618</v>
+        <v>-139339</v>
       </c>
       <c r="M11" s="14" t="n">
-        <v>-48803</v>
+        <v>-150438</v>
       </c>
       <c r="N11" s="14" t="n">
-        <v>-87843</v>
+        <v>-125789</v>
       </c>
       <c r="O11" s="14" t="n">
-        <v>-131215</v>
+        <v>-79438</v>
       </c>
       <c r="P11" s="14" t="n">
-        <v>82615</v>
+        <v>-130854</v>
       </c>
       <c r="Q11" s="14" t="n">
-        <v>-219821</v>
+        <v>-95380</v>
       </c>
       <c r="R11" s="14" t="n">
-        <v>-111698</v>
+        <v>-90735</v>
       </c>
       <c r="S11" s="14" t="n">
-        <v>9232</v>
+        <v>-105289</v>
       </c>
       <c r="T11" s="14" t="n">
-        <v>-307027</v>
+        <v>-258990</v>
       </c>
       <c r="U11" s="14" t="n">
-        <v>11856153</v>
+        <v>11862173</v>
       </c>
       <c r="V11" s="14" t="n">
-        <v>52828</v>
+        <v>-22778</v>
       </c>
       <c r="W11" s="14" t="n">
-        <v>-269560</v>
+        <v>-193698</v>
       </c>
       <c r="X11" s="14" t="n">
-        <v>246461</v>
+        <v>45676</v>
       </c>
       <c r="Y11" s="14" t="n">
-        <v>-339062</v>
+        <v>-222859</v>
       </c>
       <c r="Z11" s="14" t="n">
-        <v>33383</v>
+        <v>-17836</v>
       </c>
       <c r="AA11" s="14" t="n">
-        <v>-690051</v>
+        <v>-652824</v>
       </c>
       <c r="AB11" s="14" t="n">
-        <v>-83833</v>
+        <v>-48315</v>
       </c>
       <c r="AC11" s="14" t="n">
-        <v>-271355</v>
+        <v>-167915</v>
       </c>
       <c r="AD11" s="14" t="n">
-        <v>-125380</v>
+        <v>-86722</v>
       </c>
       <c r="AE11" s="14" t="n">
-        <v>-139616</v>
+        <v>-165737</v>
       </c>
       <c r="AF11" s="14" t="n">
-        <v>-166514</v>
+        <v>-240963</v>
       </c>
       <c r="AG11" s="14" t="n">
-        <v>-247063</v>
+        <v>-322317</v>
       </c>
       <c r="AH11" s="14" t="n">
-        <v>-329519</v>
+        <v>-413280</v>
       </c>
       <c r="AI11" s="14" t="n">
-        <v>68733</v>
+        <v>56881</v>
       </c>
       <c r="AJ11" s="14" t="n">
-        <v>142039</v>
+        <v>100035</v>
       </c>
       <c r="AK11" s="14" t="n">
-        <v>31852</v>
+        <v>62687</v>
       </c>
       <c r="AL11" s="14" t="n">
         <v>105441</v>
@@ -7925,7 +7925,7 @@
         <v>544094</v>
       </c>
       <c r="AQ11" s="14" t="n">
-        <v>61553</v>
+        <v>78169</v>
       </c>
       <c r="AR11" s="14" t="n">
         <v>475129</v>
@@ -7943,7 +7943,7 @@
         <v>388645</v>
       </c>
       <c r="AW11" s="14" t="n">
-        <v>-435269</v>
+        <v>-435033</v>
       </c>
       <c r="AX11" s="14" t="n">
         <v>324692</v>
@@ -7961,7 +7961,7 @@
         <v>1236870</v>
       </c>
       <c r="BC11" s="14" t="n">
-        <v>-605603</v>
+        <v>-605550</v>
       </c>
       <c r="BD11" s="14" t="n">
         <v>1271461</v>
@@ -7979,7 +7979,7 @@
         <v>1420633</v>
       </c>
       <c r="BI11" s="14" t="n">
-        <v>-515222</v>
+        <v>-515212</v>
       </c>
     </row>
     <row r="12">
@@ -7992,181 +7992,181 @@
         <v>3437000</v>
       </c>
       <c r="C12" s="14" t="n">
-        <v>3371980</v>
+        <v>3389280</v>
       </c>
       <c r="D12" s="14" t="n">
-        <v>3083925</v>
+        <v>3271928</v>
       </c>
       <c r="E12" s="14" t="n">
-        <v>2914007</v>
+        <v>3102011</v>
       </c>
       <c r="F12" s="14" t="n">
-        <v>2539128</v>
+        <v>2827260</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>2405118</v>
+        <v>2693250</v>
       </c>
       <c r="H12" s="14" t="n">
-        <v>2030289</v>
+        <v>2314761</v>
       </c>
       <c r="I12" s="14" t="n">
-        <v>2013659</v>
+        <v>2143644</v>
       </c>
       <c r="J12" s="14" t="n">
-        <v>1668700</v>
+        <v>1976427</v>
       </c>
       <c r="K12" s="14" t="n">
-        <v>1580082</v>
+        <v>1749854</v>
       </c>
       <c r="L12" s="14" t="n">
-        <v>1263464</v>
+        <v>1610515</v>
       </c>
       <c r="M12" s="14" t="n">
-        <v>1214661</v>
+        <v>1460077</v>
       </c>
       <c r="N12" s="14" t="n">
-        <v>1126818</v>
+        <v>1334288</v>
       </c>
       <c r="O12" s="14" t="n">
-        <v>995603</v>
+        <v>1254850</v>
       </c>
       <c r="P12" s="14" t="n">
-        <v>1078218</v>
+        <v>1123995</v>
       </c>
       <c r="Q12" s="14" t="n">
-        <v>858396</v>
+        <v>1028616</v>
       </c>
       <c r="R12" s="14" t="n">
-        <v>746698</v>
+        <v>937881</v>
       </c>
       <c r="S12" s="14" t="n">
-        <v>755931</v>
+        <v>832592</v>
       </c>
       <c r="T12" s="14" t="n">
-        <v>448904</v>
+        <v>573601</v>
       </c>
       <c r="U12" s="14" t="n">
-        <v>12305056</v>
+        <v>12435774</v>
       </c>
       <c r="V12" s="14" t="n">
-        <v>12357884</v>
+        <v>12412996</v>
       </c>
       <c r="W12" s="14" t="n">
-        <v>12088325</v>
+        <v>12219298</v>
       </c>
       <c r="X12" s="14" t="n">
-        <v>12334785</v>
+        <v>12264974</v>
       </c>
       <c r="Y12" s="14" t="n">
-        <v>11995724</v>
+        <v>12042115</v>
       </c>
       <c r="Z12" s="14" t="n">
-        <v>12029107</v>
+        <v>12024279</v>
       </c>
       <c r="AA12" s="14" t="n">
-        <v>11339056</v>
+        <v>11371455</v>
       </c>
       <c r="AB12" s="14" t="n">
-        <v>11255224</v>
+        <v>11323141</v>
       </c>
       <c r="AC12" s="14" t="n">
-        <v>10983869</v>
+        <v>11155226</v>
       </c>
       <c r="AD12" s="14" t="n">
-        <v>10858488</v>
+        <v>11068504</v>
       </c>
       <c r="AE12" s="14" t="n">
-        <v>10718872</v>
+        <v>10902767</v>
       </c>
       <c r="AF12" s="14" t="n">
-        <v>10552358</v>
+        <v>10661804</v>
       </c>
       <c r="AG12" s="14" t="n">
-        <v>10305295</v>
+        <v>10339487</v>
       </c>
       <c r="AH12" s="14" t="n">
-        <v>9975775</v>
+        <v>9926207</v>
       </c>
       <c r="AI12" s="14" t="n">
-        <v>10044508</v>
+        <v>9983087</v>
       </c>
       <c r="AJ12" s="14" t="n">
-        <v>10186548</v>
+        <v>10083122</v>
       </c>
       <c r="AK12" s="14" t="n">
-        <v>10218399</v>
+        <v>10145809</v>
       </c>
       <c r="AL12" s="14" t="n">
-        <v>10323840</v>
+        <v>10251250</v>
       </c>
       <c r="AM12" s="14" t="n">
-        <v>10128361</v>
+        <v>10055771</v>
       </c>
       <c r="AN12" s="14" t="n">
-        <v>10739118</v>
+        <v>10666527</v>
       </c>
       <c r="AO12" s="14" t="n">
-        <v>11023954</v>
+        <v>10951364</v>
       </c>
       <c r="AP12" s="14" t="n">
-        <v>11568049</v>
+        <v>11495458</v>
       </c>
       <c r="AQ12" s="14" t="n">
-        <v>11629601</v>
+        <v>11573627</v>
       </c>
       <c r="AR12" s="14" t="n">
-        <v>12104730</v>
+        <v>12048756</v>
       </c>
       <c r="AS12" s="14" t="n">
-        <v>12352055</v>
+        <v>12296081</v>
       </c>
       <c r="AT12" s="14" t="n">
-        <v>12747761</v>
+        <v>12691787</v>
       </c>
       <c r="AU12" s="14" t="n">
-        <v>13100871</v>
+        <v>13044897</v>
       </c>
       <c r="AV12" s="14" t="n">
-        <v>13489516</v>
+        <v>13433542</v>
       </c>
       <c r="AW12" s="14" t="n">
-        <v>13054247</v>
+        <v>12998508</v>
       </c>
       <c r="AX12" s="14" t="n">
-        <v>13378939</v>
+        <v>13323200</v>
       </c>
       <c r="AY12" s="14" t="n">
-        <v>13704492</v>
+        <v>13648753</v>
       </c>
       <c r="AZ12" s="14" t="n">
-        <v>14992412</v>
+        <v>14936673</v>
       </c>
       <c r="BA12" s="14" t="n">
-        <v>16003346</v>
+        <v>15947607</v>
       </c>
       <c r="BB12" s="14" t="n">
-        <v>17240216</v>
+        <v>17184477</v>
       </c>
       <c r="BC12" s="14" t="n">
-        <v>16634613</v>
+        <v>16578927</v>
       </c>
       <c r="BD12" s="14" t="n">
-        <v>17906073</v>
+        <v>17850388</v>
       </c>
       <c r="BE12" s="14" t="n">
-        <v>19032435</v>
+        <v>18976749</v>
       </c>
       <c r="BF12" s="14" t="n">
-        <v>20378481</v>
+        <v>20322796</v>
       </c>
       <c r="BG12" s="14" t="n">
-        <v>21559617</v>
+        <v>21503932</v>
       </c>
       <c r="BH12" s="14" t="n">
-        <v>22980250</v>
+        <v>22924565</v>
       </c>
       <c r="BI12" s="14" t="n">
-        <v>22465028</v>
+        <v>22409352</v>
       </c>
     </row>
     <row r="13">
@@ -8194,64 +8194,64 @@
         <v>0</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>66002</v>
+        <v>21032</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>63495</v>
+        <v>18525</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>59935</v>
+        <v>37450</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>55322</v>
+        <v>32837</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>49655</v>
+        <v>27170</v>
       </c>
       <c r="M13" s="12" t="n">
         <v>42935</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>101014</v>
+        <v>33559</v>
       </c>
       <c r="O13" s="12" t="n">
-        <v>90721</v>
+        <v>45750</v>
       </c>
       <c r="P13" s="12" t="n">
-        <v>79511</v>
+        <v>57026</v>
       </c>
       <c r="Q13" s="12" t="n">
-        <v>67384</v>
+        <v>44899</v>
       </c>
       <c r="R13" s="12" t="n">
         <v>54341</v>
       </c>
       <c r="S13" s="12" t="n">
-        <v>107836</v>
+        <v>62866</v>
       </c>
       <c r="T13" s="12" t="n">
-        <v>92479</v>
+        <v>69994</v>
       </c>
       <c r="U13" s="12" t="n">
         <v>75726</v>
       </c>
       <c r="V13" s="12" t="n">
-        <v>125031</v>
+        <v>80061</v>
       </c>
       <c r="W13" s="12" t="n">
-        <v>105485</v>
+        <v>83000</v>
       </c>
       <c r="X13" s="12" t="n">
         <v>84541</v>
       </c>
       <c r="Y13" s="12" t="n">
-        <v>129657</v>
+        <v>107172</v>
       </c>
       <c r="Z13" s="12" t="n">
         <v>101387</v>
       </c>
       <c r="AA13" s="12" t="n">
-        <v>138672</v>
+        <v>116187</v>
       </c>
       <c r="AB13" s="12" t="n">
         <v>106602</v>
@@ -8260,22 +8260,22 @@
         <v>140088</v>
       </c>
       <c r="AD13" s="12" t="n">
-        <v>171673</v>
+        <v>149188</v>
       </c>
       <c r="AE13" s="12" t="n">
-        <v>201358</v>
+        <v>178873</v>
       </c>
       <c r="AF13" s="12" t="n">
-        <v>214144</v>
+        <v>191658</v>
       </c>
       <c r="AG13" s="12" t="n">
-        <v>225029</v>
+        <v>180059</v>
       </c>
       <c r="AH13" s="12" t="n">
-        <v>234014</v>
+        <v>189044</v>
       </c>
       <c r="AI13" s="12" t="n">
-        <v>241100</v>
+        <v>218615</v>
       </c>
       <c r="AJ13" s="12" t="n">
         <v>246285</v>
@@ -8381,166 +8381,166 @@
         <v>0</v>
       </c>
       <c r="H14" s="13" t="n">
-        <v>666134</v>
+        <v>216424</v>
       </c>
       <c r="I14" s="13" t="n">
-        <v>640835</v>
+        <v>190630</v>
       </c>
       <c r="J14" s="13" t="n">
-        <v>604905</v>
+        <v>385375</v>
       </c>
       <c r="K14" s="13" t="n">
-        <v>558344</v>
+        <v>337903</v>
       </c>
       <c r="L14" s="13" t="n">
-        <v>501153</v>
+        <v>279591</v>
       </c>
       <c r="M14" s="13" t="n">
-        <v>433330</v>
+        <v>441819</v>
       </c>
       <c r="N14" s="13" t="n">
-        <v>952465</v>
+        <v>345330</v>
       </c>
       <c r="O14" s="13" t="n">
-        <v>855409</v>
+        <v>450854</v>
       </c>
       <c r="P14" s="13" t="n">
-        <v>749710</v>
+        <v>549747</v>
       </c>
       <c r="Q14" s="13" t="n">
-        <v>635367</v>
+        <v>432842</v>
       </c>
       <c r="R14" s="13" t="n">
-        <v>512381</v>
+        <v>522426</v>
       </c>
       <c r="S14" s="13" t="n">
-        <v>1012573</v>
+        <v>603414</v>
       </c>
       <c r="T14" s="13" t="n">
-        <v>868375</v>
+        <v>671147</v>
       </c>
       <c r="U14" s="13" t="n">
-        <v>711063</v>
+        <v>725600</v>
       </c>
       <c r="V14" s="13" t="n">
-        <v>1172181</v>
+        <v>766756</v>
       </c>
       <c r="W14" s="13" t="n">
-        <v>988929</v>
+        <v>794606</v>
       </c>
       <c r="X14" s="13" t="n">
-        <v>792584</v>
+        <v>809140</v>
       </c>
       <c r="Y14" s="13" t="n">
-        <v>1214585</v>
+        <v>1025366</v>
       </c>
       <c r="Z14" s="13" t="n">
-        <v>949761</v>
+        <v>956043</v>
       </c>
       <c r="AA14" s="13" t="n">
-        <v>1254844</v>
+        <v>1072147</v>
       </c>
       <c r="AB14" s="13" t="n">
-        <v>964642</v>
+        <v>975833</v>
       </c>
       <c r="AC14" s="13" t="n">
-        <v>1241645</v>
+        <v>1250652</v>
       </c>
       <c r="AD14" s="13" t="n">
-        <v>1523881</v>
+        <v>1338581</v>
       </c>
       <c r="AE14" s="13" t="n">
-        <v>1788957</v>
+        <v>1601134</v>
       </c>
       <c r="AF14" s="13" t="n">
-        <v>1903613</v>
+        <v>1713114</v>
       </c>
       <c r="AG14" s="13" t="n">
-        <v>2001178</v>
+        <v>1615374</v>
       </c>
       <c r="AH14" s="13" t="n">
-        <v>2081694</v>
+        <v>1692528</v>
       </c>
       <c r="AI14" s="13" t="n">
-        <v>2145192</v>
+        <v>1953835</v>
       </c>
       <c r="AJ14" s="13" t="n">
-        <v>2191692</v>
+        <v>2198762</v>
       </c>
       <c r="AK14" s="13" t="n">
-        <v>2421407</v>
+        <v>2427128</v>
       </c>
       <c r="AL14" s="13" t="n">
-        <v>2430916</v>
+        <v>2435302</v>
       </c>
       <c r="AM14" s="13" t="n">
-        <v>2433126</v>
+        <v>2436482</v>
       </c>
       <c r="AN14" s="13" t="n">
-        <v>2426090</v>
+        <v>2428649</v>
       </c>
       <c r="AO14" s="13" t="n">
-        <v>2408359</v>
+        <v>2410300</v>
       </c>
       <c r="AP14" s="13" t="n">
-        <v>2400837</v>
+        <v>2402300</v>
       </c>
       <c r="AQ14" s="13" t="n">
-        <v>2569077</v>
+        <v>2570190</v>
       </c>
       <c r="AR14" s="13" t="n">
-        <v>2525061</v>
+        <v>2525901</v>
       </c>
       <c r="AS14" s="13" t="n">
-        <v>2657971</v>
+        <v>2658609</v>
       </c>
       <c r="AT14" s="13" t="n">
-        <v>2773668</v>
+        <v>2774156</v>
       </c>
       <c r="AU14" s="13" t="n">
-        <v>3066880</v>
+        <v>3067260</v>
       </c>
       <c r="AV14" s="13" t="n">
-        <v>3343336</v>
+        <v>3343636</v>
       </c>
       <c r="AW14" s="13" t="n">
-        <v>3603211</v>
+        <v>3603450</v>
       </c>
       <c r="AX14" s="13" t="n">
-        <v>3692485</v>
+        <v>3692666</v>
       </c>
       <c r="AY14" s="13" t="n">
-        <v>3596263</v>
+        <v>3596398</v>
       </c>
       <c r="AZ14" s="13" t="n">
-        <v>3680588</v>
+        <v>3680690</v>
       </c>
       <c r="BA14" s="13" t="n">
-        <v>3759077</v>
+        <v>3759154</v>
       </c>
       <c r="BB14" s="13" t="n">
-        <v>3677770</v>
+        <v>3677828</v>
       </c>
       <c r="BC14" s="13" t="n">
-        <v>3768816</v>
+        <v>3768860</v>
       </c>
       <c r="BD14" s="13" t="n">
-        <v>3842754</v>
+        <v>3842787</v>
       </c>
       <c r="BE14" s="13" t="n">
-        <v>3900563</v>
+        <v>3900587</v>
       </c>
       <c r="BF14" s="13" t="n">
-        <v>3942953</v>
+        <v>3942971</v>
       </c>
       <c r="BG14" s="13" t="n">
-        <v>3970444</v>
+        <v>3970458</v>
       </c>
       <c r="BH14" s="13" t="n">
-        <v>3983421</v>
+        <v>3983431</v>
       </c>
       <c r="BI14" s="13" t="n">
-        <v>3982167</v>
+        <v>3982175</v>
       </c>
     </row>
     <row r="15">
@@ -8897,7 +8897,7 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>0.5621</v>
+        <v>0.5615</v>
       </c>
       <c r="C11" s="8" t="n">
         <v>0.6545</v>
@@ -8913,13 +8913,13 @@
         </is>
       </c>
       <c r="B12" s="13" t="n">
-        <v>-179821.973</v>
+        <v>-189443.314</v>
       </c>
       <c r="C12" s="13" t="n">
-        <v>12591841.549</v>
+        <v>12591610.0764</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>25700854.9205</v>
+        <v>25700765.0039</v>
       </c>
     </row>
     <row r="13">
@@ -8929,7 +8929,7 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>-0.0102</v>
+        <v>-0.0107</v>
       </c>
       <c r="C13" s="8" t="n">
         <v>0.2886</v>
@@ -8945,13 +8945,13 @@
         </is>
       </c>
       <c r="B14" s="13" t="n">
-        <v>-5740330.3275</v>
+        <v>-5924610.1364</v>
       </c>
       <c r="C14" s="13" t="n">
-        <v>16716718.5383</v>
+        <v>16646399.9474</v>
       </c>
       <c r="D14" s="13" t="n">
-        <v>43876719.1528</v>
+        <v>43815882.253</v>
       </c>
     </row>
     <row r="15">
@@ -8977,13 +8977,13 @@
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>8601290.9364</v>
+        <v>8600702.8167</v>
       </c>
       <c r="C16" s="13" t="n">
-        <v>5524224.698</v>
+        <v>5573793.2027</v>
       </c>
       <c r="D16" s="13" t="n">
-        <v>3336675.2557</v>
+        <v>3356538.7832</v>
       </c>
     </row>
     <row r="17">
@@ -8999,7 +8999,7 @@
         <v>33</v>
       </c>
       <c r="D17" s="17" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18">
@@ -9009,13 +9009,13 @@
         </is>
       </c>
       <c r="B18" s="13" t="n">
-        <v>1000258.3102</v>
+        <v>1207273.1908</v>
       </c>
       <c r="C18" s="13" t="n">
-        <v>448903.5758</v>
+        <v>573601.4322</v>
       </c>
       <c r="D18" s="13" t="n">
-        <v>553890.0669</v>
+        <v>629993.5093</v>
       </c>
     </row>
     <row r="19">
@@ -9025,13 +9025,13 @@
         </is>
       </c>
       <c r="B19" s="13" t="n">
-        <v>7824302.2724</v>
+        <v>7640597.8524</v>
       </c>
       <c r="C19" s="13" t="n">
-        <v>22465028.1213</v>
+        <v>22409352.2289</v>
       </c>
       <c r="D19" s="13" t="n">
-        <v>38888197.2137</v>
+        <v>38835786.5251</v>
       </c>
     </row>
   </sheetData>
@@ -9148,7 +9148,7 @@
         </is>
       </c>
       <c r="B10" s="13" t="n">
-        <v>408000</v>
+        <v>388000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -9163,11 +9163,11 @@
         </is>
       </c>
       <c r="B11" s="13" t="n">
-        <v>538434</v>
+        <v>182250</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>68,832 tins</t>
+          <t>22,944 tins</t>
         </is>
       </c>
     </row>
@@ -9178,7 +9178,7 @@
         </is>
       </c>
       <c r="B12" s="13" t="n">
-        <v>142368</v>
+        <v>49129</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -9234,7 +9234,7 @@
         </is>
       </c>
       <c r="B16" s="14" t="n">
-        <v>2514404</v>
+        <v>2044981</v>
       </c>
     </row>
     <row r="17">
@@ -9244,13 +9244,13 @@
         </is>
       </c>
       <c r="B17" s="14" t="n">
-        <v>985596</v>
+        <v>1455019</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Note: the base case dips to its lowest cash balance in month 19 at R448,904. The growth round must be closed before then, not started then.</t>
+          <t>Note: the base case dips to its lowest cash balance in month 19 at R573,601. The growth round must be closed before then, not started then.</t>
         </is>
       </c>
     </row>
@@ -9268,7 +9268,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J46"/>
+  <dimension ref="A1:J56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9350,1188 +9350,1188 @@
         <v>7</v>
       </c>
       <c r="C4" s="12" t="n">
-        <v>68832</v>
+        <v>22944</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>0.51</v>
+        <v>0.17</v>
       </c>
       <c r="E4" s="13" t="n">
-        <v>512110</v>
+        <v>170703</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>23763</v>
+        <v>10694</v>
       </c>
       <c r="G4" s="13" t="n">
-        <v>2561</v>
+        <v>854</v>
       </c>
       <c r="H4" s="13" t="n">
-        <v>128028</v>
+        <v>42676</v>
       </c>
       <c r="I4" s="13" t="n">
-        <v>14340</v>
+        <v>6453</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>9.890000000000001</v>
+        <v>10.08</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="B5" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="B5" s="12" t="n">
-        <v>13</v>
-      </c>
       <c r="C5" s="12" t="n">
-        <v>68832</v>
+        <v>22944</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>0.51</v>
+        <v>0.17</v>
       </c>
       <c r="E5" s="13" t="n">
-        <v>453741</v>
+        <v>170703</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>23763</v>
+        <v>10694</v>
       </c>
       <c r="G5" s="13" t="n">
-        <v>2269</v>
+        <v>854</v>
       </c>
       <c r="H5" s="13" t="n">
-        <v>113435</v>
+        <v>42676</v>
       </c>
       <c r="I5" s="13" t="n">
-        <v>14340</v>
+        <v>6453</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>8.83</v>
+        <v>10.08</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="12" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B6" s="12" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C6" s="12" t="n">
-        <v>68832</v>
+        <v>22944</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>0.51</v>
+        <v>0.17</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>471890</v>
+        <v>170703</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>24714</v>
+        <v>10694</v>
       </c>
       <c r="G6" s="13" t="n">
-        <v>2359</v>
+        <v>854</v>
       </c>
       <c r="H6" s="13" t="n">
-        <v>117973</v>
+        <v>42676</v>
       </c>
       <c r="I6" s="13" t="n">
-        <v>14340</v>
+        <v>6453</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>9.17</v>
+        <v>10.08</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B7" s="12" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C7" s="12" t="n">
-        <v>68832</v>
+        <v>22944</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>0.51</v>
+        <v>0.17</v>
       </c>
       <c r="E7" s="13" t="n">
-        <v>471890</v>
+        <v>151247</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>24714</v>
+        <v>10694</v>
       </c>
       <c r="G7" s="13" t="n">
-        <v>2359</v>
+        <v>756</v>
       </c>
       <c r="H7" s="13" t="n">
-        <v>117973</v>
+        <v>37812</v>
       </c>
       <c r="I7" s="13" t="n">
-        <v>14340</v>
+        <v>6453</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>9.17</v>
+        <v>9.02</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="12" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="B8" s="12" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C8" s="12" t="n">
-        <v>68832</v>
+        <v>22944</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>0.51</v>
+        <v>0.17</v>
       </c>
       <c r="E8" s="13" t="n">
-        <v>471890</v>
+        <v>151247</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>24714</v>
+        <v>10694</v>
       </c>
       <c r="G8" s="13" t="n">
-        <v>2359</v>
+        <v>756</v>
       </c>
       <c r="H8" s="13" t="n">
-        <v>117973</v>
+        <v>37812</v>
       </c>
       <c r="I8" s="13" t="n">
-        <v>14340</v>
+        <v>6453</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>9.17</v>
+        <v>9.02</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B9" s="12" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C9" s="12" t="n">
-        <v>68832</v>
+        <v>22944</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>0.51</v>
+        <v>0.17</v>
       </c>
       <c r="E9" s="13" t="n">
-        <v>429512</v>
+        <v>157297</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>24714</v>
+        <v>11121</v>
       </c>
       <c r="G9" s="13" t="n">
-        <v>2148</v>
+        <v>786</v>
       </c>
       <c r="H9" s="13" t="n">
-        <v>107378</v>
+        <v>39324</v>
       </c>
       <c r="I9" s="13" t="n">
-        <v>14340</v>
+        <v>6453</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>8.4</v>
+        <v>9.369999999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="12" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="B10" s="12" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="C10" s="12" t="n">
-        <v>68832</v>
+        <v>22944</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>0.51</v>
+        <v>0.17</v>
       </c>
       <c r="E10" s="13" t="n">
-        <v>429512</v>
+        <v>157297</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>24714</v>
+        <v>11121</v>
       </c>
       <c r="G10" s="13" t="n">
-        <v>2148</v>
+        <v>786</v>
       </c>
       <c r="H10" s="13" t="n">
-        <v>107378</v>
+        <v>39324</v>
       </c>
       <c r="I10" s="13" t="n">
-        <v>14340</v>
+        <v>6453</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>8.4</v>
+        <v>9.369999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="B11" s="12" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="C11" s="12" t="n">
-        <v>68832</v>
+        <v>22944</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>0.51</v>
+        <v>0.17</v>
       </c>
       <c r="E11" s="13" t="n">
-        <v>446692</v>
+        <v>157297</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>25703</v>
+        <v>11121</v>
       </c>
       <c r="G11" s="13" t="n">
-        <v>2233</v>
+        <v>786</v>
       </c>
       <c r="H11" s="13" t="n">
-        <v>111673</v>
+        <v>39324</v>
       </c>
       <c r="I11" s="13" t="n">
-        <v>14340</v>
+        <v>6453</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>8.73</v>
+        <v>9.369999999999999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="12" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="B12" s="12" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C12" s="12" t="n">
-        <v>68832</v>
+        <v>22944</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>0.51</v>
+        <v>0.17</v>
       </c>
       <c r="E12" s="13" t="n">
-        <v>446692</v>
+        <v>157297</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>25703</v>
+        <v>11121</v>
       </c>
       <c r="G12" s="13" t="n">
-        <v>2233</v>
+        <v>786</v>
       </c>
       <c r="H12" s="13" t="n">
-        <v>111673</v>
+        <v>39324</v>
       </c>
       <c r="I12" s="13" t="n">
-        <v>14340</v>
+        <v>6453</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>8.73</v>
+        <v>9.369999999999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="B13" s="12" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="C13" s="12" t="n">
-        <v>68832</v>
+        <v>22944</v>
       </c>
       <c r="D13" s="13" t="n">
-        <v>0.51</v>
+        <v>0.17</v>
       </c>
       <c r="E13" s="13" t="n">
-        <v>446692</v>
+        <v>157297</v>
       </c>
       <c r="F13" s="13" t="n">
-        <v>25703</v>
+        <v>11121</v>
       </c>
       <c r="G13" s="13" t="n">
-        <v>2233</v>
+        <v>786</v>
       </c>
       <c r="H13" s="13" t="n">
-        <v>111673</v>
+        <v>39324</v>
       </c>
       <c r="I13" s="13" t="n">
-        <v>14340</v>
+        <v>6453</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>8.73</v>
+        <v>9.369999999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="B14" s="12" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="C14" s="12" t="n">
-        <v>68832</v>
+        <v>22944</v>
       </c>
       <c r="D14" s="13" t="n">
-        <v>0.51</v>
+        <v>0.17</v>
       </c>
       <c r="E14" s="13" t="n">
-        <v>446692</v>
+        <v>157297</v>
       </c>
       <c r="F14" s="13" t="n">
-        <v>25703</v>
+        <v>11121</v>
       </c>
       <c r="G14" s="13" t="n">
-        <v>2233</v>
+        <v>786</v>
       </c>
       <c r="H14" s="13" t="n">
-        <v>111673</v>
+        <v>39324</v>
       </c>
       <c r="I14" s="13" t="n">
-        <v>14340</v>
+        <v>6453</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>8.73</v>
+        <v>9.369999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="B15" s="12" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="C15" s="12" t="n">
-        <v>68832</v>
+        <v>22944</v>
       </c>
       <c r="D15" s="13" t="n">
-        <v>0.51</v>
+        <v>0.17</v>
       </c>
       <c r="E15" s="13" t="n">
-        <v>446692</v>
+        <v>157297</v>
       </c>
       <c r="F15" s="13" t="n">
-        <v>25703</v>
+        <v>11121</v>
       </c>
       <c r="G15" s="13" t="n">
-        <v>2233</v>
+        <v>786</v>
       </c>
       <c r="H15" s="13" t="n">
-        <v>111673</v>
+        <v>39324</v>
       </c>
       <c r="I15" s="13" t="n">
-        <v>14340</v>
+        <v>6453</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>8.73</v>
+        <v>9.369999999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="B16" s="12" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C16" s="12" t="n">
-        <v>68832</v>
+        <v>45888</v>
       </c>
       <c r="D16" s="13" t="n">
-        <v>0.51</v>
+        <v>0.34</v>
       </c>
       <c r="E16" s="13" t="n">
-        <v>446692</v>
+        <v>314593</v>
       </c>
       <c r="F16" s="13" t="n">
-        <v>25703</v>
+        <v>22243</v>
       </c>
       <c r="G16" s="13" t="n">
-        <v>2233</v>
+        <v>1573</v>
       </c>
       <c r="H16" s="13" t="n">
-        <v>111673</v>
+        <v>78648</v>
       </c>
       <c r="I16" s="13" t="n">
-        <v>14340</v>
+        <v>12906</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>8.73</v>
+        <v>9.369999999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="12" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="B17" s="12" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="C17" s="12" t="n">
-        <v>68832</v>
+        <v>22944</v>
       </c>
       <c r="D17" s="13" t="n">
-        <v>0.51</v>
+        <v>0.17</v>
       </c>
       <c r="E17" s="13" t="n">
-        <v>446692</v>
+        <v>143171</v>
       </c>
       <c r="F17" s="13" t="n">
-        <v>25703</v>
+        <v>11121</v>
       </c>
       <c r="G17" s="13" t="n">
-        <v>2233</v>
+        <v>716</v>
       </c>
       <c r="H17" s="13" t="n">
-        <v>111673</v>
+        <v>35793</v>
       </c>
       <c r="I17" s="13" t="n">
-        <v>14340</v>
+        <v>6453</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>8.73</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="B18" s="12" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="C18" s="12" t="n">
-        <v>91776</v>
+        <v>45888</v>
       </c>
       <c r="D18" s="13" t="n">
-        <v>0.68</v>
+        <v>0.34</v>
       </c>
       <c r="E18" s="13" t="n">
-        <v>595590</v>
+        <v>286341</v>
       </c>
       <c r="F18" s="13" t="n">
-        <v>34270</v>
+        <v>22243</v>
       </c>
       <c r="G18" s="13" t="n">
-        <v>2978</v>
+        <v>1432</v>
       </c>
       <c r="H18" s="13" t="n">
-        <v>148897</v>
+        <v>71585</v>
       </c>
       <c r="I18" s="13" t="n">
-        <v>19120</v>
+        <v>12906</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>8.73</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="12" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="B19" s="12" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="C19" s="12" t="n">
-        <v>91776</v>
+        <v>22944</v>
       </c>
       <c r="D19" s="13" t="n">
-        <v>0.68</v>
+        <v>0.17</v>
       </c>
       <c r="E19" s="13" t="n">
-        <v>554295</v>
+        <v>143171</v>
       </c>
       <c r="F19" s="13" t="n">
-        <v>34270</v>
+        <v>11121</v>
       </c>
       <c r="G19" s="13" t="n">
-        <v>2771</v>
+        <v>716</v>
       </c>
       <c r="H19" s="13" t="n">
-        <v>138574</v>
+        <v>35793</v>
       </c>
       <c r="I19" s="13" t="n">
-        <v>19120</v>
+        <v>6453</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>8.16</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="B20" s="12" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="C20" s="12" t="n">
-        <v>91776</v>
+        <v>68832</v>
       </c>
       <c r="D20" s="13" t="n">
-        <v>0.68</v>
+        <v>0.51</v>
       </c>
       <c r="E20" s="13" t="n">
-        <v>554295</v>
+        <v>429512</v>
       </c>
       <c r="F20" s="13" t="n">
-        <v>34270</v>
+        <v>24714</v>
       </c>
       <c r="G20" s="13" t="n">
-        <v>2771</v>
+        <v>2148</v>
       </c>
       <c r="H20" s="13" t="n">
-        <v>138574</v>
+        <v>107378</v>
       </c>
       <c r="I20" s="13" t="n">
-        <v>19120</v>
+        <v>14340</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>8.16</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B21" s="12" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="C21" s="12" t="n">
-        <v>91776</v>
+        <v>45888</v>
       </c>
       <c r="D21" s="13" t="n">
-        <v>0.68</v>
+        <v>0.34</v>
       </c>
       <c r="E21" s="13" t="n">
-        <v>554295</v>
+        <v>297795</v>
       </c>
       <c r="F21" s="13" t="n">
-        <v>34270</v>
+        <v>23132</v>
       </c>
       <c r="G21" s="13" t="n">
-        <v>2771</v>
+        <v>1489</v>
       </c>
       <c r="H21" s="13" t="n">
-        <v>138574</v>
+        <v>74449</v>
       </c>
       <c r="I21" s="13" t="n">
-        <v>19120</v>
+        <v>12906</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>8.16</v>
+        <v>8.93</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="B22" s="12" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C22" s="12" t="n">
-        <v>91776</v>
+        <v>68832</v>
       </c>
       <c r="D22" s="13" t="n">
-        <v>0.68</v>
+        <v>0.51</v>
       </c>
       <c r="E22" s="13" t="n">
-        <v>554295</v>
+        <v>446692</v>
       </c>
       <c r="F22" s="13" t="n">
-        <v>34270</v>
+        <v>25703</v>
       </c>
       <c r="G22" s="13" t="n">
-        <v>2771</v>
+        <v>2233</v>
       </c>
       <c r="H22" s="13" t="n">
-        <v>138574</v>
+        <v>111673</v>
       </c>
       <c r="I22" s="13" t="n">
-        <v>19120</v>
+        <v>14340</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>8.16</v>
+        <v>8.73</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="12" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="B23" s="12" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="C23" s="12" t="n">
-        <v>91776</v>
+        <v>68832</v>
       </c>
       <c r="D23" s="13" t="n">
-        <v>0.68</v>
+        <v>0.51</v>
       </c>
       <c r="E23" s="13" t="n">
-        <v>576467</v>
+        <v>446692</v>
       </c>
       <c r="F23" s="13" t="n">
-        <v>35641</v>
+        <v>25703</v>
       </c>
       <c r="G23" s="13" t="n">
-        <v>2882</v>
+        <v>2233</v>
       </c>
       <c r="H23" s="13" t="n">
-        <v>144117</v>
+        <v>111673</v>
       </c>
       <c r="I23" s="13" t="n">
-        <v>19120</v>
+        <v>14340</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>8.48</v>
+        <v>8.73</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="B24" s="12" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="C24" s="12" t="n">
-        <v>114720</v>
+        <v>45888</v>
       </c>
       <c r="D24" s="13" t="n">
-        <v>0.85</v>
+        <v>0.34</v>
       </c>
       <c r="E24" s="13" t="n">
-        <v>720584</v>
+        <v>297795</v>
       </c>
       <c r="F24" s="13" t="n">
-        <v>44551</v>
+        <v>23132</v>
       </c>
       <c r="G24" s="13" t="n">
-        <v>3603</v>
+        <v>1489</v>
       </c>
       <c r="H24" s="13" t="n">
-        <v>180146</v>
+        <v>74449</v>
       </c>
       <c r="I24" s="13" t="n">
-        <v>23900</v>
+        <v>12906</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>8.48</v>
+        <v>8.93</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="12" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="B25" s="12" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C25" s="12" t="n">
-        <v>91776</v>
+        <v>68832</v>
       </c>
       <c r="D25" s="13" t="n">
-        <v>0.68</v>
+        <v>0.51</v>
       </c>
       <c r="E25" s="13" t="n">
-        <v>576467</v>
+        <v>446692</v>
       </c>
       <c r="F25" s="13" t="n">
-        <v>35641</v>
+        <v>25703</v>
       </c>
       <c r="G25" s="13" t="n">
-        <v>2882</v>
+        <v>2233</v>
       </c>
       <c r="H25" s="13" t="n">
-        <v>144117</v>
+        <v>111673</v>
       </c>
       <c r="I25" s="13" t="n">
-        <v>19120</v>
+        <v>14340</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>8.48</v>
+        <v>8.73</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B26" s="12" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="C26" s="12" t="n">
-        <v>114720</v>
+        <v>91776</v>
       </c>
       <c r="D26" s="13" t="n">
-        <v>0.85</v>
+        <v>0.68</v>
       </c>
       <c r="E26" s="13" t="n">
-        <v>720584</v>
+        <v>595590</v>
       </c>
       <c r="F26" s="13" t="n">
-        <v>44551</v>
+        <v>34270</v>
       </c>
       <c r="G26" s="13" t="n">
-        <v>3603</v>
+        <v>2978</v>
       </c>
       <c r="H26" s="13" t="n">
-        <v>180146</v>
+        <v>148897</v>
       </c>
       <c r="I26" s="13" t="n">
-        <v>23900</v>
+        <v>19120</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>8.48</v>
+        <v>8.73</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="12" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="B27" s="12" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="C27" s="12" t="n">
-        <v>114720</v>
+        <v>91776</v>
       </c>
       <c r="D27" s="13" t="n">
-        <v>0.85</v>
+        <v>0.68</v>
       </c>
       <c r="E27" s="13" t="n">
-        <v>720584</v>
+        <v>595590</v>
       </c>
       <c r="F27" s="13" t="n">
-        <v>44551</v>
+        <v>34270</v>
       </c>
       <c r="G27" s="13" t="n">
-        <v>3603</v>
+        <v>2978</v>
       </c>
       <c r="H27" s="13" t="n">
-        <v>180146</v>
+        <v>148897</v>
       </c>
       <c r="I27" s="13" t="n">
-        <v>23900</v>
+        <v>19120</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>8.48</v>
+        <v>8.73</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="B28" s="12" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C28" s="12" t="n">
-        <v>137664</v>
+        <v>91776</v>
       </c>
       <c r="D28" s="13" t="n">
-        <v>1.02</v>
+        <v>0.68</v>
       </c>
       <c r="E28" s="13" t="n">
-        <v>864701</v>
+        <v>595590</v>
       </c>
       <c r="F28" s="13" t="n">
-        <v>53461</v>
+        <v>34270</v>
       </c>
       <c r="G28" s="13" t="n">
-        <v>4324</v>
+        <v>2978</v>
       </c>
       <c r="H28" s="13" t="n">
-        <v>216175</v>
+        <v>148897</v>
       </c>
       <c r="I28" s="13" t="n">
-        <v>28680</v>
+        <v>19120</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>8.48</v>
+        <v>8.73</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="12" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="B29" s="12" t="n">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="C29" s="12" t="n">
-        <v>137664</v>
+        <v>91776</v>
       </c>
       <c r="D29" s="13" t="n">
-        <v>1.02</v>
+        <v>0.68</v>
       </c>
       <c r="E29" s="13" t="n">
-        <v>864701</v>
+        <v>554295</v>
       </c>
       <c r="F29" s="13" t="n">
-        <v>53461</v>
+        <v>34270</v>
       </c>
       <c r="G29" s="13" t="n">
-        <v>4324</v>
+        <v>2771</v>
       </c>
       <c r="H29" s="13" t="n">
-        <v>216175</v>
+        <v>138574</v>
       </c>
       <c r="I29" s="13" t="n">
-        <v>28680</v>
+        <v>19120</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>8.48</v>
+        <v>8.16</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="12" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B30" s="12" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="C30" s="12" t="n">
-        <v>137664</v>
+        <v>91776</v>
       </c>
       <c r="D30" s="13" t="n">
-        <v>1.02</v>
+        <v>0.68</v>
       </c>
       <c r="E30" s="13" t="n">
-        <v>864701</v>
+        <v>554295</v>
       </c>
       <c r="F30" s="13" t="n">
-        <v>53461</v>
+        <v>34270</v>
       </c>
       <c r="G30" s="13" t="n">
-        <v>4324</v>
+        <v>2771</v>
       </c>
       <c r="H30" s="13" t="n">
-        <v>216175</v>
+        <v>138574</v>
       </c>
       <c r="I30" s="13" t="n">
-        <v>28680</v>
+        <v>19120</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>8.48</v>
+        <v>8.16</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="12" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="B31" s="12" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C31" s="12" t="n">
-        <v>160608</v>
+        <v>91776</v>
       </c>
       <c r="D31" s="13" t="n">
-        <v>1.2</v>
+        <v>0.68</v>
       </c>
       <c r="E31" s="13" t="n">
-        <v>948115</v>
+        <v>554295</v>
       </c>
       <c r="F31" s="13" t="n">
-        <v>62371</v>
+        <v>34270</v>
       </c>
       <c r="G31" s="13" t="n">
-        <v>4741</v>
+        <v>2771</v>
       </c>
       <c r="H31" s="13" t="n">
-        <v>237029</v>
+        <v>138574</v>
       </c>
       <c r="I31" s="13" t="n">
-        <v>33460</v>
+        <v>19120</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>8.01</v>
+        <v>8.16</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="12" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="B32" s="12" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="C32" s="12" t="n">
-        <v>137664</v>
+        <v>91776</v>
       </c>
       <c r="D32" s="13" t="n">
-        <v>1.02</v>
+        <v>0.68</v>
       </c>
       <c r="E32" s="13" t="n">
-        <v>812670</v>
+        <v>554295</v>
       </c>
       <c r="F32" s="13" t="n">
-        <v>53461</v>
+        <v>34270</v>
       </c>
       <c r="G32" s="13" t="n">
-        <v>4063</v>
+        <v>2771</v>
       </c>
       <c r="H32" s="13" t="n">
-        <v>203168</v>
+        <v>138574</v>
       </c>
       <c r="I32" s="13" t="n">
-        <v>28680</v>
+        <v>19120</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>8.01</v>
+        <v>8.16</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="12" t="n">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="B33" s="12" t="n">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C33" s="12" t="n">
-        <v>160608</v>
+        <v>91776</v>
       </c>
       <c r="D33" s="13" t="n">
-        <v>1.2</v>
+        <v>0.68</v>
       </c>
       <c r="E33" s="13" t="n">
-        <v>948115</v>
+        <v>576467</v>
       </c>
       <c r="F33" s="13" t="n">
-        <v>62371</v>
+        <v>35641</v>
       </c>
       <c r="G33" s="13" t="n">
-        <v>4741</v>
+        <v>2882</v>
       </c>
       <c r="H33" s="13" t="n">
-        <v>237029</v>
+        <v>144117</v>
       </c>
       <c r="I33" s="13" t="n">
-        <v>33460</v>
+        <v>19120</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>8.01</v>
+        <v>8.48</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="12" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="B34" s="12" t="n">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="C34" s="12" t="n">
-        <v>160608</v>
+        <v>114720</v>
       </c>
       <c r="D34" s="13" t="n">
-        <v>1.2</v>
+        <v>0.85</v>
       </c>
       <c r="E34" s="13" t="n">
-        <v>948115</v>
+        <v>720584</v>
       </c>
       <c r="F34" s="13" t="n">
-        <v>62371</v>
+        <v>44551</v>
       </c>
       <c r="G34" s="13" t="n">
-        <v>4741</v>
+        <v>3603</v>
       </c>
       <c r="H34" s="13" t="n">
-        <v>237029</v>
+        <v>180146</v>
       </c>
       <c r="I34" s="13" t="n">
-        <v>33460</v>
+        <v>23900</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>8.01</v>
+        <v>8.48</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="12" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="B35" s="12" t="n">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="C35" s="12" t="n">
-        <v>137664</v>
+        <v>91776</v>
       </c>
       <c r="D35" s="13" t="n">
-        <v>1.02</v>
+        <v>0.68</v>
       </c>
       <c r="E35" s="13" t="n">
-        <v>845177</v>
+        <v>576467</v>
       </c>
       <c r="F35" s="13" t="n">
-        <v>55600</v>
+        <v>35641</v>
       </c>
       <c r="G35" s="13" t="n">
-        <v>4226</v>
+        <v>2882</v>
       </c>
       <c r="H35" s="13" t="n">
-        <v>211294</v>
+        <v>144117</v>
       </c>
       <c r="I35" s="13" t="n">
-        <v>28680</v>
+        <v>19120</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>8.32</v>
+        <v>8.48</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="12" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="B36" s="12" t="n">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="C36" s="12" t="n">
-        <v>160608</v>
+        <v>114720</v>
       </c>
       <c r="D36" s="13" t="n">
-        <v>1.2</v>
+        <v>0.85</v>
       </c>
       <c r="E36" s="13" t="n">
-        <v>986040</v>
+        <v>720584</v>
       </c>
       <c r="F36" s="13" t="n">
-        <v>64866</v>
+        <v>44551</v>
       </c>
       <c r="G36" s="13" t="n">
-        <v>4930</v>
+        <v>3603</v>
       </c>
       <c r="H36" s="13" t="n">
-        <v>246510</v>
+        <v>180146</v>
       </c>
       <c r="I36" s="13" t="n">
-        <v>33460</v>
+        <v>23900</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>8.32</v>
+        <v>8.48</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="12" t="n">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B37" s="12" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C37" s="12" t="n">
-        <v>160608</v>
+        <v>114720</v>
       </c>
       <c r="D37" s="13" t="n">
-        <v>1.2</v>
+        <v>0.85</v>
       </c>
       <c r="E37" s="13" t="n">
-        <v>986040</v>
+        <v>720584</v>
       </c>
       <c r="F37" s="13" t="n">
-        <v>64866</v>
+        <v>44551</v>
       </c>
       <c r="G37" s="13" t="n">
-        <v>4930</v>
+        <v>3603</v>
       </c>
       <c r="H37" s="13" t="n">
-        <v>246510</v>
+        <v>180146</v>
       </c>
       <c r="I37" s="13" t="n">
-        <v>33460</v>
+        <v>23900</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>8.32</v>
+        <v>8.48</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="12" t="n">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="B38" s="12" t="n">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C38" s="12" t="n">
-        <v>160608</v>
+        <v>137664</v>
       </c>
       <c r="D38" s="13" t="n">
-        <v>1.2</v>
+        <v>1.02</v>
       </c>
       <c r="E38" s="13" t="n">
-        <v>986040</v>
+        <v>864701</v>
       </c>
       <c r="F38" s="13" t="n">
-        <v>64866</v>
+        <v>53461</v>
       </c>
       <c r="G38" s="13" t="n">
-        <v>4930</v>
+        <v>4324</v>
       </c>
       <c r="H38" s="13" t="n">
-        <v>246510</v>
+        <v>216175</v>
       </c>
       <c r="I38" s="13" t="n">
-        <v>33460</v>
+        <v>28680</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>8.32</v>
+        <v>8.48</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="12" t="n">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B39" s="12" t="n">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="C39" s="12" t="n">
-        <v>160608</v>
+        <v>137664</v>
       </c>
       <c r="D39" s="13" t="n">
-        <v>1.2</v>
+        <v>1.02</v>
       </c>
       <c r="E39" s="13" t="n">
-        <v>986040</v>
+        <v>864701</v>
       </c>
       <c r="F39" s="13" t="n">
-        <v>64866</v>
+        <v>53461</v>
       </c>
       <c r="G39" s="13" t="n">
-        <v>4930</v>
+        <v>4324</v>
       </c>
       <c r="H39" s="13" t="n">
-        <v>246510</v>
+        <v>216175</v>
       </c>
       <c r="I39" s="13" t="n">
-        <v>33460</v>
+        <v>28680</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>8.32</v>
+        <v>8.48</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="12" t="n">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="B40" s="12" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="C40" s="12" t="n">
-        <v>160608</v>
+        <v>137664</v>
       </c>
       <c r="D40" s="13" t="n">
-        <v>1.2</v>
+        <v>1.02</v>
       </c>
       <c r="E40" s="13" t="n">
-        <v>986040</v>
+        <v>864701</v>
       </c>
       <c r="F40" s="13" t="n">
-        <v>64866</v>
+        <v>53461</v>
       </c>
       <c r="G40" s="13" t="n">
-        <v>4930</v>
+        <v>4324</v>
       </c>
       <c r="H40" s="13" t="n">
-        <v>246510</v>
+        <v>216175</v>
       </c>
       <c r="I40" s="13" t="n">
-        <v>33460</v>
+        <v>28680</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>8.32</v>
+        <v>8.48</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="12" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="B41" s="12" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C41" s="12" t="n">
         <v>160608</v>
@@ -10540,62 +10540,62 @@
         <v>1.2</v>
       </c>
       <c r="E41" s="13" t="n">
-        <v>986040</v>
+        <v>948115</v>
       </c>
       <c r="F41" s="13" t="n">
-        <v>64866</v>
+        <v>62371</v>
       </c>
       <c r="G41" s="13" t="n">
-        <v>4930</v>
+        <v>4741</v>
       </c>
       <c r="H41" s="13" t="n">
-        <v>246510</v>
+        <v>237029</v>
       </c>
       <c r="I41" s="13" t="n">
         <v>33460</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>8.32</v>
+        <v>8.01</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="12" t="n">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="B42" s="12" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="C42" s="12" t="n">
-        <v>160608</v>
+        <v>137664</v>
       </c>
       <c r="D42" s="13" t="n">
-        <v>1.2</v>
+        <v>1.02</v>
       </c>
       <c r="E42" s="13" t="n">
-        <v>986040</v>
+        <v>812670</v>
       </c>
       <c r="F42" s="13" t="n">
-        <v>64866</v>
+        <v>53461</v>
       </c>
       <c r="G42" s="13" t="n">
-        <v>4930</v>
+        <v>4063</v>
       </c>
       <c r="H42" s="13" t="n">
-        <v>246510</v>
+        <v>203168</v>
       </c>
       <c r="I42" s="13" t="n">
-        <v>33460</v>
+        <v>28680</v>
       </c>
       <c r="J42" s="6" t="n">
-        <v>8.32</v>
+        <v>8.01</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="12" t="n">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="B43" s="12" t="n">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="C43" s="12" t="n">
         <v>160608</v>
@@ -10604,30 +10604,30 @@
         <v>1.2</v>
       </c>
       <c r="E43" s="13" t="n">
-        <v>986040</v>
+        <v>948115</v>
       </c>
       <c r="F43" s="13" t="n">
-        <v>64866</v>
+        <v>62371</v>
       </c>
       <c r="G43" s="13" t="n">
-        <v>4930</v>
+        <v>4741</v>
       </c>
       <c r="H43" s="13" t="n">
-        <v>246510</v>
+        <v>237029</v>
       </c>
       <c r="I43" s="13" t="n">
         <v>33460</v>
       </c>
       <c r="J43" s="6" t="n">
-        <v>8.32</v>
+        <v>8.01</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="12" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="B44" s="12" t="n">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="C44" s="12" t="n">
         <v>160608</v>
@@ -10636,51 +10636,51 @@
         <v>1.2</v>
       </c>
       <c r="E44" s="13" t="n">
-        <v>986040</v>
+        <v>948115</v>
       </c>
       <c r="F44" s="13" t="n">
-        <v>64866</v>
+        <v>62371</v>
       </c>
       <c r="G44" s="13" t="n">
-        <v>4930</v>
+        <v>4741</v>
       </c>
       <c r="H44" s="13" t="n">
-        <v>246510</v>
+        <v>237029</v>
       </c>
       <c r="I44" s="13" t="n">
         <v>33460</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>8.32</v>
+        <v>8.01</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="12" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="B45" s="12" t="n">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C45" s="12" t="n">
-        <v>160608</v>
+        <v>137664</v>
       </c>
       <c r="D45" s="13" t="n">
-        <v>1.2</v>
+        <v>1.02</v>
       </c>
       <c r="E45" s="13" t="n">
-        <v>986040</v>
+        <v>845177</v>
       </c>
       <c r="F45" s="13" t="n">
-        <v>64866</v>
+        <v>55600</v>
       </c>
       <c r="G45" s="13" t="n">
-        <v>4930</v>
+        <v>4226</v>
       </c>
       <c r="H45" s="13" t="n">
-        <v>246510</v>
+        <v>211294</v>
       </c>
       <c r="I45" s="13" t="n">
-        <v>33460</v>
+        <v>28680</v>
       </c>
       <c r="J45" s="6" t="n">
         <v>8.32</v>
@@ -10688,10 +10688,10 @@
     </row>
     <row r="46">
       <c r="A46" s="12" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="B46" s="12" t="n">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C46" s="12" t="n">
         <v>160608</v>
@@ -10715,6 +10715,326 @@
         <v>33460</v>
       </c>
       <c r="J46" s="6" t="n">
+        <v>8.32</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="12" t="n">
+        <v>51</v>
+      </c>
+      <c r="B47" s="12" t="n">
+        <v>55</v>
+      </c>
+      <c r="C47" s="12" t="n">
+        <v>160608</v>
+      </c>
+      <c r="D47" s="13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E47" s="13" t="n">
+        <v>986040</v>
+      </c>
+      <c r="F47" s="13" t="n">
+        <v>64866</v>
+      </c>
+      <c r="G47" s="13" t="n">
+        <v>4930</v>
+      </c>
+      <c r="H47" s="13" t="n">
+        <v>246510</v>
+      </c>
+      <c r="I47" s="13" t="n">
+        <v>33460</v>
+      </c>
+      <c r="J47" s="6" t="n">
+        <v>8.32</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="12" t="n">
+        <v>52</v>
+      </c>
+      <c r="B48" s="12" t="n">
+        <v>56</v>
+      </c>
+      <c r="C48" s="12" t="n">
+        <v>160608</v>
+      </c>
+      <c r="D48" s="13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E48" s="13" t="n">
+        <v>986040</v>
+      </c>
+      <c r="F48" s="13" t="n">
+        <v>64866</v>
+      </c>
+      <c r="G48" s="13" t="n">
+        <v>4930</v>
+      </c>
+      <c r="H48" s="13" t="n">
+        <v>246510</v>
+      </c>
+      <c r="I48" s="13" t="n">
+        <v>33460</v>
+      </c>
+      <c r="J48" s="6" t="n">
+        <v>8.32</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="12" t="n">
+        <v>53</v>
+      </c>
+      <c r="B49" s="12" t="n">
+        <v>57</v>
+      </c>
+      <c r="C49" s="12" t="n">
+        <v>160608</v>
+      </c>
+      <c r="D49" s="13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E49" s="13" t="n">
+        <v>986040</v>
+      </c>
+      <c r="F49" s="13" t="n">
+        <v>64866</v>
+      </c>
+      <c r="G49" s="13" t="n">
+        <v>4930</v>
+      </c>
+      <c r="H49" s="13" t="n">
+        <v>246510</v>
+      </c>
+      <c r="I49" s="13" t="n">
+        <v>33460</v>
+      </c>
+      <c r="J49" s="6" t="n">
+        <v>8.32</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="12" t="n">
+        <v>54</v>
+      </c>
+      <c r="B50" s="12" t="n">
+        <v>58</v>
+      </c>
+      <c r="C50" s="12" t="n">
+        <v>160608</v>
+      </c>
+      <c r="D50" s="13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E50" s="13" t="n">
+        <v>986040</v>
+      </c>
+      <c r="F50" s="13" t="n">
+        <v>64866</v>
+      </c>
+      <c r="G50" s="13" t="n">
+        <v>4930</v>
+      </c>
+      <c r="H50" s="13" t="n">
+        <v>246510</v>
+      </c>
+      <c r="I50" s="13" t="n">
+        <v>33460</v>
+      </c>
+      <c r="J50" s="6" t="n">
+        <v>8.32</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="12" t="n">
+        <v>55</v>
+      </c>
+      <c r="B51" s="12" t="n">
+        <v>59</v>
+      </c>
+      <c r="C51" s="12" t="n">
+        <v>160608</v>
+      </c>
+      <c r="D51" s="13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E51" s="13" t="n">
+        <v>986040</v>
+      </c>
+      <c r="F51" s="13" t="n">
+        <v>64866</v>
+      </c>
+      <c r="G51" s="13" t="n">
+        <v>4930</v>
+      </c>
+      <c r="H51" s="13" t="n">
+        <v>246510</v>
+      </c>
+      <c r="I51" s="13" t="n">
+        <v>33460</v>
+      </c>
+      <c r="J51" s="6" t="n">
+        <v>8.32</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="12" t="n">
+        <v>56</v>
+      </c>
+      <c r="B52" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="C52" s="12" t="n">
+        <v>160608</v>
+      </c>
+      <c r="D52" s="13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E52" s="13" t="n">
+        <v>986040</v>
+      </c>
+      <c r="F52" s="13" t="n">
+        <v>64866</v>
+      </c>
+      <c r="G52" s="13" t="n">
+        <v>4930</v>
+      </c>
+      <c r="H52" s="13" t="n">
+        <v>246510</v>
+      </c>
+      <c r="I52" s="13" t="n">
+        <v>33460</v>
+      </c>
+      <c r="J52" s="6" t="n">
+        <v>8.32</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="12" t="n">
+        <v>57</v>
+      </c>
+      <c r="B53" s="12" t="n">
+        <v>61</v>
+      </c>
+      <c r="C53" s="12" t="n">
+        <v>160608</v>
+      </c>
+      <c r="D53" s="13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E53" s="13" t="n">
+        <v>986040</v>
+      </c>
+      <c r="F53" s="13" t="n">
+        <v>64866</v>
+      </c>
+      <c r="G53" s="13" t="n">
+        <v>4930</v>
+      </c>
+      <c r="H53" s="13" t="n">
+        <v>246510</v>
+      </c>
+      <c r="I53" s="13" t="n">
+        <v>33460</v>
+      </c>
+      <c r="J53" s="6" t="n">
+        <v>8.32</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="12" t="n">
+        <v>58</v>
+      </c>
+      <c r="B54" s="12" t="n">
+        <v>62</v>
+      </c>
+      <c r="C54" s="12" t="n">
+        <v>160608</v>
+      </c>
+      <c r="D54" s="13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E54" s="13" t="n">
+        <v>986040</v>
+      </c>
+      <c r="F54" s="13" t="n">
+        <v>64866</v>
+      </c>
+      <c r="G54" s="13" t="n">
+        <v>4930</v>
+      </c>
+      <c r="H54" s="13" t="n">
+        <v>246510</v>
+      </c>
+      <c r="I54" s="13" t="n">
+        <v>33460</v>
+      </c>
+      <c r="J54" s="6" t="n">
+        <v>8.32</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="12" t="n">
+        <v>59</v>
+      </c>
+      <c r="B55" s="12" t="n">
+        <v>63</v>
+      </c>
+      <c r="C55" s="12" t="n">
+        <v>160608</v>
+      </c>
+      <c r="D55" s="13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E55" s="13" t="n">
+        <v>986040</v>
+      </c>
+      <c r="F55" s="13" t="n">
+        <v>64866</v>
+      </c>
+      <c r="G55" s="13" t="n">
+        <v>4930</v>
+      </c>
+      <c r="H55" s="13" t="n">
+        <v>246510</v>
+      </c>
+      <c r="I55" s="13" t="n">
+        <v>33460</v>
+      </c>
+      <c r="J55" s="6" t="n">
+        <v>8.32</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="B56" s="12" t="n">
+        <v>64</v>
+      </c>
+      <c r="C56" s="12" t="n">
+        <v>160608</v>
+      </c>
+      <c r="D56" s="13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E56" s="13" t="n">
+        <v>986040</v>
+      </c>
+      <c r="F56" s="13" t="n">
+        <v>64866</v>
+      </c>
+      <c r="G56" s="13" t="n">
+        <v>4930</v>
+      </c>
+      <c r="H56" s="13" t="n">
+        <v>246510</v>
+      </c>
+      <c r="I56" s="13" t="n">
+        <v>33460</v>
+      </c>
+      <c r="J56" s="6" t="n">
         <v>8.32</v>
       </c>
     </row>

--- a/finance/outputs/mulligan-mints-5yr-model.xlsx
+++ b/finance/outputs/mulligan-mints-5yr-model.xlsx
@@ -28,7 +28,7 @@
     <numFmt numFmtId="164" formatCode="#,##0.00;[Red](#,##0.00)"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="#,##0;[Red](#,##0)"/>
-    <numFmt numFmtId="167" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="167" formatCode="0;;&quot;never&quot;"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -1424,7 +1424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G90"/>
+  <dimension ref="A1:G120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1991,7 +1991,7 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>BEAR — Bear — slow venue adoption, retail delayed, no export scale</t>
+          <t>BOOTSTRAP — Bootstrap — founder-funded, golf and bars only, no growth round</t>
         </is>
       </c>
       <c r="B33" s="5" t="n"/>
@@ -2035,19 +2035,19 @@
         </is>
       </c>
       <c r="B35" s="12" t="n">
-        <v>11034</v>
+        <v>6800</v>
       </c>
       <c r="C35" s="12" t="n">
-        <v>82395</v>
+        <v>46870</v>
       </c>
       <c r="D35" s="12" t="n">
-        <v>249588</v>
+        <v>97490</v>
       </c>
       <c r="E35" s="12" t="n">
-        <v>511526</v>
+        <v>157700</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>805764</v>
+        <v>220215</v>
       </c>
     </row>
     <row r="37">
@@ -2057,19 +2057,19 @@
         </is>
       </c>
       <c r="B37" s="13" t="n">
-        <v>126375</v>
+        <v>95060</v>
       </c>
       <c r="C37" s="13" t="n">
-        <v>832893</v>
+        <v>696909</v>
       </c>
       <c r="D37" s="13" t="n">
-        <v>1507738</v>
+        <v>1427415</v>
       </c>
       <c r="E37" s="13" t="n">
-        <v>2052826</v>
+        <v>2287340</v>
       </c>
       <c r="F37" s="13" t="n">
-        <v>2449877</v>
+        <v>3123722</v>
       </c>
     </row>
     <row r="38">
@@ -2079,19 +2079,19 @@
         </is>
       </c>
       <c r="B38" s="13" t="n">
-        <v>100526</v>
+        <v>40740</v>
       </c>
       <c r="C38" s="13" t="n">
-        <v>841697</v>
+        <v>343744</v>
       </c>
       <c r="D38" s="13" t="n">
-        <v>2080738</v>
+        <v>890296</v>
       </c>
       <c r="E38" s="13" t="n">
-        <v>3651558</v>
+        <v>1735436</v>
       </c>
       <c r="F38" s="13" t="n">
-        <v>5211067</v>
+        <v>2836773</v>
       </c>
     </row>
     <row r="39">
@@ -2101,19 +2101,19 @@
         </is>
       </c>
       <c r="B39" s="13" t="n">
-        <v>35532</v>
+        <v>42000</v>
       </c>
       <c r="C39" s="13" t="n">
-        <v>223852</v>
+        <v>220500</v>
       </c>
       <c r="D39" s="13" t="n">
-        <v>430914</v>
+        <v>416745</v>
       </c>
       <c r="E39" s="13" t="n">
-        <v>658124</v>
+        <v>583443</v>
       </c>
       <c r="F39" s="13" t="n">
-        <v>863787</v>
+        <v>765769</v>
       </c>
     </row>
     <row r="40">
@@ -2126,16 +2126,16 @@
         <v>0</v>
       </c>
       <c r="C40" s="13" t="n">
-        <v>94018</v>
+        <v>0</v>
       </c>
       <c r="D40" s="13" t="n">
-        <v>947963</v>
+        <v>0</v>
       </c>
       <c r="E40" s="13" t="n">
-        <v>2367703</v>
+        <v>0</v>
       </c>
       <c r="F40" s="13" t="n">
-        <v>3990698</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2151,13 +2151,13 @@
         <v>0</v>
       </c>
       <c r="D41" s="13" t="n">
-        <v>650569</v>
+        <v>0</v>
       </c>
       <c r="E41" s="13" t="n">
-        <v>2428790</v>
+        <v>0</v>
       </c>
       <c r="F41" s="13" t="n">
-        <v>5180153</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2179,7 +2179,7 @@
         <v>0</v>
       </c>
       <c r="F42" s="13" t="n">
-        <v>0</v>
+        <v>400000</v>
       </c>
     </row>
     <row r="43">
@@ -2189,19 +2189,19 @@
         </is>
       </c>
       <c r="B43" s="14" t="n">
-        <v>262433</v>
+        <v>177800</v>
       </c>
       <c r="C43" s="14" t="n">
-        <v>1992459</v>
+        <v>1261152</v>
       </c>
       <c r="D43" s="14" t="n">
-        <v>5617922</v>
+        <v>2734456</v>
       </c>
       <c r="E43" s="14" t="n">
-        <v>11159001</v>
+        <v>4606219</v>
       </c>
       <c r="F43" s="14" t="n">
-        <v>17695582</v>
+        <v>7126264</v>
       </c>
     </row>
     <row r="44">
@@ -2211,19 +2211,19 @@
         </is>
       </c>
       <c r="B44" s="13" t="n">
-        <v>121954</v>
+        <v>69974</v>
       </c>
       <c r="C44" s="13" t="n">
-        <v>925382</v>
+        <v>488434</v>
       </c>
       <c r="D44" s="13" t="n">
-        <v>2657361</v>
+        <v>1058633</v>
       </c>
       <c r="E44" s="13" t="n">
-        <v>5185833</v>
+        <v>1646678</v>
       </c>
       <c r="F44" s="13" t="n">
-        <v>7759367</v>
+        <v>2308431</v>
       </c>
     </row>
     <row r="45">
@@ -2233,19 +2233,19 @@
         </is>
       </c>
       <c r="B45" s="14" t="n">
-        <v>140480</v>
+        <v>107826</v>
       </c>
       <c r="C45" s="14" t="n">
-        <v>1067077</v>
+        <v>772719</v>
       </c>
       <c r="D45" s="14" t="n">
-        <v>2960561</v>
+        <v>1675823</v>
       </c>
       <c r="E45" s="14" t="n">
-        <v>5973168</v>
+        <v>2959541</v>
       </c>
       <c r="F45" s="14" t="n">
-        <v>9936216</v>
+        <v>4817833</v>
       </c>
     </row>
     <row r="47">
@@ -2255,19 +2255,19 @@
         </is>
       </c>
       <c r="B47" s="13" t="n">
-        <v>114000</v>
+        <v>0</v>
       </c>
       <c r="C47" s="13" t="n">
-        <v>1051520</v>
+        <v>190800</v>
       </c>
       <c r="D47" s="13" t="n">
-        <v>2206750</v>
+        <v>533710</v>
       </c>
       <c r="E47" s="13" t="n">
-        <v>4209051</v>
+        <v>890880</v>
       </c>
       <c r="F47" s="13" t="n">
-        <v>5923542</v>
+        <v>1333176</v>
       </c>
     </row>
     <row r="48">
@@ -2277,19 +2277,19 @@
         </is>
       </c>
       <c r="B48" s="13" t="n">
-        <v>209000</v>
+        <v>60000</v>
       </c>
       <c r="C48" s="13" t="n">
-        <v>458944</v>
+        <v>100892</v>
       </c>
       <c r="D48" s="13" t="n">
-        <v>1630330</v>
+        <v>218757</v>
       </c>
       <c r="E48" s="13" t="n">
-        <v>1659080</v>
+        <v>322435</v>
       </c>
       <c r="F48" s="13" t="n">
-        <v>1946514</v>
+        <v>498838</v>
       </c>
     </row>
     <row r="49">
@@ -2299,19 +2299,19 @@
         </is>
       </c>
       <c r="B49" s="13" t="n">
-        <v>14896</v>
+        <v>9180</v>
       </c>
       <c r="C49" s="13" t="n">
-        <v>112673</v>
+        <v>67071</v>
       </c>
       <c r="D49" s="13" t="n">
-        <v>295016</v>
+        <v>147879</v>
       </c>
       <c r="E49" s="13" t="n">
-        <v>541425</v>
+        <v>253561</v>
       </c>
       <c r="F49" s="13" t="n">
-        <v>825592</v>
+        <v>375322</v>
       </c>
     </row>
     <row r="50">
@@ -2321,19 +2321,19 @@
         </is>
       </c>
       <c r="B50" s="13" t="n">
-        <v>6807</v>
+        <v>4074</v>
       </c>
       <c r="C50" s="13" t="n">
-        <v>46450</v>
+        <v>31220</v>
       </c>
       <c r="D50" s="13" t="n">
-        <v>79564</v>
+        <v>69531</v>
       </c>
       <c r="E50" s="13" t="n">
-        <v>94449</v>
+        <v>120683</v>
       </c>
       <c r="F50" s="13" t="n">
-        <v>104763</v>
+        <v>178815</v>
       </c>
     </row>
     <row r="51">
@@ -2346,16 +2346,16 @@
         <v>0</v>
       </c>
       <c r="C51" s="13" t="n">
-        <v>29887</v>
+        <v>0</v>
       </c>
       <c r="D51" s="13" t="n">
-        <v>177415</v>
+        <v>27345</v>
       </c>
       <c r="E51" s="13" t="n">
-        <v>393195</v>
+        <v>69093</v>
       </c>
       <c r="F51" s="13" t="n">
-        <v>664721</v>
+        <v>106894</v>
       </c>
     </row>
     <row r="52">
@@ -2365,19 +2365,19 @@
         </is>
       </c>
       <c r="B52" s="13" t="n">
-        <v>392400</v>
+        <v>196200</v>
       </c>
       <c r="C52" s="13" t="n">
-        <v>554592</v>
+        <v>277296</v>
       </c>
       <c r="D52" s="13" t="n">
-        <v>587868</v>
+        <v>293934</v>
       </c>
       <c r="E52" s="13" t="n">
-        <v>623140</v>
+        <v>311570</v>
       </c>
       <c r="F52" s="13" t="n">
-        <v>660528</v>
+        <v>330264</v>
       </c>
     </row>
     <row r="53">
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="B53" s="13" t="n">
-        <v>388000</v>
+        <v>157000</v>
       </c>
       <c r="C53" s="13" t="n">
         <v>0</v>
@@ -2409,19 +2409,19 @@
         </is>
       </c>
       <c r="B54" s="14" t="n">
-        <v>1125103</v>
+        <v>426454</v>
       </c>
       <c r="C54" s="14" t="n">
-        <v>2254066</v>
+        <v>667279</v>
       </c>
       <c r="D54" s="14" t="n">
-        <v>4976943</v>
+        <v>1291155</v>
       </c>
       <c r="E54" s="14" t="n">
-        <v>7520340</v>
+        <v>1968223</v>
       </c>
       <c r="F54" s="14" t="n">
-        <v>10125659</v>
+        <v>2823309</v>
       </c>
     </row>
     <row r="56">
@@ -2431,19 +2431,19 @@
         </is>
       </c>
       <c r="B56" s="14" t="n">
-        <v>-984623</v>
+        <v>-318628</v>
       </c>
       <c r="C56" s="14" t="n">
-        <v>-1186989</v>
+        <v>105440</v>
       </c>
       <c r="D56" s="14" t="n">
-        <v>-2016383</v>
+        <v>384668</v>
       </c>
       <c r="E56" s="14" t="n">
-        <v>-1547172</v>
+        <v>991318</v>
       </c>
       <c r="F56" s="14" t="n">
-        <v>-189443</v>
+        <v>1994524</v>
       </c>
     </row>
     <row r="57">
@@ -2456,16 +2456,16 @@
         <v>0</v>
       </c>
       <c r="C57" s="13" t="n">
-        <v>0</v>
+        <v>6058</v>
       </c>
       <c r="D57" s="13" t="n">
-        <v>0</v>
+        <v>40241</v>
       </c>
       <c r="E57" s="13" t="n">
-        <v>0</v>
+        <v>267656</v>
       </c>
       <c r="F57" s="13" t="n">
-        <v>3676</v>
+        <v>538522</v>
       </c>
     </row>
     <row r="58">
@@ -2475,19 +2475,19 @@
         </is>
       </c>
       <c r="B58" s="14" t="n">
-        <v>-984623</v>
+        <v>-318628</v>
       </c>
       <c r="C58" s="14" t="n">
-        <v>-1186989</v>
+        <v>99382</v>
       </c>
       <c r="D58" s="14" t="n">
-        <v>-2016383</v>
+        <v>344427</v>
       </c>
       <c r="E58" s="14" t="n">
-        <v>-1547172</v>
+        <v>723662</v>
       </c>
       <c r="F58" s="14" t="n">
-        <v>-193120</v>
+        <v>1456003</v>
       </c>
     </row>
     <row r="59">
@@ -2497,19 +2497,19 @@
         </is>
       </c>
       <c r="B59" s="15" t="n">
-        <v>0.5352961739401985</v>
+        <v>0.6064441489274482</v>
       </c>
       <c r="C59" s="15" t="n">
-        <v>0.5355578376499529</v>
+        <v>0.6127085630312291</v>
       </c>
       <c r="D59" s="15" t="n">
-        <v>0.5269850089444209</v>
+        <v>0.6128543084418331</v>
       </c>
       <c r="E59" s="15" t="n">
-        <v>0.5352779821328782</v>
+        <v>0.6425098498730283</v>
       </c>
       <c r="F59" s="15" t="n">
-        <v>0.5615082689949957</v>
+        <v>0.6760671975951418</v>
       </c>
     </row>
     <row r="60">
@@ -2519,25 +2519,25 @@
         </is>
       </c>
       <c r="B60" s="15" t="n">
-        <v>-3.751897507520277</v>
+        <v>-1.792059788080426</v>
       </c>
       <c r="C60" s="15" t="n">
-        <v>-0.5957404224697753</v>
+        <v>0.08360617661261731</v>
       </c>
       <c r="D60" s="15" t="n">
-        <v>-0.3589196616911676</v>
+        <v>0.1406745788208537</v>
       </c>
       <c r="E60" s="15" t="n">
-        <v>-0.1386479206512514</v>
+        <v>0.2152129589740633</v>
       </c>
       <c r="F60" s="15" t="n">
-        <v>-0.01070568411541408</v>
+        <v>0.2798835697965889</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>BULL — Bull — creator-led breakout, export pulls forward</t>
+          <t>BEAR — Bear — slow venue adoption, retail delayed, no export scale</t>
         </is>
       </c>
       <c r="B63" s="5" t="n"/>
@@ -2581,19 +2581,19 @@
         </is>
       </c>
       <c r="B65" s="12" t="n">
-        <v>38006</v>
+        <v>11034</v>
       </c>
       <c r="C65" s="12" t="n">
-        <v>283805</v>
+        <v>82395</v>
       </c>
       <c r="D65" s="12" t="n">
-        <v>859692</v>
+        <v>249588</v>
       </c>
       <c r="E65" s="12" t="n">
-        <v>1761924</v>
+        <v>511526</v>
       </c>
       <c r="F65" s="12" t="n">
-        <v>2775411</v>
+        <v>805764</v>
       </c>
     </row>
     <row r="67">
@@ -2603,19 +2603,19 @@
         </is>
       </c>
       <c r="B67" s="13" t="n">
-        <v>476970</v>
+        <v>126375</v>
       </c>
       <c r="C67" s="13" t="n">
-        <v>3143533</v>
+        <v>832893</v>
       </c>
       <c r="D67" s="13" t="n">
-        <v>5690554</v>
+        <v>1507738</v>
       </c>
       <c r="E67" s="13" t="n">
-        <v>7747842</v>
+        <v>2052826</v>
       </c>
       <c r="F67" s="13" t="n">
-        <v>9246402</v>
+        <v>2449877</v>
       </c>
     </row>
     <row r="68">
@@ -2625,19 +2625,19 @@
         </is>
       </c>
       <c r="B68" s="13" t="n">
-        <v>379408</v>
+        <v>100526</v>
       </c>
       <c r="C68" s="13" t="n">
-        <v>3176758</v>
+        <v>841697</v>
       </c>
       <c r="D68" s="13" t="n">
-        <v>7853186</v>
+        <v>2080738</v>
       </c>
       <c r="E68" s="13" t="n">
-        <v>13781827</v>
+        <v>3651558</v>
       </c>
       <c r="F68" s="13" t="n">
-        <v>19667775</v>
+        <v>5211067</v>
       </c>
     </row>
     <row r="69">
@@ -2647,19 +2647,19 @@
         </is>
       </c>
       <c r="B69" s="13" t="n">
-        <v>134106</v>
+        <v>35532</v>
       </c>
       <c r="C69" s="13" t="n">
-        <v>844868</v>
+        <v>223852</v>
       </c>
       <c r="D69" s="13" t="n">
-        <v>1626371</v>
+        <v>430914</v>
       </c>
       <c r="E69" s="13" t="n">
-        <v>2483911</v>
+        <v>658124</v>
       </c>
       <c r="F69" s="13" t="n">
-        <v>3260134</v>
+        <v>863787</v>
       </c>
     </row>
     <row r="70">
@@ -2672,16 +2672,16 @@
         <v>0</v>
       </c>
       <c r="C70" s="13" t="n">
-        <v>354844</v>
+        <v>94018</v>
       </c>
       <c r="D70" s="13" t="n">
-        <v>3577830</v>
+        <v>947963</v>
       </c>
       <c r="E70" s="13" t="n">
-        <v>8936259</v>
+        <v>2367703</v>
       </c>
       <c r="F70" s="13" t="n">
-        <v>15061817</v>
+        <v>3990698</v>
       </c>
     </row>
     <row r="71">
@@ -2697,13 +2697,13 @@
         <v>0</v>
       </c>
       <c r="D71" s="13" t="n">
-        <v>2455397</v>
+        <v>650569</v>
       </c>
       <c r="E71" s="13" t="n">
-        <v>9166816</v>
+        <v>2428790</v>
       </c>
       <c r="F71" s="13" t="n">
-        <v>19551099</v>
+        <v>5180153</v>
       </c>
     </row>
     <row r="72">
@@ -2722,10 +2722,10 @@
         <v>0</v>
       </c>
       <c r="E72" s="13" t="n">
-        <v>400000</v>
+        <v>0</v>
       </c>
       <c r="F72" s="13" t="n">
-        <v>1800000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -2735,19 +2735,19 @@
         </is>
       </c>
       <c r="B73" s="14" t="n">
-        <v>990485</v>
+        <v>262433</v>
       </c>
       <c r="C73" s="14" t="n">
-        <v>7520003</v>
+        <v>1992459</v>
       </c>
       <c r="D73" s="14" t="n">
-        <v>21203339</v>
+        <v>5617922</v>
       </c>
       <c r="E73" s="14" t="n">
-        <v>42516655</v>
+        <v>11159001</v>
       </c>
       <c r="F73" s="14" t="n">
-        <v>68587227</v>
+        <v>17695582</v>
       </c>
     </row>
     <row r="74">
@@ -2757,19 +2757,19 @@
         </is>
       </c>
       <c r="B74" s="13" t="n">
-        <v>372989</v>
+        <v>121954</v>
       </c>
       <c r="C74" s="13" t="n">
-        <v>2594799</v>
+        <v>925382</v>
       </c>
       <c r="D74" s="13" t="n">
-        <v>6944339</v>
+        <v>2657361</v>
       </c>
       <c r="E74" s="13" t="n">
-        <v>13628243</v>
+        <v>5185833</v>
       </c>
       <c r="F74" s="13" t="n">
-        <v>21998999</v>
+        <v>7759367</v>
       </c>
     </row>
     <row r="75">
@@ -2779,19 +2779,19 @@
         </is>
       </c>
       <c r="B75" s="14" t="n">
-        <v>617496</v>
+        <v>140480</v>
       </c>
       <c r="C75" s="14" t="n">
-        <v>4925204</v>
+        <v>1067077</v>
       </c>
       <c r="D75" s="14" t="n">
-        <v>14258999</v>
+        <v>2960561</v>
       </c>
       <c r="E75" s="14" t="n">
-        <v>28888412</v>
+        <v>5973168</v>
       </c>
       <c r="F75" s="14" t="n">
-        <v>46588228</v>
+        <v>9936216</v>
       </c>
     </row>
     <row r="77">
@@ -2801,19 +2801,19 @@
         </is>
       </c>
       <c r="B77" s="13" t="n">
-        <v>522000</v>
+        <v>114000</v>
       </c>
       <c r="C77" s="13" t="n">
-        <v>1407680</v>
+        <v>1051520</v>
       </c>
       <c r="D77" s="13" t="n">
-        <v>3137091</v>
+        <v>2206750</v>
       </c>
       <c r="E77" s="13" t="n">
-        <v>4895076</v>
+        <v>4209051</v>
       </c>
       <c r="F77" s="13" t="n">
-        <v>6650729</v>
+        <v>5923542</v>
       </c>
     </row>
     <row r="78">
@@ -2823,19 +2823,19 @@
         </is>
       </c>
       <c r="B78" s="13" t="n">
-        <v>494000</v>
+        <v>209000</v>
       </c>
       <c r="C78" s="13" t="n">
-        <v>1232800</v>
+        <v>458944</v>
       </c>
       <c r="D78" s="13" t="n">
-        <v>3656434</v>
+        <v>1630330</v>
       </c>
       <c r="E78" s="13" t="n">
-        <v>5421999</v>
+        <v>1659080</v>
       </c>
       <c r="F78" s="13" t="n">
-        <v>7544595</v>
+        <v>1946514</v>
       </c>
     </row>
     <row r="79">
@@ -2845,19 +2845,19 @@
         </is>
       </c>
       <c r="B79" s="13" t="n">
-        <v>51308</v>
+        <v>14896</v>
       </c>
       <c r="C79" s="13" t="n">
-        <v>388094</v>
+        <v>112673</v>
       </c>
       <c r="D79" s="13" t="n">
-        <v>1016166</v>
+        <v>295016</v>
       </c>
       <c r="E79" s="13" t="n">
-        <v>1864910</v>
+        <v>541425</v>
       </c>
       <c r="F79" s="13" t="n">
-        <v>2843705</v>
+        <v>825592</v>
       </c>
     </row>
     <row r="80">
@@ -2867,19 +2867,19 @@
         </is>
       </c>
       <c r="B80" s="13" t="n">
-        <v>25691</v>
+        <v>6807</v>
       </c>
       <c r="C80" s="13" t="n">
-        <v>175313</v>
+        <v>46450</v>
       </c>
       <c r="D80" s="13" t="n">
-        <v>300294</v>
+        <v>79564</v>
       </c>
       <c r="E80" s="13" t="n">
-        <v>356472</v>
+        <v>94449</v>
       </c>
       <c r="F80" s="13" t="n">
-        <v>395399</v>
+        <v>104763</v>
       </c>
     </row>
     <row r="81">
@@ -2892,16 +2892,16 @@
         <v>0</v>
       </c>
       <c r="C81" s="13" t="n">
-        <v>112800</v>
+        <v>29887</v>
       </c>
       <c r="D81" s="13" t="n">
-        <v>669606</v>
+        <v>177415</v>
       </c>
       <c r="E81" s="13" t="n">
-        <v>1492010</v>
+        <v>393195</v>
       </c>
       <c r="F81" s="13" t="n">
-        <v>2544810</v>
+        <v>664721</v>
       </c>
     </row>
     <row r="82">
@@ -2911,19 +2911,19 @@
         </is>
       </c>
       <c r="B82" s="13" t="n">
-        <v>539550</v>
+        <v>392400</v>
       </c>
       <c r="C82" s="13" t="n">
-        <v>762564</v>
+        <v>554592</v>
       </c>
       <c r="D82" s="13" t="n">
-        <v>808318</v>
+        <v>587868</v>
       </c>
       <c r="E82" s="13" t="n">
-        <v>856817</v>
+        <v>623140</v>
       </c>
       <c r="F82" s="13" t="n">
-        <v>908226</v>
+        <v>660528</v>
       </c>
     </row>
     <row r="83">
@@ -2955,19 +2955,19 @@
         </is>
       </c>
       <c r="B84" s="14" t="n">
-        <v>2020549</v>
+        <v>1125103</v>
       </c>
       <c r="C84" s="14" t="n">
-        <v>4079252</v>
+        <v>2254066</v>
       </c>
       <c r="D84" s="14" t="n">
-        <v>9587909</v>
+        <v>4976943</v>
       </c>
       <c r="E84" s="14" t="n">
-        <v>14887283</v>
+        <v>7520340</v>
       </c>
       <c r="F84" s="14" t="n">
-        <v>20887463</v>
+        <v>10125659</v>
       </c>
     </row>
     <row r="86">
@@ -2977,19 +2977,19 @@
         </is>
       </c>
       <c r="B86" s="14" t="n">
-        <v>-1403054</v>
+        <v>-984623</v>
       </c>
       <c r="C86" s="14" t="n">
-        <v>845952</v>
+        <v>-1186989</v>
       </c>
       <c r="D86" s="14" t="n">
-        <v>4671090</v>
+        <v>-2016383</v>
       </c>
       <c r="E86" s="14" t="n">
-        <v>14001129</v>
+        <v>-1547172</v>
       </c>
       <c r="F86" s="14" t="n">
-        <v>25700765</v>
+        <v>-189443</v>
       </c>
     </row>
     <row r="87">
@@ -3002,16 +3002,16 @@
         <v>0</v>
       </c>
       <c r="C87" s="13" t="n">
-        <v>51359</v>
+        <v>0</v>
       </c>
       <c r="D87" s="13" t="n">
-        <v>1059418</v>
+        <v>0</v>
       </c>
       <c r="E87" s="13" t="n">
-        <v>3780305</v>
+        <v>0</v>
       </c>
       <c r="F87" s="13" t="n">
-        <v>6939207</v>
+        <v>3676</v>
       </c>
     </row>
     <row r="88">
@@ -3021,19 +3021,19 @@
         </is>
       </c>
       <c r="B88" s="14" t="n">
-        <v>-1403054</v>
+        <v>-984623</v>
       </c>
       <c r="C88" s="14" t="n">
-        <v>794593</v>
+        <v>-1186989</v>
       </c>
       <c r="D88" s="14" t="n">
-        <v>3611672</v>
+        <v>-2016383</v>
       </c>
       <c r="E88" s="14" t="n">
-        <v>10220824</v>
+        <v>-1547172</v>
       </c>
       <c r="F88" s="14" t="n">
-        <v>18761558</v>
+        <v>-193120</v>
       </c>
     </row>
     <row r="89">
@@ -3043,19 +3043,19 @@
         </is>
       </c>
       <c r="B89" s="15" t="n">
-        <v>0.6234281424623985</v>
+        <v>0.5352961739401985</v>
       </c>
       <c r="C89" s="15" t="n">
-        <v>0.6549471112262671</v>
+        <v>0.5355578376499529</v>
       </c>
       <c r="D89" s="15" t="n">
-        <v>0.6724884021143732</v>
+        <v>0.5269850089444209</v>
       </c>
       <c r="E89" s="15" t="n">
-        <v>0.6794610631616296</v>
+        <v>0.5352779821328782</v>
       </c>
       <c r="F89" s="15" t="n">
-        <v>0.6792551645258191</v>
+        <v>0.5615082689949957</v>
       </c>
     </row>
     <row r="90">
@@ -3065,18 +3065,564 @@
         </is>
       </c>
       <c r="B90" s="15" t="n">
+        <v>-3.751897507520277</v>
+      </c>
+      <c r="C90" s="15" t="n">
+        <v>-0.5957404224697753</v>
+      </c>
+      <c r="D90" s="15" t="n">
+        <v>-0.3589196616911676</v>
+      </c>
+      <c r="E90" s="15" t="n">
+        <v>-0.1386479206512514</v>
+      </c>
+      <c r="F90" s="15" t="n">
+        <v>-0.01070568411541408</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>BULL — Bull — creator-led breakout, export pulls forward</t>
+        </is>
+      </c>
+      <c r="B93" s="5" t="n"/>
+      <c r="C93" s="5" t="n"/>
+      <c r="D93" s="5" t="n"/>
+      <c r="E93" s="5" t="n"/>
+      <c r="F93" s="5" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="10" t="inlineStr"/>
+      <c r="B94" s="11" t="inlineStr">
+        <is>
+          <t>Year 1</t>
+        </is>
+      </c>
+      <c r="C94" s="11" t="inlineStr">
+        <is>
+          <t>Year 2</t>
+        </is>
+      </c>
+      <c r="D94" s="11" t="inlineStr">
+        <is>
+          <t>Year 3</t>
+        </is>
+      </c>
+      <c r="E94" s="11" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="F94" s="11" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Units sold</t>
+        </is>
+      </c>
+      <c r="B95" s="12" t="n">
+        <v>38006</v>
+      </c>
+      <c r="C95" s="12" t="n">
+        <v>283805</v>
+      </c>
+      <c r="D95" s="12" t="n">
+        <v>859692</v>
+      </c>
+      <c r="E95" s="12" t="n">
+        <v>1761924</v>
+      </c>
+      <c r="F95" s="12" t="n">
+        <v>2775411</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Revenue — golf clubs</t>
+        </is>
+      </c>
+      <c r="B97" s="13" t="n">
+        <v>476970</v>
+      </c>
+      <c r="C97" s="13" t="n">
+        <v>3143533</v>
+      </c>
+      <c r="D97" s="13" t="n">
+        <v>5690554</v>
+      </c>
+      <c r="E97" s="13" t="n">
+        <v>7747842</v>
+      </c>
+      <c r="F97" s="13" t="n">
+        <v>9246402</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Revenue — bars &amp; restaurants</t>
+        </is>
+      </c>
+      <c r="B98" s="13" t="n">
+        <v>379408</v>
+      </c>
+      <c r="C98" s="13" t="n">
+        <v>3176758</v>
+      </c>
+      <c r="D98" s="13" t="n">
+        <v>7853186</v>
+      </c>
+      <c r="E98" s="13" t="n">
+        <v>13781827</v>
+      </c>
+      <c r="F98" s="13" t="n">
+        <v>19667775</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Revenue — direct to consumer</t>
+        </is>
+      </c>
+      <c r="B99" s="13" t="n">
+        <v>134106</v>
+      </c>
+      <c r="C99" s="13" t="n">
+        <v>844868</v>
+      </c>
+      <c r="D99" s="13" t="n">
+        <v>1626371</v>
+      </c>
+      <c r="E99" s="13" t="n">
+        <v>2483911</v>
+      </c>
+      <c r="F99" s="13" t="n">
+        <v>3260134</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Revenue — grocery &amp; pharmacy retail</t>
+        </is>
+      </c>
+      <c r="B100" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C100" s="13" t="n">
+        <v>354844</v>
+      </c>
+      <c r="D100" s="13" t="n">
+        <v>3577830</v>
+      </c>
+      <c r="E100" s="13" t="n">
+        <v>8936259</v>
+      </c>
+      <c r="F100" s="13" t="n">
+        <v>15061817</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Revenue — export</t>
+        </is>
+      </c>
+      <c r="B101" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C101" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D101" s="13" t="n">
+        <v>2455397</v>
+      </c>
+      <c r="E101" s="13" t="n">
+        <v>9166816</v>
+      </c>
+      <c r="F101" s="13" t="n">
+        <v>19551099</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Revenue — brand licensing</t>
+        </is>
+      </c>
+      <c r="B102" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C102" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" s="13" t="n">
+        <v>400000</v>
+      </c>
+      <c r="F102" s="13" t="n">
+        <v>1800000</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>NET REVENUE</t>
+        </is>
+      </c>
+      <c r="B103" s="14" t="n">
+        <v>990485</v>
+      </c>
+      <c r="C103" s="14" t="n">
+        <v>7520003</v>
+      </c>
+      <c r="D103" s="14" t="n">
+        <v>21203339</v>
+      </c>
+      <c r="E103" s="14" t="n">
+        <v>42516655</v>
+      </c>
+      <c r="F103" s="14" t="n">
+        <v>68587227</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Cost of goods sold</t>
+        </is>
+      </c>
+      <c r="B104" s="13" t="n">
+        <v>372989</v>
+      </c>
+      <c r="C104" s="13" t="n">
+        <v>2594799</v>
+      </c>
+      <c r="D104" s="13" t="n">
+        <v>6944339</v>
+      </c>
+      <c r="E104" s="13" t="n">
+        <v>13628243</v>
+      </c>
+      <c r="F104" s="13" t="n">
+        <v>21998999</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>GROSS PROFIT</t>
+        </is>
+      </c>
+      <c r="B105" s="14" t="n">
+        <v>617496</v>
+      </c>
+      <c r="C105" s="14" t="n">
+        <v>4925204</v>
+      </c>
+      <c r="D105" s="14" t="n">
+        <v>14258999</v>
+      </c>
+      <c r="E105" s="14" t="n">
+        <v>28888412</v>
+      </c>
+      <c r="F105" s="14" t="n">
+        <v>46588228</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Salaries &amp; employer costs</t>
+        </is>
+      </c>
+      <c r="B107" s="13" t="n">
+        <v>522000</v>
+      </c>
+      <c r="C107" s="13" t="n">
+        <v>1407680</v>
+      </c>
+      <c r="D107" s="13" t="n">
+        <v>3137091</v>
+      </c>
+      <c r="E107" s="13" t="n">
+        <v>4895076</v>
+      </c>
+      <c r="F107" s="13" t="n">
+        <v>6650729</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Marketing, trade &amp; listing fees</t>
+        </is>
+      </c>
+      <c r="B108" s="13" t="n">
+        <v>494000</v>
+      </c>
+      <c r="C108" s="13" t="n">
+        <v>1232800</v>
+      </c>
+      <c r="D108" s="13" t="n">
+        <v>3656434</v>
+      </c>
+      <c r="E108" s="13" t="n">
+        <v>5421999</v>
+      </c>
+      <c r="F108" s="13" t="n">
+        <v>7544595</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Logistics &amp; warehousing</t>
+        </is>
+      </c>
+      <c r="B109" s="13" t="n">
+        <v>51308</v>
+      </c>
+      <c r="C109" s="13" t="n">
+        <v>388094</v>
+      </c>
+      <c r="D109" s="13" t="n">
+        <v>1016166</v>
+      </c>
+      <c r="E109" s="13" t="n">
+        <v>1864910</v>
+      </c>
+      <c r="F109" s="13" t="n">
+        <v>2843705</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Sales commission</t>
+        </is>
+      </c>
+      <c r="B110" s="13" t="n">
+        <v>25691</v>
+      </c>
+      <c r="C110" s="13" t="n">
+        <v>175313</v>
+      </c>
+      <c r="D110" s="13" t="n">
+        <v>300294</v>
+      </c>
+      <c r="E110" s="13" t="n">
+        <v>356472</v>
+      </c>
+      <c r="F110" s="13" t="n">
+        <v>395399</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Product &amp; export development</t>
+        </is>
+      </c>
+      <c r="B111" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C111" s="13" t="n">
+        <v>112800</v>
+      </c>
+      <c r="D111" s="13" t="n">
+        <v>669606</v>
+      </c>
+      <c r="E111" s="13" t="n">
+        <v>1492010</v>
+      </c>
+      <c r="F111" s="13" t="n">
+        <v>2544810</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Fixed overheads</t>
+        </is>
+      </c>
+      <c r="B112" s="13" t="n">
+        <v>539550</v>
+      </c>
+      <c r="C112" s="13" t="n">
+        <v>762564</v>
+      </c>
+      <c r="D112" s="13" t="n">
+        <v>808318</v>
+      </c>
+      <c r="E112" s="13" t="n">
+        <v>856817</v>
+      </c>
+      <c r="F112" s="13" t="n">
+        <v>908226</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>One-off setup costs</t>
+        </is>
+      </c>
+      <c r="B113" s="13" t="n">
+        <v>388000</v>
+      </c>
+      <c r="C113" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D113" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F113" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>TOTAL OPERATING COSTS</t>
+        </is>
+      </c>
+      <c r="B114" s="14" t="n">
+        <v>2020549</v>
+      </c>
+      <c r="C114" s="14" t="n">
+        <v>4079252</v>
+      </c>
+      <c r="D114" s="14" t="n">
+        <v>9587909</v>
+      </c>
+      <c r="E114" s="14" t="n">
+        <v>14887283</v>
+      </c>
+      <c r="F114" s="14" t="n">
+        <v>20887463</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B116" s="14" t="n">
+        <v>-1403054</v>
+      </c>
+      <c r="C116" s="14" t="n">
+        <v>845952</v>
+      </c>
+      <c r="D116" s="14" t="n">
+        <v>4671090</v>
+      </c>
+      <c r="E116" s="14" t="n">
+        <v>14001129</v>
+      </c>
+      <c r="F116" s="14" t="n">
+        <v>25700765</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Tax charge</t>
+        </is>
+      </c>
+      <c r="B117" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C117" s="13" t="n">
+        <v>51359</v>
+      </c>
+      <c r="D117" s="13" t="n">
+        <v>1059418</v>
+      </c>
+      <c r="E117" s="13" t="n">
+        <v>3780305</v>
+      </c>
+      <c r="F117" s="13" t="n">
+        <v>6939207</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>NET PROFIT</t>
+        </is>
+      </c>
+      <c r="B118" s="14" t="n">
+        <v>-1403054</v>
+      </c>
+      <c r="C118" s="14" t="n">
+        <v>794593</v>
+      </c>
+      <c r="D118" s="14" t="n">
+        <v>3611672</v>
+      </c>
+      <c r="E118" s="14" t="n">
+        <v>10220824</v>
+      </c>
+      <c r="F118" s="14" t="n">
+        <v>18761558</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B119" s="15" t="n">
+        <v>0.6234281424623985</v>
+      </c>
+      <c r="C119" s="15" t="n">
+        <v>0.6549471112262671</v>
+      </c>
+      <c r="D119" s="15" t="n">
+        <v>0.6724884021143732</v>
+      </c>
+      <c r="E119" s="15" t="n">
+        <v>0.6794610631616296</v>
+      </c>
+      <c r="F119" s="15" t="n">
+        <v>0.6792551645258191</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>EBITDA margin %</t>
+        </is>
+      </c>
+      <c r="B120" s="15" t="n">
         <v>-1.416532426685895</v>
       </c>
-      <c r="C90" s="15" t="n">
+      <c r="C120" s="15" t="n">
         <v>0.1124935956326389</v>
       </c>
-      <c r="D90" s="15" t="n">
+      <c r="D120" s="15" t="n">
         <v>0.2202997407136895</v>
       </c>
-      <c r="E90" s="15" t="n">
+      <c r="E120" s="15" t="n">
         <v>0.3293092689823605</v>
       </c>
-      <c r="F90" s="15" t="n">
+      <c r="F120" s="15" t="n">
         <v>0.3747164896496309</v>
       </c>
     </row>
@@ -8744,13 +9290,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -8764,15 +9311,20 @@
       <c r="A3" s="10" t="inlineStr"/>
       <c r="B3" s="11" t="inlineStr">
         <is>
+          <t>BOOTSTRAP</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
           <t>BEAR</t>
         </is>
       </c>
-      <c r="C3" s="11" t="inlineStr">
+      <c r="D3" s="11" t="inlineStr">
         <is>
           <t>BASE</t>
         </is>
       </c>
-      <c r="D3" s="11" t="inlineStr">
+      <c r="E3" s="11" t="inlineStr">
         <is>
           <t>BULL</t>
         </is>
@@ -8781,16 +9333,19 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Volume multiplier</t>
-        </is>
-      </c>
-      <c r="B4" s="16" t="n">
+          <t>Year 5 units vs base</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="n">
+        <v>0.123</v>
+      </c>
+      <c r="C4" s="8" t="n">
         <v>0.45</v>
       </c>
-      <c r="C4" s="16" t="n">
+      <c r="D4" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="D4" s="16" t="n">
+      <c r="E4" s="8" t="n">
         <v>1.55</v>
       </c>
     </row>
@@ -8801,12 +9356,15 @@
         </is>
       </c>
       <c r="B5" s="12" t="n">
+        <v>6800</v>
+      </c>
+      <c r="C5" s="12" t="n">
         <v>11034</v>
       </c>
-      <c r="C5" s="12" t="n">
+      <c r="D5" s="12" t="n">
         <v>24520</v>
       </c>
-      <c r="D5" s="12" t="n">
+      <c r="E5" s="12" t="n">
         <v>38006</v>
       </c>
     </row>
@@ -8817,12 +9375,15 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
+        <v>97490</v>
+      </c>
+      <c r="C6" s="12" t="n">
         <v>249588</v>
       </c>
-      <c r="C6" s="12" t="n">
+      <c r="D6" s="12" t="n">
         <v>554640</v>
       </c>
-      <c r="D6" s="12" t="n">
+      <c r="E6" s="12" t="n">
         <v>859692</v>
       </c>
     </row>
@@ -8833,12 +9394,15 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
+        <v>220215</v>
+      </c>
+      <c r="C7" s="12" t="n">
         <v>805764.375</v>
       </c>
-      <c r="C7" s="12" t="n">
+      <c r="D7" s="12" t="n">
         <v>1790587.5</v>
       </c>
-      <c r="D7" s="12" t="n">
+      <c r="E7" s="12" t="n">
         <v>2775410.625</v>
       </c>
     </row>
@@ -8849,12 +9413,15 @@
         </is>
       </c>
       <c r="B8" s="13" t="n">
+        <v>177800</v>
+      </c>
+      <c r="C8" s="13" t="n">
         <v>262433.43</v>
       </c>
-      <c r="C8" s="13" t="n">
+      <c r="D8" s="13" t="n">
         <v>620410</v>
       </c>
-      <c r="D8" s="13" t="n">
+      <c r="E8" s="13" t="n">
         <v>990484.5649999999</v>
       </c>
     </row>
@@ -8865,12 +9432,15 @@
         </is>
       </c>
       <c r="B9" s="13" t="n">
+        <v>2734456.3312</v>
+      </c>
+      <c r="C9" s="13" t="n">
         <v>5617921.8469</v>
       </c>
-      <c r="C9" s="13" t="n">
+      <c r="D9" s="13" t="n">
         <v>13281139.118</v>
       </c>
-      <c r="D9" s="13" t="n">
+      <c r="E9" s="13" t="n">
         <v>21203338.6018</v>
       </c>
     </row>
@@ -8881,12 +9451,15 @@
         </is>
       </c>
       <c r="B10" s="13" t="n">
+        <v>7126263.6488</v>
+      </c>
+      <c r="C10" s="13" t="n">
         <v>17695582.2721</v>
       </c>
-      <c r="C10" s="13" t="n">
+      <c r="D10" s="13" t="n">
         <v>43633527.83</v>
       </c>
-      <c r="D10" s="13" t="n">
+      <c r="E10" s="13" t="n">
         <v>68587227.1806</v>
       </c>
     </row>
@@ -8897,12 +9470,15 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
+        <v>0.6761</v>
+      </c>
+      <c r="C11" s="8" t="n">
         <v>0.5615</v>
       </c>
-      <c r="C11" s="8" t="n">
+      <c r="D11" s="8" t="n">
         <v>0.6545</v>
       </c>
-      <c r="D11" s="8" t="n">
+      <c r="E11" s="8" t="n">
         <v>0.6793</v>
       </c>
     </row>
@@ -8913,12 +9489,15 @@
         </is>
       </c>
       <c r="B12" s="13" t="n">
+        <v>1994524.1093</v>
+      </c>
+      <c r="C12" s="13" t="n">
         <v>-189443.314</v>
       </c>
-      <c r="C12" s="13" t="n">
+      <c r="D12" s="13" t="n">
         <v>12591610.0764</v>
       </c>
-      <c r="D12" s="13" t="n">
+      <c r="E12" s="13" t="n">
         <v>25700765.0039</v>
       </c>
     </row>
@@ -8929,12 +9508,15 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
+        <v>0.2799</v>
+      </c>
+      <c r="C13" s="8" t="n">
         <v>-0.0107</v>
       </c>
-      <c r="C13" s="8" t="n">
+      <c r="D13" s="8" t="n">
         <v>0.2886</v>
       </c>
-      <c r="D13" s="8" t="n">
+      <c r="E13" s="8" t="n">
         <v>0.3747</v>
       </c>
     </row>
@@ -8945,12 +9527,15 @@
         </is>
       </c>
       <c r="B14" s="13" t="n">
+        <v>3157322.4809</v>
+      </c>
+      <c r="C14" s="13" t="n">
         <v>-5924610.1364</v>
       </c>
-      <c r="C14" s="13" t="n">
+      <c r="D14" s="13" t="n">
         <v>16646399.9474</v>
       </c>
-      <c r="D14" s="13" t="n">
+      <c r="E14" s="13" t="n">
         <v>43815882.253</v>
       </c>
     </row>
@@ -8960,13 +9545,16 @@
           <t>First EBITDA-positive year</t>
         </is>
       </c>
-      <c r="B15" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="17" t="n">
+      <c r="B15" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="D15" s="17" t="n">
+      <c r="E15" s="16" t="n">
         <v>2</v>
       </c>
     </row>
@@ -8977,12 +9565,15 @@
         </is>
       </c>
       <c r="B16" s="13" t="n">
+        <v>671299.5111999999</v>
+      </c>
+      <c r="C16" s="13" t="n">
         <v>8600702.8167</v>
       </c>
-      <c r="C16" s="13" t="n">
+      <c r="D16" s="13" t="n">
         <v>5573793.2027</v>
       </c>
-      <c r="D16" s="13" t="n">
+      <c r="E16" s="13" t="n">
         <v>3356538.7832</v>
       </c>
     </row>
@@ -8993,14 +9584,17 @@
         </is>
       </c>
       <c r="B17" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="C17" s="17" t="n">
         <v>50</v>
-      </c>
-      <c r="C17" s="17" t="n">
-        <v>33</v>
       </c>
       <c r="D17" s="17" t="n">
         <v>33</v>
       </c>
+      <c r="E17" s="17" t="n">
+        <v>33</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -9009,12 +9603,15 @@
         </is>
       </c>
       <c r="B18" s="13" t="n">
+        <v>158587.5803</v>
+      </c>
+      <c r="C18" s="13" t="n">
         <v>1207273.1908</v>
       </c>
-      <c r="C18" s="13" t="n">
+      <c r="D18" s="13" t="n">
         <v>573601.4322</v>
       </c>
-      <c r="D18" s="13" t="n">
+      <c r="E18" s="13" t="n">
         <v>629993.5093</v>
       </c>
     </row>
@@ -9025,18 +9622,21 @@
         </is>
       </c>
       <c r="B19" s="13" t="n">
+        <v>2701395.4743</v>
+      </c>
+      <c r="C19" s="13" t="n">
         <v>7640597.8524</v>
       </c>
-      <c r="C19" s="13" t="n">
+      <c r="D19" s="13" t="n">
         <v>22409352.2289</v>
       </c>
-      <c r="D19" s="13" t="n">
+      <c r="E19" s="13" t="n">
         <v>38835786.5251</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/finance/outputs/mulligan-mints-5yr-model.xlsx
+++ b/finance/outputs/mulligan-mints-5yr-model.xlsx
@@ -512,7 +512,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G120"/>
+  <dimension ref="A1:G124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1903,245 +1903,245 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>Finance costs (trade finance interest)</t>
+        </is>
+      </c>
+      <c r="B27" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>Tax charge</t>
         </is>
       </c>
-      <c r="B27" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C27" s="13" t="n">
+      <c r="B28" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="13" t="n">
         <v>2778</v>
       </c>
-      <c r="D27" s="13" t="n">
+      <c r="D28" s="13" t="n">
         <v>65290</v>
       </c>
-      <c r="E27" s="13" t="n">
+      <c r="E28" s="13" t="n">
         <v>1026725</v>
       </c>
-      <c r="F27" s="13" t="n">
+      <c r="F28" s="13" t="n">
         <v>3399735</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>NET PROFIT</t>
-        </is>
-      </c>
-      <c r="B28" s="14" t="n">
-        <v>-1461603</v>
-      </c>
-      <c r="C28" s="14" t="n">
-        <v>-428895</v>
-      </c>
-      <c r="D28" s="14" t="n">
-        <v>464896</v>
-      </c>
-      <c r="E28" s="14" t="n">
-        <v>4385599</v>
-      </c>
-      <c r="F28" s="14" t="n">
-        <v>9191875</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Gross margin %</t>
-        </is>
-      </c>
-      <c r="B29" s="15" t="n">
-        <v>0.593303070108392</v>
-      </c>
-      <c r="C29" s="15" t="n">
-        <v>0.6252449339150132</v>
-      </c>
-      <c r="D29" s="15" t="n">
-        <v>0.6243264960928632</v>
-      </c>
-      <c r="E29" s="15" t="n">
-        <v>0.6341896151101259</v>
-      </c>
-      <c r="F29" s="15" t="n">
-        <v>0.6544839772955371</v>
+          <t>NET PROFIT</t>
+        </is>
+      </c>
+      <c r="B29" s="14" t="n">
+        <v>-1461603</v>
+      </c>
+      <c r="C29" s="14" t="n">
+        <v>-428895</v>
+      </c>
+      <c r="D29" s="14" t="n">
+        <v>464896</v>
+      </c>
+      <c r="E29" s="14" t="n">
+        <v>4385599</v>
+      </c>
+      <c r="F29" s="14" t="n">
+        <v>9191875</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B30" s="15" t="n">
+        <v>0.593303070108392</v>
+      </c>
+      <c r="C30" s="15" t="n">
+        <v>0.6252449339150132</v>
+      </c>
+      <c r="D30" s="15" t="n">
+        <v>0.6243264960928632</v>
+      </c>
+      <c r="E30" s="15" t="n">
+        <v>0.6341896151101259</v>
+      </c>
+      <c r="F30" s="15" t="n">
+        <v>0.6544839772955371</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
           <t>EBITDA margin %</t>
         </is>
       </c>
-      <c r="B30" s="15" t="n">
+      <c r="B31" s="15" t="n">
         <v>-2.355866511297452</v>
       </c>
-      <c r="C30" s="15" t="n">
+      <c r="C31" s="15" t="n">
         <v>-0.09046483530983451</v>
       </c>
-      <c r="D30" s="15" t="n">
+      <c r="D31" s="15" t="n">
         <v>0.03992020614522623</v>
       </c>
-      <c r="E30" s="15" t="n">
+      <c r="E31" s="15" t="n">
         <v>0.2020985651790186</v>
       </c>
-      <c r="F30" s="15" t="n">
+      <c r="F31" s="15" t="n">
         <v>0.2885764847039652</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>BOOTSTRAP — Bootstrap — founder-funded, golf and bars only, no growth round</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="n"/>
-      <c r="C33" s="5" t="n"/>
-      <c r="D33" s="5" t="n"/>
-      <c r="E33" s="5" t="n"/>
-      <c r="F33" s="5" t="n"/>
-    </row>
     <row r="34">
-      <c r="A34" s="10" t="inlineStr"/>
-      <c r="B34" s="11" t="inlineStr">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>BOOTSTRAP — Bootstrap — founder-funded, licence the brand globally</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n"/>
+      <c r="C34" s="5" t="n"/>
+      <c r="D34" s="5" t="n"/>
+      <c r="E34" s="5" t="n"/>
+      <c r="F34" s="5" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="10" t="inlineStr"/>
+      <c r="B35" s="11" t="inlineStr">
         <is>
           <t>Year 1</t>
         </is>
       </c>
-      <c r="C34" s="11" t="inlineStr">
+      <c r="C35" s="11" t="inlineStr">
         <is>
           <t>Year 2</t>
         </is>
       </c>
-      <c r="D34" s="11" t="inlineStr">
+      <c r="D35" s="11" t="inlineStr">
         <is>
           <t>Year 3</t>
         </is>
       </c>
-      <c r="E34" s="11" t="inlineStr">
+      <c r="E35" s="11" t="inlineStr">
         <is>
           <t>Year 4</t>
         </is>
       </c>
-      <c r="F34" s="11" t="inlineStr">
+      <c r="F35" s="11" t="inlineStr">
         <is>
           <t>Year 5</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>Units sold</t>
         </is>
       </c>
-      <c r="B35" s="12" t="n">
-        <v>6800</v>
-      </c>
-      <c r="C35" s="12" t="n">
-        <v>46870</v>
-      </c>
-      <c r="D35" s="12" t="n">
-        <v>97490</v>
-      </c>
-      <c r="E35" s="12" t="n">
-        <v>157700</v>
-      </c>
-      <c r="F35" s="12" t="n">
-        <v>220215</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Revenue — golf clubs</t>
-        </is>
-      </c>
-      <c r="B37" s="13" t="n">
-        <v>95060</v>
-      </c>
-      <c r="C37" s="13" t="n">
-        <v>696909</v>
-      </c>
-      <c r="D37" s="13" t="n">
-        <v>1427415</v>
-      </c>
-      <c r="E37" s="13" t="n">
-        <v>2287340</v>
-      </c>
-      <c r="F37" s="13" t="n">
-        <v>3123722</v>
+      <c r="B36" s="12" t="n">
+        <v>10760</v>
+      </c>
+      <c r="C36" s="12" t="n">
+        <v>71980</v>
+      </c>
+      <c r="D36" s="12" t="n">
+        <v>145530</v>
+      </c>
+      <c r="E36" s="12" t="n">
+        <v>228635</v>
+      </c>
+      <c r="F36" s="12" t="n">
+        <v>313600</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Revenue — bars &amp; restaurants</t>
+          <t>Revenue — golf clubs</t>
         </is>
       </c>
       <c r="B38" s="13" t="n">
-        <v>40740</v>
+        <v>162960</v>
       </c>
       <c r="C38" s="13" t="n">
-        <v>343744</v>
+        <v>1074008</v>
       </c>
       <c r="D38" s="13" t="n">
-        <v>890296</v>
+        <v>2103826</v>
       </c>
       <c r="E38" s="13" t="n">
-        <v>1735436</v>
+        <v>3278717</v>
       </c>
       <c r="F38" s="13" t="n">
-        <v>2836773</v>
+        <v>4450880</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Revenue — direct to consumer</t>
+          <t>Revenue — bars &amp; restaurants</t>
         </is>
       </c>
       <c r="B39" s="13" t="n">
-        <v>42000</v>
+        <v>54320</v>
       </c>
       <c r="C39" s="13" t="n">
-        <v>220500</v>
+        <v>483788</v>
       </c>
       <c r="D39" s="13" t="n">
-        <v>416745</v>
+        <v>1305768</v>
       </c>
       <c r="E39" s="13" t="n">
-        <v>583443</v>
+        <v>2465880</v>
       </c>
       <c r="F39" s="13" t="n">
-        <v>765769</v>
+        <v>3908521</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Revenue — grocery &amp; pharmacy retail</t>
+          <t>Revenue — direct to consumer</t>
         </is>
       </c>
       <c r="B40" s="13" t="n">
-        <v>0</v>
+        <v>63000</v>
       </c>
       <c r="C40" s="13" t="n">
-        <v>0</v>
+        <v>396900</v>
       </c>
       <c r="D40" s="13" t="n">
-        <v>0</v>
+        <v>694575</v>
       </c>
       <c r="E40" s="13" t="n">
-        <v>0</v>
+        <v>972405</v>
       </c>
       <c r="F40" s="13" t="n">
-        <v>0</v>
+        <v>1276282</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Revenue — export</t>
+          <t>Revenue — grocery &amp; pharmacy retail</t>
         </is>
       </c>
       <c r="B41" s="13" t="n">
@@ -2163,861 +2163,861 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>Revenue — export</t>
+        </is>
+      </c>
+      <c r="B42" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
           <t>Revenue — brand licensing</t>
         </is>
       </c>
-      <c r="B42" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C42" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D42" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E42" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F42" s="13" t="n">
-        <v>400000</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="B43" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="13" t="n">
+        <v>300000</v>
+      </c>
+      <c r="E43" s="13" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="F43" s="13" t="n">
+        <v>2280000</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>NET REVENUE</t>
         </is>
       </c>
-      <c r="B43" s="14" t="n">
-        <v>177800</v>
-      </c>
-      <c r="C43" s="14" t="n">
-        <v>1261152</v>
-      </c>
-      <c r="D43" s="14" t="n">
-        <v>2734456</v>
-      </c>
-      <c r="E43" s="14" t="n">
-        <v>4606219</v>
-      </c>
-      <c r="F43" s="14" t="n">
-        <v>7126264</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="B44" s="14" t="n">
+        <v>280280</v>
+      </c>
+      <c r="C44" s="14" t="n">
+        <v>1954696</v>
+      </c>
+      <c r="D44" s="14" t="n">
+        <v>4404169</v>
+      </c>
+      <c r="E44" s="14" t="n">
+        <v>7917002</v>
+      </c>
+      <c r="F44" s="14" t="n">
+        <v>11915683</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t>Cost of goods sold</t>
         </is>
       </c>
-      <c r="B44" s="13" t="n">
-        <v>69974</v>
-      </c>
-      <c r="C44" s="13" t="n">
-        <v>488434</v>
-      </c>
-      <c r="D44" s="13" t="n">
-        <v>1058633</v>
-      </c>
-      <c r="E44" s="13" t="n">
-        <v>1646678</v>
-      </c>
-      <c r="F44" s="13" t="n">
-        <v>2308431</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+      <c r="B45" s="13" t="n">
+        <v>110724</v>
+      </c>
+      <c r="C45" s="13" t="n">
+        <v>750319</v>
+      </c>
+      <c r="D45" s="13" t="n">
+        <v>1576593</v>
+      </c>
+      <c r="E45" s="13" t="n">
+        <v>2379049</v>
+      </c>
+      <c r="F45" s="13" t="n">
+        <v>3288288</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>GROSS PROFIT</t>
         </is>
       </c>
-      <c r="B45" s="14" t="n">
-        <v>107826</v>
-      </c>
-      <c r="C45" s="14" t="n">
-        <v>772719</v>
-      </c>
-      <c r="D45" s="14" t="n">
-        <v>1675823</v>
-      </c>
-      <c r="E45" s="14" t="n">
-        <v>2959541</v>
-      </c>
-      <c r="F45" s="14" t="n">
-        <v>4817833</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Salaries &amp; employer costs</t>
-        </is>
-      </c>
-      <c r="B47" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C47" s="13" t="n">
-        <v>190800</v>
-      </c>
-      <c r="D47" s="13" t="n">
-        <v>533710</v>
-      </c>
-      <c r="E47" s="13" t="n">
-        <v>890880</v>
-      </c>
-      <c r="F47" s="13" t="n">
-        <v>1333176</v>
+      <c r="B46" s="14" t="n">
+        <v>169556</v>
+      </c>
+      <c r="C46" s="14" t="n">
+        <v>1204377</v>
+      </c>
+      <c r="D46" s="14" t="n">
+        <v>2827577</v>
+      </c>
+      <c r="E46" s="14" t="n">
+        <v>5537953</v>
+      </c>
+      <c r="F46" s="14" t="n">
+        <v>8627394</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Marketing, trade &amp; listing fees</t>
+          <t>Salaries &amp; employer costs</t>
         </is>
       </c>
       <c r="B48" s="13" t="n">
-        <v>60000</v>
+        <v>0</v>
       </c>
       <c r="C48" s="13" t="n">
-        <v>100892</v>
+        <v>381600</v>
       </c>
       <c r="D48" s="13" t="n">
-        <v>218757</v>
+        <v>870790</v>
       </c>
       <c r="E48" s="13" t="n">
-        <v>322435</v>
+        <v>1391107</v>
       </c>
       <c r="F48" s="13" t="n">
-        <v>498838</v>
+        <v>1863416</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Logistics &amp; warehousing</t>
+          <t>Marketing, trade &amp; listing fees</t>
         </is>
       </c>
       <c r="B49" s="13" t="n">
-        <v>9180</v>
+        <v>60000</v>
       </c>
       <c r="C49" s="13" t="n">
-        <v>67071</v>
+        <v>136829</v>
       </c>
       <c r="D49" s="13" t="n">
-        <v>147879</v>
+        <v>308292</v>
       </c>
       <c r="E49" s="13" t="n">
-        <v>253561</v>
+        <v>475020</v>
       </c>
       <c r="F49" s="13" t="n">
-        <v>375322</v>
+        <v>714941</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sales commission</t>
+          <t>Logistics &amp; warehousing</t>
         </is>
       </c>
       <c r="B50" s="13" t="n">
-        <v>4074</v>
+        <v>14526</v>
       </c>
       <c r="C50" s="13" t="n">
-        <v>31220</v>
+        <v>103003</v>
       </c>
       <c r="D50" s="13" t="n">
-        <v>69531</v>
+        <v>220749</v>
       </c>
       <c r="E50" s="13" t="n">
-        <v>120683</v>
+        <v>367616</v>
       </c>
       <c r="F50" s="13" t="n">
-        <v>178815</v>
+        <v>534482</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Product &amp; export development</t>
+          <t>Sales commission</t>
         </is>
       </c>
       <c r="B51" s="13" t="n">
-        <v>0</v>
+        <v>6518</v>
       </c>
       <c r="C51" s="13" t="n">
-        <v>0</v>
+        <v>46734</v>
       </c>
       <c r="D51" s="13" t="n">
-        <v>27345</v>
+        <v>102288</v>
       </c>
       <c r="E51" s="13" t="n">
-        <v>69093</v>
+        <v>172338</v>
       </c>
       <c r="F51" s="13" t="n">
-        <v>106894</v>
+        <v>250782</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Fixed overheads</t>
+          <t>Product &amp; export development</t>
         </is>
       </c>
       <c r="B52" s="13" t="n">
-        <v>196200</v>
+        <v>0</v>
       </c>
       <c r="C52" s="13" t="n">
-        <v>277296</v>
+        <v>120000</v>
       </c>
       <c r="D52" s="13" t="n">
-        <v>293934</v>
+        <v>224042</v>
       </c>
       <c r="E52" s="13" t="n">
-        <v>311570</v>
+        <v>358755</v>
       </c>
       <c r="F52" s="13" t="n">
-        <v>330264</v>
+        <v>458735</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>Fixed overheads</t>
+        </is>
+      </c>
+      <c r="B53" s="13" t="n">
+        <v>196200</v>
+      </c>
+      <c r="C53" s="13" t="n">
+        <v>277296</v>
+      </c>
+      <c r="D53" s="13" t="n">
+        <v>293934</v>
+      </c>
+      <c r="E53" s="13" t="n">
+        <v>311570</v>
+      </c>
+      <c r="F53" s="13" t="n">
+        <v>330264</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
           <t>One-off setup costs</t>
         </is>
       </c>
-      <c r="B53" s="13" t="n">
-        <v>157000</v>
-      </c>
-      <c r="C53" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D53" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E53" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F53" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="B54" s="13" t="n">
+        <v>125000</v>
+      </c>
+      <c r="C54" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>TOTAL OPERATING COSTS</t>
         </is>
       </c>
-      <c r="B54" s="14" t="n">
-        <v>426454</v>
-      </c>
-      <c r="C54" s="14" t="n">
-        <v>667279</v>
-      </c>
-      <c r="D54" s="14" t="n">
-        <v>1291155</v>
-      </c>
-      <c r="E54" s="14" t="n">
-        <v>1968223</v>
-      </c>
-      <c r="F54" s="14" t="n">
-        <v>2823309</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="B55" s="14" t="n">
+        <v>402244</v>
+      </c>
+      <c r="C55" s="14" t="n">
+        <v>1065462</v>
+      </c>
+      <c r="D55" s="14" t="n">
+        <v>2020094</v>
+      </c>
+      <c r="E55" s="14" t="n">
+        <v>3076405</v>
+      </c>
+      <c r="F55" s="14" t="n">
+        <v>4152620</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B56" s="14" t="n">
-        <v>-318628</v>
-      </c>
-      <c r="C56" s="14" t="n">
-        <v>105440</v>
-      </c>
-      <c r="D56" s="14" t="n">
-        <v>384668</v>
-      </c>
-      <c r="E56" s="14" t="n">
-        <v>991318</v>
-      </c>
-      <c r="F56" s="14" t="n">
-        <v>1994524</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="B57" s="14" t="n">
+        <v>-232688</v>
+      </c>
+      <c r="C57" s="14" t="n">
+        <v>138915</v>
+      </c>
+      <c r="D57" s="14" t="n">
+        <v>807483</v>
+      </c>
+      <c r="E57" s="14" t="n">
+        <v>2461548</v>
+      </c>
+      <c r="F57" s="14" t="n">
+        <v>4474774</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Finance costs (trade finance interest)</t>
+        </is>
+      </c>
+      <c r="B58" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" s="13" t="n">
+        <v>42493</v>
+      </c>
+      <c r="D58" s="13" t="n">
+        <v>86507</v>
+      </c>
+      <c r="E58" s="13" t="n">
+        <v>129413</v>
+      </c>
+      <c r="F58" s="13" t="n">
+        <v>170300</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
         <is>
           <t>Tax charge</t>
         </is>
       </c>
-      <c r="B57" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C57" s="13" t="n">
-        <v>6058</v>
-      </c>
-      <c r="D57" s="13" t="n">
-        <v>40241</v>
-      </c>
-      <c r="E57" s="13" t="n">
-        <v>267656</v>
-      </c>
-      <c r="F57" s="13" t="n">
-        <v>538522</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>NET PROFIT</t>
-        </is>
-      </c>
-      <c r="B58" s="14" t="n">
-        <v>-318628</v>
-      </c>
-      <c r="C58" s="14" t="n">
-        <v>99382</v>
-      </c>
-      <c r="D58" s="14" t="n">
-        <v>344427</v>
-      </c>
-      <c r="E58" s="14" t="n">
-        <v>723662</v>
-      </c>
-      <c r="F58" s="14" t="n">
-        <v>1456003</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>Gross margin %</t>
-        </is>
-      </c>
-      <c r="B59" s="15" t="n">
-        <v>0.6064441489274482</v>
-      </c>
-      <c r="C59" s="15" t="n">
-        <v>0.6127085630312291</v>
-      </c>
-      <c r="D59" s="15" t="n">
-        <v>0.6128543084418331</v>
-      </c>
-      <c r="E59" s="15" t="n">
-        <v>0.6425098498730283</v>
-      </c>
-      <c r="F59" s="15" t="n">
-        <v>0.6760671975951418</v>
+      <c r="B59" s="13" t="n">
+        <v>334</v>
+      </c>
+      <c r="C59" s="13" t="n">
+        <v>5890</v>
+      </c>
+      <c r="D59" s="13" t="n">
+        <v>151648</v>
+      </c>
+      <c r="E59" s="13" t="n">
+        <v>629676</v>
+      </c>
+      <c r="F59" s="13" t="n">
+        <v>1162208</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>NET PROFIT</t>
+        </is>
+      </c>
+      <c r="B60" s="14" t="n">
+        <v>-233022</v>
+      </c>
+      <c r="C60" s="14" t="n">
+        <v>90532</v>
+      </c>
+      <c r="D60" s="14" t="n">
+        <v>569328</v>
+      </c>
+      <c r="E60" s="14" t="n">
+        <v>1702459</v>
+      </c>
+      <c r="F60" s="14" t="n">
+        <v>3142266</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B61" s="15" t="n">
+        <v>0.6049524434332847</v>
+      </c>
+      <c r="C61" s="15" t="n">
+        <v>0.616145576540252</v>
+      </c>
+      <c r="D61" s="15" t="n">
+        <v>0.6420227169103438</v>
+      </c>
+      <c r="E61" s="15" t="n">
+        <v>0.6995012815943289</v>
+      </c>
+      <c r="F61" s="15" t="n">
+        <v>0.7240369423781725</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
           <t>EBITDA margin %</t>
         </is>
       </c>
-      <c r="B60" s="15" t="n">
-        <v>-1.792059788080426</v>
-      </c>
-      <c r="C60" s="15" t="n">
-        <v>0.08360617661261731</v>
-      </c>
-      <c r="D60" s="15" t="n">
-        <v>0.1406745788208537</v>
-      </c>
-      <c r="E60" s="15" t="n">
-        <v>0.2152129589740633</v>
-      </c>
-      <c r="F60" s="15" t="n">
-        <v>0.2798835697965889</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="4" t="inlineStr">
+      <c r="B62" s="15" t="n">
+        <v>-0.8301995474329918</v>
+      </c>
+      <c r="C62" s="15" t="n">
+        <v>0.07106742051520307</v>
+      </c>
+      <c r="D62" s="15" t="n">
+        <v>0.1833451215566309</v>
+      </c>
+      <c r="E62" s="15" t="n">
+        <v>0.310919177085396</v>
+      </c>
+      <c r="F62" s="15" t="n">
+        <v>0.3755365203946371</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
         <is>
           <t>BEAR — Bear — slow venue adoption, retail delayed, no export scale</t>
         </is>
       </c>
-      <c r="B63" s="5" t="n"/>
-      <c r="C63" s="5" t="n"/>
-      <c r="D63" s="5" t="n"/>
-      <c r="E63" s="5" t="n"/>
-      <c r="F63" s="5" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="10" t="inlineStr"/>
-      <c r="B64" s="11" t="inlineStr">
+      <c r="B65" s="5" t="n"/>
+      <c r="C65" s="5" t="n"/>
+      <c r="D65" s="5" t="n"/>
+      <c r="E65" s="5" t="n"/>
+      <c r="F65" s="5" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="10" t="inlineStr"/>
+      <c r="B66" s="11" t="inlineStr">
         <is>
           <t>Year 1</t>
         </is>
       </c>
-      <c r="C64" s="11" t="inlineStr">
+      <c r="C66" s="11" t="inlineStr">
         <is>
           <t>Year 2</t>
         </is>
       </c>
-      <c r="D64" s="11" t="inlineStr">
+      <c r="D66" s="11" t="inlineStr">
         <is>
           <t>Year 3</t>
         </is>
       </c>
-      <c r="E64" s="11" t="inlineStr">
+      <c r="E66" s="11" t="inlineStr">
         <is>
           <t>Year 4</t>
         </is>
       </c>
-      <c r="F64" s="11" t="inlineStr">
+      <c r="F66" s="11" t="inlineStr">
         <is>
           <t>Year 5</t>
         </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Units sold</t>
-        </is>
-      </c>
-      <c r="B65" s="12" t="n">
-        <v>11034</v>
-      </c>
-      <c r="C65" s="12" t="n">
-        <v>82395</v>
-      </c>
-      <c r="D65" s="12" t="n">
-        <v>249588</v>
-      </c>
-      <c r="E65" s="12" t="n">
-        <v>511526</v>
-      </c>
-      <c r="F65" s="12" t="n">
-        <v>805764</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Revenue — golf clubs</t>
-        </is>
-      </c>
-      <c r="B67" s="13" t="n">
-        <v>126375</v>
-      </c>
-      <c r="C67" s="13" t="n">
-        <v>832893</v>
-      </c>
-      <c r="D67" s="13" t="n">
-        <v>1507738</v>
-      </c>
-      <c r="E67" s="13" t="n">
-        <v>2052826</v>
-      </c>
-      <c r="F67" s="13" t="n">
-        <v>2449877</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Revenue — bars &amp; restaurants</t>
-        </is>
-      </c>
-      <c r="B68" s="13" t="n">
-        <v>100526</v>
-      </c>
-      <c r="C68" s="13" t="n">
-        <v>841697</v>
-      </c>
-      <c r="D68" s="13" t="n">
-        <v>2080738</v>
-      </c>
-      <c r="E68" s="13" t="n">
-        <v>3651558</v>
-      </c>
-      <c r="F68" s="13" t="n">
-        <v>5211067</v>
+          <t>Units sold</t>
+        </is>
+      </c>
+      <c r="B67" s="12" t="n">
+        <v>11034</v>
+      </c>
+      <c r="C67" s="12" t="n">
+        <v>82395</v>
+      </c>
+      <c r="D67" s="12" t="n">
+        <v>249588</v>
+      </c>
+      <c r="E67" s="12" t="n">
+        <v>511526</v>
+      </c>
+      <c r="F67" s="12" t="n">
+        <v>805764</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Revenue — direct to consumer</t>
+          <t>Revenue — golf clubs</t>
         </is>
       </c>
       <c r="B69" s="13" t="n">
-        <v>35532</v>
+        <v>126375</v>
       </c>
       <c r="C69" s="13" t="n">
-        <v>223852</v>
+        <v>832893</v>
       </c>
       <c r="D69" s="13" t="n">
-        <v>430914</v>
+        <v>1507738</v>
       </c>
       <c r="E69" s="13" t="n">
-        <v>658124</v>
+        <v>2052826</v>
       </c>
       <c r="F69" s="13" t="n">
-        <v>863787</v>
+        <v>2449877</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Revenue — grocery &amp; pharmacy retail</t>
+          <t>Revenue — bars &amp; restaurants</t>
         </is>
       </c>
       <c r="B70" s="13" t="n">
-        <v>0</v>
+        <v>100526</v>
       </c>
       <c r="C70" s="13" t="n">
-        <v>94018</v>
+        <v>841697</v>
       </c>
       <c r="D70" s="13" t="n">
-        <v>947963</v>
+        <v>2080738</v>
       </c>
       <c r="E70" s="13" t="n">
-        <v>2367703</v>
+        <v>3651558</v>
       </c>
       <c r="F70" s="13" t="n">
-        <v>3990698</v>
+        <v>5211067</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Revenue — export</t>
+          <t>Revenue — direct to consumer</t>
         </is>
       </c>
       <c r="B71" s="13" t="n">
-        <v>0</v>
+        <v>35532</v>
       </c>
       <c r="C71" s="13" t="n">
-        <v>0</v>
+        <v>223852</v>
       </c>
       <c r="D71" s="13" t="n">
-        <v>650569</v>
+        <v>430914</v>
       </c>
       <c r="E71" s="13" t="n">
-        <v>2428790</v>
+        <v>658124</v>
       </c>
       <c r="F71" s="13" t="n">
-        <v>5180153</v>
+        <v>863787</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Revenue — brand licensing</t>
+          <t>Revenue — grocery &amp; pharmacy retail</t>
         </is>
       </c>
       <c r="B72" s="13" t="n">
         <v>0</v>
       </c>
       <c r="C72" s="13" t="n">
-        <v>0</v>
+        <v>94018</v>
       </c>
       <c r="D72" s="13" t="n">
-        <v>0</v>
+        <v>947963</v>
       </c>
       <c r="E72" s="13" t="n">
-        <v>0</v>
+        <v>2367703</v>
       </c>
       <c r="F72" s="13" t="n">
-        <v>0</v>
+        <v>3990698</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>NET REVENUE</t>
-        </is>
-      </c>
-      <c r="B73" s="14" t="n">
-        <v>262433</v>
-      </c>
-      <c r="C73" s="14" t="n">
-        <v>1992459</v>
-      </c>
-      <c r="D73" s="14" t="n">
-        <v>5617922</v>
-      </c>
-      <c r="E73" s="14" t="n">
-        <v>11159001</v>
-      </c>
-      <c r="F73" s="14" t="n">
-        <v>17695582</v>
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Revenue — export</t>
+        </is>
+      </c>
+      <c r="B73" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C73" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" s="13" t="n">
+        <v>650569</v>
+      </c>
+      <c r="E73" s="13" t="n">
+        <v>2428790</v>
+      </c>
+      <c r="F73" s="13" t="n">
+        <v>5180153</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Cost of goods sold</t>
+          <t>Revenue — brand licensing</t>
         </is>
       </c>
       <c r="B74" s="13" t="n">
-        <v>121954</v>
+        <v>0</v>
       </c>
       <c r="C74" s="13" t="n">
-        <v>925382</v>
+        <v>0</v>
       </c>
       <c r="D74" s="13" t="n">
-        <v>2657361</v>
+        <v>0</v>
       </c>
       <c r="E74" s="13" t="n">
-        <v>5185833</v>
+        <v>0</v>
       </c>
       <c r="F74" s="13" t="n">
-        <v>7759367</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>NET REVENUE</t>
+        </is>
+      </c>
+      <c r="B75" s="14" t="n">
+        <v>262433</v>
+      </c>
+      <c r="C75" s="14" t="n">
+        <v>1992459</v>
+      </c>
+      <c r="D75" s="14" t="n">
+        <v>5617922</v>
+      </c>
+      <c r="E75" s="14" t="n">
+        <v>11159001</v>
+      </c>
+      <c r="F75" s="14" t="n">
+        <v>17695582</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Cost of goods sold</t>
+        </is>
+      </c>
+      <c r="B76" s="13" t="n">
+        <v>121954</v>
+      </c>
+      <c r="C76" s="13" t="n">
+        <v>925382</v>
+      </c>
+      <c r="D76" s="13" t="n">
+        <v>2657361</v>
+      </c>
+      <c r="E76" s="13" t="n">
+        <v>5185833</v>
+      </c>
+      <c r="F76" s="13" t="n">
+        <v>7759367</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
           <t>GROSS PROFIT</t>
         </is>
       </c>
-      <c r="B75" s="14" t="n">
+      <c r="B77" s="14" t="n">
         <v>140480</v>
       </c>
-      <c r="C75" s="14" t="n">
+      <c r="C77" s="14" t="n">
         <v>1067077</v>
       </c>
-      <c r="D75" s="14" t="n">
+      <c r="D77" s="14" t="n">
         <v>2960561</v>
       </c>
-      <c r="E75" s="14" t="n">
+      <c r="E77" s="14" t="n">
         <v>5973168</v>
       </c>
-      <c r="F75" s="14" t="n">
+      <c r="F77" s="14" t="n">
         <v>9936216</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Salaries &amp; employer costs</t>
-        </is>
-      </c>
-      <c r="B77" s="13" t="n">
-        <v>114000</v>
-      </c>
-      <c r="C77" s="13" t="n">
-        <v>1051520</v>
-      </c>
-      <c r="D77" s="13" t="n">
-        <v>2206750</v>
-      </c>
-      <c r="E77" s="13" t="n">
-        <v>4209051</v>
-      </c>
-      <c r="F77" s="13" t="n">
-        <v>5923542</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Marketing, trade &amp; listing fees</t>
-        </is>
-      </c>
-      <c r="B78" s="13" t="n">
-        <v>209000</v>
-      </c>
-      <c r="C78" s="13" t="n">
-        <v>458944</v>
-      </c>
-      <c r="D78" s="13" t="n">
-        <v>1630330</v>
-      </c>
-      <c r="E78" s="13" t="n">
-        <v>1659080</v>
-      </c>
-      <c r="F78" s="13" t="n">
-        <v>1946514</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Logistics &amp; warehousing</t>
+          <t>Salaries &amp; employer costs</t>
         </is>
       </c>
       <c r="B79" s="13" t="n">
-        <v>14896</v>
+        <v>114000</v>
       </c>
       <c r="C79" s="13" t="n">
-        <v>112673</v>
+        <v>1051520</v>
       </c>
       <c r="D79" s="13" t="n">
-        <v>295016</v>
+        <v>2206750</v>
       </c>
       <c r="E79" s="13" t="n">
-        <v>541425</v>
+        <v>4209051</v>
       </c>
       <c r="F79" s="13" t="n">
-        <v>825592</v>
+        <v>5923542</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Sales commission</t>
+          <t>Marketing, trade &amp; listing fees</t>
         </is>
       </c>
       <c r="B80" s="13" t="n">
-        <v>6807</v>
+        <v>209000</v>
       </c>
       <c r="C80" s="13" t="n">
-        <v>46450</v>
+        <v>458944</v>
       </c>
       <c r="D80" s="13" t="n">
-        <v>79564</v>
+        <v>1630330</v>
       </c>
       <c r="E80" s="13" t="n">
-        <v>94449</v>
+        <v>1659080</v>
       </c>
       <c r="F80" s="13" t="n">
-        <v>104763</v>
+        <v>1946514</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Product &amp; export development</t>
+          <t>Logistics &amp; warehousing</t>
         </is>
       </c>
       <c r="B81" s="13" t="n">
-        <v>0</v>
+        <v>14896</v>
       </c>
       <c r="C81" s="13" t="n">
-        <v>29887</v>
+        <v>112673</v>
       </c>
       <c r="D81" s="13" t="n">
-        <v>177415</v>
+        <v>295016</v>
       </c>
       <c r="E81" s="13" t="n">
-        <v>393195</v>
+        <v>541425</v>
       </c>
       <c r="F81" s="13" t="n">
-        <v>664721</v>
+        <v>825592</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Fixed overheads</t>
+          <t>Sales commission</t>
         </is>
       </c>
       <c r="B82" s="13" t="n">
-        <v>392400</v>
+        <v>6807</v>
       </c>
       <c r="C82" s="13" t="n">
-        <v>554592</v>
+        <v>46450</v>
       </c>
       <c r="D82" s="13" t="n">
-        <v>587868</v>
+        <v>79564</v>
       </c>
       <c r="E82" s="13" t="n">
-        <v>623140</v>
+        <v>94449</v>
       </c>
       <c r="F82" s="13" t="n">
-        <v>660528</v>
+        <v>104763</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
+          <t>Product &amp; export development</t>
+        </is>
+      </c>
+      <c r="B83" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C83" s="13" t="n">
+        <v>29887</v>
+      </c>
+      <c r="D83" s="13" t="n">
+        <v>177415</v>
+      </c>
+      <c r="E83" s="13" t="n">
+        <v>393195</v>
+      </c>
+      <c r="F83" s="13" t="n">
+        <v>664721</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Fixed overheads</t>
+        </is>
+      </c>
+      <c r="B84" s="13" t="n">
+        <v>392400</v>
+      </c>
+      <c r="C84" s="13" t="n">
+        <v>554592</v>
+      </c>
+      <c r="D84" s="13" t="n">
+        <v>587868</v>
+      </c>
+      <c r="E84" s="13" t="n">
+        <v>623140</v>
+      </c>
+      <c r="F84" s="13" t="n">
+        <v>660528</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
           <t>One-off setup costs</t>
         </is>
       </c>
-      <c r="B83" s="13" t="n">
+      <c r="B85" s="13" t="n">
         <v>388000</v>
       </c>
-      <c r="C83" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D83" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E83" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F83" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>TOTAL OPERATING COSTS</t>
-        </is>
-      </c>
-      <c r="B84" s="14" t="n">
-        <v>1125103</v>
-      </c>
-      <c r="C84" s="14" t="n">
-        <v>2254066</v>
-      </c>
-      <c r="D84" s="14" t="n">
-        <v>4976943</v>
-      </c>
-      <c r="E84" s="14" t="n">
-        <v>7520340</v>
-      </c>
-      <c r="F84" s="14" t="n">
-        <v>10125659</v>
+      <c r="C85" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" s="13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>EBITDA</t>
+          <t>TOTAL OPERATING COSTS</t>
         </is>
       </c>
       <c r="B86" s="14" t="n">
-        <v>-984623</v>
+        <v>1125103</v>
       </c>
       <c r="C86" s="14" t="n">
-        <v>-1186989</v>
+        <v>2254066</v>
       </c>
       <c r="D86" s="14" t="n">
-        <v>-2016383</v>
+        <v>4976943</v>
       </c>
       <c r="E86" s="14" t="n">
-        <v>-1547172</v>
+        <v>7520340</v>
       </c>
       <c r="F86" s="14" t="n">
-        <v>-189443</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Tax charge</t>
-        </is>
-      </c>
-      <c r="B87" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C87" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D87" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E87" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F87" s="13" t="n">
-        <v>3676</v>
+        <v>10125659</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>NET PROFIT</t>
+          <t>EBITDA</t>
         </is>
       </c>
       <c r="B88" s="14" t="n">
@@ -3033,596 +3033,684 @@
         <v>-1547172</v>
       </c>
       <c r="F88" s="14" t="n">
+        <v>-189443</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Finance costs (trade finance interest)</t>
+        </is>
+      </c>
+      <c r="B89" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C89" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D89" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Tax charge</t>
+        </is>
+      </c>
+      <c r="B90" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C90" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D90" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E90" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" s="13" t="n">
+        <v>3676</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>NET PROFIT</t>
+        </is>
+      </c>
+      <c r="B91" s="14" t="n">
+        <v>-984623</v>
+      </c>
+      <c r="C91" s="14" t="n">
+        <v>-1186989</v>
+      </c>
+      <c r="D91" s="14" t="n">
+        <v>-2016383</v>
+      </c>
+      <c r="E91" s="14" t="n">
+        <v>-1547172</v>
+      </c>
+      <c r="F91" s="14" t="n">
         <v>-193120</v>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="B89" s="15" t="n">
+      <c r="B92" s="15" t="n">
         <v>0.5352961739401985</v>
       </c>
-      <c r="C89" s="15" t="n">
+      <c r="C92" s="15" t="n">
         <v>0.5355578376499529</v>
       </c>
-      <c r="D89" s="15" t="n">
+      <c r="D92" s="15" t="n">
         <v>0.5269850089444209</v>
       </c>
-      <c r="E89" s="15" t="n">
+      <c r="E92" s="15" t="n">
         <v>0.5352779821328782</v>
       </c>
-      <c r="F89" s="15" t="n">
+      <c r="F92" s="15" t="n">
         <v>0.5615082689949957</v>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>EBITDA margin %</t>
         </is>
       </c>
-      <c r="B90" s="15" t="n">
+      <c r="B93" s="15" t="n">
         <v>-3.751897507520277</v>
       </c>
-      <c r="C90" s="15" t="n">
+      <c r="C93" s="15" t="n">
         <v>-0.5957404224697753</v>
       </c>
-      <c r="D90" s="15" t="n">
+      <c r="D93" s="15" t="n">
         <v>-0.3589196616911676</v>
       </c>
-      <c r="E90" s="15" t="n">
+      <c r="E93" s="15" t="n">
         <v>-0.1386479206512514</v>
       </c>
-      <c r="F90" s="15" t="n">
+      <c r="F93" s="15" t="n">
         <v>-0.01070568411541408</v>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="4" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="4" t="inlineStr">
         <is>
           <t>BULL — Bull — creator-led breakout, export pulls forward</t>
         </is>
       </c>
-      <c r="B93" s="5" t="n"/>
-      <c r="C93" s="5" t="n"/>
-      <c r="D93" s="5" t="n"/>
-      <c r="E93" s="5" t="n"/>
-      <c r="F93" s="5" t="n"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="10" t="inlineStr"/>
-      <c r="B94" s="11" t="inlineStr">
+      <c r="B96" s="5" t="n"/>
+      <c r="C96" s="5" t="n"/>
+      <c r="D96" s="5" t="n"/>
+      <c r="E96" s="5" t="n"/>
+      <c r="F96" s="5" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="10" t="inlineStr"/>
+      <c r="B97" s="11" t="inlineStr">
         <is>
           <t>Year 1</t>
         </is>
       </c>
-      <c r="C94" s="11" t="inlineStr">
+      <c r="C97" s="11" t="inlineStr">
         <is>
           <t>Year 2</t>
         </is>
       </c>
-      <c r="D94" s="11" t="inlineStr">
+      <c r="D97" s="11" t="inlineStr">
         <is>
           <t>Year 3</t>
         </is>
       </c>
-      <c r="E94" s="11" t="inlineStr">
+      <c r="E97" s="11" t="inlineStr">
         <is>
           <t>Year 4</t>
         </is>
       </c>
-      <c r="F94" s="11" t="inlineStr">
+      <c r="F97" s="11" t="inlineStr">
         <is>
           <t>Year 5</t>
         </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Units sold</t>
-        </is>
-      </c>
-      <c r="B95" s="12" t="n">
-        <v>38006</v>
-      </c>
-      <c r="C95" s="12" t="n">
-        <v>283805</v>
-      </c>
-      <c r="D95" s="12" t="n">
-        <v>859692</v>
-      </c>
-      <c r="E95" s="12" t="n">
-        <v>1761924</v>
-      </c>
-      <c r="F95" s="12" t="n">
-        <v>2775411</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Revenue — golf clubs</t>
-        </is>
-      </c>
-      <c r="B97" s="13" t="n">
-        <v>476970</v>
-      </c>
-      <c r="C97" s="13" t="n">
-        <v>3143533</v>
-      </c>
-      <c r="D97" s="13" t="n">
-        <v>5690554</v>
-      </c>
-      <c r="E97" s="13" t="n">
-        <v>7747842</v>
-      </c>
-      <c r="F97" s="13" t="n">
-        <v>9246402</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Revenue — bars &amp; restaurants</t>
-        </is>
-      </c>
-      <c r="B98" s="13" t="n">
-        <v>379408</v>
-      </c>
-      <c r="C98" s="13" t="n">
-        <v>3176758</v>
-      </c>
-      <c r="D98" s="13" t="n">
-        <v>7853186</v>
-      </c>
-      <c r="E98" s="13" t="n">
-        <v>13781827</v>
-      </c>
-      <c r="F98" s="13" t="n">
-        <v>19667775</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Revenue — direct to consumer</t>
-        </is>
-      </c>
-      <c r="B99" s="13" t="n">
-        <v>134106</v>
-      </c>
-      <c r="C99" s="13" t="n">
-        <v>844868</v>
-      </c>
-      <c r="D99" s="13" t="n">
-        <v>1626371</v>
-      </c>
-      <c r="E99" s="13" t="n">
-        <v>2483911</v>
-      </c>
-      <c r="F99" s="13" t="n">
-        <v>3260134</v>
+          <t>Units sold</t>
+        </is>
+      </c>
+      <c r="B98" s="12" t="n">
+        <v>38006</v>
+      </c>
+      <c r="C98" s="12" t="n">
+        <v>283805</v>
+      </c>
+      <c r="D98" s="12" t="n">
+        <v>859692</v>
+      </c>
+      <c r="E98" s="12" t="n">
+        <v>1761924</v>
+      </c>
+      <c r="F98" s="12" t="n">
+        <v>2775411</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Revenue — grocery &amp; pharmacy retail</t>
+          <t>Revenue — golf clubs</t>
         </is>
       </c>
       <c r="B100" s="13" t="n">
-        <v>0</v>
+        <v>476970</v>
       </c>
       <c r="C100" s="13" t="n">
-        <v>354844</v>
+        <v>3143533</v>
       </c>
       <c r="D100" s="13" t="n">
-        <v>3577830</v>
+        <v>5690554</v>
       </c>
       <c r="E100" s="13" t="n">
-        <v>8936259</v>
+        <v>7747842</v>
       </c>
       <c r="F100" s="13" t="n">
-        <v>15061817</v>
+        <v>9246402</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Revenue — export</t>
+          <t>Revenue — bars &amp; restaurants</t>
         </is>
       </c>
       <c r="B101" s="13" t="n">
-        <v>0</v>
+        <v>379408</v>
       </c>
       <c r="C101" s="13" t="n">
-        <v>0</v>
+        <v>3176758</v>
       </c>
       <c r="D101" s="13" t="n">
-        <v>2455397</v>
+        <v>7853186</v>
       </c>
       <c r="E101" s="13" t="n">
-        <v>9166816</v>
+        <v>13781827</v>
       </c>
       <c r="F101" s="13" t="n">
-        <v>19551099</v>
+        <v>19667775</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Revenue — brand licensing</t>
+          <t>Revenue — direct to consumer</t>
         </is>
       </c>
       <c r="B102" s="13" t="n">
-        <v>0</v>
+        <v>134106</v>
       </c>
       <c r="C102" s="13" t="n">
-        <v>0</v>
+        <v>844868</v>
       </c>
       <c r="D102" s="13" t="n">
-        <v>0</v>
+        <v>1626371</v>
       </c>
       <c r="E102" s="13" t="n">
-        <v>400000</v>
+        <v>2483911</v>
       </c>
       <c r="F102" s="13" t="n">
-        <v>1800000</v>
+        <v>3260134</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="inlineStr">
-        <is>
-          <t>NET REVENUE</t>
-        </is>
-      </c>
-      <c r="B103" s="14" t="n">
-        <v>990485</v>
-      </c>
-      <c r="C103" s="14" t="n">
-        <v>7520003</v>
-      </c>
-      <c r="D103" s="14" t="n">
-        <v>21203339</v>
-      </c>
-      <c r="E103" s="14" t="n">
-        <v>42516655</v>
-      </c>
-      <c r="F103" s="14" t="n">
-        <v>68587227</v>
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Revenue — grocery &amp; pharmacy retail</t>
+        </is>
+      </c>
+      <c r="B103" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C103" s="13" t="n">
+        <v>354844</v>
+      </c>
+      <c r="D103" s="13" t="n">
+        <v>3577830</v>
+      </c>
+      <c r="E103" s="13" t="n">
+        <v>8936259</v>
+      </c>
+      <c r="F103" s="13" t="n">
+        <v>15061817</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Cost of goods sold</t>
+          <t>Revenue — export</t>
         </is>
       </c>
       <c r="B104" s="13" t="n">
-        <v>372989</v>
+        <v>0</v>
       </c>
       <c r="C104" s="13" t="n">
-        <v>2594799</v>
+        <v>0</v>
       </c>
       <c r="D104" s="13" t="n">
-        <v>6944339</v>
+        <v>2455397</v>
       </c>
       <c r="E104" s="13" t="n">
-        <v>13628243</v>
+        <v>9166816</v>
       </c>
       <c r="F104" s="13" t="n">
-        <v>21998999</v>
+        <v>19551099</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="inlineStr">
-        <is>
-          <t>GROSS PROFIT</t>
-        </is>
-      </c>
-      <c r="B105" s="14" t="n">
-        <v>617496</v>
-      </c>
-      <c r="C105" s="14" t="n">
-        <v>4925204</v>
-      </c>
-      <c r="D105" s="14" t="n">
-        <v>14258999</v>
-      </c>
-      <c r="E105" s="14" t="n">
-        <v>28888412</v>
-      </c>
-      <c r="F105" s="14" t="n">
-        <v>46588228</v>
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Revenue — brand licensing</t>
+        </is>
+      </c>
+      <c r="B105" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C105" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D105" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" s="13" t="n">
+        <v>400000</v>
+      </c>
+      <c r="F105" s="13" t="n">
+        <v>1800000</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>NET REVENUE</t>
+        </is>
+      </c>
+      <c r="B106" s="14" t="n">
+        <v>990485</v>
+      </c>
+      <c r="C106" s="14" t="n">
+        <v>7520003</v>
+      </c>
+      <c r="D106" s="14" t="n">
+        <v>21203339</v>
+      </c>
+      <c r="E106" s="14" t="n">
+        <v>42516655</v>
+      </c>
+      <c r="F106" s="14" t="n">
+        <v>68587227</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Salaries &amp; employer costs</t>
+          <t>Cost of goods sold</t>
         </is>
       </c>
       <c r="B107" s="13" t="n">
-        <v>522000</v>
+        <v>372989</v>
       </c>
       <c r="C107" s="13" t="n">
-        <v>1407680</v>
+        <v>2594799</v>
       </c>
       <c r="D107" s="13" t="n">
-        <v>3137091</v>
+        <v>6944339</v>
       </c>
       <c r="E107" s="13" t="n">
-        <v>4895076</v>
+        <v>13628243</v>
       </c>
       <c r="F107" s="13" t="n">
-        <v>6650729</v>
+        <v>21998999</v>
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Marketing, trade &amp; listing fees</t>
-        </is>
-      </c>
-      <c r="B108" s="13" t="n">
-        <v>494000</v>
-      </c>
-      <c r="C108" s="13" t="n">
-        <v>1232800</v>
-      </c>
-      <c r="D108" s="13" t="n">
-        <v>3656434</v>
-      </c>
-      <c r="E108" s="13" t="n">
-        <v>5421999</v>
-      </c>
-      <c r="F108" s="13" t="n">
-        <v>7544595</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Logistics &amp; warehousing</t>
-        </is>
-      </c>
-      <c r="B109" s="13" t="n">
-        <v>51308</v>
-      </c>
-      <c r="C109" s="13" t="n">
-        <v>388094</v>
-      </c>
-      <c r="D109" s="13" t="n">
-        <v>1016166</v>
-      </c>
-      <c r="E109" s="13" t="n">
-        <v>1864910</v>
-      </c>
-      <c r="F109" s="13" t="n">
-        <v>2843705</v>
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>GROSS PROFIT</t>
+        </is>
+      </c>
+      <c r="B108" s="14" t="n">
+        <v>617496</v>
+      </c>
+      <c r="C108" s="14" t="n">
+        <v>4925204</v>
+      </c>
+      <c r="D108" s="14" t="n">
+        <v>14258999</v>
+      </c>
+      <c r="E108" s="14" t="n">
+        <v>28888412</v>
+      </c>
+      <c r="F108" s="14" t="n">
+        <v>46588228</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Sales commission</t>
+          <t>Salaries &amp; employer costs</t>
         </is>
       </c>
       <c r="B110" s="13" t="n">
-        <v>25691</v>
+        <v>522000</v>
       </c>
       <c r="C110" s="13" t="n">
-        <v>175313</v>
+        <v>1407680</v>
       </c>
       <c r="D110" s="13" t="n">
-        <v>300294</v>
+        <v>3137091</v>
       </c>
       <c r="E110" s="13" t="n">
-        <v>356472</v>
+        <v>4895076</v>
       </c>
       <c r="F110" s="13" t="n">
-        <v>395399</v>
+        <v>6650729</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Product &amp; export development</t>
+          <t>Marketing, trade &amp; listing fees</t>
         </is>
       </c>
       <c r="B111" s="13" t="n">
-        <v>0</v>
+        <v>494000</v>
       </c>
       <c r="C111" s="13" t="n">
-        <v>112800</v>
+        <v>1232800</v>
       </c>
       <c r="D111" s="13" t="n">
-        <v>669606</v>
+        <v>3656434</v>
       </c>
       <c r="E111" s="13" t="n">
-        <v>1492010</v>
+        <v>5421999</v>
       </c>
       <c r="F111" s="13" t="n">
-        <v>2544810</v>
+        <v>7544595</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Fixed overheads</t>
+          <t>Logistics &amp; warehousing</t>
         </is>
       </c>
       <c r="B112" s="13" t="n">
-        <v>539550</v>
+        <v>51308</v>
       </c>
       <c r="C112" s="13" t="n">
-        <v>762564</v>
+        <v>388094</v>
       </c>
       <c r="D112" s="13" t="n">
-        <v>808318</v>
+        <v>1016166</v>
       </c>
       <c r="E112" s="13" t="n">
-        <v>856817</v>
+        <v>1864910</v>
       </c>
       <c r="F112" s="13" t="n">
-        <v>908226</v>
+        <v>2843705</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
+          <t>Sales commission</t>
+        </is>
+      </c>
+      <c r="B113" s="13" t="n">
+        <v>25691</v>
+      </c>
+      <c r="C113" s="13" t="n">
+        <v>175313</v>
+      </c>
+      <c r="D113" s="13" t="n">
+        <v>300294</v>
+      </c>
+      <c r="E113" s="13" t="n">
+        <v>356472</v>
+      </c>
+      <c r="F113" s="13" t="n">
+        <v>395399</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Product &amp; export development</t>
+        </is>
+      </c>
+      <c r="B114" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C114" s="13" t="n">
+        <v>112800</v>
+      </c>
+      <c r="D114" s="13" t="n">
+        <v>669606</v>
+      </c>
+      <c r="E114" s="13" t="n">
+        <v>1492010</v>
+      </c>
+      <c r="F114" s="13" t="n">
+        <v>2544810</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Fixed overheads</t>
+        </is>
+      </c>
+      <c r="B115" s="13" t="n">
+        <v>539550</v>
+      </c>
+      <c r="C115" s="13" t="n">
+        <v>762564</v>
+      </c>
+      <c r="D115" s="13" t="n">
+        <v>808318</v>
+      </c>
+      <c r="E115" s="13" t="n">
+        <v>856817</v>
+      </c>
+      <c r="F115" s="13" t="n">
+        <v>908226</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
           <t>One-off setup costs</t>
         </is>
       </c>
-      <c r="B113" s="13" t="n">
+      <c r="B116" s="13" t="n">
         <v>388000</v>
       </c>
-      <c r="C113" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D113" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E113" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F113" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+      <c r="C116" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D116" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E116" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F116" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>TOTAL OPERATING COSTS</t>
         </is>
       </c>
-      <c r="B114" s="14" t="n">
+      <c r="B117" s="14" t="n">
         <v>2020549</v>
       </c>
-      <c r="C114" s="14" t="n">
+      <c r="C117" s="14" t="n">
         <v>4079252</v>
       </c>
-      <c r="D114" s="14" t="n">
+      <c r="D117" s="14" t="n">
         <v>9587909</v>
       </c>
-      <c r="E114" s="14" t="n">
+      <c r="E117" s="14" t="n">
         <v>14887283</v>
       </c>
-      <c r="F114" s="14" t="n">
+      <c r="F117" s="14" t="n">
         <v>20887463</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
-        <is>
-          <t>EBITDA</t>
-        </is>
-      </c>
-      <c r="B116" s="14" t="n">
-        <v>-1403054</v>
-      </c>
-      <c r="C116" s="14" t="n">
-        <v>845952</v>
-      </c>
-      <c r="D116" s="14" t="n">
-        <v>4671090</v>
-      </c>
-      <c r="E116" s="14" t="n">
-        <v>14001129</v>
-      </c>
-      <c r="F116" s="14" t="n">
-        <v>25700765</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Tax charge</t>
-        </is>
-      </c>
-      <c r="B117" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C117" s="13" t="n">
-        <v>51359</v>
-      </c>
-      <c r="D117" s="13" t="n">
-        <v>1059418</v>
-      </c>
-      <c r="E117" s="13" t="n">
-        <v>3780305</v>
-      </c>
-      <c r="F117" s="13" t="n">
-        <v>6939207</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
-        <is>
-          <t>NET PROFIT</t>
-        </is>
-      </c>
-      <c r="B118" s="14" t="n">
-        <v>-1403054</v>
-      </c>
-      <c r="C118" s="14" t="n">
-        <v>794593</v>
-      </c>
-      <c r="D118" s="14" t="n">
-        <v>3611672</v>
-      </c>
-      <c r="E118" s="14" t="n">
-        <v>10220824</v>
-      </c>
-      <c r="F118" s="14" t="n">
-        <v>18761558</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B119" s="14" t="n">
+        <v>-1403054</v>
+      </c>
+      <c r="C119" s="14" t="n">
+        <v>845952</v>
+      </c>
+      <c r="D119" s="14" t="n">
+        <v>4671090</v>
+      </c>
+      <c r="E119" s="14" t="n">
+        <v>14001129</v>
+      </c>
+      <c r="F119" s="14" t="n">
+        <v>25700765</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Finance costs (trade finance interest)</t>
+        </is>
+      </c>
+      <c r="B120" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C120" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D120" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E120" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F120" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Tax charge</t>
+        </is>
+      </c>
+      <c r="B121" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C121" s="13" t="n">
+        <v>51359</v>
+      </c>
+      <c r="D121" s="13" t="n">
+        <v>1059418</v>
+      </c>
+      <c r="E121" s="13" t="n">
+        <v>3780305</v>
+      </c>
+      <c r="F121" s="13" t="n">
+        <v>6939207</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>NET PROFIT</t>
+        </is>
+      </c>
+      <c r="B122" s="14" t="n">
+        <v>-1403054</v>
+      </c>
+      <c r="C122" s="14" t="n">
+        <v>794593</v>
+      </c>
+      <c r="D122" s="14" t="n">
+        <v>3611672</v>
+      </c>
+      <c r="E122" s="14" t="n">
+        <v>10220824</v>
+      </c>
+      <c r="F122" s="14" t="n">
+        <v>18761558</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="B119" s="15" t="n">
+      <c r="B123" s="15" t="n">
         <v>0.6234281424623985</v>
       </c>
-      <c r="C119" s="15" t="n">
+      <c r="C123" s="15" t="n">
         <v>0.6549471112262671</v>
       </c>
-      <c r="D119" s="15" t="n">
+      <c r="D123" s="15" t="n">
         <v>0.6724884021143732</v>
       </c>
-      <c r="E119" s="15" t="n">
+      <c r="E123" s="15" t="n">
         <v>0.6794610631616296</v>
       </c>
-      <c r="F119" s="15" t="n">
+      <c r="F123" s="15" t="n">
         <v>0.6792551645258191</v>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>EBITDA margin %</t>
         </is>
       </c>
-      <c r="B120" s="15" t="n">
+      <c r="B124" s="15" t="n">
         <v>-1.416532426685895</v>
       </c>
-      <c r="C120" s="15" t="n">
+      <c r="C124" s="15" t="n">
         <v>0.1124935956326389</v>
       </c>
-      <c r="D120" s="15" t="n">
+      <c r="D124" s="15" t="n">
         <v>0.2202997407136895</v>
       </c>
-      <c r="E120" s="15" t="n">
+      <c r="E124" s="15" t="n">
         <v>0.3293092689823605</v>
       </c>
-      <c r="F120" s="15" t="n">
+      <c r="F124" s="15" t="n">
         <v>0.3747164896496309</v>
       </c>
     </row>
@@ -6652,7 +6740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI15"/>
+  <dimension ref="A1:BI18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -8157,1123 +8245,1684 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Trade finance drawn</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI10" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Trade finance repaid</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI11" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>Funding received</t>
         </is>
       </c>
-      <c r="B10" s="13" t="n">
+      <c r="B12" s="13" t="n">
         <v>3500000</v>
       </c>
-      <c r="C10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" s="13" t="n">
+      <c r="C12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" s="13" t="n">
         <v>12000000</v>
       </c>
-      <c r="V10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI10" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="V12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI12" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>NET CASHFLOW</t>
         </is>
       </c>
-      <c r="B11" s="14" t="n">
+      <c r="B13" s="14" t="n">
         <v>3437000</v>
       </c>
-      <c r="C11" s="14" t="n">
+      <c r="C13" s="14" t="n">
         <v>-47720</v>
       </c>
-      <c r="D11" s="14" t="n">
+      <c r="D13" s="14" t="n">
         <v>-117352</v>
       </c>
-      <c r="E11" s="14" t="n">
+      <c r="E13" s="14" t="n">
         <v>-169918</v>
       </c>
-      <c r="F11" s="14" t="n">
+      <c r="F13" s="14" t="n">
         <v>-274750</v>
       </c>
-      <c r="G11" s="14" t="n">
+      <c r="G13" s="14" t="n">
         <v>-134010</v>
       </c>
-      <c r="H11" s="14" t="n">
+      <c r="H13" s="14" t="n">
         <v>-378489</v>
       </c>
-      <c r="I11" s="14" t="n">
+      <c r="I13" s="14" t="n">
         <v>-171117</v>
       </c>
-      <c r="J11" s="14" t="n">
+      <c r="J13" s="14" t="n">
         <v>-167217</v>
       </c>
-      <c r="K11" s="14" t="n">
+      <c r="K13" s="14" t="n">
         <v>-226573</v>
       </c>
-      <c r="L11" s="14" t="n">
+      <c r="L13" s="14" t="n">
         <v>-139339</v>
       </c>
-      <c r="M11" s="14" t="n">
+      <c r="M13" s="14" t="n">
         <v>-150438</v>
       </c>
-      <c r="N11" s="14" t="n">
+      <c r="N13" s="14" t="n">
         <v>-125789</v>
       </c>
-      <c r="O11" s="14" t="n">
+      <c r="O13" s="14" t="n">
         <v>-79438</v>
       </c>
-      <c r="P11" s="14" t="n">
+      <c r="P13" s="14" t="n">
         <v>-130854</v>
       </c>
-      <c r="Q11" s="14" t="n">
+      <c r="Q13" s="14" t="n">
         <v>-95380</v>
       </c>
-      <c r="R11" s="14" t="n">
+      <c r="R13" s="14" t="n">
         <v>-90735</v>
       </c>
-      <c r="S11" s="14" t="n">
+      <c r="S13" s="14" t="n">
         <v>-105289</v>
       </c>
-      <c r="T11" s="14" t="n">
+      <c r="T13" s="14" t="n">
         <v>-258990</v>
       </c>
-      <c r="U11" s="14" t="n">
+      <c r="U13" s="14" t="n">
         <v>11862173</v>
       </c>
-      <c r="V11" s="14" t="n">
+      <c r="V13" s="14" t="n">
         <v>-22778</v>
       </c>
-      <c r="W11" s="14" t="n">
+      <c r="W13" s="14" t="n">
         <v>-193698</v>
       </c>
-      <c r="X11" s="14" t="n">
+      <c r="X13" s="14" t="n">
         <v>45676</v>
       </c>
-      <c r="Y11" s="14" t="n">
+      <c r="Y13" s="14" t="n">
         <v>-222859</v>
       </c>
-      <c r="Z11" s="14" t="n">
+      <c r="Z13" s="14" t="n">
         <v>-17836</v>
       </c>
-      <c r="AA11" s="14" t="n">
+      <c r="AA13" s="14" t="n">
         <v>-652824</v>
       </c>
-      <c r="AB11" s="14" t="n">
+      <c r="AB13" s="14" t="n">
         <v>-48315</v>
       </c>
-      <c r="AC11" s="14" t="n">
+      <c r="AC13" s="14" t="n">
         <v>-167915</v>
       </c>
-      <c r="AD11" s="14" t="n">
+      <c r="AD13" s="14" t="n">
         <v>-86722</v>
       </c>
-      <c r="AE11" s="14" t="n">
+      <c r="AE13" s="14" t="n">
         <v>-165737</v>
       </c>
-      <c r="AF11" s="14" t="n">
+      <c r="AF13" s="14" t="n">
         <v>-240963</v>
       </c>
-      <c r="AG11" s="14" t="n">
+      <c r="AG13" s="14" t="n">
         <v>-322317</v>
       </c>
-      <c r="AH11" s="14" t="n">
+      <c r="AH13" s="14" t="n">
         <v>-413280</v>
       </c>
-      <c r="AI11" s="14" t="n">
+      <c r="AI13" s="14" t="n">
         <v>56881</v>
       </c>
-      <c r="AJ11" s="14" t="n">
+      <c r="AJ13" s="14" t="n">
         <v>100035</v>
       </c>
-      <c r="AK11" s="14" t="n">
+      <c r="AK13" s="14" t="n">
         <v>62687</v>
       </c>
-      <c r="AL11" s="14" t="n">
+      <c r="AL13" s="14" t="n">
         <v>105441</v>
       </c>
-      <c r="AM11" s="14" t="n">
+      <c r="AM13" s="14" t="n">
         <v>-195479</v>
       </c>
-      <c r="AN11" s="14" t="n">
+      <c r="AN13" s="14" t="n">
         <v>610756</v>
       </c>
-      <c r="AO11" s="14" t="n">
+      <c r="AO13" s="14" t="n">
         <v>284837</v>
       </c>
-      <c r="AP11" s="14" t="n">
+      <c r="AP13" s="14" t="n">
         <v>544094</v>
       </c>
-      <c r="AQ11" s="14" t="n">
+      <c r="AQ13" s="14" t="n">
         <v>78169</v>
       </c>
-      <c r="AR11" s="14" t="n">
+      <c r="AR13" s="14" t="n">
         <v>475129</v>
       </c>
-      <c r="AS11" s="14" t="n">
+      <c r="AS13" s="14" t="n">
         <v>247325</v>
       </c>
-      <c r="AT11" s="14" t="n">
+      <c r="AT13" s="14" t="n">
         <v>395706</v>
       </c>
-      <c r="AU11" s="14" t="n">
+      <c r="AU13" s="14" t="n">
         <v>353110</v>
       </c>
-      <c r="AV11" s="14" t="n">
+      <c r="AV13" s="14" t="n">
         <v>388645</v>
       </c>
-      <c r="AW11" s="14" t="n">
+      <c r="AW13" s="14" t="n">
         <v>-435033</v>
       </c>
-      <c r="AX11" s="14" t="n">
+      <c r="AX13" s="14" t="n">
         <v>324692</v>
       </c>
-      <c r="AY11" s="14" t="n">
+      <c r="AY13" s="14" t="n">
         <v>325553</v>
       </c>
-      <c r="AZ11" s="14" t="n">
+      <c r="AZ13" s="14" t="n">
         <v>1287920</v>
       </c>
-      <c r="BA11" s="14" t="n">
+      <c r="BA13" s="14" t="n">
         <v>1010934</v>
       </c>
-      <c r="BB11" s="14" t="n">
+      <c r="BB13" s="14" t="n">
         <v>1236870</v>
       </c>
-      <c r="BC11" s="14" t="n">
+      <c r="BC13" s="14" t="n">
         <v>-605550</v>
       </c>
-      <c r="BD11" s="14" t="n">
+      <c r="BD13" s="14" t="n">
         <v>1271461</v>
       </c>
-      <c r="BE11" s="14" t="n">
+      <c r="BE13" s="14" t="n">
         <v>1126361</v>
       </c>
-      <c r="BF11" s="14" t="n">
+      <c r="BF13" s="14" t="n">
         <v>1346047</v>
       </c>
-      <c r="BG11" s="14" t="n">
+      <c r="BG13" s="14" t="n">
         <v>1181136</v>
       </c>
-      <c r="BH11" s="14" t="n">
+      <c r="BH13" s="14" t="n">
         <v>1420633</v>
       </c>
-      <c r="BI11" s="14" t="n">
+      <c r="BI13" s="14" t="n">
         <v>-515212</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>CLOSING CASH</t>
         </is>
       </c>
-      <c r="B12" s="14" t="n">
+      <c r="B14" s="14" t="n">
         <v>3437000</v>
       </c>
-      <c r="C12" s="14" t="n">
+      <c r="C14" s="14" t="n">
         <v>3389280</v>
       </c>
-      <c r="D12" s="14" t="n">
+      <c r="D14" s="14" t="n">
         <v>3271928</v>
       </c>
-      <c r="E12" s="14" t="n">
+      <c r="E14" s="14" t="n">
         <v>3102011</v>
       </c>
-      <c r="F12" s="14" t="n">
+      <c r="F14" s="14" t="n">
         <v>2827260</v>
       </c>
-      <c r="G12" s="14" t="n">
+      <c r="G14" s="14" t="n">
         <v>2693250</v>
       </c>
-      <c r="H12" s="14" t="n">
+      <c r="H14" s="14" t="n">
         <v>2314761</v>
       </c>
-      <c r="I12" s="14" t="n">
+      <c r="I14" s="14" t="n">
         <v>2143644</v>
       </c>
-      <c r="J12" s="14" t="n">
+      <c r="J14" s="14" t="n">
         <v>1976427</v>
       </c>
-      <c r="K12" s="14" t="n">
+      <c r="K14" s="14" t="n">
         <v>1749854</v>
       </c>
-      <c r="L12" s="14" t="n">
+      <c r="L14" s="14" t="n">
         <v>1610515</v>
       </c>
-      <c r="M12" s="14" t="n">
+      <c r="M14" s="14" t="n">
         <v>1460077</v>
       </c>
-      <c r="N12" s="14" t="n">
+      <c r="N14" s="14" t="n">
         <v>1334288</v>
       </c>
-      <c r="O12" s="14" t="n">
+      <c r="O14" s="14" t="n">
         <v>1254850</v>
       </c>
-      <c r="P12" s="14" t="n">
+      <c r="P14" s="14" t="n">
         <v>1123995</v>
       </c>
-      <c r="Q12" s="14" t="n">
+      <c r="Q14" s="14" t="n">
         <v>1028616</v>
       </c>
-      <c r="R12" s="14" t="n">
+      <c r="R14" s="14" t="n">
         <v>937881</v>
       </c>
-      <c r="S12" s="14" t="n">
+      <c r="S14" s="14" t="n">
         <v>832592</v>
       </c>
-      <c r="T12" s="14" t="n">
+      <c r="T14" s="14" t="n">
         <v>573601</v>
       </c>
-      <c r="U12" s="14" t="n">
+      <c r="U14" s="14" t="n">
         <v>12435774</v>
       </c>
-      <c r="V12" s="14" t="n">
+      <c r="V14" s="14" t="n">
         <v>12412996</v>
       </c>
-      <c r="W12" s="14" t="n">
+      <c r="W14" s="14" t="n">
         <v>12219298</v>
       </c>
-      <c r="X12" s="14" t="n">
+      <c r="X14" s="14" t="n">
         <v>12264974</v>
       </c>
-      <c r="Y12" s="14" t="n">
+      <c r="Y14" s="14" t="n">
         <v>12042115</v>
       </c>
-      <c r="Z12" s="14" t="n">
+      <c r="Z14" s="14" t="n">
         <v>12024279</v>
       </c>
-      <c r="AA12" s="14" t="n">
+      <c r="AA14" s="14" t="n">
         <v>11371455</v>
       </c>
-      <c r="AB12" s="14" t="n">
+      <c r="AB14" s="14" t="n">
         <v>11323141</v>
       </c>
-      <c r="AC12" s="14" t="n">
+      <c r="AC14" s="14" t="n">
         <v>11155226</v>
       </c>
-      <c r="AD12" s="14" t="n">
+      <c r="AD14" s="14" t="n">
         <v>11068504</v>
       </c>
-      <c r="AE12" s="14" t="n">
+      <c r="AE14" s="14" t="n">
         <v>10902767</v>
       </c>
-      <c r="AF12" s="14" t="n">
+      <c r="AF14" s="14" t="n">
         <v>10661804</v>
       </c>
-      <c r="AG12" s="14" t="n">
+      <c r="AG14" s="14" t="n">
         <v>10339487</v>
       </c>
-      <c r="AH12" s="14" t="n">
+      <c r="AH14" s="14" t="n">
         <v>9926207</v>
       </c>
-      <c r="AI12" s="14" t="n">
+      <c r="AI14" s="14" t="n">
         <v>9983087</v>
       </c>
-      <c r="AJ12" s="14" t="n">
+      <c r="AJ14" s="14" t="n">
         <v>10083122</v>
       </c>
-      <c r="AK12" s="14" t="n">
+      <c r="AK14" s="14" t="n">
         <v>10145809</v>
       </c>
-      <c r="AL12" s="14" t="n">
+      <c r="AL14" s="14" t="n">
         <v>10251250</v>
       </c>
-      <c r="AM12" s="14" t="n">
+      <c r="AM14" s="14" t="n">
         <v>10055771</v>
       </c>
-      <c r="AN12" s="14" t="n">
+      <c r="AN14" s="14" t="n">
         <v>10666527</v>
       </c>
-      <c r="AO12" s="14" t="n">
+      <c r="AO14" s="14" t="n">
         <v>10951364</v>
       </c>
-      <c r="AP12" s="14" t="n">
+      <c r="AP14" s="14" t="n">
         <v>11495458</v>
       </c>
-      <c r="AQ12" s="14" t="n">
+      <c r="AQ14" s="14" t="n">
         <v>11573627</v>
       </c>
-      <c r="AR12" s="14" t="n">
+      <c r="AR14" s="14" t="n">
         <v>12048756</v>
       </c>
-      <c r="AS12" s="14" t="n">
+      <c r="AS14" s="14" t="n">
         <v>12296081</v>
       </c>
-      <c r="AT12" s="14" t="n">
+      <c r="AT14" s="14" t="n">
         <v>12691787</v>
       </c>
-      <c r="AU12" s="14" t="n">
+      <c r="AU14" s="14" t="n">
         <v>13044897</v>
       </c>
-      <c r="AV12" s="14" t="n">
+      <c r="AV14" s="14" t="n">
         <v>13433542</v>
       </c>
-      <c r="AW12" s="14" t="n">
+      <c r="AW14" s="14" t="n">
         <v>12998508</v>
       </c>
-      <c r="AX12" s="14" t="n">
+      <c r="AX14" s="14" t="n">
         <v>13323200</v>
       </c>
-      <c r="AY12" s="14" t="n">
+      <c r="AY14" s="14" t="n">
         <v>13648753</v>
       </c>
-      <c r="AZ12" s="14" t="n">
+      <c r="AZ14" s="14" t="n">
         <v>14936673</v>
       </c>
-      <c r="BA12" s="14" t="n">
+      <c r="BA14" s="14" t="n">
         <v>15947607</v>
       </c>
-      <c r="BB12" s="14" t="n">
+      <c r="BB14" s="14" t="n">
         <v>17184477</v>
       </c>
-      <c r="BC12" s="14" t="n">
+      <c r="BC14" s="14" t="n">
         <v>16578927</v>
       </c>
-      <c r="BD12" s="14" t="n">
+      <c r="BD14" s="14" t="n">
         <v>17850388</v>
       </c>
-      <c r="BE12" s="14" t="n">
+      <c r="BE14" s="14" t="n">
         <v>18976749</v>
       </c>
-      <c r="BF12" s="14" t="n">
+      <c r="BF14" s="14" t="n">
         <v>20322796</v>
       </c>
-      <c r="BG12" s="14" t="n">
+      <c r="BG14" s="14" t="n">
         <v>21503932</v>
       </c>
-      <c r="BH12" s="14" t="n">
+      <c r="BH14" s="14" t="n">
         <v>22924565</v>
       </c>
-      <c r="BI12" s="14" t="n">
+      <c r="BI14" s="14" t="n">
         <v>22409352</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Stock on hand (units)</t>
-        </is>
-      </c>
-      <c r="B13" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="12" t="n">
-        <v>21032</v>
-      </c>
-      <c r="I13" s="12" t="n">
-        <v>18525</v>
-      </c>
-      <c r="J13" s="12" t="n">
-        <v>37450</v>
-      </c>
-      <c r="K13" s="12" t="n">
-        <v>32837</v>
-      </c>
-      <c r="L13" s="12" t="n">
-        <v>27170</v>
-      </c>
-      <c r="M13" s="12" t="n">
-        <v>42935</v>
-      </c>
-      <c r="N13" s="12" t="n">
-        <v>33559</v>
-      </c>
-      <c r="O13" s="12" t="n">
-        <v>45750</v>
-      </c>
-      <c r="P13" s="12" t="n">
-        <v>57026</v>
-      </c>
-      <c r="Q13" s="12" t="n">
-        <v>44899</v>
-      </c>
-      <c r="R13" s="12" t="n">
-        <v>54341</v>
-      </c>
-      <c r="S13" s="12" t="n">
-        <v>62866</v>
-      </c>
-      <c r="T13" s="12" t="n">
-        <v>69994</v>
-      </c>
-      <c r="U13" s="12" t="n">
-        <v>75726</v>
-      </c>
-      <c r="V13" s="12" t="n">
-        <v>80061</v>
-      </c>
-      <c r="W13" s="12" t="n">
-        <v>83000</v>
-      </c>
-      <c r="X13" s="12" t="n">
-        <v>84541</v>
-      </c>
-      <c r="Y13" s="12" t="n">
-        <v>107172</v>
-      </c>
-      <c r="Z13" s="12" t="n">
-        <v>101387</v>
-      </c>
-      <c r="AA13" s="12" t="n">
-        <v>116187</v>
-      </c>
-      <c r="AB13" s="12" t="n">
-        <v>106602</v>
-      </c>
-      <c r="AC13" s="12" t="n">
-        <v>140088</v>
-      </c>
-      <c r="AD13" s="12" t="n">
-        <v>149188</v>
-      </c>
-      <c r="AE13" s="12" t="n">
-        <v>178873</v>
-      </c>
-      <c r="AF13" s="12" t="n">
-        <v>191658</v>
-      </c>
-      <c r="AG13" s="12" t="n">
-        <v>180059</v>
-      </c>
-      <c r="AH13" s="12" t="n">
-        <v>189044</v>
-      </c>
-      <c r="AI13" s="12" t="n">
-        <v>218615</v>
-      </c>
-      <c r="AJ13" s="12" t="n">
-        <v>246285</v>
-      </c>
-      <c r="AK13" s="12" t="n">
-        <v>272056</v>
-      </c>
-      <c r="AL13" s="12" t="n">
-        <v>277558</v>
-      </c>
-      <c r="AM13" s="12" t="n">
-        <v>281191</v>
-      </c>
-      <c r="AN13" s="12" t="n">
-        <v>282952</v>
-      </c>
-      <c r="AO13" s="12" t="n">
-        <v>282842</v>
-      </c>
-      <c r="AP13" s="12" t="n">
-        <v>280862</v>
-      </c>
-      <c r="AQ13" s="12" t="n">
-        <v>299496</v>
-      </c>
-      <c r="AR13" s="12" t="n">
-        <v>293774</v>
-      </c>
-      <c r="AS13" s="12" t="n">
-        <v>308666</v>
-      </c>
-      <c r="AT13" s="12" t="n">
-        <v>321688</v>
-      </c>
-      <c r="AU13" s="12" t="n">
-        <v>355323</v>
-      </c>
-      <c r="AV13" s="12" t="n">
-        <v>387088</v>
-      </c>
-      <c r="AW13" s="12" t="n">
-        <v>416982</v>
-      </c>
-      <c r="AX13" s="12" t="n">
-        <v>433814</v>
-      </c>
-      <c r="AY13" s="12" t="n">
-        <v>426587</v>
-      </c>
-      <c r="AZ13" s="12" t="n">
-        <v>440272</v>
-      </c>
-      <c r="BA13" s="12" t="n">
-        <v>452385</v>
-      </c>
-      <c r="BB13" s="12" t="n">
-        <v>440439</v>
-      </c>
-      <c r="BC13" s="12" t="n">
-        <v>449406</v>
-      </c>
-      <c r="BD13" s="12" t="n">
-        <v>456800</v>
-      </c>
-      <c r="BE13" s="12" t="n">
-        <v>462621</v>
-      </c>
-      <c r="BF13" s="12" t="n">
-        <v>466868</v>
-      </c>
-      <c r="BG13" s="12" t="n">
-        <v>469543</v>
-      </c>
-      <c r="BH13" s="12" t="n">
-        <v>470646</v>
-      </c>
-      <c r="BI13" s="12" t="n">
-        <v>470175</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Stock on hand (value)</t>
-        </is>
-      </c>
-      <c r="B14" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="13" t="n">
-        <v>216424</v>
-      </c>
-      <c r="I14" s="13" t="n">
-        <v>190630</v>
-      </c>
-      <c r="J14" s="13" t="n">
-        <v>385375</v>
-      </c>
-      <c r="K14" s="13" t="n">
-        <v>337903</v>
-      </c>
-      <c r="L14" s="13" t="n">
-        <v>279591</v>
-      </c>
-      <c r="M14" s="13" t="n">
-        <v>441819</v>
-      </c>
-      <c r="N14" s="13" t="n">
-        <v>345330</v>
-      </c>
-      <c r="O14" s="13" t="n">
-        <v>450854</v>
-      </c>
-      <c r="P14" s="13" t="n">
-        <v>549747</v>
-      </c>
-      <c r="Q14" s="13" t="n">
-        <v>432842</v>
-      </c>
-      <c r="R14" s="13" t="n">
-        <v>522426</v>
-      </c>
-      <c r="S14" s="13" t="n">
-        <v>603414</v>
-      </c>
-      <c r="T14" s="13" t="n">
-        <v>671147</v>
-      </c>
-      <c r="U14" s="13" t="n">
-        <v>725600</v>
-      </c>
-      <c r="V14" s="13" t="n">
-        <v>766756</v>
-      </c>
-      <c r="W14" s="13" t="n">
-        <v>794606</v>
-      </c>
-      <c r="X14" s="13" t="n">
-        <v>809140</v>
-      </c>
-      <c r="Y14" s="13" t="n">
-        <v>1025366</v>
-      </c>
-      <c r="Z14" s="13" t="n">
-        <v>956043</v>
-      </c>
-      <c r="AA14" s="13" t="n">
-        <v>1072147</v>
-      </c>
-      <c r="AB14" s="13" t="n">
-        <v>975833</v>
-      </c>
-      <c r="AC14" s="13" t="n">
-        <v>1250652</v>
-      </c>
-      <c r="AD14" s="13" t="n">
-        <v>1338581</v>
-      </c>
-      <c r="AE14" s="13" t="n">
-        <v>1601134</v>
-      </c>
-      <c r="AF14" s="13" t="n">
-        <v>1713114</v>
-      </c>
-      <c r="AG14" s="13" t="n">
-        <v>1615374</v>
-      </c>
-      <c r="AH14" s="13" t="n">
-        <v>1692528</v>
-      </c>
-      <c r="AI14" s="13" t="n">
-        <v>1953835</v>
-      </c>
-      <c r="AJ14" s="13" t="n">
-        <v>2198762</v>
-      </c>
-      <c r="AK14" s="13" t="n">
-        <v>2427128</v>
-      </c>
-      <c r="AL14" s="13" t="n">
-        <v>2435302</v>
-      </c>
-      <c r="AM14" s="13" t="n">
-        <v>2436482</v>
-      </c>
-      <c r="AN14" s="13" t="n">
-        <v>2428649</v>
-      </c>
-      <c r="AO14" s="13" t="n">
-        <v>2410300</v>
-      </c>
-      <c r="AP14" s="13" t="n">
-        <v>2402300</v>
-      </c>
-      <c r="AQ14" s="13" t="n">
-        <v>2570190</v>
-      </c>
-      <c r="AR14" s="13" t="n">
-        <v>2525901</v>
-      </c>
-      <c r="AS14" s="13" t="n">
-        <v>2658609</v>
-      </c>
-      <c r="AT14" s="13" t="n">
-        <v>2774156</v>
-      </c>
-      <c r="AU14" s="13" t="n">
-        <v>3067260</v>
-      </c>
-      <c r="AV14" s="13" t="n">
-        <v>3343636</v>
-      </c>
-      <c r="AW14" s="13" t="n">
-        <v>3603450</v>
-      </c>
-      <c r="AX14" s="13" t="n">
-        <v>3692666</v>
-      </c>
-      <c r="AY14" s="13" t="n">
-        <v>3596398</v>
-      </c>
-      <c r="AZ14" s="13" t="n">
-        <v>3680690</v>
-      </c>
-      <c r="BA14" s="13" t="n">
-        <v>3759154</v>
-      </c>
-      <c r="BB14" s="13" t="n">
-        <v>3677828</v>
-      </c>
-      <c r="BC14" s="13" t="n">
-        <v>3768860</v>
-      </c>
-      <c r="BD14" s="13" t="n">
-        <v>3842787</v>
-      </c>
-      <c r="BE14" s="13" t="n">
-        <v>3900587</v>
-      </c>
-      <c r="BF14" s="13" t="n">
-        <v>3942971</v>
-      </c>
-      <c r="BG14" s="13" t="n">
-        <v>3970458</v>
-      </c>
-      <c r="BH14" s="13" t="n">
-        <v>3983431</v>
-      </c>
-      <c r="BI14" s="13" t="n">
-        <v>3982175</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>Stock on hand (units)</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="12" t="n">
+        <v>21032</v>
+      </c>
+      <c r="I15" s="12" t="n">
+        <v>18525</v>
+      </c>
+      <c r="J15" s="12" t="n">
+        <v>37450</v>
+      </c>
+      <c r="K15" s="12" t="n">
+        <v>32837</v>
+      </c>
+      <c r="L15" s="12" t="n">
+        <v>27170</v>
+      </c>
+      <c r="M15" s="12" t="n">
+        <v>42935</v>
+      </c>
+      <c r="N15" s="12" t="n">
+        <v>33559</v>
+      </c>
+      <c r="O15" s="12" t="n">
+        <v>45750</v>
+      </c>
+      <c r="P15" s="12" t="n">
+        <v>57026</v>
+      </c>
+      <c r="Q15" s="12" t="n">
+        <v>44899</v>
+      </c>
+      <c r="R15" s="12" t="n">
+        <v>54341</v>
+      </c>
+      <c r="S15" s="12" t="n">
+        <v>62866</v>
+      </c>
+      <c r="T15" s="12" t="n">
+        <v>69994</v>
+      </c>
+      <c r="U15" s="12" t="n">
+        <v>75726</v>
+      </c>
+      <c r="V15" s="12" t="n">
+        <v>80061</v>
+      </c>
+      <c r="W15" s="12" t="n">
+        <v>83000</v>
+      </c>
+      <c r="X15" s="12" t="n">
+        <v>84541</v>
+      </c>
+      <c r="Y15" s="12" t="n">
+        <v>107172</v>
+      </c>
+      <c r="Z15" s="12" t="n">
+        <v>101387</v>
+      </c>
+      <c r="AA15" s="12" t="n">
+        <v>116187</v>
+      </c>
+      <c r="AB15" s="12" t="n">
+        <v>106602</v>
+      </c>
+      <c r="AC15" s="12" t="n">
+        <v>140088</v>
+      </c>
+      <c r="AD15" s="12" t="n">
+        <v>149188</v>
+      </c>
+      <c r="AE15" s="12" t="n">
+        <v>178873</v>
+      </c>
+      <c r="AF15" s="12" t="n">
+        <v>191658</v>
+      </c>
+      <c r="AG15" s="12" t="n">
+        <v>180059</v>
+      </c>
+      <c r="AH15" s="12" t="n">
+        <v>189044</v>
+      </c>
+      <c r="AI15" s="12" t="n">
+        <v>218615</v>
+      </c>
+      <c r="AJ15" s="12" t="n">
+        <v>246285</v>
+      </c>
+      <c r="AK15" s="12" t="n">
+        <v>272056</v>
+      </c>
+      <c r="AL15" s="12" t="n">
+        <v>277558</v>
+      </c>
+      <c r="AM15" s="12" t="n">
+        <v>281191</v>
+      </c>
+      <c r="AN15" s="12" t="n">
+        <v>282952</v>
+      </c>
+      <c r="AO15" s="12" t="n">
+        <v>282842</v>
+      </c>
+      <c r="AP15" s="12" t="n">
+        <v>280862</v>
+      </c>
+      <c r="AQ15" s="12" t="n">
+        <v>299496</v>
+      </c>
+      <c r="AR15" s="12" t="n">
+        <v>293774</v>
+      </c>
+      <c r="AS15" s="12" t="n">
+        <v>308666</v>
+      </c>
+      <c r="AT15" s="12" t="n">
+        <v>321688</v>
+      </c>
+      <c r="AU15" s="12" t="n">
+        <v>355323</v>
+      </c>
+      <c r="AV15" s="12" t="n">
+        <v>387088</v>
+      </c>
+      <c r="AW15" s="12" t="n">
+        <v>416982</v>
+      </c>
+      <c r="AX15" s="12" t="n">
+        <v>433814</v>
+      </c>
+      <c r="AY15" s="12" t="n">
+        <v>426587</v>
+      </c>
+      <c r="AZ15" s="12" t="n">
+        <v>440272</v>
+      </c>
+      <c r="BA15" s="12" t="n">
+        <v>452385</v>
+      </c>
+      <c r="BB15" s="12" t="n">
+        <v>440439</v>
+      </c>
+      <c r="BC15" s="12" t="n">
+        <v>449406</v>
+      </c>
+      <c r="BD15" s="12" t="n">
+        <v>456800</v>
+      </c>
+      <c r="BE15" s="12" t="n">
+        <v>462621</v>
+      </c>
+      <c r="BF15" s="12" t="n">
+        <v>466868</v>
+      </c>
+      <c r="BG15" s="12" t="n">
+        <v>469543</v>
+      </c>
+      <c r="BH15" s="12" t="n">
+        <v>470646</v>
+      </c>
+      <c r="BI15" s="12" t="n">
+        <v>470175</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Stock on hand (value)</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="13" t="n">
+        <v>216424</v>
+      </c>
+      <c r="I16" s="13" t="n">
+        <v>190630</v>
+      </c>
+      <c r="J16" s="13" t="n">
+        <v>385375</v>
+      </c>
+      <c r="K16" s="13" t="n">
+        <v>337903</v>
+      </c>
+      <c r="L16" s="13" t="n">
+        <v>279591</v>
+      </c>
+      <c r="M16" s="13" t="n">
+        <v>441819</v>
+      </c>
+      <c r="N16" s="13" t="n">
+        <v>345330</v>
+      </c>
+      <c r="O16" s="13" t="n">
+        <v>450854</v>
+      </c>
+      <c r="P16" s="13" t="n">
+        <v>549747</v>
+      </c>
+      <c r="Q16" s="13" t="n">
+        <v>432842</v>
+      </c>
+      <c r="R16" s="13" t="n">
+        <v>522426</v>
+      </c>
+      <c r="S16" s="13" t="n">
+        <v>603414</v>
+      </c>
+      <c r="T16" s="13" t="n">
+        <v>671147</v>
+      </c>
+      <c r="U16" s="13" t="n">
+        <v>725600</v>
+      </c>
+      <c r="V16" s="13" t="n">
+        <v>766756</v>
+      </c>
+      <c r="W16" s="13" t="n">
+        <v>794606</v>
+      </c>
+      <c r="X16" s="13" t="n">
+        <v>809140</v>
+      </c>
+      <c r="Y16" s="13" t="n">
+        <v>1025366</v>
+      </c>
+      <c r="Z16" s="13" t="n">
+        <v>956043</v>
+      </c>
+      <c r="AA16" s="13" t="n">
+        <v>1072147</v>
+      </c>
+      <c r="AB16" s="13" t="n">
+        <v>975833</v>
+      </c>
+      <c r="AC16" s="13" t="n">
+        <v>1250652</v>
+      </c>
+      <c r="AD16" s="13" t="n">
+        <v>1338581</v>
+      </c>
+      <c r="AE16" s="13" t="n">
+        <v>1601134</v>
+      </c>
+      <c r="AF16" s="13" t="n">
+        <v>1713114</v>
+      </c>
+      <c r="AG16" s="13" t="n">
+        <v>1615374</v>
+      </c>
+      <c r="AH16" s="13" t="n">
+        <v>1692528</v>
+      </c>
+      <c r="AI16" s="13" t="n">
+        <v>1953835</v>
+      </c>
+      <c r="AJ16" s="13" t="n">
+        <v>2198762</v>
+      </c>
+      <c r="AK16" s="13" t="n">
+        <v>2427128</v>
+      </c>
+      <c r="AL16" s="13" t="n">
+        <v>2435302</v>
+      </c>
+      <c r="AM16" s="13" t="n">
+        <v>2436482</v>
+      </c>
+      <c r="AN16" s="13" t="n">
+        <v>2428649</v>
+      </c>
+      <c r="AO16" s="13" t="n">
+        <v>2410300</v>
+      </c>
+      <c r="AP16" s="13" t="n">
+        <v>2402300</v>
+      </c>
+      <c r="AQ16" s="13" t="n">
+        <v>2570190</v>
+      </c>
+      <c r="AR16" s="13" t="n">
+        <v>2525901</v>
+      </c>
+      <c r="AS16" s="13" t="n">
+        <v>2658609</v>
+      </c>
+      <c r="AT16" s="13" t="n">
+        <v>2774156</v>
+      </c>
+      <c r="AU16" s="13" t="n">
+        <v>3067260</v>
+      </c>
+      <c r="AV16" s="13" t="n">
+        <v>3343636</v>
+      </c>
+      <c r="AW16" s="13" t="n">
+        <v>3603450</v>
+      </c>
+      <c r="AX16" s="13" t="n">
+        <v>3692666</v>
+      </c>
+      <c r="AY16" s="13" t="n">
+        <v>3596398</v>
+      </c>
+      <c r="AZ16" s="13" t="n">
+        <v>3680690</v>
+      </c>
+      <c r="BA16" s="13" t="n">
+        <v>3759154</v>
+      </c>
+      <c r="BB16" s="13" t="n">
+        <v>3677828</v>
+      </c>
+      <c r="BC16" s="13" t="n">
+        <v>3768860</v>
+      </c>
+      <c r="BD16" s="13" t="n">
+        <v>3842787</v>
+      </c>
+      <c r="BE16" s="13" t="n">
+        <v>3900587</v>
+      </c>
+      <c r="BF16" s="13" t="n">
+        <v>3942971</v>
+      </c>
+      <c r="BG16" s="13" t="n">
+        <v>3970458</v>
+      </c>
+      <c r="BH16" s="13" t="n">
+        <v>3983431</v>
+      </c>
+      <c r="BI16" s="13" t="n">
+        <v>3982175</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>Debtors</t>
         </is>
       </c>
-      <c r="B15" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="13" t="n">
+      <c r="B17" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="13" t="n">
         <v>29375</v>
       </c>
-      <c r="I15" s="13" t="n">
+      <c r="I17" s="13" t="n">
         <v>58750</v>
       </c>
-      <c r="J15" s="13" t="n">
+      <c r="J17" s="13" t="n">
         <v>88124</v>
       </c>
-      <c r="K15" s="13" t="n">
+      <c r="K17" s="13" t="n">
         <v>117499</v>
       </c>
-      <c r="L15" s="13" t="n">
+      <c r="L17" s="13" t="n">
         <v>146874</v>
       </c>
-      <c r="M15" s="13" t="n">
+      <c r="M17" s="13" t="n">
         <v>176249</v>
       </c>
-      <c r="N15" s="13" t="n">
+      <c r="N17" s="13" t="n">
         <v>235298</v>
       </c>
-      <c r="O15" s="13" t="n">
+      <c r="O17" s="13" t="n">
         <v>261496</v>
       </c>
-      <c r="P15" s="13" t="n">
+      <c r="P17" s="13" t="n">
         <v>287695</v>
       </c>
-      <c r="Q15" s="13" t="n">
+      <c r="Q17" s="13" t="n">
         <v>313893</v>
       </c>
-      <c r="R15" s="13" t="n">
+      <c r="R17" s="13" t="n">
         <v>340091</v>
       </c>
-      <c r="S15" s="13" t="n">
+      <c r="S17" s="13" t="n">
         <v>366290</v>
       </c>
-      <c r="T15" s="13" t="n">
+      <c r="T17" s="13" t="n">
         <v>404660</v>
       </c>
-      <c r="U15" s="13" t="n">
+      <c r="U17" s="13" t="n">
         <v>455201</v>
       </c>
-      <c r="V15" s="13" t="n">
+      <c r="V17" s="13" t="n">
         <v>505743</v>
       </c>
-      <c r="W15" s="13" t="n">
+      <c r="W17" s="13" t="n">
         <v>556284</v>
       </c>
-      <c r="X15" s="13" t="n">
+      <c r="X17" s="13" t="n">
         <v>606826</v>
       </c>
-      <c r="Y15" s="13" t="n">
+      <c r="Y17" s="13" t="n">
         <v>657368</v>
       </c>
-      <c r="Z15" s="13" t="n">
+      <c r="Z17" s="13" t="n">
         <v>814707</v>
       </c>
-      <c r="AA15" s="13" t="n">
+      <c r="AA17" s="13" t="n">
         <v>899728</v>
       </c>
-      <c r="AB15" s="13" t="n">
+      <c r="AB17" s="13" t="n">
         <v>971512</v>
       </c>
-      <c r="AC15" s="13" t="n">
+      <c r="AC17" s="13" t="n">
         <v>1043296</v>
       </c>
-      <c r="AD15" s="13" t="n">
+      <c r="AD17" s="13" t="n">
         <v>1115080</v>
       </c>
-      <c r="AE15" s="13" t="n">
+      <c r="AE17" s="13" t="n">
         <v>1186865</v>
       </c>
-      <c r="AF15" s="13" t="n">
+      <c r="AF17" s="13" t="n">
         <v>1514980</v>
       </c>
-      <c r="AG15" s="13" t="n">
+      <c r="AG17" s="13" t="n">
         <v>1843095</v>
       </c>
-      <c r="AH15" s="13" t="n">
+      <c r="AH17" s="13" t="n">
         <v>1914879</v>
       </c>
-      <c r="AI15" s="13" t="n">
+      <c r="AI17" s="13" t="n">
         <v>1986663</v>
       </c>
-      <c r="AJ15" s="13" t="n">
+      <c r="AJ17" s="13" t="n">
         <v>2058448</v>
       </c>
-      <c r="AK15" s="13" t="n">
+      <c r="AK17" s="13" t="n">
         <v>2130232</v>
       </c>
-      <c r="AL15" s="13" t="n">
+      <c r="AL17" s="13" t="n">
         <v>2638969</v>
       </c>
-      <c r="AM15" s="13" t="n">
+      <c r="AM17" s="13" t="n">
         <v>3024009</v>
       </c>
-      <c r="AN15" s="13" t="n">
+      <c r="AN17" s="13" t="n">
         <v>3099646</v>
       </c>
-      <c r="AO15" s="13" t="n">
+      <c r="AO17" s="13" t="n">
         <v>3175283</v>
       </c>
-      <c r="AP15" s="13" t="n">
+      <c r="AP17" s="13" t="n">
         <v>3250920</v>
       </c>
-      <c r="AQ15" s="13" t="n">
+      <c r="AQ17" s="13" t="n">
         <v>3326557</v>
       </c>
-      <c r="AR15" s="13" t="n">
+      <c r="AR17" s="13" t="n">
         <v>3402194</v>
       </c>
-      <c r="AS15" s="13" t="n">
+      <c r="AS17" s="13" t="n">
         <v>3477831</v>
       </c>
-      <c r="AT15" s="13" t="n">
+      <c r="AT17" s="13" t="n">
         <v>3553467</v>
       </c>
-      <c r="AU15" s="13" t="n">
+      <c r="AU17" s="13" t="n">
         <v>3629104</v>
       </c>
-      <c r="AV15" s="13" t="n">
+      <c r="AV17" s="13" t="n">
         <v>3704741</v>
       </c>
-      <c r="AW15" s="13" t="n">
+      <c r="AW17" s="13" t="n">
         <v>3780378</v>
       </c>
-      <c r="AX15" s="13" t="n">
+      <c r="AX17" s="13" t="n">
         <v>4748621</v>
       </c>
-      <c r="AY15" s="13" t="n">
+      <c r="AY17" s="13" t="n">
         <v>5555762</v>
       </c>
-      <c r="AZ15" s="13" t="n">
+      <c r="AZ17" s="13" t="n">
         <v>5623687</v>
       </c>
-      <c r="BA15" s="13" t="n">
+      <c r="BA17" s="13" t="n">
         <v>5691612</v>
       </c>
-      <c r="BB15" s="13" t="n">
+      <c r="BB17" s="13" t="n">
         <v>5759537</v>
       </c>
-      <c r="BC15" s="13" t="n">
+      <c r="BC17" s="13" t="n">
         <v>5827463</v>
       </c>
-      <c r="BD15" s="13" t="n">
+      <c r="BD17" s="13" t="n">
         <v>5895388</v>
       </c>
-      <c r="BE15" s="13" t="n">
+      <c r="BE17" s="13" t="n">
         <v>5963313</v>
       </c>
-      <c r="BF15" s="13" t="n">
+      <c r="BF17" s="13" t="n">
         <v>6031238</v>
       </c>
-      <c r="BG15" s="13" t="n">
+      <c r="BG17" s="13" t="n">
         <v>6099163</v>
       </c>
-      <c r="BH15" s="13" t="n">
+      <c r="BH17" s="13" t="n">
         <v>6167088</v>
       </c>
-      <c r="BI15" s="13" t="n">
+      <c r="BI17" s="13" t="n">
         <v>6235014</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Trade finance outstanding</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI18" s="13" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -9337,7 +9986,7 @@
         </is>
       </c>
       <c r="B4" s="8" t="n">
-        <v>0.123</v>
+        <v>0.1751</v>
       </c>
       <c r="C4" s="8" t="n">
         <v>0.45</v>
@@ -9356,7 +10005,7 @@
         </is>
       </c>
       <c r="B5" s="12" t="n">
-        <v>6800</v>
+        <v>10760</v>
       </c>
       <c r="C5" s="12" t="n">
         <v>11034</v>
@@ -9375,7 +10024,7 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>97490</v>
+        <v>145530</v>
       </c>
       <c r="C6" s="12" t="n">
         <v>249588</v>
@@ -9394,7 +10043,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>220215</v>
+        <v>313600</v>
       </c>
       <c r="C7" s="12" t="n">
         <v>805764.375</v>
@@ -9413,7 +10062,7 @@
         </is>
       </c>
       <c r="B8" s="13" t="n">
-        <v>177800</v>
+        <v>280280</v>
       </c>
       <c r="C8" s="13" t="n">
         <v>262433.43</v>
@@ -9432,7 +10081,7 @@
         </is>
       </c>
       <c r="B9" s="13" t="n">
-        <v>2734456.3312</v>
+        <v>4404169.2563</v>
       </c>
       <c r="C9" s="13" t="n">
         <v>5617921.8469</v>
@@ -9451,7 +10100,7 @@
         </is>
       </c>
       <c r="B10" s="13" t="n">
-        <v>7126263.6488</v>
+        <v>11915682.6956</v>
       </c>
       <c r="C10" s="13" t="n">
         <v>17695582.2721</v>
@@ -9470,7 +10119,7 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>0.6761</v>
+        <v>0.724</v>
       </c>
       <c r="C11" s="8" t="n">
         <v>0.5615</v>
@@ -9489,7 +10138,7 @@
         </is>
       </c>
       <c r="B12" s="13" t="n">
-        <v>1994524.1093</v>
+        <v>4474774.0176</v>
       </c>
       <c r="C12" s="13" t="n">
         <v>-189443.314</v>
@@ -9508,7 +10157,7 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>0.2799</v>
+        <v>0.3755</v>
       </c>
       <c r="C13" s="8" t="n">
         <v>-0.0107</v>
@@ -9527,7 +10176,7 @@
         </is>
       </c>
       <c r="B14" s="13" t="n">
-        <v>3157322.4809</v>
+        <v>7650031.5221</v>
       </c>
       <c r="C14" s="13" t="n">
         <v>-5924610.1364</v>
@@ -9565,7 +10214,7 @@
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>671299.5111999999</v>
+        <v>619242.5996</v>
       </c>
       <c r="C16" s="13" t="n">
         <v>8600702.8167</v>
@@ -9584,7 +10233,7 @@
         </is>
       </c>
       <c r="B17" s="17" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="C17" s="17" t="n">
         <v>50</v>
@@ -9603,7 +10252,7 @@
         </is>
       </c>
       <c r="B18" s="13" t="n">
-        <v>158587.5803</v>
+        <v>130757.4004</v>
       </c>
       <c r="C18" s="13" t="n">
         <v>1207273.1908</v>
@@ -9622,7 +10271,7 @@
         </is>
       </c>
       <c r="B19" s="13" t="n">
-        <v>2701395.4743</v>
+        <v>5878702.5544</v>
       </c>
       <c r="C19" s="13" t="n">
         <v>7640597.8524</v>

--- a/finance/outputs/mulligan-mints-5yr-model.xlsx
+++ b/finance/outputs/mulligan-mints-5yr-model.xlsx
@@ -6740,7 +6740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI18"/>
+  <dimension ref="A1:BI20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -8619,942 +8619,942 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Investor revenue share (R2/tin)</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI12" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>Funding received</t>
         </is>
       </c>
-      <c r="B12" s="13" t="n">
+      <c r="B13" s="13" t="n">
         <v>3500000</v>
       </c>
-      <c r="C12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" s="13" t="n">
+      <c r="C13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" s="13" t="n">
         <v>12000000</v>
       </c>
-      <c r="V12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI12" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>NET CASHFLOW</t>
-        </is>
-      </c>
-      <c r="B13" s="14" t="n">
-        <v>3437000</v>
-      </c>
-      <c r="C13" s="14" t="n">
-        <v>-47720</v>
-      </c>
-      <c r="D13" s="14" t="n">
-        <v>-117352</v>
-      </c>
-      <c r="E13" s="14" t="n">
-        <v>-169918</v>
-      </c>
-      <c r="F13" s="14" t="n">
-        <v>-274750</v>
-      </c>
-      <c r="G13" s="14" t="n">
-        <v>-134010</v>
-      </c>
-      <c r="H13" s="14" t="n">
-        <v>-378489</v>
-      </c>
-      <c r="I13" s="14" t="n">
-        <v>-171117</v>
-      </c>
-      <c r="J13" s="14" t="n">
-        <v>-167217</v>
-      </c>
-      <c r="K13" s="14" t="n">
-        <v>-226573</v>
-      </c>
-      <c r="L13" s="14" t="n">
-        <v>-139339</v>
-      </c>
-      <c r="M13" s="14" t="n">
-        <v>-150438</v>
-      </c>
-      <c r="N13" s="14" t="n">
-        <v>-125789</v>
-      </c>
-      <c r="O13" s="14" t="n">
-        <v>-79438</v>
-      </c>
-      <c r="P13" s="14" t="n">
-        <v>-130854</v>
-      </c>
-      <c r="Q13" s="14" t="n">
-        <v>-95380</v>
-      </c>
-      <c r="R13" s="14" t="n">
-        <v>-90735</v>
-      </c>
-      <c r="S13" s="14" t="n">
-        <v>-105289</v>
-      </c>
-      <c r="T13" s="14" t="n">
-        <v>-258990</v>
-      </c>
-      <c r="U13" s="14" t="n">
-        <v>11862173</v>
-      </c>
-      <c r="V13" s="14" t="n">
-        <v>-22778</v>
-      </c>
-      <c r="W13" s="14" t="n">
-        <v>-193698</v>
-      </c>
-      <c r="X13" s="14" t="n">
-        <v>45676</v>
-      </c>
-      <c r="Y13" s="14" t="n">
-        <v>-222859</v>
-      </c>
-      <c r="Z13" s="14" t="n">
-        <v>-17836</v>
-      </c>
-      <c r="AA13" s="14" t="n">
-        <v>-652824</v>
-      </c>
-      <c r="AB13" s="14" t="n">
-        <v>-48315</v>
-      </c>
-      <c r="AC13" s="14" t="n">
-        <v>-167915</v>
-      </c>
-      <c r="AD13" s="14" t="n">
-        <v>-86722</v>
-      </c>
-      <c r="AE13" s="14" t="n">
-        <v>-165737</v>
-      </c>
-      <c r="AF13" s="14" t="n">
-        <v>-240963</v>
-      </c>
-      <c r="AG13" s="14" t="n">
-        <v>-322317</v>
-      </c>
-      <c r="AH13" s="14" t="n">
-        <v>-413280</v>
-      </c>
-      <c r="AI13" s="14" t="n">
-        <v>56881</v>
-      </c>
-      <c r="AJ13" s="14" t="n">
-        <v>100035</v>
-      </c>
-      <c r="AK13" s="14" t="n">
-        <v>62687</v>
-      </c>
-      <c r="AL13" s="14" t="n">
-        <v>105441</v>
-      </c>
-      <c r="AM13" s="14" t="n">
-        <v>-195479</v>
-      </c>
-      <c r="AN13" s="14" t="n">
-        <v>610756</v>
-      </c>
-      <c r="AO13" s="14" t="n">
-        <v>284837</v>
-      </c>
-      <c r="AP13" s="14" t="n">
-        <v>544094</v>
-      </c>
-      <c r="AQ13" s="14" t="n">
-        <v>78169</v>
-      </c>
-      <c r="AR13" s="14" t="n">
-        <v>475129</v>
-      </c>
-      <c r="AS13" s="14" t="n">
-        <v>247325</v>
-      </c>
-      <c r="AT13" s="14" t="n">
-        <v>395706</v>
-      </c>
-      <c r="AU13" s="14" t="n">
-        <v>353110</v>
-      </c>
-      <c r="AV13" s="14" t="n">
-        <v>388645</v>
-      </c>
-      <c r="AW13" s="14" t="n">
-        <v>-435033</v>
-      </c>
-      <c r="AX13" s="14" t="n">
-        <v>324692</v>
-      </c>
-      <c r="AY13" s="14" t="n">
-        <v>325553</v>
-      </c>
-      <c r="AZ13" s="14" t="n">
-        <v>1287920</v>
-      </c>
-      <c r="BA13" s="14" t="n">
-        <v>1010934</v>
-      </c>
-      <c r="BB13" s="14" t="n">
-        <v>1236870</v>
-      </c>
-      <c r="BC13" s="14" t="n">
-        <v>-605550</v>
-      </c>
-      <c r="BD13" s="14" t="n">
-        <v>1271461</v>
-      </c>
-      <c r="BE13" s="14" t="n">
-        <v>1126361</v>
-      </c>
-      <c r="BF13" s="14" t="n">
-        <v>1346047</v>
-      </c>
-      <c r="BG13" s="14" t="n">
-        <v>1181136</v>
-      </c>
-      <c r="BH13" s="14" t="n">
-        <v>1420633</v>
-      </c>
-      <c r="BI13" s="14" t="n">
-        <v>-515212</v>
+      <c r="V13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI13" s="13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>CLOSING CASH</t>
+          <t>NET CASHFLOW</t>
         </is>
       </c>
       <c r="B14" s="14" t="n">
         <v>3437000</v>
       </c>
       <c r="C14" s="14" t="n">
+        <v>-47720</v>
+      </c>
+      <c r="D14" s="14" t="n">
+        <v>-117352</v>
+      </c>
+      <c r="E14" s="14" t="n">
+        <v>-169918</v>
+      </c>
+      <c r="F14" s="14" t="n">
+        <v>-274750</v>
+      </c>
+      <c r="G14" s="14" t="n">
+        <v>-134010</v>
+      </c>
+      <c r="H14" s="14" t="n">
+        <v>-378489</v>
+      </c>
+      <c r="I14" s="14" t="n">
+        <v>-171117</v>
+      </c>
+      <c r="J14" s="14" t="n">
+        <v>-167217</v>
+      </c>
+      <c r="K14" s="14" t="n">
+        <v>-226573</v>
+      </c>
+      <c r="L14" s="14" t="n">
+        <v>-139339</v>
+      </c>
+      <c r="M14" s="14" t="n">
+        <v>-150438</v>
+      </c>
+      <c r="N14" s="14" t="n">
+        <v>-125789</v>
+      </c>
+      <c r="O14" s="14" t="n">
+        <v>-79438</v>
+      </c>
+      <c r="P14" s="14" t="n">
+        <v>-130854</v>
+      </c>
+      <c r="Q14" s="14" t="n">
+        <v>-95380</v>
+      </c>
+      <c r="R14" s="14" t="n">
+        <v>-90735</v>
+      </c>
+      <c r="S14" s="14" t="n">
+        <v>-105289</v>
+      </c>
+      <c r="T14" s="14" t="n">
+        <v>-258990</v>
+      </c>
+      <c r="U14" s="14" t="n">
+        <v>11862173</v>
+      </c>
+      <c r="V14" s="14" t="n">
+        <v>-22778</v>
+      </c>
+      <c r="W14" s="14" t="n">
+        <v>-193698</v>
+      </c>
+      <c r="X14" s="14" t="n">
+        <v>45676</v>
+      </c>
+      <c r="Y14" s="14" t="n">
+        <v>-222859</v>
+      </c>
+      <c r="Z14" s="14" t="n">
+        <v>-17836</v>
+      </c>
+      <c r="AA14" s="14" t="n">
+        <v>-652824</v>
+      </c>
+      <c r="AB14" s="14" t="n">
+        <v>-48315</v>
+      </c>
+      <c r="AC14" s="14" t="n">
+        <v>-167915</v>
+      </c>
+      <c r="AD14" s="14" t="n">
+        <v>-86722</v>
+      </c>
+      <c r="AE14" s="14" t="n">
+        <v>-165737</v>
+      </c>
+      <c r="AF14" s="14" t="n">
+        <v>-240963</v>
+      </c>
+      <c r="AG14" s="14" t="n">
+        <v>-322317</v>
+      </c>
+      <c r="AH14" s="14" t="n">
+        <v>-413280</v>
+      </c>
+      <c r="AI14" s="14" t="n">
+        <v>56881</v>
+      </c>
+      <c r="AJ14" s="14" t="n">
+        <v>100035</v>
+      </c>
+      <c r="AK14" s="14" t="n">
+        <v>62687</v>
+      </c>
+      <c r="AL14" s="14" t="n">
+        <v>105441</v>
+      </c>
+      <c r="AM14" s="14" t="n">
+        <v>-195479</v>
+      </c>
+      <c r="AN14" s="14" t="n">
+        <v>610756</v>
+      </c>
+      <c r="AO14" s="14" t="n">
+        <v>284837</v>
+      </c>
+      <c r="AP14" s="14" t="n">
+        <v>544094</v>
+      </c>
+      <c r="AQ14" s="14" t="n">
+        <v>78169</v>
+      </c>
+      <c r="AR14" s="14" t="n">
+        <v>475129</v>
+      </c>
+      <c r="AS14" s="14" t="n">
+        <v>247325</v>
+      </c>
+      <c r="AT14" s="14" t="n">
+        <v>395706</v>
+      </c>
+      <c r="AU14" s="14" t="n">
+        <v>353110</v>
+      </c>
+      <c r="AV14" s="14" t="n">
+        <v>388645</v>
+      </c>
+      <c r="AW14" s="14" t="n">
+        <v>-435033</v>
+      </c>
+      <c r="AX14" s="14" t="n">
+        <v>324692</v>
+      </c>
+      <c r="AY14" s="14" t="n">
+        <v>325553</v>
+      </c>
+      <c r="AZ14" s="14" t="n">
+        <v>1287920</v>
+      </c>
+      <c r="BA14" s="14" t="n">
+        <v>1010934</v>
+      </c>
+      <c r="BB14" s="14" t="n">
+        <v>1236870</v>
+      </c>
+      <c r="BC14" s="14" t="n">
+        <v>-605550</v>
+      </c>
+      <c r="BD14" s="14" t="n">
+        <v>1271461</v>
+      </c>
+      <c r="BE14" s="14" t="n">
+        <v>1126361</v>
+      </c>
+      <c r="BF14" s="14" t="n">
+        <v>1346047</v>
+      </c>
+      <c r="BG14" s="14" t="n">
+        <v>1181136</v>
+      </c>
+      <c r="BH14" s="14" t="n">
+        <v>1420633</v>
+      </c>
+      <c r="BI14" s="14" t="n">
+        <v>-515212</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>CLOSING CASH</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="n">
+        <v>3437000</v>
+      </c>
+      <c r="C15" s="14" t="n">
         <v>3389280</v>
       </c>
-      <c r="D14" s="14" t="n">
+      <c r="D15" s="14" t="n">
         <v>3271928</v>
       </c>
-      <c r="E14" s="14" t="n">
+      <c r="E15" s="14" t="n">
         <v>3102011</v>
       </c>
-      <c r="F14" s="14" t="n">
+      <c r="F15" s="14" t="n">
         <v>2827260</v>
       </c>
-      <c r="G14" s="14" t="n">
+      <c r="G15" s="14" t="n">
         <v>2693250</v>
       </c>
-      <c r="H14" s="14" t="n">
+      <c r="H15" s="14" t="n">
         <v>2314761</v>
       </c>
-      <c r="I14" s="14" t="n">
+      <c r="I15" s="14" t="n">
         <v>2143644</v>
       </c>
-      <c r="J14" s="14" t="n">
+      <c r="J15" s="14" t="n">
         <v>1976427</v>
       </c>
-      <c r="K14" s="14" t="n">
+      <c r="K15" s="14" t="n">
         <v>1749854</v>
       </c>
-      <c r="L14" s="14" t="n">
+      <c r="L15" s="14" t="n">
         <v>1610515</v>
       </c>
-      <c r="M14" s="14" t="n">
+      <c r="M15" s="14" t="n">
         <v>1460077</v>
       </c>
-      <c r="N14" s="14" t="n">
+      <c r="N15" s="14" t="n">
         <v>1334288</v>
       </c>
-      <c r="O14" s="14" t="n">
+      <c r="O15" s="14" t="n">
         <v>1254850</v>
       </c>
-      <c r="P14" s="14" t="n">
+      <c r="P15" s="14" t="n">
         <v>1123995</v>
       </c>
-      <c r="Q14" s="14" t="n">
+      <c r="Q15" s="14" t="n">
         <v>1028616</v>
       </c>
-      <c r="R14" s="14" t="n">
+      <c r="R15" s="14" t="n">
         <v>937881</v>
       </c>
-      <c r="S14" s="14" t="n">
+      <c r="S15" s="14" t="n">
         <v>832592</v>
       </c>
-      <c r="T14" s="14" t="n">
+      <c r="T15" s="14" t="n">
         <v>573601</v>
       </c>
-      <c r="U14" s="14" t="n">
+      <c r="U15" s="14" t="n">
         <v>12435774</v>
       </c>
-      <c r="V14" s="14" t="n">
+      <c r="V15" s="14" t="n">
         <v>12412996</v>
       </c>
-      <c r="W14" s="14" t="n">
+      <c r="W15" s="14" t="n">
         <v>12219298</v>
       </c>
-      <c r="X14" s="14" t="n">
+      <c r="X15" s="14" t="n">
         <v>12264974</v>
       </c>
-      <c r="Y14" s="14" t="n">
+      <c r="Y15" s="14" t="n">
         <v>12042115</v>
       </c>
-      <c r="Z14" s="14" t="n">
+      <c r="Z15" s="14" t="n">
         <v>12024279</v>
       </c>
-      <c r="AA14" s="14" t="n">
+      <c r="AA15" s="14" t="n">
         <v>11371455</v>
       </c>
-      <c r="AB14" s="14" t="n">
+      <c r="AB15" s="14" t="n">
         <v>11323141</v>
       </c>
-      <c r="AC14" s="14" t="n">
+      <c r="AC15" s="14" t="n">
         <v>11155226</v>
       </c>
-      <c r="AD14" s="14" t="n">
+      <c r="AD15" s="14" t="n">
         <v>11068504</v>
       </c>
-      <c r="AE14" s="14" t="n">
+      <c r="AE15" s="14" t="n">
         <v>10902767</v>
       </c>
-      <c r="AF14" s="14" t="n">
+      <c r="AF15" s="14" t="n">
         <v>10661804</v>
       </c>
-      <c r="AG14" s="14" t="n">
+      <c r="AG15" s="14" t="n">
         <v>10339487</v>
       </c>
-      <c r="AH14" s="14" t="n">
+      <c r="AH15" s="14" t="n">
         <v>9926207</v>
       </c>
-      <c r="AI14" s="14" t="n">
+      <c r="AI15" s="14" t="n">
         <v>9983087</v>
       </c>
-      <c r="AJ14" s="14" t="n">
+      <c r="AJ15" s="14" t="n">
         <v>10083122</v>
       </c>
-      <c r="AK14" s="14" t="n">
+      <c r="AK15" s="14" t="n">
         <v>10145809</v>
       </c>
-      <c r="AL14" s="14" t="n">
+      <c r="AL15" s="14" t="n">
         <v>10251250</v>
       </c>
-      <c r="AM14" s="14" t="n">
+      <c r="AM15" s="14" t="n">
         <v>10055771</v>
       </c>
-      <c r="AN14" s="14" t="n">
+      <c r="AN15" s="14" t="n">
         <v>10666527</v>
       </c>
-      <c r="AO14" s="14" t="n">
+      <c r="AO15" s="14" t="n">
         <v>10951364</v>
       </c>
-      <c r="AP14" s="14" t="n">
+      <c r="AP15" s="14" t="n">
         <v>11495458</v>
       </c>
-      <c r="AQ14" s="14" t="n">
+      <c r="AQ15" s="14" t="n">
         <v>11573627</v>
       </c>
-      <c r="AR14" s="14" t="n">
+      <c r="AR15" s="14" t="n">
         <v>12048756</v>
       </c>
-      <c r="AS14" s="14" t="n">
+      <c r="AS15" s="14" t="n">
         <v>12296081</v>
       </c>
-      <c r="AT14" s="14" t="n">
+      <c r="AT15" s="14" t="n">
         <v>12691787</v>
       </c>
-      <c r="AU14" s="14" t="n">
+      <c r="AU15" s="14" t="n">
         <v>13044897</v>
       </c>
-      <c r="AV14" s="14" t="n">
+      <c r="AV15" s="14" t="n">
         <v>13433542</v>
       </c>
-      <c r="AW14" s="14" t="n">
+      <c r="AW15" s="14" t="n">
         <v>12998508</v>
       </c>
-      <c r="AX14" s="14" t="n">
+      <c r="AX15" s="14" t="n">
         <v>13323200</v>
       </c>
-      <c r="AY14" s="14" t="n">
+      <c r="AY15" s="14" t="n">
         <v>13648753</v>
       </c>
-      <c r="AZ14" s="14" t="n">
+      <c r="AZ15" s="14" t="n">
         <v>14936673</v>
       </c>
-      <c r="BA14" s="14" t="n">
+      <c r="BA15" s="14" t="n">
         <v>15947607</v>
       </c>
-      <c r="BB14" s="14" t="n">
+      <c r="BB15" s="14" t="n">
         <v>17184477</v>
       </c>
-      <c r="BC14" s="14" t="n">
+      <c r="BC15" s="14" t="n">
         <v>16578927</v>
       </c>
-      <c r="BD14" s="14" t="n">
+      <c r="BD15" s="14" t="n">
         <v>17850388</v>
       </c>
-      <c r="BE14" s="14" t="n">
+      <c r="BE15" s="14" t="n">
         <v>18976749</v>
       </c>
-      <c r="BF14" s="14" t="n">
+      <c r="BF15" s="14" t="n">
         <v>20322796</v>
       </c>
-      <c r="BG14" s="14" t="n">
+      <c r="BG15" s="14" t="n">
         <v>21503932</v>
       </c>
-      <c r="BH14" s="14" t="n">
+      <c r="BH15" s="14" t="n">
         <v>22924565</v>
       </c>
-      <c r="BI14" s="14" t="n">
+      <c r="BI15" s="14" t="n">
         <v>22409352</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Stock on hand (units)</t>
-        </is>
-      </c>
-      <c r="B15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="12" t="n">
-        <v>21032</v>
-      </c>
-      <c r="I15" s="12" t="n">
-        <v>18525</v>
-      </c>
-      <c r="J15" s="12" t="n">
-        <v>37450</v>
-      </c>
-      <c r="K15" s="12" t="n">
-        <v>32837</v>
-      </c>
-      <c r="L15" s="12" t="n">
-        <v>27170</v>
-      </c>
-      <c r="M15" s="12" t="n">
-        <v>42935</v>
-      </c>
-      <c r="N15" s="12" t="n">
-        <v>33559</v>
-      </c>
-      <c r="O15" s="12" t="n">
-        <v>45750</v>
-      </c>
-      <c r="P15" s="12" t="n">
-        <v>57026</v>
-      </c>
-      <c r="Q15" s="12" t="n">
-        <v>44899</v>
-      </c>
-      <c r="R15" s="12" t="n">
-        <v>54341</v>
-      </c>
-      <c r="S15" s="12" t="n">
-        <v>62866</v>
-      </c>
-      <c r="T15" s="12" t="n">
-        <v>69994</v>
-      </c>
-      <c r="U15" s="12" t="n">
-        <v>75726</v>
-      </c>
-      <c r="V15" s="12" t="n">
-        <v>80061</v>
-      </c>
-      <c r="W15" s="12" t="n">
-        <v>83000</v>
-      </c>
-      <c r="X15" s="12" t="n">
-        <v>84541</v>
-      </c>
-      <c r="Y15" s="12" t="n">
-        <v>107172</v>
-      </c>
-      <c r="Z15" s="12" t="n">
-        <v>101387</v>
-      </c>
-      <c r="AA15" s="12" t="n">
-        <v>116187</v>
-      </c>
-      <c r="AB15" s="12" t="n">
-        <v>106602</v>
-      </c>
-      <c r="AC15" s="12" t="n">
-        <v>140088</v>
-      </c>
-      <c r="AD15" s="12" t="n">
-        <v>149188</v>
-      </c>
-      <c r="AE15" s="12" t="n">
-        <v>178873</v>
-      </c>
-      <c r="AF15" s="12" t="n">
-        <v>191658</v>
-      </c>
-      <c r="AG15" s="12" t="n">
-        <v>180059</v>
-      </c>
-      <c r="AH15" s="12" t="n">
-        <v>189044</v>
-      </c>
-      <c r="AI15" s="12" t="n">
-        <v>218615</v>
-      </c>
-      <c r="AJ15" s="12" t="n">
-        <v>246285</v>
-      </c>
-      <c r="AK15" s="12" t="n">
-        <v>272056</v>
-      </c>
-      <c r="AL15" s="12" t="n">
-        <v>277558</v>
-      </c>
-      <c r="AM15" s="12" t="n">
-        <v>281191</v>
-      </c>
-      <c r="AN15" s="12" t="n">
-        <v>282952</v>
-      </c>
-      <c r="AO15" s="12" t="n">
-        <v>282842</v>
-      </c>
-      <c r="AP15" s="12" t="n">
-        <v>280862</v>
-      </c>
-      <c r="AQ15" s="12" t="n">
-        <v>299496</v>
-      </c>
-      <c r="AR15" s="12" t="n">
-        <v>293774</v>
-      </c>
-      <c r="AS15" s="12" t="n">
-        <v>308666</v>
-      </c>
-      <c r="AT15" s="12" t="n">
-        <v>321688</v>
-      </c>
-      <c r="AU15" s="12" t="n">
-        <v>355323</v>
-      </c>
-      <c r="AV15" s="12" t="n">
-        <v>387088</v>
-      </c>
-      <c r="AW15" s="12" t="n">
-        <v>416982</v>
-      </c>
-      <c r="AX15" s="12" t="n">
-        <v>433814</v>
-      </c>
-      <c r="AY15" s="12" t="n">
-        <v>426587</v>
-      </c>
-      <c r="AZ15" s="12" t="n">
-        <v>440272</v>
-      </c>
-      <c r="BA15" s="12" t="n">
-        <v>452385</v>
-      </c>
-      <c r="BB15" s="12" t="n">
-        <v>440439</v>
-      </c>
-      <c r="BC15" s="12" t="n">
-        <v>449406</v>
-      </c>
-      <c r="BD15" s="12" t="n">
-        <v>456800</v>
-      </c>
-      <c r="BE15" s="12" t="n">
-        <v>462621</v>
-      </c>
-      <c r="BF15" s="12" t="n">
-        <v>466868</v>
-      </c>
-      <c r="BG15" s="12" t="n">
-        <v>469543</v>
-      </c>
-      <c r="BH15" s="12" t="n">
-        <v>470646</v>
-      </c>
-      <c r="BI15" s="12" t="n">
-        <v>470175</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Stock on hand (value)</t>
-        </is>
-      </c>
-      <c r="B16" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="13" t="n">
-        <v>216424</v>
-      </c>
-      <c r="I16" s="13" t="n">
-        <v>190630</v>
-      </c>
-      <c r="J16" s="13" t="n">
-        <v>385375</v>
-      </c>
-      <c r="K16" s="13" t="n">
-        <v>337903</v>
-      </c>
-      <c r="L16" s="13" t="n">
-        <v>279591</v>
-      </c>
-      <c r="M16" s="13" t="n">
-        <v>441819</v>
-      </c>
-      <c r="N16" s="13" t="n">
-        <v>345330</v>
-      </c>
-      <c r="O16" s="13" t="n">
-        <v>450854</v>
-      </c>
-      <c r="P16" s="13" t="n">
-        <v>549747</v>
-      </c>
-      <c r="Q16" s="13" t="n">
-        <v>432842</v>
-      </c>
-      <c r="R16" s="13" t="n">
-        <v>522426</v>
-      </c>
-      <c r="S16" s="13" t="n">
-        <v>603414</v>
-      </c>
-      <c r="T16" s="13" t="n">
-        <v>671147</v>
-      </c>
-      <c r="U16" s="13" t="n">
-        <v>725600</v>
-      </c>
-      <c r="V16" s="13" t="n">
-        <v>766756</v>
-      </c>
-      <c r="W16" s="13" t="n">
-        <v>794606</v>
-      </c>
-      <c r="X16" s="13" t="n">
-        <v>809140</v>
-      </c>
-      <c r="Y16" s="13" t="n">
-        <v>1025366</v>
-      </c>
-      <c r="Z16" s="13" t="n">
-        <v>956043</v>
-      </c>
-      <c r="AA16" s="13" t="n">
-        <v>1072147</v>
-      </c>
-      <c r="AB16" s="13" t="n">
-        <v>975833</v>
-      </c>
-      <c r="AC16" s="13" t="n">
-        <v>1250652</v>
-      </c>
-      <c r="AD16" s="13" t="n">
-        <v>1338581</v>
-      </c>
-      <c r="AE16" s="13" t="n">
-        <v>1601134</v>
-      </c>
-      <c r="AF16" s="13" t="n">
-        <v>1713114</v>
-      </c>
-      <c r="AG16" s="13" t="n">
-        <v>1615374</v>
-      </c>
-      <c r="AH16" s="13" t="n">
-        <v>1692528</v>
-      </c>
-      <c r="AI16" s="13" t="n">
-        <v>1953835</v>
-      </c>
-      <c r="AJ16" s="13" t="n">
-        <v>2198762</v>
-      </c>
-      <c r="AK16" s="13" t="n">
-        <v>2427128</v>
-      </c>
-      <c r="AL16" s="13" t="n">
-        <v>2435302</v>
-      </c>
-      <c r="AM16" s="13" t="n">
-        <v>2436482</v>
-      </c>
-      <c r="AN16" s="13" t="n">
-        <v>2428649</v>
-      </c>
-      <c r="AO16" s="13" t="n">
-        <v>2410300</v>
-      </c>
-      <c r="AP16" s="13" t="n">
-        <v>2402300</v>
-      </c>
-      <c r="AQ16" s="13" t="n">
-        <v>2570190</v>
-      </c>
-      <c r="AR16" s="13" t="n">
-        <v>2525901</v>
-      </c>
-      <c r="AS16" s="13" t="n">
-        <v>2658609</v>
-      </c>
-      <c r="AT16" s="13" t="n">
-        <v>2774156</v>
-      </c>
-      <c r="AU16" s="13" t="n">
-        <v>3067260</v>
-      </c>
-      <c r="AV16" s="13" t="n">
-        <v>3343636</v>
-      </c>
-      <c r="AW16" s="13" t="n">
-        <v>3603450</v>
-      </c>
-      <c r="AX16" s="13" t="n">
-        <v>3692666</v>
-      </c>
-      <c r="AY16" s="13" t="n">
-        <v>3596398</v>
-      </c>
-      <c r="AZ16" s="13" t="n">
-        <v>3680690</v>
-      </c>
-      <c r="BA16" s="13" t="n">
-        <v>3759154</v>
-      </c>
-      <c r="BB16" s="13" t="n">
-        <v>3677828</v>
-      </c>
-      <c r="BC16" s="13" t="n">
-        <v>3768860</v>
-      </c>
-      <c r="BD16" s="13" t="n">
-        <v>3842787</v>
-      </c>
-      <c r="BE16" s="13" t="n">
-        <v>3900587</v>
-      </c>
-      <c r="BF16" s="13" t="n">
-        <v>3942971</v>
-      </c>
-      <c r="BG16" s="13" t="n">
-        <v>3970458</v>
-      </c>
-      <c r="BH16" s="13" t="n">
-        <v>3983431</v>
-      </c>
-      <c r="BI16" s="13" t="n">
-        <v>3982175</v>
+          <t>Stock on hand (units)</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="12" t="n">
+        <v>21032</v>
+      </c>
+      <c r="I16" s="12" t="n">
+        <v>18525</v>
+      </c>
+      <c r="J16" s="12" t="n">
+        <v>37450</v>
+      </c>
+      <c r="K16" s="12" t="n">
+        <v>32837</v>
+      </c>
+      <c r="L16" s="12" t="n">
+        <v>27170</v>
+      </c>
+      <c r="M16" s="12" t="n">
+        <v>42935</v>
+      </c>
+      <c r="N16" s="12" t="n">
+        <v>33559</v>
+      </c>
+      <c r="O16" s="12" t="n">
+        <v>45750</v>
+      </c>
+      <c r="P16" s="12" t="n">
+        <v>57026</v>
+      </c>
+      <c r="Q16" s="12" t="n">
+        <v>44899</v>
+      </c>
+      <c r="R16" s="12" t="n">
+        <v>54341</v>
+      </c>
+      <c r="S16" s="12" t="n">
+        <v>62866</v>
+      </c>
+      <c r="T16" s="12" t="n">
+        <v>69994</v>
+      </c>
+      <c r="U16" s="12" t="n">
+        <v>75726</v>
+      </c>
+      <c r="V16" s="12" t="n">
+        <v>80061</v>
+      </c>
+      <c r="W16" s="12" t="n">
+        <v>83000</v>
+      </c>
+      <c r="X16" s="12" t="n">
+        <v>84541</v>
+      </c>
+      <c r="Y16" s="12" t="n">
+        <v>107172</v>
+      </c>
+      <c r="Z16" s="12" t="n">
+        <v>101387</v>
+      </c>
+      <c r="AA16" s="12" t="n">
+        <v>116187</v>
+      </c>
+      <c r="AB16" s="12" t="n">
+        <v>106602</v>
+      </c>
+      <c r="AC16" s="12" t="n">
+        <v>140088</v>
+      </c>
+      <c r="AD16" s="12" t="n">
+        <v>149188</v>
+      </c>
+      <c r="AE16" s="12" t="n">
+        <v>178873</v>
+      </c>
+      <c r="AF16" s="12" t="n">
+        <v>191658</v>
+      </c>
+      <c r="AG16" s="12" t="n">
+        <v>180059</v>
+      </c>
+      <c r="AH16" s="12" t="n">
+        <v>189044</v>
+      </c>
+      <c r="AI16" s="12" t="n">
+        <v>218615</v>
+      </c>
+      <c r="AJ16" s="12" t="n">
+        <v>246285</v>
+      </c>
+      <c r="AK16" s="12" t="n">
+        <v>272056</v>
+      </c>
+      <c r="AL16" s="12" t="n">
+        <v>277558</v>
+      </c>
+      <c r="AM16" s="12" t="n">
+        <v>281191</v>
+      </c>
+      <c r="AN16" s="12" t="n">
+        <v>282952</v>
+      </c>
+      <c r="AO16" s="12" t="n">
+        <v>282842</v>
+      </c>
+      <c r="AP16" s="12" t="n">
+        <v>280862</v>
+      </c>
+      <c r="AQ16" s="12" t="n">
+        <v>299496</v>
+      </c>
+      <c r="AR16" s="12" t="n">
+        <v>293774</v>
+      </c>
+      <c r="AS16" s="12" t="n">
+        <v>308666</v>
+      </c>
+      <c r="AT16" s="12" t="n">
+        <v>321688</v>
+      </c>
+      <c r="AU16" s="12" t="n">
+        <v>355323</v>
+      </c>
+      <c r="AV16" s="12" t="n">
+        <v>387088</v>
+      </c>
+      <c r="AW16" s="12" t="n">
+        <v>416982</v>
+      </c>
+      <c r="AX16" s="12" t="n">
+        <v>433814</v>
+      </c>
+      <c r="AY16" s="12" t="n">
+        <v>426587</v>
+      </c>
+      <c r="AZ16" s="12" t="n">
+        <v>440272</v>
+      </c>
+      <c r="BA16" s="12" t="n">
+        <v>452385</v>
+      </c>
+      <c r="BB16" s="12" t="n">
+        <v>440439</v>
+      </c>
+      <c r="BC16" s="12" t="n">
+        <v>449406</v>
+      </c>
+      <c r="BD16" s="12" t="n">
+        <v>456800</v>
+      </c>
+      <c r="BE16" s="12" t="n">
+        <v>462621</v>
+      </c>
+      <c r="BF16" s="12" t="n">
+        <v>466868</v>
+      </c>
+      <c r="BG16" s="12" t="n">
+        <v>469543</v>
+      </c>
+      <c r="BH16" s="12" t="n">
+        <v>470646</v>
+      </c>
+      <c r="BI16" s="12" t="n">
+        <v>470175</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Debtors</t>
+          <t>Stock on hand (value)</t>
         </is>
       </c>
       <c r="B17" s="13" t="n">
@@ -9576,352 +9576,726 @@
         <v>0</v>
       </c>
       <c r="H17" s="13" t="n">
-        <v>29375</v>
+        <v>216424</v>
       </c>
       <c r="I17" s="13" t="n">
-        <v>58750</v>
+        <v>190630</v>
       </c>
       <c r="J17" s="13" t="n">
-        <v>88124</v>
+        <v>385375</v>
       </c>
       <c r="K17" s="13" t="n">
-        <v>117499</v>
+        <v>337903</v>
       </c>
       <c r="L17" s="13" t="n">
-        <v>146874</v>
+        <v>279591</v>
       </c>
       <c r="M17" s="13" t="n">
-        <v>176249</v>
+        <v>441819</v>
       </c>
       <c r="N17" s="13" t="n">
-        <v>235298</v>
+        <v>345330</v>
       </c>
       <c r="O17" s="13" t="n">
-        <v>261496</v>
+        <v>450854</v>
       </c>
       <c r="P17" s="13" t="n">
-        <v>287695</v>
+        <v>549747</v>
       </c>
       <c r="Q17" s="13" t="n">
-        <v>313893</v>
+        <v>432842</v>
       </c>
       <c r="R17" s="13" t="n">
-        <v>340091</v>
+        <v>522426</v>
       </c>
       <c r="S17" s="13" t="n">
-        <v>366290</v>
+        <v>603414</v>
       </c>
       <c r="T17" s="13" t="n">
-        <v>404660</v>
+        <v>671147</v>
       </c>
       <c r="U17" s="13" t="n">
-        <v>455201</v>
+        <v>725600</v>
       </c>
       <c r="V17" s="13" t="n">
-        <v>505743</v>
+        <v>766756</v>
       </c>
       <c r="W17" s="13" t="n">
-        <v>556284</v>
+        <v>794606</v>
       </c>
       <c r="X17" s="13" t="n">
-        <v>606826</v>
+        <v>809140</v>
       </c>
       <c r="Y17" s="13" t="n">
-        <v>657368</v>
+        <v>1025366</v>
       </c>
       <c r="Z17" s="13" t="n">
-        <v>814707</v>
+        <v>956043</v>
       </c>
       <c r="AA17" s="13" t="n">
-        <v>899728</v>
+        <v>1072147</v>
       </c>
       <c r="AB17" s="13" t="n">
-        <v>971512</v>
+        <v>975833</v>
       </c>
       <c r="AC17" s="13" t="n">
-        <v>1043296</v>
+        <v>1250652</v>
       </c>
       <c r="AD17" s="13" t="n">
-        <v>1115080</v>
+        <v>1338581</v>
       </c>
       <c r="AE17" s="13" t="n">
-        <v>1186865</v>
+        <v>1601134</v>
       </c>
       <c r="AF17" s="13" t="n">
-        <v>1514980</v>
+        <v>1713114</v>
       </c>
       <c r="AG17" s="13" t="n">
-        <v>1843095</v>
+        <v>1615374</v>
       </c>
       <c r="AH17" s="13" t="n">
-        <v>1914879</v>
+        <v>1692528</v>
       </c>
       <c r="AI17" s="13" t="n">
-        <v>1986663</v>
+        <v>1953835</v>
       </c>
       <c r="AJ17" s="13" t="n">
-        <v>2058448</v>
+        <v>2198762</v>
       </c>
       <c r="AK17" s="13" t="n">
-        <v>2130232</v>
+        <v>2427128</v>
       </c>
       <c r="AL17" s="13" t="n">
-        <v>2638969</v>
+        <v>2435302</v>
       </c>
       <c r="AM17" s="13" t="n">
-        <v>3024009</v>
+        <v>2436482</v>
       </c>
       <c r="AN17" s="13" t="n">
-        <v>3099646</v>
+        <v>2428649</v>
       </c>
       <c r="AO17" s="13" t="n">
-        <v>3175283</v>
+        <v>2410300</v>
       </c>
       <c r="AP17" s="13" t="n">
-        <v>3250920</v>
+        <v>2402300</v>
       </c>
       <c r="AQ17" s="13" t="n">
-        <v>3326557</v>
+        <v>2570190</v>
       </c>
       <c r="AR17" s="13" t="n">
-        <v>3402194</v>
+        <v>2525901</v>
       </c>
       <c r="AS17" s="13" t="n">
-        <v>3477831</v>
+        <v>2658609</v>
       </c>
       <c r="AT17" s="13" t="n">
-        <v>3553467</v>
+        <v>2774156</v>
       </c>
       <c r="AU17" s="13" t="n">
-        <v>3629104</v>
+        <v>3067260</v>
       </c>
       <c r="AV17" s="13" t="n">
-        <v>3704741</v>
+        <v>3343636</v>
       </c>
       <c r="AW17" s="13" t="n">
-        <v>3780378</v>
+        <v>3603450</v>
       </c>
       <c r="AX17" s="13" t="n">
-        <v>4748621</v>
+        <v>3692666</v>
       </c>
       <c r="AY17" s="13" t="n">
-        <v>5555762</v>
+        <v>3596398</v>
       </c>
       <c r="AZ17" s="13" t="n">
-        <v>5623687</v>
+        <v>3680690</v>
       </c>
       <c r="BA17" s="13" t="n">
-        <v>5691612</v>
+        <v>3759154</v>
       </c>
       <c r="BB17" s="13" t="n">
-        <v>5759537</v>
+        <v>3677828</v>
       </c>
       <c r="BC17" s="13" t="n">
-        <v>5827463</v>
+        <v>3768860</v>
       </c>
       <c r="BD17" s="13" t="n">
-        <v>5895388</v>
+        <v>3842787</v>
       </c>
       <c r="BE17" s="13" t="n">
-        <v>5963313</v>
+        <v>3900587</v>
       </c>
       <c r="BF17" s="13" t="n">
-        <v>6031238</v>
+        <v>3942971</v>
       </c>
       <c r="BG17" s="13" t="n">
-        <v>6099163</v>
+        <v>3970458</v>
       </c>
       <c r="BH17" s="13" t="n">
-        <v>6167088</v>
+        <v>3983431</v>
       </c>
       <c r="BI17" s="13" t="n">
-        <v>6235014</v>
+        <v>3982175</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>Debtors</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="13" t="n">
+        <v>29375</v>
+      </c>
+      <c r="I18" s="13" t="n">
+        <v>58750</v>
+      </c>
+      <c r="J18" s="13" t="n">
+        <v>88124</v>
+      </c>
+      <c r="K18" s="13" t="n">
+        <v>117499</v>
+      </c>
+      <c r="L18" s="13" t="n">
+        <v>146874</v>
+      </c>
+      <c r="M18" s="13" t="n">
+        <v>176249</v>
+      </c>
+      <c r="N18" s="13" t="n">
+        <v>235298</v>
+      </c>
+      <c r="O18" s="13" t="n">
+        <v>261496</v>
+      </c>
+      <c r="P18" s="13" t="n">
+        <v>287695</v>
+      </c>
+      <c r="Q18" s="13" t="n">
+        <v>313893</v>
+      </c>
+      <c r="R18" s="13" t="n">
+        <v>340091</v>
+      </c>
+      <c r="S18" s="13" t="n">
+        <v>366290</v>
+      </c>
+      <c r="T18" s="13" t="n">
+        <v>404660</v>
+      </c>
+      <c r="U18" s="13" t="n">
+        <v>455201</v>
+      </c>
+      <c r="V18" s="13" t="n">
+        <v>505743</v>
+      </c>
+      <c r="W18" s="13" t="n">
+        <v>556284</v>
+      </c>
+      <c r="X18" s="13" t="n">
+        <v>606826</v>
+      </c>
+      <c r="Y18" s="13" t="n">
+        <v>657368</v>
+      </c>
+      <c r="Z18" s="13" t="n">
+        <v>814707</v>
+      </c>
+      <c r="AA18" s="13" t="n">
+        <v>899728</v>
+      </c>
+      <c r="AB18" s="13" t="n">
+        <v>971512</v>
+      </c>
+      <c r="AC18" s="13" t="n">
+        <v>1043296</v>
+      </c>
+      <c r="AD18" s="13" t="n">
+        <v>1115080</v>
+      </c>
+      <c r="AE18" s="13" t="n">
+        <v>1186865</v>
+      </c>
+      <c r="AF18" s="13" t="n">
+        <v>1514980</v>
+      </c>
+      <c r="AG18" s="13" t="n">
+        <v>1843095</v>
+      </c>
+      <c r="AH18" s="13" t="n">
+        <v>1914879</v>
+      </c>
+      <c r="AI18" s="13" t="n">
+        <v>1986663</v>
+      </c>
+      <c r="AJ18" s="13" t="n">
+        <v>2058448</v>
+      </c>
+      <c r="AK18" s="13" t="n">
+        <v>2130232</v>
+      </c>
+      <c r="AL18" s="13" t="n">
+        <v>2638969</v>
+      </c>
+      <c r="AM18" s="13" t="n">
+        <v>3024009</v>
+      </c>
+      <c r="AN18" s="13" t="n">
+        <v>3099646</v>
+      </c>
+      <c r="AO18" s="13" t="n">
+        <v>3175283</v>
+      </c>
+      <c r="AP18" s="13" t="n">
+        <v>3250920</v>
+      </c>
+      <c r="AQ18" s="13" t="n">
+        <v>3326557</v>
+      </c>
+      <c r="AR18" s="13" t="n">
+        <v>3402194</v>
+      </c>
+      <c r="AS18" s="13" t="n">
+        <v>3477831</v>
+      </c>
+      <c r="AT18" s="13" t="n">
+        <v>3553467</v>
+      </c>
+      <c r="AU18" s="13" t="n">
+        <v>3629104</v>
+      </c>
+      <c r="AV18" s="13" t="n">
+        <v>3704741</v>
+      </c>
+      <c r="AW18" s="13" t="n">
+        <v>3780378</v>
+      </c>
+      <c r="AX18" s="13" t="n">
+        <v>4748621</v>
+      </c>
+      <c r="AY18" s="13" t="n">
+        <v>5555762</v>
+      </c>
+      <c r="AZ18" s="13" t="n">
+        <v>5623687</v>
+      </c>
+      <c r="BA18" s="13" t="n">
+        <v>5691612</v>
+      </c>
+      <c r="BB18" s="13" t="n">
+        <v>5759537</v>
+      </c>
+      <c r="BC18" s="13" t="n">
+        <v>5827463</v>
+      </c>
+      <c r="BD18" s="13" t="n">
+        <v>5895388</v>
+      </c>
+      <c r="BE18" s="13" t="n">
+        <v>5963313</v>
+      </c>
+      <c r="BF18" s="13" t="n">
+        <v>6031238</v>
+      </c>
+      <c r="BG18" s="13" t="n">
+        <v>6099163</v>
+      </c>
+      <c r="BH18" s="13" t="n">
+        <v>6167088</v>
+      </c>
+      <c r="BI18" s="13" t="n">
+        <v>6235014</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>Trade finance outstanding</t>
         </is>
       </c>
-      <c r="B18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI18" s="13" t="n">
+      <c r="B19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI19" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Investor capital outstanding</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI20" s="13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10214,7 +10588,7 @@
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>619242.5996</v>
+        <v>693272.4198</v>
       </c>
       <c r="C16" s="13" t="n">
         <v>8600702.8167</v>
@@ -10233,7 +10607,7 @@
         </is>
       </c>
       <c r="B17" s="17" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="C17" s="17" t="n">
         <v>50</v>
@@ -10252,7 +10626,7 @@
         </is>
       </c>
       <c r="B18" s="13" t="n">
-        <v>130757.4004</v>
+        <v>306727.5802</v>
       </c>
       <c r="C18" s="13" t="n">
         <v>1207273.1908</v>
@@ -10271,7 +10645,7 @@
         </is>
       </c>
       <c r="B19" s="13" t="n">
-        <v>5878702.5544</v>
+        <v>5128702.5544</v>
       </c>
       <c r="C19" s="13" t="n">
         <v>7640597.8524</v>

--- a/finance/outputs/mulligan-mints-5yr-model.xlsx
+++ b/finance/outputs/mulligan-mints-5yr-model.xlsx
@@ -10588,7 +10588,7 @@
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>693272.4198</v>
+        <v>630002.5996</v>
       </c>
       <c r="C16" s="13" t="n">
         <v>8600702.8167</v>
@@ -10607,7 +10607,7 @@
         </is>
       </c>
       <c r="B17" s="17" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C17" s="17" t="n">
         <v>50</v>
@@ -10626,7 +10626,7 @@
         </is>
       </c>
       <c r="B18" s="13" t="n">
-        <v>306727.5802</v>
+        <v>369997.4004</v>
       </c>
       <c r="C18" s="13" t="n">
         <v>1207273.1908</v>
@@ -10645,7 +10645,7 @@
         </is>
       </c>
       <c r="B19" s="13" t="n">
-        <v>5128702.5544</v>
+        <v>5358197.5544</v>
       </c>
       <c r="C19" s="13" t="n">
         <v>7640597.8524</v>

--- a/finance/outputs/mulligan-mints-5yr-model.xlsx
+++ b/finance/outputs/mulligan-mints-5yr-model.xlsx
@@ -6740,7 +6740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI20"/>
+  <dimension ref="A1:BI22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -8619,7 +8619,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Investor revenue share (R2/tin)</t>
+          <t>Investor revenue share</t>
         </is>
       </c>
       <c r="B12" s="13" t="n">
@@ -8806,942 +8806,942 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>Dividends declared</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI13" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>Funding received</t>
         </is>
       </c>
-      <c r="B13" s="13" t="n">
+      <c r="B14" s="13" t="n">
         <v>3500000</v>
       </c>
-      <c r="C13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" s="13" t="n">
+      <c r="C14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" s="13" t="n">
         <v>12000000</v>
       </c>
-      <c r="V13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI13" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>NET CASHFLOW</t>
-        </is>
-      </c>
-      <c r="B14" s="14" t="n">
-        <v>3437000</v>
-      </c>
-      <c r="C14" s="14" t="n">
-        <v>-47720</v>
-      </c>
-      <c r="D14" s="14" t="n">
-        <v>-117352</v>
-      </c>
-      <c r="E14" s="14" t="n">
-        <v>-169918</v>
-      </c>
-      <c r="F14" s="14" t="n">
-        <v>-274750</v>
-      </c>
-      <c r="G14" s="14" t="n">
-        <v>-134010</v>
-      </c>
-      <c r="H14" s="14" t="n">
-        <v>-378489</v>
-      </c>
-      <c r="I14" s="14" t="n">
-        <v>-171117</v>
-      </c>
-      <c r="J14" s="14" t="n">
-        <v>-167217</v>
-      </c>
-      <c r="K14" s="14" t="n">
-        <v>-226573</v>
-      </c>
-      <c r="L14" s="14" t="n">
-        <v>-139339</v>
-      </c>
-      <c r="M14" s="14" t="n">
-        <v>-150438</v>
-      </c>
-      <c r="N14" s="14" t="n">
-        <v>-125789</v>
-      </c>
-      <c r="O14" s="14" t="n">
-        <v>-79438</v>
-      </c>
-      <c r="P14" s="14" t="n">
-        <v>-130854</v>
-      </c>
-      <c r="Q14" s="14" t="n">
-        <v>-95380</v>
-      </c>
-      <c r="R14" s="14" t="n">
-        <v>-90735</v>
-      </c>
-      <c r="S14" s="14" t="n">
-        <v>-105289</v>
-      </c>
-      <c r="T14" s="14" t="n">
-        <v>-258990</v>
-      </c>
-      <c r="U14" s="14" t="n">
-        <v>11862173</v>
-      </c>
-      <c r="V14" s="14" t="n">
-        <v>-22778</v>
-      </c>
-      <c r="W14" s="14" t="n">
-        <v>-193698</v>
-      </c>
-      <c r="X14" s="14" t="n">
-        <v>45676</v>
-      </c>
-      <c r="Y14" s="14" t="n">
-        <v>-222859</v>
-      </c>
-      <c r="Z14" s="14" t="n">
-        <v>-17836</v>
-      </c>
-      <c r="AA14" s="14" t="n">
-        <v>-652824</v>
-      </c>
-      <c r="AB14" s="14" t="n">
-        <v>-48315</v>
-      </c>
-      <c r="AC14" s="14" t="n">
-        <v>-167915</v>
-      </c>
-      <c r="AD14" s="14" t="n">
-        <v>-86722</v>
-      </c>
-      <c r="AE14" s="14" t="n">
-        <v>-165737</v>
-      </c>
-      <c r="AF14" s="14" t="n">
-        <v>-240963</v>
-      </c>
-      <c r="AG14" s="14" t="n">
-        <v>-322317</v>
-      </c>
-      <c r="AH14" s="14" t="n">
-        <v>-413280</v>
-      </c>
-      <c r="AI14" s="14" t="n">
-        <v>56881</v>
-      </c>
-      <c r="AJ14" s="14" t="n">
-        <v>100035</v>
-      </c>
-      <c r="AK14" s="14" t="n">
-        <v>62687</v>
-      </c>
-      <c r="AL14" s="14" t="n">
-        <v>105441</v>
-      </c>
-      <c r="AM14" s="14" t="n">
-        <v>-195479</v>
-      </c>
-      <c r="AN14" s="14" t="n">
-        <v>610756</v>
-      </c>
-      <c r="AO14" s="14" t="n">
-        <v>284837</v>
-      </c>
-      <c r="AP14" s="14" t="n">
-        <v>544094</v>
-      </c>
-      <c r="AQ14" s="14" t="n">
-        <v>78169</v>
-      </c>
-      <c r="AR14" s="14" t="n">
-        <v>475129</v>
-      </c>
-      <c r="AS14" s="14" t="n">
-        <v>247325</v>
-      </c>
-      <c r="AT14" s="14" t="n">
-        <v>395706</v>
-      </c>
-      <c r="AU14" s="14" t="n">
-        <v>353110</v>
-      </c>
-      <c r="AV14" s="14" t="n">
-        <v>388645</v>
-      </c>
-      <c r="AW14" s="14" t="n">
-        <v>-435033</v>
-      </c>
-      <c r="AX14" s="14" t="n">
-        <v>324692</v>
-      </c>
-      <c r="AY14" s="14" t="n">
-        <v>325553</v>
-      </c>
-      <c r="AZ14" s="14" t="n">
-        <v>1287920</v>
-      </c>
-      <c r="BA14" s="14" t="n">
-        <v>1010934</v>
-      </c>
-      <c r="BB14" s="14" t="n">
-        <v>1236870</v>
-      </c>
-      <c r="BC14" s="14" t="n">
-        <v>-605550</v>
-      </c>
-      <c r="BD14" s="14" t="n">
-        <v>1271461</v>
-      </c>
-      <c r="BE14" s="14" t="n">
-        <v>1126361</v>
-      </c>
-      <c r="BF14" s="14" t="n">
-        <v>1346047</v>
-      </c>
-      <c r="BG14" s="14" t="n">
-        <v>1181136</v>
-      </c>
-      <c r="BH14" s="14" t="n">
-        <v>1420633</v>
-      </c>
-      <c r="BI14" s="14" t="n">
-        <v>-515212</v>
+      <c r="V14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI14" s="13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>CLOSING CASH</t>
+          <t>NET CASHFLOW</t>
         </is>
       </c>
       <c r="B15" s="14" t="n">
         <v>3437000</v>
       </c>
       <c r="C15" s="14" t="n">
+        <v>-47720</v>
+      </c>
+      <c r="D15" s="14" t="n">
+        <v>-117352</v>
+      </c>
+      <c r="E15" s="14" t="n">
+        <v>-169918</v>
+      </c>
+      <c r="F15" s="14" t="n">
+        <v>-274750</v>
+      </c>
+      <c r="G15" s="14" t="n">
+        <v>-134010</v>
+      </c>
+      <c r="H15" s="14" t="n">
+        <v>-378489</v>
+      </c>
+      <c r="I15" s="14" t="n">
+        <v>-171117</v>
+      </c>
+      <c r="J15" s="14" t="n">
+        <v>-167217</v>
+      </c>
+      <c r="K15" s="14" t="n">
+        <v>-226573</v>
+      </c>
+      <c r="L15" s="14" t="n">
+        <v>-139339</v>
+      </c>
+      <c r="M15" s="14" t="n">
+        <v>-150438</v>
+      </c>
+      <c r="N15" s="14" t="n">
+        <v>-125789</v>
+      </c>
+      <c r="O15" s="14" t="n">
+        <v>-79438</v>
+      </c>
+      <c r="P15" s="14" t="n">
+        <v>-130854</v>
+      </c>
+      <c r="Q15" s="14" t="n">
+        <v>-95380</v>
+      </c>
+      <c r="R15" s="14" t="n">
+        <v>-90735</v>
+      </c>
+      <c r="S15" s="14" t="n">
+        <v>-105289</v>
+      </c>
+      <c r="T15" s="14" t="n">
+        <v>-258990</v>
+      </c>
+      <c r="U15" s="14" t="n">
+        <v>11862173</v>
+      </c>
+      <c r="V15" s="14" t="n">
+        <v>-22778</v>
+      </c>
+      <c r="W15" s="14" t="n">
+        <v>-193698</v>
+      </c>
+      <c r="X15" s="14" t="n">
+        <v>45676</v>
+      </c>
+      <c r="Y15" s="14" t="n">
+        <v>-222859</v>
+      </c>
+      <c r="Z15" s="14" t="n">
+        <v>-17836</v>
+      </c>
+      <c r="AA15" s="14" t="n">
+        <v>-652824</v>
+      </c>
+      <c r="AB15" s="14" t="n">
+        <v>-48315</v>
+      </c>
+      <c r="AC15" s="14" t="n">
+        <v>-167915</v>
+      </c>
+      <c r="AD15" s="14" t="n">
+        <v>-86722</v>
+      </c>
+      <c r="AE15" s="14" t="n">
+        <v>-165737</v>
+      </c>
+      <c r="AF15" s="14" t="n">
+        <v>-240963</v>
+      </c>
+      <c r="AG15" s="14" t="n">
+        <v>-322317</v>
+      </c>
+      <c r="AH15" s="14" t="n">
+        <v>-413280</v>
+      </c>
+      <c r="AI15" s="14" t="n">
+        <v>56881</v>
+      </c>
+      <c r="AJ15" s="14" t="n">
+        <v>100035</v>
+      </c>
+      <c r="AK15" s="14" t="n">
+        <v>62687</v>
+      </c>
+      <c r="AL15" s="14" t="n">
+        <v>105441</v>
+      </c>
+      <c r="AM15" s="14" t="n">
+        <v>-195479</v>
+      </c>
+      <c r="AN15" s="14" t="n">
+        <v>610756</v>
+      </c>
+      <c r="AO15" s="14" t="n">
+        <v>284837</v>
+      </c>
+      <c r="AP15" s="14" t="n">
+        <v>544094</v>
+      </c>
+      <c r="AQ15" s="14" t="n">
+        <v>78169</v>
+      </c>
+      <c r="AR15" s="14" t="n">
+        <v>475129</v>
+      </c>
+      <c r="AS15" s="14" t="n">
+        <v>247325</v>
+      </c>
+      <c r="AT15" s="14" t="n">
+        <v>395706</v>
+      </c>
+      <c r="AU15" s="14" t="n">
+        <v>353110</v>
+      </c>
+      <c r="AV15" s="14" t="n">
+        <v>388645</v>
+      </c>
+      <c r="AW15" s="14" t="n">
+        <v>-435033</v>
+      </c>
+      <c r="AX15" s="14" t="n">
+        <v>324692</v>
+      </c>
+      <c r="AY15" s="14" t="n">
+        <v>325553</v>
+      </c>
+      <c r="AZ15" s="14" t="n">
+        <v>1287920</v>
+      </c>
+      <c r="BA15" s="14" t="n">
+        <v>1010934</v>
+      </c>
+      <c r="BB15" s="14" t="n">
+        <v>1236870</v>
+      </c>
+      <c r="BC15" s="14" t="n">
+        <v>-605550</v>
+      </c>
+      <c r="BD15" s="14" t="n">
+        <v>1271461</v>
+      </c>
+      <c r="BE15" s="14" t="n">
+        <v>1126361</v>
+      </c>
+      <c r="BF15" s="14" t="n">
+        <v>1346047</v>
+      </c>
+      <c r="BG15" s="14" t="n">
+        <v>1181136</v>
+      </c>
+      <c r="BH15" s="14" t="n">
+        <v>1420633</v>
+      </c>
+      <c r="BI15" s="14" t="n">
+        <v>-515212</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>CLOSING CASH</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="n">
+        <v>3437000</v>
+      </c>
+      <c r="C16" s="14" t="n">
         <v>3389280</v>
       </c>
-      <c r="D15" s="14" t="n">
+      <c r="D16" s="14" t="n">
         <v>3271928</v>
       </c>
-      <c r="E15" s="14" t="n">
+      <c r="E16" s="14" t="n">
         <v>3102011</v>
       </c>
-      <c r="F15" s="14" t="n">
+      <c r="F16" s="14" t="n">
         <v>2827260</v>
       </c>
-      <c r="G15" s="14" t="n">
+      <c r="G16" s="14" t="n">
         <v>2693250</v>
       </c>
-      <c r="H15" s="14" t="n">
+      <c r="H16" s="14" t="n">
         <v>2314761</v>
       </c>
-      <c r="I15" s="14" t="n">
+      <c r="I16" s="14" t="n">
         <v>2143644</v>
       </c>
-      <c r="J15" s="14" t="n">
+      <c r="J16" s="14" t="n">
         <v>1976427</v>
       </c>
-      <c r="K15" s="14" t="n">
+      <c r="K16" s="14" t="n">
         <v>1749854</v>
       </c>
-      <c r="L15" s="14" t="n">
+      <c r="L16" s="14" t="n">
         <v>1610515</v>
       </c>
-      <c r="M15" s="14" t="n">
+      <c r="M16" s="14" t="n">
         <v>1460077</v>
       </c>
-      <c r="N15" s="14" t="n">
+      <c r="N16" s="14" t="n">
         <v>1334288</v>
       </c>
-      <c r="O15" s="14" t="n">
+      <c r="O16" s="14" t="n">
         <v>1254850</v>
       </c>
-      <c r="P15" s="14" t="n">
+      <c r="P16" s="14" t="n">
         <v>1123995</v>
       </c>
-      <c r="Q15" s="14" t="n">
+      <c r="Q16" s="14" t="n">
         <v>1028616</v>
       </c>
-      <c r="R15" s="14" t="n">
+      <c r="R16" s="14" t="n">
         <v>937881</v>
       </c>
-      <c r="S15" s="14" t="n">
+      <c r="S16" s="14" t="n">
         <v>832592</v>
       </c>
-      <c r="T15" s="14" t="n">
+      <c r="T16" s="14" t="n">
         <v>573601</v>
       </c>
-      <c r="U15" s="14" t="n">
+      <c r="U16" s="14" t="n">
         <v>12435774</v>
       </c>
-      <c r="V15" s="14" t="n">
+      <c r="V16" s="14" t="n">
         <v>12412996</v>
       </c>
-      <c r="W15" s="14" t="n">
+      <c r="W16" s="14" t="n">
         <v>12219298</v>
       </c>
-      <c r="X15" s="14" t="n">
+      <c r="X16" s="14" t="n">
         <v>12264974</v>
       </c>
-      <c r="Y15" s="14" t="n">
+      <c r="Y16" s="14" t="n">
         <v>12042115</v>
       </c>
-      <c r="Z15" s="14" t="n">
+      <c r="Z16" s="14" t="n">
         <v>12024279</v>
       </c>
-      <c r="AA15" s="14" t="n">
+      <c r="AA16" s="14" t="n">
         <v>11371455</v>
       </c>
-      <c r="AB15" s="14" t="n">
+      <c r="AB16" s="14" t="n">
         <v>11323141</v>
       </c>
-      <c r="AC15" s="14" t="n">
+      <c r="AC16" s="14" t="n">
         <v>11155226</v>
       </c>
-      <c r="AD15" s="14" t="n">
+      <c r="AD16" s="14" t="n">
         <v>11068504</v>
       </c>
-      <c r="AE15" s="14" t="n">
+      <c r="AE16" s="14" t="n">
         <v>10902767</v>
       </c>
-      <c r="AF15" s="14" t="n">
+      <c r="AF16" s="14" t="n">
         <v>10661804</v>
       </c>
-      <c r="AG15" s="14" t="n">
+      <c r="AG16" s="14" t="n">
         <v>10339487</v>
       </c>
-      <c r="AH15" s="14" t="n">
+      <c r="AH16" s="14" t="n">
         <v>9926207</v>
       </c>
-      <c r="AI15" s="14" t="n">
+      <c r="AI16" s="14" t="n">
         <v>9983087</v>
       </c>
-      <c r="AJ15" s="14" t="n">
+      <c r="AJ16" s="14" t="n">
         <v>10083122</v>
       </c>
-      <c r="AK15" s="14" t="n">
+      <c r="AK16" s="14" t="n">
         <v>10145809</v>
       </c>
-      <c r="AL15" s="14" t="n">
+      <c r="AL16" s="14" t="n">
         <v>10251250</v>
       </c>
-      <c r="AM15" s="14" t="n">
+      <c r="AM16" s="14" t="n">
         <v>10055771</v>
       </c>
-      <c r="AN15" s="14" t="n">
+      <c r="AN16" s="14" t="n">
         <v>10666527</v>
       </c>
-      <c r="AO15" s="14" t="n">
+      <c r="AO16" s="14" t="n">
         <v>10951364</v>
       </c>
-      <c r="AP15" s="14" t="n">
+      <c r="AP16" s="14" t="n">
         <v>11495458</v>
       </c>
-      <c r="AQ15" s="14" t="n">
+      <c r="AQ16" s="14" t="n">
         <v>11573627</v>
       </c>
-      <c r="AR15" s="14" t="n">
+      <c r="AR16" s="14" t="n">
         <v>12048756</v>
       </c>
-      <c r="AS15" s="14" t="n">
+      <c r="AS16" s="14" t="n">
         <v>12296081</v>
       </c>
-      <c r="AT15" s="14" t="n">
+      <c r="AT16" s="14" t="n">
         <v>12691787</v>
       </c>
-      <c r="AU15" s="14" t="n">
+      <c r="AU16" s="14" t="n">
         <v>13044897</v>
       </c>
-      <c r="AV15" s="14" t="n">
+      <c r="AV16" s="14" t="n">
         <v>13433542</v>
       </c>
-      <c r="AW15" s="14" t="n">
+      <c r="AW16" s="14" t="n">
         <v>12998508</v>
       </c>
-      <c r="AX15" s="14" t="n">
+      <c r="AX16" s="14" t="n">
         <v>13323200</v>
       </c>
-      <c r="AY15" s="14" t="n">
+      <c r="AY16" s="14" t="n">
         <v>13648753</v>
       </c>
-      <c r="AZ15" s="14" t="n">
+      <c r="AZ16" s="14" t="n">
         <v>14936673</v>
       </c>
-      <c r="BA15" s="14" t="n">
+      <c r="BA16" s="14" t="n">
         <v>15947607</v>
       </c>
-      <c r="BB15" s="14" t="n">
+      <c r="BB16" s="14" t="n">
         <v>17184477</v>
       </c>
-      <c r="BC15" s="14" t="n">
+      <c r="BC16" s="14" t="n">
         <v>16578927</v>
       </c>
-      <c r="BD15" s="14" t="n">
+      <c r="BD16" s="14" t="n">
         <v>17850388</v>
       </c>
-      <c r="BE15" s="14" t="n">
+      <c r="BE16" s="14" t="n">
         <v>18976749</v>
       </c>
-      <c r="BF15" s="14" t="n">
+      <c r="BF16" s="14" t="n">
         <v>20322796</v>
       </c>
-      <c r="BG15" s="14" t="n">
+      <c r="BG16" s="14" t="n">
         <v>21503932</v>
       </c>
-      <c r="BH15" s="14" t="n">
+      <c r="BH16" s="14" t="n">
         <v>22924565</v>
       </c>
-      <c r="BI15" s="14" t="n">
+      <c r="BI16" s="14" t="n">
         <v>22409352</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Stock on hand (units)</t>
-        </is>
-      </c>
-      <c r="B16" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="12" t="n">
-        <v>21032</v>
-      </c>
-      <c r="I16" s="12" t="n">
-        <v>18525</v>
-      </c>
-      <c r="J16" s="12" t="n">
-        <v>37450</v>
-      </c>
-      <c r="K16" s="12" t="n">
-        <v>32837</v>
-      </c>
-      <c r="L16" s="12" t="n">
-        <v>27170</v>
-      </c>
-      <c r="M16" s="12" t="n">
-        <v>42935</v>
-      </c>
-      <c r="N16" s="12" t="n">
-        <v>33559</v>
-      </c>
-      <c r="O16" s="12" t="n">
-        <v>45750</v>
-      </c>
-      <c r="P16" s="12" t="n">
-        <v>57026</v>
-      </c>
-      <c r="Q16" s="12" t="n">
-        <v>44899</v>
-      </c>
-      <c r="R16" s="12" t="n">
-        <v>54341</v>
-      </c>
-      <c r="S16" s="12" t="n">
-        <v>62866</v>
-      </c>
-      <c r="T16" s="12" t="n">
-        <v>69994</v>
-      </c>
-      <c r="U16" s="12" t="n">
-        <v>75726</v>
-      </c>
-      <c r="V16" s="12" t="n">
-        <v>80061</v>
-      </c>
-      <c r="W16" s="12" t="n">
-        <v>83000</v>
-      </c>
-      <c r="X16" s="12" t="n">
-        <v>84541</v>
-      </c>
-      <c r="Y16" s="12" t="n">
-        <v>107172</v>
-      </c>
-      <c r="Z16" s="12" t="n">
-        <v>101387</v>
-      </c>
-      <c r="AA16" s="12" t="n">
-        <v>116187</v>
-      </c>
-      <c r="AB16" s="12" t="n">
-        <v>106602</v>
-      </c>
-      <c r="AC16" s="12" t="n">
-        <v>140088</v>
-      </c>
-      <c r="AD16" s="12" t="n">
-        <v>149188</v>
-      </c>
-      <c r="AE16" s="12" t="n">
-        <v>178873</v>
-      </c>
-      <c r="AF16" s="12" t="n">
-        <v>191658</v>
-      </c>
-      <c r="AG16" s="12" t="n">
-        <v>180059</v>
-      </c>
-      <c r="AH16" s="12" t="n">
-        <v>189044</v>
-      </c>
-      <c r="AI16" s="12" t="n">
-        <v>218615</v>
-      </c>
-      <c r="AJ16" s="12" t="n">
-        <v>246285</v>
-      </c>
-      <c r="AK16" s="12" t="n">
-        <v>272056</v>
-      </c>
-      <c r="AL16" s="12" t="n">
-        <v>277558</v>
-      </c>
-      <c r="AM16" s="12" t="n">
-        <v>281191</v>
-      </c>
-      <c r="AN16" s="12" t="n">
-        <v>282952</v>
-      </c>
-      <c r="AO16" s="12" t="n">
-        <v>282842</v>
-      </c>
-      <c r="AP16" s="12" t="n">
-        <v>280862</v>
-      </c>
-      <c r="AQ16" s="12" t="n">
-        <v>299496</v>
-      </c>
-      <c r="AR16" s="12" t="n">
-        <v>293774</v>
-      </c>
-      <c r="AS16" s="12" t="n">
-        <v>308666</v>
-      </c>
-      <c r="AT16" s="12" t="n">
-        <v>321688</v>
-      </c>
-      <c r="AU16" s="12" t="n">
-        <v>355323</v>
-      </c>
-      <c r="AV16" s="12" t="n">
-        <v>387088</v>
-      </c>
-      <c r="AW16" s="12" t="n">
-        <v>416982</v>
-      </c>
-      <c r="AX16" s="12" t="n">
-        <v>433814</v>
-      </c>
-      <c r="AY16" s="12" t="n">
-        <v>426587</v>
-      </c>
-      <c r="AZ16" s="12" t="n">
-        <v>440272</v>
-      </c>
-      <c r="BA16" s="12" t="n">
-        <v>452385</v>
-      </c>
-      <c r="BB16" s="12" t="n">
-        <v>440439</v>
-      </c>
-      <c r="BC16" s="12" t="n">
-        <v>449406</v>
-      </c>
-      <c r="BD16" s="12" t="n">
-        <v>456800</v>
-      </c>
-      <c r="BE16" s="12" t="n">
-        <v>462621</v>
-      </c>
-      <c r="BF16" s="12" t="n">
-        <v>466868</v>
-      </c>
-      <c r="BG16" s="12" t="n">
-        <v>469543</v>
-      </c>
-      <c r="BH16" s="12" t="n">
-        <v>470646</v>
-      </c>
-      <c r="BI16" s="12" t="n">
-        <v>470175</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Stock on hand (value)</t>
-        </is>
-      </c>
-      <c r="B17" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="13" t="n">
-        <v>216424</v>
-      </c>
-      <c r="I17" s="13" t="n">
-        <v>190630</v>
-      </c>
-      <c r="J17" s="13" t="n">
-        <v>385375</v>
-      </c>
-      <c r="K17" s="13" t="n">
-        <v>337903</v>
-      </c>
-      <c r="L17" s="13" t="n">
-        <v>279591</v>
-      </c>
-      <c r="M17" s="13" t="n">
-        <v>441819</v>
-      </c>
-      <c r="N17" s="13" t="n">
-        <v>345330</v>
-      </c>
-      <c r="O17" s="13" t="n">
-        <v>450854</v>
-      </c>
-      <c r="P17" s="13" t="n">
-        <v>549747</v>
-      </c>
-      <c r="Q17" s="13" t="n">
-        <v>432842</v>
-      </c>
-      <c r="R17" s="13" t="n">
-        <v>522426</v>
-      </c>
-      <c r="S17" s="13" t="n">
-        <v>603414</v>
-      </c>
-      <c r="T17" s="13" t="n">
-        <v>671147</v>
-      </c>
-      <c r="U17" s="13" t="n">
-        <v>725600</v>
-      </c>
-      <c r="V17" s="13" t="n">
-        <v>766756</v>
-      </c>
-      <c r="W17" s="13" t="n">
-        <v>794606</v>
-      </c>
-      <c r="X17" s="13" t="n">
-        <v>809140</v>
-      </c>
-      <c r="Y17" s="13" t="n">
-        <v>1025366</v>
-      </c>
-      <c r="Z17" s="13" t="n">
-        <v>956043</v>
-      </c>
-      <c r="AA17" s="13" t="n">
-        <v>1072147</v>
-      </c>
-      <c r="AB17" s="13" t="n">
-        <v>975833</v>
-      </c>
-      <c r="AC17" s="13" t="n">
-        <v>1250652</v>
-      </c>
-      <c r="AD17" s="13" t="n">
-        <v>1338581</v>
-      </c>
-      <c r="AE17" s="13" t="n">
-        <v>1601134</v>
-      </c>
-      <c r="AF17" s="13" t="n">
-        <v>1713114</v>
-      </c>
-      <c r="AG17" s="13" t="n">
-        <v>1615374</v>
-      </c>
-      <c r="AH17" s="13" t="n">
-        <v>1692528</v>
-      </c>
-      <c r="AI17" s="13" t="n">
-        <v>1953835</v>
-      </c>
-      <c r="AJ17" s="13" t="n">
-        <v>2198762</v>
-      </c>
-      <c r="AK17" s="13" t="n">
-        <v>2427128</v>
-      </c>
-      <c r="AL17" s="13" t="n">
-        <v>2435302</v>
-      </c>
-      <c r="AM17" s="13" t="n">
-        <v>2436482</v>
-      </c>
-      <c r="AN17" s="13" t="n">
-        <v>2428649</v>
-      </c>
-      <c r="AO17" s="13" t="n">
-        <v>2410300</v>
-      </c>
-      <c r="AP17" s="13" t="n">
-        <v>2402300</v>
-      </c>
-      <c r="AQ17" s="13" t="n">
-        <v>2570190</v>
-      </c>
-      <c r="AR17" s="13" t="n">
-        <v>2525901</v>
-      </c>
-      <c r="AS17" s="13" t="n">
-        <v>2658609</v>
-      </c>
-      <c r="AT17" s="13" t="n">
-        <v>2774156</v>
-      </c>
-      <c r="AU17" s="13" t="n">
-        <v>3067260</v>
-      </c>
-      <c r="AV17" s="13" t="n">
-        <v>3343636</v>
-      </c>
-      <c r="AW17" s="13" t="n">
-        <v>3603450</v>
-      </c>
-      <c r="AX17" s="13" t="n">
-        <v>3692666</v>
-      </c>
-      <c r="AY17" s="13" t="n">
-        <v>3596398</v>
-      </c>
-      <c r="AZ17" s="13" t="n">
-        <v>3680690</v>
-      </c>
-      <c r="BA17" s="13" t="n">
-        <v>3759154</v>
-      </c>
-      <c r="BB17" s="13" t="n">
-        <v>3677828</v>
-      </c>
-      <c r="BC17" s="13" t="n">
-        <v>3768860</v>
-      </c>
-      <c r="BD17" s="13" t="n">
-        <v>3842787</v>
-      </c>
-      <c r="BE17" s="13" t="n">
-        <v>3900587</v>
-      </c>
-      <c r="BF17" s="13" t="n">
-        <v>3942971</v>
-      </c>
-      <c r="BG17" s="13" t="n">
-        <v>3970458</v>
-      </c>
-      <c r="BH17" s="13" t="n">
-        <v>3983431</v>
-      </c>
-      <c r="BI17" s="13" t="n">
-        <v>3982175</v>
+          <t>Stock on hand (units)</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="12" t="n">
+        <v>21032</v>
+      </c>
+      <c r="I17" s="12" t="n">
+        <v>18525</v>
+      </c>
+      <c r="J17" s="12" t="n">
+        <v>37450</v>
+      </c>
+      <c r="K17" s="12" t="n">
+        <v>32837</v>
+      </c>
+      <c r="L17" s="12" t="n">
+        <v>27170</v>
+      </c>
+      <c r="M17" s="12" t="n">
+        <v>42935</v>
+      </c>
+      <c r="N17" s="12" t="n">
+        <v>33559</v>
+      </c>
+      <c r="O17" s="12" t="n">
+        <v>45750</v>
+      </c>
+      <c r="P17" s="12" t="n">
+        <v>57026</v>
+      </c>
+      <c r="Q17" s="12" t="n">
+        <v>44899</v>
+      </c>
+      <c r="R17" s="12" t="n">
+        <v>54341</v>
+      </c>
+      <c r="S17" s="12" t="n">
+        <v>62866</v>
+      </c>
+      <c r="T17" s="12" t="n">
+        <v>69994</v>
+      </c>
+      <c r="U17" s="12" t="n">
+        <v>75726</v>
+      </c>
+      <c r="V17" s="12" t="n">
+        <v>80061</v>
+      </c>
+      <c r="W17" s="12" t="n">
+        <v>83000</v>
+      </c>
+      <c r="X17" s="12" t="n">
+        <v>84541</v>
+      </c>
+      <c r="Y17" s="12" t="n">
+        <v>107172</v>
+      </c>
+      <c r="Z17" s="12" t="n">
+        <v>101387</v>
+      </c>
+      <c r="AA17" s="12" t="n">
+        <v>116187</v>
+      </c>
+      <c r="AB17" s="12" t="n">
+        <v>106602</v>
+      </c>
+      <c r="AC17" s="12" t="n">
+        <v>140088</v>
+      </c>
+      <c r="AD17" s="12" t="n">
+        <v>149188</v>
+      </c>
+      <c r="AE17" s="12" t="n">
+        <v>178873</v>
+      </c>
+      <c r="AF17" s="12" t="n">
+        <v>191658</v>
+      </c>
+      <c r="AG17" s="12" t="n">
+        <v>180059</v>
+      </c>
+      <c r="AH17" s="12" t="n">
+        <v>189044</v>
+      </c>
+      <c r="AI17" s="12" t="n">
+        <v>218615</v>
+      </c>
+      <c r="AJ17" s="12" t="n">
+        <v>246285</v>
+      </c>
+      <c r="AK17" s="12" t="n">
+        <v>272056</v>
+      </c>
+      <c r="AL17" s="12" t="n">
+        <v>277558</v>
+      </c>
+      <c r="AM17" s="12" t="n">
+        <v>281191</v>
+      </c>
+      <c r="AN17" s="12" t="n">
+        <v>282952</v>
+      </c>
+      <c r="AO17" s="12" t="n">
+        <v>282842</v>
+      </c>
+      <c r="AP17" s="12" t="n">
+        <v>280862</v>
+      </c>
+      <c r="AQ17" s="12" t="n">
+        <v>299496</v>
+      </c>
+      <c r="AR17" s="12" t="n">
+        <v>293774</v>
+      </c>
+      <c r="AS17" s="12" t="n">
+        <v>308666</v>
+      </c>
+      <c r="AT17" s="12" t="n">
+        <v>321688</v>
+      </c>
+      <c r="AU17" s="12" t="n">
+        <v>355323</v>
+      </c>
+      <c r="AV17" s="12" t="n">
+        <v>387088</v>
+      </c>
+      <c r="AW17" s="12" t="n">
+        <v>416982</v>
+      </c>
+      <c r="AX17" s="12" t="n">
+        <v>433814</v>
+      </c>
+      <c r="AY17" s="12" t="n">
+        <v>426587</v>
+      </c>
+      <c r="AZ17" s="12" t="n">
+        <v>440272</v>
+      </c>
+      <c r="BA17" s="12" t="n">
+        <v>452385</v>
+      </c>
+      <c r="BB17" s="12" t="n">
+        <v>440439</v>
+      </c>
+      <c r="BC17" s="12" t="n">
+        <v>449406</v>
+      </c>
+      <c r="BD17" s="12" t="n">
+        <v>456800</v>
+      </c>
+      <c r="BE17" s="12" t="n">
+        <v>462621</v>
+      </c>
+      <c r="BF17" s="12" t="n">
+        <v>466868</v>
+      </c>
+      <c r="BG17" s="12" t="n">
+        <v>469543</v>
+      </c>
+      <c r="BH17" s="12" t="n">
+        <v>470646</v>
+      </c>
+      <c r="BI17" s="12" t="n">
+        <v>470175</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Debtors</t>
+          <t>Stock on hand (value)</t>
         </is>
       </c>
       <c r="B18" s="13" t="n">
@@ -9763,172 +9763,172 @@
         <v>0</v>
       </c>
       <c r="H18" s="13" t="n">
-        <v>29375</v>
+        <v>216424</v>
       </c>
       <c r="I18" s="13" t="n">
-        <v>58750</v>
+        <v>190630</v>
       </c>
       <c r="J18" s="13" t="n">
-        <v>88124</v>
+        <v>385375</v>
       </c>
       <c r="K18" s="13" t="n">
-        <v>117499</v>
+        <v>337903</v>
       </c>
       <c r="L18" s="13" t="n">
-        <v>146874</v>
+        <v>279591</v>
       </c>
       <c r="M18" s="13" t="n">
-        <v>176249</v>
+        <v>441819</v>
       </c>
       <c r="N18" s="13" t="n">
-        <v>235298</v>
+        <v>345330</v>
       </c>
       <c r="O18" s="13" t="n">
-        <v>261496</v>
+        <v>450854</v>
       </c>
       <c r="P18" s="13" t="n">
-        <v>287695</v>
+        <v>549747</v>
       </c>
       <c r="Q18" s="13" t="n">
-        <v>313893</v>
+        <v>432842</v>
       </c>
       <c r="R18" s="13" t="n">
-        <v>340091</v>
+        <v>522426</v>
       </c>
       <c r="S18" s="13" t="n">
-        <v>366290</v>
+        <v>603414</v>
       </c>
       <c r="T18" s="13" t="n">
-        <v>404660</v>
+        <v>671147</v>
       </c>
       <c r="U18" s="13" t="n">
-        <v>455201</v>
+        <v>725600</v>
       </c>
       <c r="V18" s="13" t="n">
-        <v>505743</v>
+        <v>766756</v>
       </c>
       <c r="W18" s="13" t="n">
-        <v>556284</v>
+        <v>794606</v>
       </c>
       <c r="X18" s="13" t="n">
-        <v>606826</v>
+        <v>809140</v>
       </c>
       <c r="Y18" s="13" t="n">
-        <v>657368</v>
+        <v>1025366</v>
       </c>
       <c r="Z18" s="13" t="n">
-        <v>814707</v>
+        <v>956043</v>
       </c>
       <c r="AA18" s="13" t="n">
-        <v>899728</v>
+        <v>1072147</v>
       </c>
       <c r="AB18" s="13" t="n">
-        <v>971512</v>
+        <v>975833</v>
       </c>
       <c r="AC18" s="13" t="n">
-        <v>1043296</v>
+        <v>1250652</v>
       </c>
       <c r="AD18" s="13" t="n">
-        <v>1115080</v>
+        <v>1338581</v>
       </c>
       <c r="AE18" s="13" t="n">
-        <v>1186865</v>
+        <v>1601134</v>
       </c>
       <c r="AF18" s="13" t="n">
-        <v>1514980</v>
+        <v>1713114</v>
       </c>
       <c r="AG18" s="13" t="n">
-        <v>1843095</v>
+        <v>1615374</v>
       </c>
       <c r="AH18" s="13" t="n">
-        <v>1914879</v>
+        <v>1692528</v>
       </c>
       <c r="AI18" s="13" t="n">
-        <v>1986663</v>
+        <v>1953835</v>
       </c>
       <c r="AJ18" s="13" t="n">
-        <v>2058448</v>
+        <v>2198762</v>
       </c>
       <c r="AK18" s="13" t="n">
-        <v>2130232</v>
+        <v>2427128</v>
       </c>
       <c r="AL18" s="13" t="n">
-        <v>2638969</v>
+        <v>2435302</v>
       </c>
       <c r="AM18" s="13" t="n">
-        <v>3024009</v>
+        <v>2436482</v>
       </c>
       <c r="AN18" s="13" t="n">
-        <v>3099646</v>
+        <v>2428649</v>
       </c>
       <c r="AO18" s="13" t="n">
-        <v>3175283</v>
+        <v>2410300</v>
       </c>
       <c r="AP18" s="13" t="n">
-        <v>3250920</v>
+        <v>2402300</v>
       </c>
       <c r="AQ18" s="13" t="n">
-        <v>3326557</v>
+        <v>2570190</v>
       </c>
       <c r="AR18" s="13" t="n">
-        <v>3402194</v>
+        <v>2525901</v>
       </c>
       <c r="AS18" s="13" t="n">
-        <v>3477831</v>
+        <v>2658609</v>
       </c>
       <c r="AT18" s="13" t="n">
-        <v>3553467</v>
+        <v>2774156</v>
       </c>
       <c r="AU18" s="13" t="n">
-        <v>3629104</v>
+        <v>3067260</v>
       </c>
       <c r="AV18" s="13" t="n">
-        <v>3704741</v>
+        <v>3343636</v>
       </c>
       <c r="AW18" s="13" t="n">
-        <v>3780378</v>
+        <v>3603450</v>
       </c>
       <c r="AX18" s="13" t="n">
-        <v>4748621</v>
+        <v>3692666</v>
       </c>
       <c r="AY18" s="13" t="n">
-        <v>5555762</v>
+        <v>3596398</v>
       </c>
       <c r="AZ18" s="13" t="n">
-        <v>5623687</v>
+        <v>3680690</v>
       </c>
       <c r="BA18" s="13" t="n">
-        <v>5691612</v>
+        <v>3759154</v>
       </c>
       <c r="BB18" s="13" t="n">
-        <v>5759537</v>
+        <v>3677828</v>
       </c>
       <c r="BC18" s="13" t="n">
-        <v>5827463</v>
+        <v>3768860</v>
       </c>
       <c r="BD18" s="13" t="n">
-        <v>5895388</v>
+        <v>3842787</v>
       </c>
       <c r="BE18" s="13" t="n">
-        <v>5963313</v>
+        <v>3900587</v>
       </c>
       <c r="BF18" s="13" t="n">
-        <v>6031238</v>
+        <v>3942971</v>
       </c>
       <c r="BG18" s="13" t="n">
-        <v>6099163</v>
+        <v>3970458</v>
       </c>
       <c r="BH18" s="13" t="n">
-        <v>6167088</v>
+        <v>3983431</v>
       </c>
       <c r="BI18" s="13" t="n">
-        <v>6235014</v>
+        <v>3982175</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Trade finance outstanding</t>
+          <t>Debtors</t>
         </is>
       </c>
       <c r="B19" s="13" t="n">
@@ -9950,352 +9950,726 @@
         <v>0</v>
       </c>
       <c r="H19" s="13" t="n">
-        <v>0</v>
+        <v>29375</v>
       </c>
       <c r="I19" s="13" t="n">
-        <v>0</v>
+        <v>58750</v>
       </c>
       <c r="J19" s="13" t="n">
-        <v>0</v>
+        <v>88124</v>
       </c>
       <c r="K19" s="13" t="n">
-        <v>0</v>
+        <v>117499</v>
       </c>
       <c r="L19" s="13" t="n">
-        <v>0</v>
+        <v>146874</v>
       </c>
       <c r="M19" s="13" t="n">
-        <v>0</v>
+        <v>176249</v>
       </c>
       <c r="N19" s="13" t="n">
-        <v>0</v>
+        <v>235298</v>
       </c>
       <c r="O19" s="13" t="n">
-        <v>0</v>
+        <v>261496</v>
       </c>
       <c r="P19" s="13" t="n">
-        <v>0</v>
+        <v>287695</v>
       </c>
       <c r="Q19" s="13" t="n">
-        <v>0</v>
+        <v>313893</v>
       </c>
       <c r="R19" s="13" t="n">
-        <v>0</v>
+        <v>340091</v>
       </c>
       <c r="S19" s="13" t="n">
-        <v>0</v>
+        <v>366290</v>
       </c>
       <c r="T19" s="13" t="n">
-        <v>0</v>
+        <v>404660</v>
       </c>
       <c r="U19" s="13" t="n">
-        <v>0</v>
+        <v>455201</v>
       </c>
       <c r="V19" s="13" t="n">
-        <v>0</v>
+        <v>505743</v>
       </c>
       <c r="W19" s="13" t="n">
-        <v>0</v>
+        <v>556284</v>
       </c>
       <c r="X19" s="13" t="n">
-        <v>0</v>
+        <v>606826</v>
       </c>
       <c r="Y19" s="13" t="n">
-        <v>0</v>
+        <v>657368</v>
       </c>
       <c r="Z19" s="13" t="n">
-        <v>0</v>
+        <v>814707</v>
       </c>
       <c r="AA19" s="13" t="n">
-        <v>0</v>
+        <v>899728</v>
       </c>
       <c r="AB19" s="13" t="n">
-        <v>0</v>
+        <v>971512</v>
       </c>
       <c r="AC19" s="13" t="n">
-        <v>0</v>
+        <v>1043296</v>
       </c>
       <c r="AD19" s="13" t="n">
-        <v>0</v>
+        <v>1115080</v>
       </c>
       <c r="AE19" s="13" t="n">
-        <v>0</v>
+        <v>1186865</v>
       </c>
       <c r="AF19" s="13" t="n">
-        <v>0</v>
+        <v>1514980</v>
       </c>
       <c r="AG19" s="13" t="n">
-        <v>0</v>
+        <v>1843095</v>
       </c>
       <c r="AH19" s="13" t="n">
-        <v>0</v>
+        <v>1914879</v>
       </c>
       <c r="AI19" s="13" t="n">
-        <v>0</v>
+        <v>1986663</v>
       </c>
       <c r="AJ19" s="13" t="n">
-        <v>0</v>
+        <v>2058448</v>
       </c>
       <c r="AK19" s="13" t="n">
-        <v>0</v>
+        <v>2130232</v>
       </c>
       <c r="AL19" s="13" t="n">
-        <v>0</v>
+        <v>2638969</v>
       </c>
       <c r="AM19" s="13" t="n">
-        <v>0</v>
+        <v>3024009</v>
       </c>
       <c r="AN19" s="13" t="n">
-        <v>0</v>
+        <v>3099646</v>
       </c>
       <c r="AO19" s="13" t="n">
-        <v>0</v>
+        <v>3175283</v>
       </c>
       <c r="AP19" s="13" t="n">
-        <v>0</v>
+        <v>3250920</v>
       </c>
       <c r="AQ19" s="13" t="n">
-        <v>0</v>
+        <v>3326557</v>
       </c>
       <c r="AR19" s="13" t="n">
-        <v>0</v>
+        <v>3402194</v>
       </c>
       <c r="AS19" s="13" t="n">
-        <v>0</v>
+        <v>3477831</v>
       </c>
       <c r="AT19" s="13" t="n">
-        <v>0</v>
+        <v>3553467</v>
       </c>
       <c r="AU19" s="13" t="n">
-        <v>0</v>
+        <v>3629104</v>
       </c>
       <c r="AV19" s="13" t="n">
-        <v>0</v>
+        <v>3704741</v>
       </c>
       <c r="AW19" s="13" t="n">
-        <v>0</v>
+        <v>3780378</v>
       </c>
       <c r="AX19" s="13" t="n">
-        <v>0</v>
+        <v>4748621</v>
       </c>
       <c r="AY19" s="13" t="n">
-        <v>0</v>
+        <v>5555762</v>
       </c>
       <c r="AZ19" s="13" t="n">
-        <v>0</v>
+        <v>5623687</v>
       </c>
       <c r="BA19" s="13" t="n">
-        <v>0</v>
+        <v>5691612</v>
       </c>
       <c r="BB19" s="13" t="n">
-        <v>0</v>
+        <v>5759537</v>
       </c>
       <c r="BC19" s="13" t="n">
-        <v>0</v>
+        <v>5827463</v>
       </c>
       <c r="BD19" s="13" t="n">
-        <v>0</v>
+        <v>5895388</v>
       </c>
       <c r="BE19" s="13" t="n">
-        <v>0</v>
+        <v>5963313</v>
       </c>
       <c r="BF19" s="13" t="n">
-        <v>0</v>
+        <v>6031238</v>
       </c>
       <c r="BG19" s="13" t="n">
-        <v>0</v>
+        <v>6099163</v>
       </c>
       <c r="BH19" s="13" t="n">
-        <v>0</v>
+        <v>6167088</v>
       </c>
       <c r="BI19" s="13" t="n">
-        <v>0</v>
+        <v>6235014</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>Trade finance outstanding</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI20" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>Investor capital outstanding</t>
         </is>
       </c>
-      <c r="B20" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA20" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB20" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC20" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD20" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE20" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF20" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG20" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH20" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI20" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ20" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK20" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL20" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM20" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN20" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO20" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP20" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ20" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR20" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS20" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT20" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU20" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV20" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW20" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX20" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY20" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ20" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA20" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB20" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC20" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD20" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE20" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF20" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG20" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH20" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI20" s="13" t="n">
+      <c r="B21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI21" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  of dividends, to investor</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG22" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI22" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ22" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK22" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL22" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM22" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN22" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO22" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ22" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR22" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS22" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT22" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU22" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV22" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW22" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX22" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY22" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ22" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA22" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB22" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC22" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD22" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE22" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF22" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG22" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH22" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI22" s="13" t="n">
         <v>0</v>
       </c>
     </row>

--- a/finance/outputs/mulligan-mints-5yr-model.xlsx
+++ b/finance/outputs/mulligan-mints-5yr-model.xlsx
@@ -16,6 +16,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenarios" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Funding" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Purchase orders" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exit" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -96,7 +97,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
@@ -125,6 +126,7 @@
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -604,6 +606,317 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>POTENTIAL EXIT AT MONTH 60 — BOOTSTRAP SCENARIO</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>WHAT IS BEING SOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Year-5 EBITDA</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="n">
+        <v>4474774</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Year-5 revenue</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="n">
+        <v>11915683</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  of which brand licensing</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="n">
+        <v>2280000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Cash at bank</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="n">
+        <v>5358198</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  less working capital left in (2 months opex)</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="n">
+        <v>-692103</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  surplus cash to sellers</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="n">
+        <v>4666094</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Trade finance owed</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="n">
+        <v>-905496</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Investor capital still owed</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="n">
+        <v>-229495</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>EBITDA multiple</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>Enterprise value</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>Equity value</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>Founders 80%</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>Founders after CGT</t>
+        </is>
+      </c>
+      <c r="F13" s="11" t="inlineStr">
+        <is>
+          <t>PJ Offner 10%</t>
+        </is>
+      </c>
+      <c r="G13" s="11" t="inlineStr">
+        <is>
+          <t>Investor at exit</t>
+        </is>
+      </c>
+      <c r="H13" s="11" t="inlineStr">
+        <is>
+          <t>Investor IRR</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="18" t="inlineStr">
+        <is>
+          <t>4x</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="n">
+        <v>17899096.0706</v>
+      </c>
+      <c r="C14" s="13" t="n">
+        <v>21430199.2394</v>
+      </c>
+      <c r="D14" s="13" t="n">
+        <v>17144159.3915</v>
+      </c>
+      <c r="E14" s="13" t="n">
+        <v>14058210.701</v>
+      </c>
+      <c r="F14" s="13" t="n">
+        <v>2143019.9239</v>
+      </c>
+      <c r="G14" s="13" t="n">
+        <v>2372514.9239</v>
+      </c>
+      <c r="H14" s="8" t="n">
+        <v>0.2926</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="18" t="inlineStr">
+        <is>
+          <t>6x</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="n">
+        <v>26848644.1058</v>
+      </c>
+      <c r="C15" s="13" t="n">
+        <v>30379747.2746</v>
+      </c>
+      <c r="D15" s="13" t="n">
+        <v>24303797.8197</v>
+      </c>
+      <c r="E15" s="13" t="n">
+        <v>19929114.2122</v>
+      </c>
+      <c r="F15" s="13" t="n">
+        <v>3037974.7275</v>
+      </c>
+      <c r="G15" s="13" t="n">
+        <v>3267469.7275</v>
+      </c>
+      <c r="H15" s="8" t="n">
+        <v>0.3602</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="18" t="inlineStr">
+        <is>
+          <t>8x</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="n">
+        <v>35798192.1411</v>
+      </c>
+      <c r="C16" s="13" t="n">
+        <v>39329295.3099</v>
+      </c>
+      <c r="D16" s="13" t="n">
+        <v>31463436.2479</v>
+      </c>
+      <c r="E16" s="13" t="n">
+        <v>25800017.7233</v>
+      </c>
+      <c r="F16" s="13" t="n">
+        <v>3932929.531</v>
+      </c>
+      <c r="G16" s="13" t="n">
+        <v>4162424.531</v>
+      </c>
+      <c r="H16" s="8" t="n">
+        <v>0.416</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="18" t="inlineStr">
+        <is>
+          <t>10x</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="n">
+        <v>44747740.1764</v>
+      </c>
+      <c r="C17" s="13" t="n">
+        <v>48278843.3452</v>
+      </c>
+      <c r="D17" s="13" t="n">
+        <v>38623074.6762</v>
+      </c>
+      <c r="E17" s="13" t="n">
+        <v>31670921.2345</v>
+      </c>
+      <c r="F17" s="13" t="n">
+        <v>4827884.3345</v>
+      </c>
+      <c r="G17" s="13" t="n">
+        <v>5057379.3345</v>
+      </c>
+      <c r="H17" s="8" t="n">
+        <v>0.464</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Equity value = enterprise value + surplus cash - trade finance - investor capital owed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Founders' CGT at 18% effective (40% inclusion x 45% marginal, individuals holding shares).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>The investor is also repaid R770,505 of capital at R1 a tin across the five years,</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>so their all-in return runs from R3,143,020 at 4x to R5,827,884 at 10x, on R1,000,000.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Every multiple here is an estimate. Nobody has offered anything.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/finance/outputs/mulligan-mints-5yr-model.xlsx
+++ b/finance/outputs/mulligan-mints-5yr-model.xlsx
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="B4" s="13" t="n">
-        <v>4474774</v>
+        <v>9218236</v>
       </c>
     </row>
     <row r="5">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B5" s="13" t="n">
-        <v>11915683</v>
+        <v>20641984</v>
       </c>
     </row>
     <row r="6">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="B7" s="13" t="n">
-        <v>5358198</v>
+        <v>8647487</v>
       </c>
     </row>
     <row r="8">
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="B8" s="13" t="n">
-        <v>-692103</v>
+        <v>-890105</v>
       </c>
     </row>
     <row r="9">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="B9" s="13" t="n">
-        <v>4666094</v>
+        <v>7757382</v>
       </c>
     </row>
     <row r="10">
@@ -704,7 +704,7 @@
         </is>
       </c>
       <c r="B10" s="13" t="n">
-        <v>-905496</v>
+        <v>-1526893</v>
       </c>
     </row>
     <row r="11">
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="B11" s="13" t="n">
-        <v>-229495</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -766,25 +766,25 @@
         </is>
       </c>
       <c r="B14" s="13" t="n">
-        <v>17899096.0706</v>
+        <v>36872944.8596</v>
       </c>
       <c r="C14" s="13" t="n">
-        <v>21430199.2394</v>
+        <v>43103433.4475</v>
       </c>
       <c r="D14" s="13" t="n">
-        <v>17144159.3915</v>
+        <v>34482746.758</v>
       </c>
       <c r="E14" s="13" t="n">
-        <v>14058210.701</v>
+        <v>28275852.3415</v>
       </c>
       <c r="F14" s="13" t="n">
-        <v>2143019.9239</v>
+        <v>4310343.3447</v>
       </c>
       <c r="G14" s="13" t="n">
-        <v>2372514.9239</v>
+        <v>4310343.3447</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>0.2926</v>
+        <v>0.4858</v>
       </c>
     </row>
     <row r="15">
@@ -794,25 +794,25 @@
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>26848644.1058</v>
+        <v>55309417.2894</v>
       </c>
       <c r="C15" s="13" t="n">
-        <v>30379747.2746</v>
+        <v>61539905.8772</v>
       </c>
       <c r="D15" s="13" t="n">
-        <v>24303797.8197</v>
+        <v>49231924.7018</v>
       </c>
       <c r="E15" s="13" t="n">
-        <v>19929114.2122</v>
+        <v>40370178.2555</v>
       </c>
       <c r="F15" s="13" t="n">
-        <v>3037974.7275</v>
+        <v>6153990.5877</v>
       </c>
       <c r="G15" s="13" t="n">
-        <v>3267469.7275</v>
+        <v>6153990.5877</v>
       </c>
       <c r="H15" s="8" t="n">
-        <v>0.3602</v>
+        <v>0.5698</v>
       </c>
     </row>
     <row r="16">
@@ -822,25 +822,25 @@
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>35798192.1411</v>
+        <v>73745889.7191</v>
       </c>
       <c r="C16" s="13" t="n">
-        <v>39329295.3099</v>
+        <v>79976378.307</v>
       </c>
       <c r="D16" s="13" t="n">
-        <v>31463436.2479</v>
+        <v>63981102.6456</v>
       </c>
       <c r="E16" s="13" t="n">
-        <v>25800017.7233</v>
+        <v>52464504.1694</v>
       </c>
       <c r="F16" s="13" t="n">
-        <v>3932929.531</v>
+        <v>7997637.8307</v>
       </c>
       <c r="G16" s="13" t="n">
-        <v>4162424.531</v>
+        <v>7997637.8307</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>0.416</v>
+        <v>0.638</v>
       </c>
     </row>
     <row r="17">
@@ -850,25 +850,25 @@
         </is>
       </c>
       <c r="B17" s="13" t="n">
-        <v>44747740.1764</v>
+        <v>92182362.1489</v>
       </c>
       <c r="C17" s="13" t="n">
-        <v>48278843.3452</v>
+        <v>98412850.7368</v>
       </c>
       <c r="D17" s="13" t="n">
-        <v>38623074.6762</v>
+        <v>78730280.58939999</v>
       </c>
       <c r="E17" s="13" t="n">
-        <v>31670921.2345</v>
+        <v>64558830.0833</v>
       </c>
       <c r="F17" s="13" t="n">
-        <v>4827884.3345</v>
+        <v>9841285.0737</v>
       </c>
       <c r="G17" s="13" t="n">
-        <v>5057379.3345</v>
+        <v>9841285.0737</v>
       </c>
       <c r="H17" s="8" t="n">
-        <v>0.464</v>
+        <v>0.696</v>
       </c>
     </row>
     <row r="20">
@@ -888,14 +888,14 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>The investor is also repaid R770,505 of capital at R1 a tin across the five years,</t>
+          <t>The investor is also repaid R1,000,000 of capital at R1 a tin across the five years,</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>so their all-in return runs from R3,143,020 at 4x to R5,827,884 at 10x, on R1,000,000.</t>
+          <t>so their all-in return runs from R5,310,343 at 4x to R10,841,285 at 10x, on R1,000,000.</t>
         </is>
       </c>
     </row>
@@ -2326,7 +2326,7 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>BOOTSTRAP — Bootstrap — founder-funded, licence the brand globally</t>
+          <t>BOOTSTRAP — Plan of record — R1m, distributor-led from day 1, brand licensed globally</t>
         </is>
       </c>
       <c r="B34" s="5" t="n"/>
@@ -2370,19 +2370,19 @@
         </is>
       </c>
       <c r="B36" s="12" t="n">
-        <v>10760</v>
+        <v>22275</v>
       </c>
       <c r="C36" s="12" t="n">
-        <v>71980</v>
+        <v>145110</v>
       </c>
       <c r="D36" s="12" t="n">
-        <v>145530</v>
+        <v>287775</v>
       </c>
       <c r="E36" s="12" t="n">
-        <v>228635</v>
+        <v>463480</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>313600</v>
+        <v>638005</v>
       </c>
     </row>
     <row r="38">
@@ -2392,19 +2392,19 @@
         </is>
       </c>
       <c r="B38" s="13" t="n">
-        <v>162960</v>
+        <v>252000</v>
       </c>
       <c r="C38" s="13" t="n">
-        <v>1074008</v>
+        <v>1481760</v>
       </c>
       <c r="D38" s="13" t="n">
-        <v>2103826</v>
+        <v>2460780</v>
       </c>
       <c r="E38" s="13" t="n">
-        <v>3278717</v>
+        <v>3343916</v>
       </c>
       <c r="F38" s="13" t="n">
-        <v>4450880</v>
+        <v>3933500</v>
       </c>
     </row>
     <row r="39">
@@ -2414,19 +2414,19 @@
         </is>
       </c>
       <c r="B39" s="13" t="n">
-        <v>54320</v>
+        <v>190969</v>
       </c>
       <c r="C39" s="13" t="n">
-        <v>483788</v>
+        <v>1623234</v>
       </c>
       <c r="D39" s="13" t="n">
-        <v>1305768</v>
+        <v>4228907</v>
       </c>
       <c r="E39" s="13" t="n">
-        <v>2465880</v>
+        <v>8282763</v>
       </c>
       <c r="F39" s="13" t="n">
-        <v>3908521</v>
+        <v>13152203</v>
       </c>
     </row>
     <row r="40">
@@ -2524,19 +2524,19 @@
         </is>
       </c>
       <c r="B44" s="14" t="n">
-        <v>280280</v>
+        <v>505969</v>
       </c>
       <c r="C44" s="14" t="n">
-        <v>1954696</v>
+        <v>3501894</v>
       </c>
       <c r="D44" s="14" t="n">
-        <v>4404169</v>
+        <v>7684262</v>
       </c>
       <c r="E44" s="14" t="n">
-        <v>7917002</v>
+        <v>13799084</v>
       </c>
       <c r="F44" s="14" t="n">
-        <v>11915683</v>
+        <v>20641984</v>
       </c>
     </row>
     <row r="45">
@@ -2546,19 +2546,19 @@
         </is>
       </c>
       <c r="B45" s="13" t="n">
-        <v>110724</v>
+        <v>229217</v>
       </c>
       <c r="C45" s="13" t="n">
-        <v>750319</v>
+        <v>1519292</v>
       </c>
       <c r="D45" s="13" t="n">
-        <v>1576593</v>
+        <v>2881122</v>
       </c>
       <c r="E45" s="13" t="n">
-        <v>2379049</v>
+        <v>4377668</v>
       </c>
       <c r="F45" s="13" t="n">
-        <v>3288288</v>
+        <v>6083119</v>
       </c>
     </row>
     <row r="46">
@@ -2568,19 +2568,19 @@
         </is>
       </c>
       <c r="B46" s="14" t="n">
-        <v>169556</v>
+        <v>276752</v>
       </c>
       <c r="C46" s="14" t="n">
-        <v>1204377</v>
+        <v>1982603</v>
       </c>
       <c r="D46" s="14" t="n">
-        <v>2827577</v>
+        <v>4803141</v>
       </c>
       <c r="E46" s="14" t="n">
-        <v>5537953</v>
+        <v>9421416</v>
       </c>
       <c r="F46" s="14" t="n">
-        <v>8627394</v>
+        <v>14558866</v>
       </c>
     </row>
     <row r="48">
@@ -2596,13 +2596,13 @@
         <v>381600</v>
       </c>
       <c r="D48" s="13" t="n">
-        <v>870790</v>
+        <v>910116</v>
       </c>
       <c r="E48" s="13" t="n">
-        <v>1391107</v>
+        <v>1500680</v>
       </c>
       <c r="F48" s="13" t="n">
-        <v>1863416</v>
+        <v>2166410</v>
       </c>
     </row>
     <row r="49">
@@ -2612,19 +2612,19 @@
         </is>
       </c>
       <c r="B49" s="13" t="n">
-        <v>60000</v>
+        <v>120000</v>
       </c>
       <c r="C49" s="13" t="n">
-        <v>136829</v>
+        <v>350189</v>
       </c>
       <c r="D49" s="13" t="n">
-        <v>308292</v>
+        <v>768426</v>
       </c>
       <c r="E49" s="13" t="n">
-        <v>475020</v>
+        <v>1241918</v>
       </c>
       <c r="F49" s="13" t="n">
-        <v>714941</v>
+        <v>1857779</v>
       </c>
     </row>
     <row r="50">
@@ -2634,19 +2634,19 @@
         </is>
       </c>
       <c r="B50" s="13" t="n">
-        <v>14526</v>
+        <v>11644</v>
       </c>
       <c r="C50" s="13" t="n">
-        <v>103003</v>
+        <v>79521</v>
       </c>
       <c r="D50" s="13" t="n">
-        <v>220749</v>
+        <v>163707</v>
       </c>
       <c r="E50" s="13" t="n">
-        <v>367616</v>
+        <v>274131</v>
       </c>
       <c r="F50" s="13" t="n">
-        <v>534482</v>
+        <v>396547</v>
       </c>
     </row>
     <row r="51">
@@ -2656,19 +2656,19 @@
         </is>
       </c>
       <c r="B51" s="13" t="n">
-        <v>6518</v>
+        <v>0</v>
       </c>
       <c r="C51" s="13" t="n">
-        <v>46734</v>
+        <v>0</v>
       </c>
       <c r="D51" s="13" t="n">
-        <v>102288</v>
+        <v>0</v>
       </c>
       <c r="E51" s="13" t="n">
-        <v>172338</v>
+        <v>0</v>
       </c>
       <c r="F51" s="13" t="n">
-        <v>250782</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -2684,13 +2684,13 @@
         <v>120000</v>
       </c>
       <c r="D52" s="13" t="n">
-        <v>224042</v>
+        <v>256843</v>
       </c>
       <c r="E52" s="13" t="n">
-        <v>358755</v>
+        <v>446986</v>
       </c>
       <c r="F52" s="13" t="n">
-        <v>458735</v>
+        <v>589630</v>
       </c>
     </row>
     <row r="53">
@@ -2744,19 +2744,19 @@
         </is>
       </c>
       <c r="B55" s="14" t="n">
-        <v>402244</v>
+        <v>452844</v>
       </c>
       <c r="C55" s="14" t="n">
-        <v>1065462</v>
+        <v>1208606</v>
       </c>
       <c r="D55" s="14" t="n">
-        <v>2020094</v>
+        <v>2393026</v>
       </c>
       <c r="E55" s="14" t="n">
-        <v>3076405</v>
+        <v>3775285</v>
       </c>
       <c r="F55" s="14" t="n">
-        <v>4152620</v>
+        <v>5340630</v>
       </c>
     </row>
     <row r="57">
@@ -2766,19 +2766,19 @@
         </is>
       </c>
       <c r="B57" s="14" t="n">
-        <v>-232688</v>
+        <v>-176092</v>
       </c>
       <c r="C57" s="14" t="n">
-        <v>138915</v>
+        <v>773997</v>
       </c>
       <c r="D57" s="14" t="n">
-        <v>807483</v>
+        <v>2410115</v>
       </c>
       <c r="E57" s="14" t="n">
-        <v>2461548</v>
+        <v>5646131</v>
       </c>
       <c r="F57" s="14" t="n">
-        <v>4474774</v>
+        <v>9218236</v>
       </c>
     </row>
     <row r="58">
@@ -2791,16 +2791,16 @@
         <v>0</v>
       </c>
       <c r="C58" s="13" t="n">
-        <v>42493</v>
+        <v>81965</v>
       </c>
       <c r="D58" s="13" t="n">
-        <v>86507</v>
+        <v>159136</v>
       </c>
       <c r="E58" s="13" t="n">
-        <v>129413</v>
+        <v>238633</v>
       </c>
       <c r="F58" s="13" t="n">
-        <v>170300</v>
+        <v>315308</v>
       </c>
     </row>
     <row r="59">
@@ -2810,19 +2810,19 @@
         </is>
       </c>
       <c r="B59" s="13" t="n">
-        <v>334</v>
+        <v>2967</v>
       </c>
       <c r="C59" s="13" t="n">
-        <v>5890</v>
+        <v>136336</v>
       </c>
       <c r="D59" s="13" t="n">
-        <v>151648</v>
+        <v>607764</v>
       </c>
       <c r="E59" s="13" t="n">
-        <v>629676</v>
+        <v>1460024</v>
       </c>
       <c r="F59" s="13" t="n">
-        <v>1162208</v>
+        <v>2403790</v>
       </c>
     </row>
     <row r="60">
@@ -2832,19 +2832,19 @@
         </is>
       </c>
       <c r="B60" s="14" t="n">
-        <v>-233022</v>
+        <v>-179059</v>
       </c>
       <c r="C60" s="14" t="n">
-        <v>90532</v>
+        <v>555696</v>
       </c>
       <c r="D60" s="14" t="n">
-        <v>569328</v>
+        <v>1643215</v>
       </c>
       <c r="E60" s="14" t="n">
-        <v>1702459</v>
+        <v>3947473</v>
       </c>
       <c r="F60" s="14" t="n">
-        <v>3142266</v>
+        <v>6499137</v>
       </c>
     </row>
     <row r="61">
@@ -2854,19 +2854,19 @@
         </is>
       </c>
       <c r="B61" s="15" t="n">
-        <v>0.6049524434332847</v>
+        <v>0.5469738873394191</v>
       </c>
       <c r="C61" s="15" t="n">
-        <v>0.616145576540252</v>
+        <v>0.5661515101709023</v>
       </c>
       <c r="D61" s="15" t="n">
-        <v>0.6420227169103438</v>
+        <v>0.6250620487848355</v>
       </c>
       <c r="E61" s="15" t="n">
-        <v>0.6995012815943289</v>
+        <v>0.6827566456700157</v>
       </c>
       <c r="F61" s="15" t="n">
-        <v>0.7240369423781725</v>
+        <v>0.705303598258332</v>
       </c>
     </row>
     <row r="62">
@@ -2876,19 +2876,19 @@
         </is>
       </c>
       <c r="B62" s="15" t="n">
-        <v>-0.8301995474329918</v>
+        <v>-0.3480295096095031</v>
       </c>
       <c r="C62" s="15" t="n">
-        <v>0.07106742051520307</v>
+        <v>0.2210222806520935</v>
       </c>
       <c r="D62" s="15" t="n">
-        <v>0.1833451215566309</v>
+        <v>0.3136429954082527</v>
       </c>
       <c r="E62" s="15" t="n">
-        <v>0.310919177085396</v>
+        <v>0.4091670981558133</v>
       </c>
       <c r="F62" s="15" t="n">
-        <v>0.3755365203946371</v>
+        <v>0.4465770364218457</v>
       </c>
     </row>
     <row r="65">
@@ -11047,7 +11047,7 @@
         </is>
       </c>
       <c r="B4" s="8" t="n">
-        <v>0.1751</v>
+        <v>0.3563</v>
       </c>
       <c r="C4" s="8" t="n">
         <v>0.45</v>
@@ -11066,7 +11066,7 @@
         </is>
       </c>
       <c r="B5" s="12" t="n">
-        <v>10760</v>
+        <v>22275</v>
       </c>
       <c r="C5" s="12" t="n">
         <v>11034</v>
@@ -11085,7 +11085,7 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>145530</v>
+        <v>287775</v>
       </c>
       <c r="C6" s="12" t="n">
         <v>249588</v>
@@ -11104,7 +11104,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>313600</v>
+        <v>638005</v>
       </c>
       <c r="C7" s="12" t="n">
         <v>805764.375</v>
@@ -11123,7 +11123,7 @@
         </is>
       </c>
       <c r="B8" s="13" t="n">
-        <v>280280</v>
+        <v>505968.75</v>
       </c>
       <c r="C8" s="13" t="n">
         <v>262433.43</v>
@@ -11142,7 +11142,7 @@
         </is>
       </c>
       <c r="B9" s="13" t="n">
-        <v>4404169.2563</v>
+        <v>7684262.4844</v>
       </c>
       <c r="C9" s="13" t="n">
         <v>5617921.8469</v>
@@ -11161,7 +11161,7 @@
         </is>
       </c>
       <c r="B10" s="13" t="n">
-        <v>11915682.6956</v>
+        <v>20641984.3903</v>
       </c>
       <c r="C10" s="13" t="n">
         <v>17695582.2721</v>
@@ -11180,7 +11180,7 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>0.724</v>
+        <v>0.7053</v>
       </c>
       <c r="C11" s="8" t="n">
         <v>0.5615</v>
@@ -11199,7 +11199,7 @@
         </is>
       </c>
       <c r="B12" s="13" t="n">
-        <v>4474774.0176</v>
+        <v>9218236.2149</v>
       </c>
       <c r="C12" s="13" t="n">
         <v>-189443.314</v>
@@ -11218,7 +11218,7 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>0.3755</v>
+        <v>0.4466</v>
       </c>
       <c r="C13" s="8" t="n">
         <v>-0.0107</v>
@@ -11237,7 +11237,7 @@
         </is>
       </c>
       <c r="B14" s="13" t="n">
-        <v>7650031.5221</v>
+        <v>17872387.1169</v>
       </c>
       <c r="C14" s="13" t="n">
         <v>-5924610.1364</v>
@@ -11275,7 +11275,7 @@
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>630002.5996</v>
+        <v>983567.9997</v>
       </c>
       <c r="C16" s="13" t="n">
         <v>8600702.8167</v>
@@ -11313,7 +11313,7 @@
         </is>
       </c>
       <c r="B18" s="13" t="n">
-        <v>369997.4004</v>
+        <v>16432.0003</v>
       </c>
       <c r="C18" s="13" t="n">
         <v>1207273.1908</v>
@@ -11332,7 +11332,7 @@
         </is>
       </c>
       <c r="B19" s="13" t="n">
-        <v>5358197.5544</v>
+        <v>8647487.017899999</v>
       </c>
       <c r="C19" s="13" t="n">
         <v>7640597.8524</v>

--- a/finance/outputs/mulligan-mints-5yr-model.xlsx
+++ b/finance/outputs/mulligan-mints-5yr-model.xlsx
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="B4" s="13" t="n">
-        <v>9218236</v>
+        <v>9492700</v>
       </c>
     </row>
     <row r="5">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="B7" s="13" t="n">
-        <v>8647487</v>
+        <v>8994940</v>
       </c>
     </row>
     <row r="8">
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="B8" s="13" t="n">
-        <v>-890105</v>
+        <v>-844361</v>
       </c>
     </row>
     <row r="9">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="B9" s="13" t="n">
-        <v>7757382</v>
+        <v>8150579</v>
       </c>
     </row>
     <row r="10">
@@ -766,25 +766,25 @@
         </is>
       </c>
       <c r="B14" s="13" t="n">
-        <v>36872944.8596</v>
+        <v>37970801.1364</v>
       </c>
       <c r="C14" s="13" t="n">
-        <v>43103433.4475</v>
+        <v>44594486.8552</v>
       </c>
       <c r="D14" s="13" t="n">
-        <v>34482746.758</v>
+        <v>35675589.4841</v>
       </c>
       <c r="E14" s="13" t="n">
-        <v>28275852.3415</v>
+        <v>29253983.377</v>
       </c>
       <c r="F14" s="13" t="n">
-        <v>4310343.3447</v>
+        <v>4459448.6855</v>
       </c>
       <c r="G14" s="13" t="n">
-        <v>4310343.3447</v>
+        <v>4459448.6855</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>0.4858</v>
+        <v>0.4939</v>
       </c>
     </row>
     <row r="15">
@@ -794,25 +794,25 @@
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>55309417.2894</v>
+        <v>56956201.7046</v>
       </c>
       <c r="C15" s="13" t="n">
-        <v>61539905.8772</v>
+        <v>63579887.4234</v>
       </c>
       <c r="D15" s="13" t="n">
-        <v>49231924.7018</v>
+        <v>50863909.9387</v>
       </c>
       <c r="E15" s="13" t="n">
-        <v>40370178.2555</v>
+        <v>41708406.1497</v>
       </c>
       <c r="F15" s="13" t="n">
-        <v>6153990.5877</v>
+        <v>6357988.7423</v>
       </c>
       <c r="G15" s="13" t="n">
-        <v>6153990.5877</v>
+        <v>6357988.7423</v>
       </c>
       <c r="H15" s="8" t="n">
-        <v>0.5698</v>
+        <v>0.5783</v>
       </c>
     </row>
     <row r="16">
@@ -822,25 +822,25 @@
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>73745889.7191</v>
+        <v>75941602.2727</v>
       </c>
       <c r="C16" s="13" t="n">
-        <v>79976378.307</v>
+        <v>82565287.99160001</v>
       </c>
       <c r="D16" s="13" t="n">
-        <v>63981102.6456</v>
+        <v>66052230.3932</v>
       </c>
       <c r="E16" s="13" t="n">
-        <v>52464504.1694</v>
+        <v>54162828.9225</v>
       </c>
       <c r="F16" s="13" t="n">
-        <v>7997637.8307</v>
+        <v>8256528.7992</v>
       </c>
       <c r="G16" s="13" t="n">
-        <v>7997637.8307</v>
+        <v>8256528.7992</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>0.638</v>
+        <v>0.647</v>
       </c>
     </row>
     <row r="17">
@@ -850,25 +850,25 @@
         </is>
       </c>
       <c r="B17" s="13" t="n">
-        <v>92182362.1489</v>
+        <v>94927002.8409</v>
       </c>
       <c r="C17" s="13" t="n">
-        <v>98412850.7368</v>
+        <v>101550688.5597</v>
       </c>
       <c r="D17" s="13" t="n">
-        <v>78730280.58939999</v>
+        <v>81240550.8478</v>
       </c>
       <c r="E17" s="13" t="n">
-        <v>64558830.0833</v>
+        <v>66617251.6952</v>
       </c>
       <c r="F17" s="13" t="n">
-        <v>9841285.0737</v>
+        <v>10155068.856</v>
       </c>
       <c r="G17" s="13" t="n">
-        <v>9841285.0737</v>
+        <v>10155068.856</v>
       </c>
       <c r="H17" s="8" t="n">
-        <v>0.696</v>
+        <v>0.7053</v>
       </c>
     </row>
     <row r="20">
@@ -895,7 +895,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>so their all-in return runs from R5,310,343 at 4x to R10,841,285 at 10x, on R1,000,000.</t>
+          <t>so their all-in return runs from R5,459,449 at 4x to R11,155,069 at 10x, on R1,000,000.</t>
         </is>
       </c>
     </row>
@@ -2634,19 +2634,19 @@
         </is>
       </c>
       <c r="B50" s="13" t="n">
-        <v>11644</v>
+        <v>6525</v>
       </c>
       <c r="C50" s="13" t="n">
-        <v>79521</v>
+        <v>43929</v>
       </c>
       <c r="D50" s="13" t="n">
-        <v>163707</v>
+        <v>87927</v>
       </c>
       <c r="E50" s="13" t="n">
-        <v>274131</v>
+        <v>143274</v>
       </c>
       <c r="F50" s="13" t="n">
-        <v>396547</v>
+        <v>204649</v>
       </c>
     </row>
     <row r="51">
@@ -2700,19 +2700,19 @@
         </is>
       </c>
       <c r="B53" s="13" t="n">
-        <v>196200</v>
+        <v>147150</v>
       </c>
       <c r="C53" s="13" t="n">
-        <v>277296</v>
+        <v>207972</v>
       </c>
       <c r="D53" s="13" t="n">
-        <v>293934</v>
+        <v>220450</v>
       </c>
       <c r="E53" s="13" t="n">
-        <v>311570</v>
+        <v>233677</v>
       </c>
       <c r="F53" s="13" t="n">
-        <v>330264</v>
+        <v>247698</v>
       </c>
     </row>
     <row r="54">
@@ -2744,19 +2744,19 @@
         </is>
       </c>
       <c r="B55" s="14" t="n">
-        <v>452844</v>
+        <v>398675</v>
       </c>
       <c r="C55" s="14" t="n">
-        <v>1208606</v>
+        <v>1103690</v>
       </c>
       <c r="D55" s="14" t="n">
-        <v>2393026</v>
+        <v>2243763</v>
       </c>
       <c r="E55" s="14" t="n">
-        <v>3775285</v>
+        <v>3566536</v>
       </c>
       <c r="F55" s="14" t="n">
-        <v>5340630</v>
+        <v>5066166</v>
       </c>
     </row>
     <row r="57">
@@ -2766,19 +2766,19 @@
         </is>
       </c>
       <c r="B57" s="14" t="n">
-        <v>-176092</v>
+        <v>-121923</v>
       </c>
       <c r="C57" s="14" t="n">
-        <v>773997</v>
+        <v>878913</v>
       </c>
       <c r="D57" s="14" t="n">
-        <v>2410115</v>
+        <v>2559378</v>
       </c>
       <c r="E57" s="14" t="n">
-        <v>5646131</v>
+        <v>5854881</v>
       </c>
       <c r="F57" s="14" t="n">
-        <v>9218236</v>
+        <v>9492700</v>
       </c>
     </row>
     <row r="58">
@@ -2788,10 +2788,10 @@
         </is>
       </c>
       <c r="B58" s="13" t="n">
-        <v>0</v>
+        <v>18215</v>
       </c>
       <c r="C58" s="13" t="n">
-        <v>81965</v>
+        <v>95732</v>
       </c>
       <c r="D58" s="13" t="n">
         <v>159136</v>
@@ -2810,19 +2810,19 @@
         </is>
       </c>
       <c r="B59" s="13" t="n">
-        <v>2967</v>
+        <v>3338</v>
       </c>
       <c r="C59" s="13" t="n">
-        <v>136336</v>
+        <v>170284</v>
       </c>
       <c r="D59" s="13" t="n">
-        <v>607764</v>
+        <v>648065</v>
       </c>
       <c r="E59" s="13" t="n">
-        <v>1460024</v>
+        <v>1516387</v>
       </c>
       <c r="F59" s="13" t="n">
-        <v>2403790</v>
+        <v>2477896</v>
       </c>
     </row>
     <row r="60">
@@ -2832,19 +2832,19 @@
         </is>
       </c>
       <c r="B60" s="14" t="n">
-        <v>-179059</v>
+        <v>-143475</v>
       </c>
       <c r="C60" s="14" t="n">
-        <v>555696</v>
+        <v>612897</v>
       </c>
       <c r="D60" s="14" t="n">
-        <v>1643215</v>
+        <v>1752177</v>
       </c>
       <c r="E60" s="14" t="n">
-        <v>3947473</v>
+        <v>4099861</v>
       </c>
       <c r="F60" s="14" t="n">
-        <v>6499137</v>
+        <v>6699496</v>
       </c>
     </row>
     <row r="61">
@@ -2876,19 +2876,19 @@
         </is>
       </c>
       <c r="B62" s="15" t="n">
-        <v>-0.3480295096095031</v>
+        <v>-0.24097003212201</v>
       </c>
       <c r="C62" s="15" t="n">
-        <v>0.2210222806520935</v>
+        <v>0.2509821077528182</v>
       </c>
       <c r="D62" s="15" t="n">
-        <v>0.3136429954082527</v>
+        <v>0.3330675319598748</v>
       </c>
       <c r="E62" s="15" t="n">
-        <v>0.4091670981558133</v>
+        <v>0.4242948685012269</v>
       </c>
       <c r="F62" s="15" t="n">
-        <v>0.4465770364218457</v>
+        <v>0.459873435838222</v>
       </c>
     </row>
     <row r="65">
@@ -11199,7 +11199,7 @@
         </is>
       </c>
       <c r="B12" s="13" t="n">
-        <v>9218236.2149</v>
+        <v>9492700.2841</v>
       </c>
       <c r="C12" s="13" t="n">
         <v>-189443.314</v>
@@ -11218,7 +11218,7 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>0.4466</v>
+        <v>0.4599</v>
       </c>
       <c r="C13" s="8" t="n">
         <v>-0.0107</v>
@@ -11237,7 +11237,7 @@
         </is>
       </c>
       <c r="B14" s="13" t="n">
-        <v>17872387.1169</v>
+        <v>18663948.6979</v>
       </c>
       <c r="C14" s="13" t="n">
         <v>-5924610.1364</v>
@@ -11275,7 +11275,7 @@
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>983567.9997</v>
+        <v>699726.901</v>
       </c>
       <c r="C16" s="13" t="n">
         <v>8600702.8167</v>
@@ -11294,7 +11294,7 @@
         </is>
       </c>
       <c r="B17" s="17" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C17" s="17" t="n">
         <v>50</v>
@@ -11313,7 +11313,7 @@
         </is>
       </c>
       <c r="B18" s="13" t="n">
-        <v>16432.0003</v>
+        <v>300273.099</v>
       </c>
       <c r="C18" s="13" t="n">
         <v>1207273.1908</v>
@@ -11332,7 +11332,7 @@
         </is>
       </c>
       <c r="B19" s="13" t="n">
-        <v>8647487.017899999</v>
+        <v>8994940.1373</v>
       </c>
       <c r="C19" s="13" t="n">
         <v>7640597.8524</v>
